--- a/4 четверть_MSSQL.xlsx
+++ b/4 четверть_MSSQL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlexServHW\Desktop\GB_Developer_Workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13F94700-DDE3-46D6-A3AE-40E453FA1F40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7571CD00-1A0F-4A75-BC93-5EE2E6C2C7B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-9600" yWindow="-18885" windowWidth="18030" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-5190" yWindow="-19365" windowWidth="29085" windowHeight="15270" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Изучить" sheetId="21" r:id="rId1"/>
@@ -19,10 +19,12 @@
     <sheet name="TABLE" sheetId="20" r:id="rId4"/>
     <sheet name="SELECT" sheetId="15" r:id="rId5"/>
     <sheet name="WHERE" sheetId="19" r:id="rId6"/>
-    <sheet name="template" sheetId="14" r:id="rId7"/>
-    <sheet name="Каскадное удаление" sheetId="16" r:id="rId8"/>
-    <sheet name="Транзакции" sheetId="17" r:id="rId9"/>
-    <sheet name="bc Массивы" sheetId="18" r:id="rId10"/>
+    <sheet name="IF" sheetId="23" r:id="rId7"/>
+    <sheet name="template" sheetId="14" r:id="rId8"/>
+    <sheet name="Каскадное удаление" sheetId="16" r:id="rId9"/>
+    <sheet name="Транзакции" sheetId="17" r:id="rId10"/>
+    <sheet name="bc Массивы" sheetId="18" r:id="rId11"/>
+    <sheet name="bc JSON" sheetId="22" r:id="rId12"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -37,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="237">
   <si>
     <t>Урок 1 часть 1</t>
   </si>
@@ -1803,287 +1805,6 @@
     <t>Массив чисел NVarChar</t>
   </si>
   <si>
-    <t>Cоздаем пустую таблицу (массив сущностей)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">    </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">DECLARE </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>@UserMails</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> TABLE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (UserMail NVARCHAR(255));</t>
-    </r>
-  </si>
-  <si>
-    <t>Наполняем таблицу массивом значений</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">    </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>INSERT INTO</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> @UserMails (UserMail)
-    </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>SELECT</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> value </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>FROM STRING_SPLIT</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(@userMailsToArray, ',');</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">    </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>INSERT INTO</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> @TargetGroups (idMailGroup)
-    </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>SELECT</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> value </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>FROM</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>STRING_SPLIT</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(@idMailGroupsToArray, ',');</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">    </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>DECLARE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> @TargetGroups </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>TABLE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (idMailGroup INT);</t>
-    </r>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">Инициализация </t>
     </r>
@@ -2474,79 +2195,6 @@
   </si>
   <si>
     <t>WHERE UserMail IN (SELECT UserMail FROM @UserMails)</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Для чего?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Защиты от дубликатов:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Чтобы не добавить одного и того же пользователя в одну и ту же группу дважды.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Поиска отсутствующих записей: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Найти всех пользователей, у которых еще нет какой-либо настройки.</t>
-    </r>
   </si>
   <si>
     <r>
@@ -6090,17 +5738,1735 @@
   <si>
     <t>`https://metanit.com/sql/sqlserver/3.2.php#:~:text=%D0%A1%D0%BE%D0%B7%D0%B4%D0%B0%D0%BD%D0%B8%D0%B5%20%D1%82%D0%B0%D0%B1%D0%BB%D0%B8%D1%86%D1%8B%20%D0%B2%20SQL%20Management%20Studio</t>
   </si>
+  <si>
+    <t>`-- Парсим JSON в табличное представление
+DECLARE @ParsedReceivers TABLE (
+    UserMail NVARCHAR(255),
+    CompanyName NVARCHAR(255)
+);
+INSERT INTO @ParsedReceivers (UserMail, CompanyName)
+SELECT UserMail, CompanyName
+FROM OPENJSON(@mailReceiversJson)
+WITH (
+    UserMail NVARCHAR(255) '$.UserMail',
+    CompanyName NVARCHAR(255) '$.CompanyName'
+);
+-- 1. Добавляем новых пользователей, которых ещё нет в таблице пользователей
+INSERT INTO LK_DATA.dbo.site_UserMails (UserMail, CompanyName, StatusOrigin)
+SELECT pr.UserMail, pr.CompanyName, 'CompanyContacts'
+FROM @ParsedReceivers pr
+WHERE NOT EXISTS (
+    SELECT 1 
+    FROM LK_DATA.dbo.site_UserMails existing
+    WHERE existing.UserMail = pr.UserMail
+);
+-- 2. Добавляем связи пользователей с группой рассылки (если ещё нет)
+INSERT INTO LK_DATA.dbo.site_MailGroupsCrossUserMail (idMailGroup, UserMail)
+SELECT @idMailGroup, pr.UserMail
+FROM @ParsedReceivers pr
+WHERE NOT EXISTS (
+    SELECT 1 
+    FROM LK_DATA.dbo.site_MailGroupsCrossUserMail existing
+    WHERE existing.idMailGroup = @idMailGroup
+      AND existing.UserMail = pr.UserMail
+);</t>
+  </si>
+  <si>
+    <t>Для чего?</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Для чего?</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Защиты от дубликатов:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 
+Чтобы не добавить одного и того же пользователя в одну и ту же группу дважды.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Поиска отсутствующих записей: 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Найти всех пользователей, у которых еще нет какой-либо настройки.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Правило!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> MSSQL может работать с объектами, переведенными в строки.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>const mailReceiverJson = JSON.stringify(newMlRcvr);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>DECLARE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> @ParsedReceivers </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>TABLE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (
+    UserMail </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>NVARCHAR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">(255),
+    CompanyName </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>NVARCHAR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(255)
+);</t>
+    </r>
+  </si>
+  <si>
+    <t>Таблица из &gt;1 столбца</t>
+  </si>
+  <si>
+    <t>Таблица из 1 столбца</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Наполняем таблицу </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>массивом сущностей</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Cоздаем пустую таблицу (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>массив</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>сущностей</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Cоздаем пустую таблицу (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>массив</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>значений</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Наполняем таблицу </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>массивом значений</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">DECLARE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>@UserMails</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> TABLE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (UserMail </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>NVARCHAR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(255));</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>DECLARE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> @TargetGroups </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>TABLE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (idMailGroup </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>INT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>);</t>
+    </r>
+  </si>
+  <si>
+    <t>Добавляем новых пользователей, которых ещё нет в таблице пользователей</t>
+  </si>
+  <si>
+    <t>Добавляем связи пользователей с группой рассылки (если ещё нет)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>INSERT INTO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> LK_DATA.dbo.site_UserMail (UserMail, CompanyName, StatusOrigin)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SELECT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> pr.UserMail, pr.CompanyName, 'CompanyContacts'
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>FROM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> @ParsedReceivers pr
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>WHERE NOT EXISTS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (
+    </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SELECT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 1 
+    </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>FROM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> LK_DATA.dbo.site_UserMail existing
+    </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>WHERE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> existing.UserMail = pr.UserMail
+);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>INSERT INTO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> LK_DATA.dbo.site_MailGroupsCrossUserMail (idMailGroup, UserMail)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SELECT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> @idMailGroup, pr.UserMail
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>FROM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> @ParsedReceivers pr
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>WHERE NOT EXISTS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (
+    </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SELECT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 1 
+    </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>FROM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> LK_DATA.dbo.site_MailGroupsCrossUserMail existing
+    </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>WHERE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> existing.idMailGroup = @idMailGroup
+      </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>AND</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> existing.UserMail = pr.UserMail
+);</t>
+    </r>
+  </si>
+  <si>
+    <t>IF многострочный</t>
+  </si>
+  <si>
+    <t>IF однострочный</t>
+  </si>
+  <si>
+    <t>IF @@ROWCOUNT &gt; 0 PRINT 'Успех' ELSE PRINT 'Нет изменений';</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Правило!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Только одна команда для каждой ветки</t>
+    </r>
+  </si>
+  <si>
+    <t>IIF</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Пояснение!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Как IF, но если нужно вернуть результат</t>
+    </r>
+  </si>
+  <si>
+    <t>CASE</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">SELECT 
+ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>IIF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(@@ROWCOUNT &gt; 0, 'success', 'userInDbAlready') 
+ AS Result;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">SELECT 
+ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CASE WHEN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> @@ROWCOUNT &gt; 0 
+ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>THEN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 'success'
+ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ELSE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 'userInDbAlready' 
+ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>END</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 
+ AS Result;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>INSERT INTO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> @ParsedReceivers (UserMail, CompanyName)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SELECT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> UserMail, CompanyName</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>FROM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>OPENJSON</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">(@mailReceiversJson)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>WITH</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (
+    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">UserMail </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>NVARCHAR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">(255) '$.UserMail',
+    CompanyName </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>NVARCHAR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(255) '$.CompanyName'
+);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>INSERT INTO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> @UserMails (UserMail)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SELECT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> value </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>FROM STRING_SPLIT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(@userMailsToArray, ',');</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>INSERT INTO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> @TargetGroups (idMailGroup)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SELECT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> value </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>FROM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>STRING_SPLIT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(@idMailGroupsToArray, ',');</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">IF @@ROWCOUNT &gt; 0 BEGIN
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">    INSERT INTO LK_DATA.dbo.site_MailGroupsCrossUserMail (idMailGroup, UserMail)
+    SELECT @idMailGroup, pr.UserMail
+    FROM @ParsedReceiver pr
+    WHERE NOT EXISTS (
+        SELECT 1 
+        FROM LK_DATA.dbo.site_MailGroupsCrossUserMail existing
+        WHERE existing.idMailGroup = @idMailGroup
+          AND existing.UserMail = pr.UserMail
+    );
+    SELECT 'success' AS Result; -- Успех, есть новые записи
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">END ELSE BEGIN
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">    SELECT 'userInDbAlready' AS Result; -- "Успех", но записи уже существовали
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>END</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>DECLARE @IdExist INT
+SET @IdExist = (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SELECT</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> TOP(1)</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> [IdFile]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> FROM [dbo].[usr_FilesAnalitic] WHERE [FileName] = @FileName)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>IF (ISNULL(@IdExist, 0) = 0) BEGIN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+      INSERT INTO [dbo].[usr_FilesAnalitic]
+           ([IdUser]
+           ,[FileName]
+           ,[JsonData]
+           ,[Link]
+           ,[Params])
+     VALUES
+           (@IdUser, 
+           @FileName,
+           @JsonData,
+           @Link,
+           @Params)
+      SELECT @@IDENTITY AS IdFile 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>END ELSE BEGIN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+      UPDATE [dbo].[usr_FilesAnalitic]
+      SET [Insdate] = GETDATE(), [Acesss] = GETDATE()+(2)
+      WHERE [IdFile] = @IdExist
+      SELECT @IdExist AS IdFile 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>END</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="26" x14ac:knownFonts="1">
+  <fonts count="31" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -6311,6 +7677,23 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FFA626A4"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF7030A0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="12">
     <fill>
@@ -6391,9 +7774,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -6404,112 +7787,130 @@
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="24" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="27" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="24" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -6580,54 +7981,6 @@
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="4097" name="AutoShape 1" descr="Первый запрос на SQL в SQL Management Studio">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A68FE80D-779F-4770-A362-D6C748309722}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="2468880" y="3108960"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
@@ -7196,7 +8549,7 @@
       <c r="B4" s="9"/>
       <c r="C4" s="40"/>
       <c r="D4" s="22" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
     </row>
     <row r="5" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
@@ -7204,7 +8557,7 @@
       <c r="B5" s="9"/>
       <c r="C5" s="40"/>
       <c r="D5" s="22" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
     </row>
     <row r="6" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
@@ -7212,17 +8565,17 @@
       <c r="B6" s="9"/>
       <c r="C6" s="40"/>
       <c r="D6" s="22" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A7" s="9"/>
       <c r="B7" s="9"/>
       <c r="C7" s="22" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="D7" s="40" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.3">
@@ -7230,7 +8583,7 @@
       <c r="B8" s="9"/>
       <c r="C8" s="40"/>
       <c r="D8" s="40" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.3">
@@ -7238,17 +8591,17 @@
       <c r="B9" s="9"/>
       <c r="C9" s="40"/>
       <c r="D9" s="40" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
     </row>
     <row r="10" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="9"/>
       <c r="B10" s="9"/>
       <c r="C10" s="22" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="D10" s="22" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
     </row>
     <row r="11" spans="1:22" ht="57.6" x14ac:dyDescent="0.3">
@@ -7256,7 +8609,7 @@
       <c r="B11" s="9"/>
       <c r="C11" s="40"/>
       <c r="D11" s="22" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.3">
@@ -7277,9 +8630,11 @@
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:22" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A15" s="9"/>
-      <c r="B15" s="9"/>
+      <c r="B15" s="41" t="s">
+        <v>206</v>
+      </c>
       <c r="C15" s="9"/>
       <c r="D15" s="9"/>
     </row>
@@ -7488,11 +8843,11 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B13A24C-6305-48F4-A1E6-55B31CAA1F4A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16AAE27B-B1A5-470A-8C56-1AC981AA4A71}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:V49"/>
+  <dimension ref="A2:V44"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="36" style="1" customWidth="1"/>
@@ -7554,96 +8909,87 @@
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A4" s="20" t="s">
-        <v>85</v>
+        <v>135</v>
       </c>
       <c r="B4" s="9"/>
       <c r="C4" s="9"/>
       <c r="D4" s="9"/>
     </row>
-    <row r="5" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A5" s="23" t="s">
-        <v>99</v>
-      </c>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A5" s="9"/>
+      <c r="B5" s="32" t="s">
+        <v>136</v>
+      </c>
+      <c r="C5" s="35" t="s">
+        <v>140</v>
+      </c>
       <c r="D5" s="9"/>
     </row>
-    <row r="6" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A6" s="9"/>
-      <c r="C6" s="19" t="s">
-        <v>88</v>
+      <c r="B6" s="32" t="s">
+        <v>137</v>
+      </c>
+      <c r="C6" s="36" t="s">
+        <v>141</v>
       </c>
       <c r="D6" s="9"/>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A7" s="9"/>
-      <c r="B7" s="19" t="s">
-        <v>86</v>
-      </c>
-      <c r="C7" s="19" t="s">
-        <v>98</v>
-      </c>
-      <c r="D7" s="19" t="s">
-        <v>93</v>
-      </c>
+      <c r="B7" s="32" t="s">
+        <v>138</v>
+      </c>
+      <c r="C7" s="36" t="s">
+        <v>142</v>
+      </c>
+      <c r="D7" s="9"/>
     </row>
     <row r="8" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="9"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="D8" s="19" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="B8" s="32" t="s">
+        <v>139</v>
+      </c>
+      <c r="C8" s="36" t="s">
+        <v>143</v>
+      </c>
+      <c r="D8" s="9"/>
+    </row>
+    <row r="9" spans="1:22" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A9" s="9"/>
-      <c r="B9" s="19" t="s">
-        <v>92</v>
-      </c>
+      <c r="B9" s="9"/>
       <c r="C9" s="19" t="s">
-        <v>94</v>
-      </c>
-      <c r="D9" s="19"/>
-    </row>
-    <row r="10" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
+        <v>90</v>
+      </c>
+      <c r="D9" s="9"/>
+    </row>
+    <row r="10" spans="1:22" ht="144" x14ac:dyDescent="0.3">
       <c r="A10" s="9"/>
-      <c r="B10" s="9"/>
+      <c r="B10" s="22" t="s">
+        <v>89</v>
+      </c>
       <c r="C10" s="19" t="s">
-        <v>96</v>
-      </c>
-      <c r="D10" s="19"/>
+        <v>91</v>
+      </c>
+      <c r="D10" s="9"/>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A11" s="23" t="s">
-        <v>100</v>
-      </c>
+      <c r="A11" s="9"/>
       <c r="B11" s="9"/>
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
     </row>
-    <row r="12" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A12" s="9"/>
-      <c r="B12" s="19" t="s">
-        <v>103</v>
-      </c>
-      <c r="C12" s="19" t="s">
-        <v>102</v>
-      </c>
-      <c r="D12" s="19" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="13" spans="1:22" ht="201.6" x14ac:dyDescent="0.3">
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A13" s="9"/>
       <c r="B13" s="9"/>
-      <c r="C13" s="19" t="s">
-        <v>105</v>
-      </c>
-      <c r="D13" s="19" t="s">
-        <v>104</v>
-      </c>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A14" s="9"/>
@@ -7663,11 +9009,1254 @@
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
     </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="9"/>
+      <c r="B17" s="31"/>
+      <c r="C17" s="32"/>
+      <c r="D17" s="9"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="9"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="9"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="9"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="9"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" s="9"/>
+      <c r="B22" s="9"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" s="9"/>
+      <c r="B23" s="9"/>
+      <c r="C23" s="9"/>
+      <c r="D23" s="9"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" s="9"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="9"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" s="9"/>
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" s="9"/>
+      <c r="B26" s="9"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" s="9"/>
+      <c r="B27" s="9"/>
+      <c r="C27" s="9"/>
+      <c r="D27" s="9"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" s="9"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="9"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" s="9"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="9"/>
+      <c r="D29" s="9"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30" s="9"/>
+      <c r="B30" s="9"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="9"/>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31" s="9"/>
+      <c r="B31" s="9"/>
+      <c r="C31" s="9"/>
+      <c r="D31" s="9"/>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A32" s="9"/>
+      <c r="B32" s="9"/>
+      <c r="C32" s="9"/>
+      <c r="D32" s="9"/>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33" s="9"/>
+      <c r="B33" s="9"/>
+      <c r="C33" s="9"/>
+      <c r="D33" s="9"/>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A34" s="9"/>
+      <c r="B34" s="9"/>
+      <c r="C34" s="9"/>
+      <c r="D34" s="9"/>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A35" s="9"/>
+      <c r="B35" s="9"/>
+      <c r="C35" s="9"/>
+      <c r="D35" s="9"/>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A36" s="9"/>
+      <c r="B36" s="9"/>
+      <c r="C36" s="9"/>
+      <c r="D36" s="9"/>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A37" s="9"/>
+      <c r="B37" s="9"/>
+      <c r="C37" s="9"/>
+      <c r="D37" s="9"/>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A38" s="9"/>
+      <c r="B38" s="9"/>
+      <c r="C38" s="9"/>
+      <c r="D38" s="9"/>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A39" s="9"/>
+      <c r="B39" s="9"/>
+      <c r="C39" s="9"/>
+      <c r="D39" s="9"/>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A40" s="9"/>
+      <c r="B40" s="9"/>
+      <c r="C40" s="9"/>
+      <c r="D40" s="9"/>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A41" s="9"/>
+      <c r="B41" s="9"/>
+      <c r="C41" s="9"/>
+      <c r="D41" s="9"/>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A42" s="9"/>
+      <c r="B42" s="9"/>
+      <c r="C42" s="9"/>
+      <c r="D42" s="9"/>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A43" s="9"/>
+      <c r="B43" s="9"/>
+      <c r="C43" s="9"/>
+      <c r="D43" s="9"/>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A44" s="9"/>
+      <c r="B44" s="9"/>
+      <c r="C44" s="9"/>
+      <c r="D44" s="9"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B13A24C-6305-48F4-A1E6-55B31CAA1F4A}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A2:V51"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="36" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.5546875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="71.21875" style="4" customWidth="1"/>
+    <col min="4" max="4" width="56.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="6.21875" style="7" customWidth="1"/>
+    <col min="6" max="6" width="43.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="55.109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="67.88671875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="64.33203125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="7.77734375" style="7" customWidth="1"/>
+    <col min="11" max="11" width="39.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="48.88671875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="72.6640625" style="1" customWidth="1"/>
+    <col min="14" max="14" width="43.88671875" style="1" customWidth="1"/>
+    <col min="15" max="15" width="7.77734375" style="7" customWidth="1"/>
+    <col min="16" max="16" width="56.77734375" style="2" customWidth="1"/>
+    <col min="17" max="17" width="46.77734375" style="2" customWidth="1"/>
+    <col min="18" max="18" width="62.88671875" style="2" customWidth="1"/>
+    <col min="19" max="19" width="49.21875" style="1" customWidth="1"/>
+    <col min="20" max="20" width="8.77734375" style="8"/>
+    <col min="21" max="21" width="67.77734375" style="2" customWidth="1"/>
+    <col min="22" max="22" width="68.33203125" style="1" customWidth="1"/>
+    <col min="23" max="24" width="59.33203125" style="1" customWidth="1"/>
+    <col min="25" max="25" width="59.6640625" style="1" customWidth="1"/>
+    <col min="26" max="26" width="99.44140625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="41.21875" style="1" customWidth="1"/>
+    <col min="28" max="16384" width="8.77734375" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A2" s="3"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="P2" s="5"/>
+      <c r="Q2" s="5"/>
+      <c r="R2" s="5"/>
+      <c r="S2" s="5"/>
+      <c r="U2" s="5"/>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="9"/>
+      <c r="P3" s="1"/>
+      <c r="U3" s="1"/>
+      <c r="V3" s="2"/>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A4" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+    </row>
+    <row r="5" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A5" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+    </row>
+    <row r="6" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A6" s="9"/>
+      <c r="C6" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="D6" s="9"/>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A7" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="C7" s="1"/>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A8" s="9"/>
+      <c r="B8" s="44" t="s">
+        <v>212</v>
+      </c>
+      <c r="C8" s="43" t="s">
+        <v>218</v>
+      </c>
+      <c r="D8" s="43" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A9" s="9"/>
+      <c r="B9" s="9"/>
+      <c r="C9" s="43" t="s">
+        <v>234</v>
+      </c>
+      <c r="D9" s="43" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A10" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="C10" s="1"/>
+      <c r="D10" s="19"/>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A11" s="9"/>
+      <c r="B11" s="44" t="s">
+        <v>212</v>
+      </c>
+      <c r="C11" s="43" t="s">
+        <v>217</v>
+      </c>
+      <c r="D11" s="19"/>
+    </row>
+    <row r="12" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A12" s="9"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="43" t="s">
+        <v>233</v>
+      </c>
+      <c r="D12" s="19"/>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A13" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+    </row>
+    <row r="14" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A14" s="9"/>
+      <c r="B14" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="D14" s="19" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" ht="201.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="9"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="D15" s="19" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A16" s="9"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
+    </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A17" s="9"/>
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A18" s="9"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+    </row>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A19" s="9"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+    </row>
+    <row r="20" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="9"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1"/>
+      <c r="M20" s="1"/>
+      <c r="N20" s="1"/>
+      <c r="P20" s="2"/>
+      <c r="Q20" s="2"/>
+      <c r="R20" s="2"/>
+      <c r="S20" s="1"/>
+      <c r="T20" s="8"/>
+      <c r="U20" s="2"/>
+      <c r="V20" s="1"/>
+    </row>
+    <row r="21" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="9"/>
+      <c r="B21" s="9"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="9"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1"/>
+      <c r="M21" s="1"/>
+      <c r="N21" s="1"/>
+      <c r="P21" s="2"/>
+      <c r="Q21" s="2"/>
+      <c r="R21" s="2"/>
+      <c r="S21" s="1"/>
+      <c r="T21" s="8"/>
+      <c r="U21" s="2"/>
+      <c r="V21" s="1"/>
+    </row>
+    <row r="22" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="9"/>
+      <c r="B22" s="9"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+      <c r="K22" s="1"/>
+      <c r="L22" s="1"/>
+      <c r="M22" s="1"/>
+      <c r="N22" s="1"/>
+      <c r="P22" s="2"/>
+      <c r="Q22" s="2"/>
+      <c r="R22" s="2"/>
+      <c r="S22" s="1"/>
+      <c r="T22" s="8"/>
+      <c r="U22" s="2"/>
+      <c r="V22" s="1"/>
+    </row>
+    <row r="23" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="9"/>
+      <c r="B23" s="9"/>
+      <c r="C23" s="9"/>
+      <c r="D23" s="9"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+      <c r="K23" s="1"/>
+      <c r="L23" s="1"/>
+      <c r="M23" s="1"/>
+      <c r="N23" s="1"/>
+      <c r="P23" s="2"/>
+      <c r="Q23" s="2"/>
+      <c r="R23" s="2"/>
+      <c r="S23" s="1"/>
+      <c r="T23" s="8"/>
+      <c r="U23" s="2"/>
+      <c r="V23" s="1"/>
+    </row>
+    <row r="24" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="9"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="9"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
+      <c r="K24" s="1"/>
+      <c r="L24" s="1"/>
+      <c r="M24" s="1"/>
+      <c r="N24" s="1"/>
+      <c r="P24" s="2"/>
+      <c r="Q24" s="2"/>
+      <c r="R24" s="2"/>
+      <c r="S24" s="1"/>
+      <c r="T24" s="8"/>
+      <c r="U24" s="2"/>
+      <c r="V24" s="1"/>
+    </row>
+    <row r="25" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="9"/>
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
+      <c r="K25" s="1"/>
+      <c r="L25" s="1"/>
+      <c r="M25" s="1"/>
+      <c r="N25" s="1"/>
+      <c r="P25" s="2"/>
+      <c r="Q25" s="2"/>
+      <c r="R25" s="2"/>
+      <c r="S25" s="1"/>
+      <c r="T25" s="8"/>
+      <c r="U25" s="2"/>
+      <c r="V25" s="1"/>
+    </row>
+    <row r="26" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="9"/>
+      <c r="B26" s="9"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+      <c r="K26" s="1"/>
+      <c r="L26" s="1"/>
+      <c r="M26" s="1"/>
+      <c r="N26" s="1"/>
+      <c r="P26" s="2"/>
+      <c r="Q26" s="2"/>
+      <c r="R26" s="2"/>
+      <c r="S26" s="1"/>
+      <c r="T26" s="8"/>
+      <c r="U26" s="2"/>
+      <c r="V26" s="1"/>
+    </row>
+    <row r="27" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="9"/>
+      <c r="B27" s="9"/>
+      <c r="C27" s="9"/>
+      <c r="D27" s="9"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+      <c r="K27" s="1"/>
+      <c r="L27" s="1"/>
+      <c r="M27" s="1"/>
+      <c r="N27" s="1"/>
+      <c r="P27" s="2"/>
+      <c r="Q27" s="2"/>
+      <c r="R27" s="2"/>
+      <c r="S27" s="1"/>
+      <c r="T27" s="8"/>
+      <c r="U27" s="2"/>
+      <c r="V27" s="1"/>
+    </row>
+    <row r="28" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="9"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="9"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+      <c r="K28" s="1"/>
+      <c r="L28" s="1"/>
+      <c r="M28" s="1"/>
+      <c r="N28" s="1"/>
+      <c r="P28" s="2"/>
+      <c r="Q28" s="2"/>
+      <c r="R28" s="2"/>
+      <c r="S28" s="1"/>
+      <c r="T28" s="8"/>
+      <c r="U28" s="2"/>
+      <c r="V28" s="1"/>
+    </row>
+    <row r="29" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="9"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="9"/>
+      <c r="D29" s="9"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+      <c r="K29" s="1"/>
+      <c r="L29" s="1"/>
+      <c r="M29" s="1"/>
+      <c r="N29" s="1"/>
+      <c r="P29" s="2"/>
+      <c r="Q29" s="2"/>
+      <c r="R29" s="2"/>
+      <c r="S29" s="1"/>
+      <c r="T29" s="8"/>
+      <c r="U29" s="2"/>
+      <c r="V29" s="1"/>
+    </row>
+    <row r="30" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="9"/>
+      <c r="B30" s="9"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="9"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
+      <c r="K30" s="1"/>
+      <c r="L30" s="1"/>
+      <c r="M30" s="1"/>
+      <c r="N30" s="1"/>
+      <c r="P30" s="2"/>
+      <c r="Q30" s="2"/>
+      <c r="R30" s="2"/>
+      <c r="S30" s="1"/>
+      <c r="T30" s="8"/>
+      <c r="U30" s="2"/>
+      <c r="V30" s="1"/>
+    </row>
+    <row r="31" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="9"/>
+      <c r="B31" s="9"/>
+      <c r="C31" s="9"/>
+      <c r="D31" s="9"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+      <c r="K31" s="1"/>
+      <c r="L31" s="1"/>
+      <c r="M31" s="1"/>
+      <c r="N31" s="1"/>
+      <c r="P31" s="2"/>
+      <c r="Q31" s="2"/>
+      <c r="R31" s="2"/>
+      <c r="S31" s="1"/>
+      <c r="T31" s="8"/>
+      <c r="U31" s="2"/>
+      <c r="V31" s="1"/>
+    </row>
+    <row r="32" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="9"/>
+      <c r="B32" s="9"/>
+      <c r="C32" s="9"/>
+      <c r="D32" s="9"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+      <c r="K32" s="1"/>
+      <c r="L32" s="1"/>
+      <c r="M32" s="1"/>
+      <c r="N32" s="1"/>
+      <c r="P32" s="2"/>
+      <c r="Q32" s="2"/>
+      <c r="R32" s="2"/>
+      <c r="S32" s="1"/>
+      <c r="T32" s="8"/>
+      <c r="U32" s="2"/>
+      <c r="V32" s="1"/>
+    </row>
+    <row r="33" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="9"/>
+      <c r="B33" s="9"/>
+      <c r="C33" s="9"/>
+      <c r="D33" s="9"/>
+      <c r="F33" s="1"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
+      <c r="K33" s="1"/>
+      <c r="L33" s="1"/>
+      <c r="M33" s="1"/>
+      <c r="N33" s="1"/>
+      <c r="P33" s="2"/>
+      <c r="Q33" s="2"/>
+      <c r="R33" s="2"/>
+      <c r="S33" s="1"/>
+      <c r="T33" s="8"/>
+      <c r="U33" s="2"/>
+      <c r="V33" s="1"/>
+    </row>
+    <row r="34" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="9"/>
+      <c r="B34" s="9"/>
+      <c r="C34" s="9"/>
+      <c r="D34" s="9"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
+      <c r="K34" s="1"/>
+      <c r="L34" s="1"/>
+      <c r="M34" s="1"/>
+      <c r="N34" s="1"/>
+      <c r="P34" s="2"/>
+      <c r="Q34" s="2"/>
+      <c r="R34" s="2"/>
+      <c r="S34" s="1"/>
+      <c r="T34" s="8"/>
+      <c r="U34" s="2"/>
+      <c r="V34" s="1"/>
+    </row>
+    <row r="35" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="9"/>
+      <c r="B35" s="9"/>
+      <c r="C35" s="9"/>
+      <c r="D35" s="9"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="2"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
+      <c r="K35" s="1"/>
+      <c r="L35" s="1"/>
+      <c r="M35" s="1"/>
+      <c r="N35" s="1"/>
+      <c r="P35" s="2"/>
+      <c r="Q35" s="2"/>
+      <c r="R35" s="2"/>
+      <c r="S35" s="1"/>
+      <c r="T35" s="8"/>
+      <c r="U35" s="2"/>
+      <c r="V35" s="1"/>
+    </row>
+    <row r="36" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="9"/>
+      <c r="B36" s="9"/>
+      <c r="C36" s="9"/>
+      <c r="D36" s="9"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="1"/>
+      <c r="I36" s="1"/>
+      <c r="K36" s="1"/>
+      <c r="L36" s="1"/>
+      <c r="M36" s="1"/>
+      <c r="N36" s="1"/>
+      <c r="P36" s="2"/>
+      <c r="Q36" s="2"/>
+      <c r="R36" s="2"/>
+      <c r="S36" s="1"/>
+      <c r="T36" s="8"/>
+      <c r="U36" s="2"/>
+      <c r="V36" s="1"/>
+    </row>
+    <row r="37" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="9"/>
+      <c r="B37" s="9"/>
+      <c r="C37" s="9"/>
+      <c r="D37" s="9"/>
+      <c r="F37" s="1"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="1"/>
+      <c r="I37" s="1"/>
+      <c r="K37" s="1"/>
+      <c r="L37" s="1"/>
+      <c r="M37" s="1"/>
+      <c r="N37" s="1"/>
+      <c r="P37" s="2"/>
+      <c r="Q37" s="2"/>
+      <c r="R37" s="2"/>
+      <c r="S37" s="1"/>
+      <c r="T37" s="8"/>
+      <c r="U37" s="2"/>
+      <c r="V37" s="1"/>
+    </row>
+    <row r="38" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="9"/>
+      <c r="B38" s="9"/>
+      <c r="C38" s="9"/>
+      <c r="D38" s="9"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="1"/>
+      <c r="I38" s="1"/>
+      <c r="K38" s="1"/>
+      <c r="L38" s="1"/>
+      <c r="M38" s="1"/>
+      <c r="N38" s="1"/>
+      <c r="P38" s="2"/>
+      <c r="Q38" s="2"/>
+      <c r="R38" s="2"/>
+      <c r="S38" s="1"/>
+      <c r="T38" s="8"/>
+      <c r="U38" s="2"/>
+      <c r="V38" s="1"/>
+    </row>
+    <row r="39" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="9"/>
+      <c r="B39" s="9"/>
+      <c r="C39" s="9"/>
+      <c r="D39" s="9"/>
+      <c r="F39" s="1"/>
+      <c r="G39" s="2"/>
+      <c r="H39" s="1"/>
+      <c r="I39" s="1"/>
+      <c r="K39" s="1"/>
+      <c r="L39" s="1"/>
+      <c r="M39" s="1"/>
+      <c r="N39" s="1"/>
+      <c r="P39" s="2"/>
+      <c r="Q39" s="2"/>
+      <c r="R39" s="2"/>
+      <c r="S39" s="1"/>
+      <c r="T39" s="8"/>
+      <c r="U39" s="2"/>
+      <c r="V39" s="1"/>
+    </row>
+    <row r="40" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="9"/>
+      <c r="B40" s="9"/>
+      <c r="C40" s="9"/>
+      <c r="D40" s="9"/>
+      <c r="F40" s="1"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="1"/>
+      <c r="I40" s="1"/>
+      <c r="K40" s="1"/>
+      <c r="L40" s="1"/>
+      <c r="M40" s="1"/>
+      <c r="N40" s="1"/>
+      <c r="P40" s="2"/>
+      <c r="Q40" s="2"/>
+      <c r="R40" s="2"/>
+      <c r="S40" s="1"/>
+      <c r="T40" s="8"/>
+      <c r="U40" s="2"/>
+      <c r="V40" s="1"/>
+    </row>
+    <row r="41" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="9"/>
+      <c r="B41" s="9"/>
+      <c r="C41" s="9"/>
+      <c r="D41" s="9"/>
+      <c r="F41" s="1"/>
+      <c r="G41" s="2"/>
+      <c r="H41" s="1"/>
+      <c r="I41" s="1"/>
+      <c r="K41" s="1"/>
+      <c r="L41" s="1"/>
+      <c r="M41" s="1"/>
+      <c r="N41" s="1"/>
+      <c r="P41" s="2"/>
+      <c r="Q41" s="2"/>
+      <c r="R41" s="2"/>
+      <c r="S41" s="1"/>
+      <c r="T41" s="8"/>
+      <c r="U41" s="2"/>
+      <c r="V41" s="1"/>
+    </row>
+    <row r="42" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="9"/>
+      <c r="B42" s="9"/>
+      <c r="C42" s="9"/>
+      <c r="D42" s="9"/>
+      <c r="F42" s="1"/>
+      <c r="G42" s="2"/>
+      <c r="H42" s="1"/>
+      <c r="I42" s="1"/>
+      <c r="K42" s="1"/>
+      <c r="L42" s="1"/>
+      <c r="M42" s="1"/>
+      <c r="N42" s="1"/>
+      <c r="P42" s="2"/>
+      <c r="Q42" s="2"/>
+      <c r="R42" s="2"/>
+      <c r="S42" s="1"/>
+      <c r="T42" s="8"/>
+      <c r="U42" s="2"/>
+      <c r="V42" s="1"/>
+    </row>
+    <row r="43" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="9"/>
+      <c r="B43" s="9"/>
+      <c r="C43" s="9"/>
+      <c r="D43" s="9"/>
+      <c r="F43" s="1"/>
+      <c r="G43" s="2"/>
+      <c r="H43" s="1"/>
+      <c r="I43" s="1"/>
+      <c r="K43" s="1"/>
+      <c r="L43" s="1"/>
+      <c r="M43" s="1"/>
+      <c r="N43" s="1"/>
+      <c r="P43" s="2"/>
+      <c r="Q43" s="2"/>
+      <c r="R43" s="2"/>
+      <c r="S43" s="1"/>
+      <c r="T43" s="8"/>
+      <c r="U43" s="2"/>
+      <c r="V43" s="1"/>
+    </row>
+    <row r="44" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="9"/>
+      <c r="B44" s="9"/>
+      <c r="C44" s="9"/>
+      <c r="D44" s="9"/>
+      <c r="F44" s="1"/>
+      <c r="G44" s="2"/>
+      <c r="H44" s="1"/>
+      <c r="I44" s="1"/>
+      <c r="K44" s="1"/>
+      <c r="L44" s="1"/>
+      <c r="M44" s="1"/>
+      <c r="N44" s="1"/>
+      <c r="P44" s="2"/>
+      <c r="Q44" s="2"/>
+      <c r="R44" s="2"/>
+      <c r="S44" s="1"/>
+      <c r="T44" s="8"/>
+      <c r="U44" s="2"/>
+      <c r="V44" s="1"/>
+    </row>
+    <row r="45" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="9"/>
+      <c r="B45" s="9"/>
+      <c r="C45" s="9"/>
+      <c r="D45" s="9"/>
+      <c r="F45" s="1"/>
+      <c r="G45" s="2"/>
+      <c r="H45" s="1"/>
+      <c r="I45" s="1"/>
+      <c r="K45" s="1"/>
+      <c r="L45" s="1"/>
+      <c r="M45" s="1"/>
+      <c r="N45" s="1"/>
+      <c r="P45" s="2"/>
+      <c r="Q45" s="2"/>
+      <c r="R45" s="2"/>
+      <c r="S45" s="1"/>
+      <c r="T45" s="8"/>
+      <c r="U45" s="2"/>
+      <c r="V45" s="1"/>
+    </row>
+    <row r="46" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="9"/>
+      <c r="B46" s="9"/>
+      <c r="C46" s="9"/>
+      <c r="D46" s="9"/>
+      <c r="F46" s="1"/>
+      <c r="G46" s="2"/>
+      <c r="H46" s="1"/>
+      <c r="I46" s="1"/>
+      <c r="K46" s="1"/>
+      <c r="L46" s="1"/>
+      <c r="M46" s="1"/>
+      <c r="N46" s="1"/>
+      <c r="P46" s="2"/>
+      <c r="Q46" s="2"/>
+      <c r="R46" s="2"/>
+      <c r="S46" s="1"/>
+      <c r="T46" s="8"/>
+      <c r="U46" s="2"/>
+      <c r="V46" s="1"/>
+    </row>
+    <row r="47" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="9"/>
+      <c r="B47" s="9"/>
+      <c r="C47" s="9"/>
+      <c r="D47" s="9"/>
+      <c r="F47" s="1"/>
+      <c r="G47" s="2"/>
+      <c r="H47" s="1"/>
+      <c r="I47" s="1"/>
+      <c r="K47" s="1"/>
+      <c r="L47" s="1"/>
+      <c r="M47" s="1"/>
+      <c r="N47" s="1"/>
+      <c r="P47" s="2"/>
+      <c r="Q47" s="2"/>
+      <c r="R47" s="2"/>
+      <c r="S47" s="1"/>
+      <c r="T47" s="8"/>
+      <c r="U47" s="2"/>
+      <c r="V47" s="1"/>
+    </row>
+    <row r="48" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="9"/>
+      <c r="B48" s="9"/>
+      <c r="C48" s="9"/>
+      <c r="D48" s="9"/>
+      <c r="F48" s="1"/>
+      <c r="G48" s="2"/>
+      <c r="H48" s="1"/>
+      <c r="I48" s="1"/>
+      <c r="K48" s="1"/>
+      <c r="L48" s="1"/>
+      <c r="M48" s="1"/>
+      <c r="N48" s="1"/>
+      <c r="P48" s="2"/>
+      <c r="Q48" s="2"/>
+      <c r="R48" s="2"/>
+      <c r="S48" s="1"/>
+      <c r="T48" s="8"/>
+      <c r="U48" s="2"/>
+      <c r="V48" s="1"/>
+    </row>
+    <row r="49" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="9"/>
+      <c r="B49" s="9"/>
+      <c r="C49" s="9"/>
+      <c r="D49" s="9"/>
+      <c r="F49" s="1"/>
+      <c r="G49" s="2"/>
+      <c r="H49" s="1"/>
+      <c r="I49" s="1"/>
+      <c r="K49" s="1"/>
+      <c r="L49" s="1"/>
+      <c r="M49" s="1"/>
+      <c r="N49" s="1"/>
+      <c r="P49" s="2"/>
+      <c r="Q49" s="2"/>
+      <c r="R49" s="2"/>
+      <c r="S49" s="1"/>
+      <c r="T49" s="8"/>
+      <c r="U49" s="2"/>
+      <c r="V49" s="1"/>
+    </row>
+    <row r="50" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="9"/>
+      <c r="B50" s="9"/>
+      <c r="C50" s="9"/>
+      <c r="D50" s="9"/>
+      <c r="F50" s="1"/>
+      <c r="G50" s="2"/>
+      <c r="H50" s="1"/>
+      <c r="I50" s="1"/>
+      <c r="K50" s="1"/>
+      <c r="L50" s="1"/>
+      <c r="M50" s="1"/>
+      <c r="N50" s="1"/>
+      <c r="P50" s="2"/>
+      <c r="Q50" s="2"/>
+      <c r="R50" s="2"/>
+      <c r="S50" s="1"/>
+      <c r="T50" s="8"/>
+      <c r="U50" s="2"/>
+      <c r="V50" s="1"/>
+    </row>
+    <row r="51" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="9"/>
+      <c r="B51" s="9"/>
+      <c r="C51" s="9"/>
+      <c r="D51" s="9"/>
+      <c r="F51" s="1"/>
+      <c r="G51" s="2"/>
+      <c r="H51" s="1"/>
+      <c r="I51" s="1"/>
+      <c r="K51" s="1"/>
+      <c r="L51" s="1"/>
+      <c r="M51" s="1"/>
+      <c r="N51" s="1"/>
+      <c r="P51" s="2"/>
+      <c r="Q51" s="2"/>
+      <c r="R51" s="2"/>
+      <c r="S51" s="1"/>
+      <c r="T51" s="8"/>
+      <c r="U51" s="2"/>
+      <c r="V51" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA83B601-5B0E-4344-A36B-7DD0432A3007}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A2:V47"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="36" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.5546875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="71.21875" style="4" customWidth="1"/>
+    <col min="4" max="4" width="56.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="6.21875" style="7" customWidth="1"/>
+    <col min="6" max="6" width="43.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="55.109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="67.88671875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="64.33203125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="7.77734375" style="7" customWidth="1"/>
+    <col min="11" max="11" width="39.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="48.88671875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="72.6640625" style="1" customWidth="1"/>
+    <col min="14" max="14" width="43.88671875" style="1" customWidth="1"/>
+    <col min="15" max="15" width="7.77734375" style="7" customWidth="1"/>
+    <col min="16" max="16" width="56.77734375" style="2" customWidth="1"/>
+    <col min="17" max="17" width="46.77734375" style="2" customWidth="1"/>
+    <col min="18" max="18" width="62.88671875" style="2" customWidth="1"/>
+    <col min="19" max="19" width="49.21875" style="1" customWidth="1"/>
+    <col min="20" max="20" width="8.77734375" style="8"/>
+    <col min="21" max="21" width="67.77734375" style="2" customWidth="1"/>
+    <col min="22" max="22" width="68.33203125" style="1" customWidth="1"/>
+    <col min="23" max="24" width="59.33203125" style="1" customWidth="1"/>
+    <col min="25" max="25" width="59.6640625" style="1" customWidth="1"/>
+    <col min="26" max="26" width="99.44140625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="41.21875" style="1" customWidth="1"/>
+    <col min="28" max="16384" width="8.77734375" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A2" s="3"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="P2" s="5"/>
+      <c r="Q2" s="5"/>
+      <c r="R2" s="5"/>
+      <c r="S2" s="5"/>
+      <c r="U2" s="5"/>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="9"/>
+      <c r="P3" s="1"/>
+      <c r="U3" s="1"/>
+      <c r="V3" s="2"/>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A4" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+    </row>
+    <row r="5" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A5" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+    </row>
+    <row r="6" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="9"/>
+      <c r="C6" s="43" t="s">
+        <v>209</v>
+      </c>
+      <c r="D6" s="9"/>
+    </row>
+    <row r="7" spans="1:22" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="9"/>
+      <c r="B7" s="44" t="s">
+        <v>211</v>
+      </c>
+      <c r="C7" s="43" t="s">
+        <v>210</v>
+      </c>
+      <c r="D7" s="43" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="9"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="43" t="s">
+        <v>232</v>
+      </c>
+      <c r="D8" s="43" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A9" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="B9" s="9"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
+    </row>
+    <row r="10" spans="1:22" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A10" s="9"/>
+      <c r="B10" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="C10" s="43" t="s">
+        <v>221</v>
+      </c>
+      <c r="D10" s="43" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="9"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="43" t="s">
+        <v>222</v>
+      </c>
+      <c r="D11" s="43" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A12" s="9"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A13" s="9"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A14" s="9"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A15" s="9"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+    </row>
+    <row r="16" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="9"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="K16" s="1"/>
+      <c r="L16" s="1"/>
+      <c r="M16" s="1"/>
+      <c r="N16" s="1"/>
+      <c r="P16" s="2"/>
+      <c r="Q16" s="2"/>
+      <c r="R16" s="2"/>
+      <c r="S16" s="1"/>
+      <c r="T16" s="8"/>
+      <c r="U16" s="2"/>
+      <c r="V16" s="1"/>
+    </row>
+    <row r="17" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="9"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="K17" s="1"/>
+      <c r="L17" s="1"/>
+      <c r="M17" s="1"/>
+      <c r="N17" s="1"/>
+      <c r="P17" s="2"/>
+      <c r="Q17" s="2"/>
+      <c r="R17" s="2"/>
+      <c r="S17" s="1"/>
+      <c r="T17" s="8"/>
+      <c r="U17" s="2"/>
+      <c r="V17" s="1"/>
     </row>
     <row r="18" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" s="9"/>
@@ -8298,48 +10887,6 @@
       <c r="T47" s="8"/>
       <c r="U47" s="2"/>
       <c r="V47" s="1"/>
-    </row>
-    <row r="48" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="9"/>
-      <c r="B48" s="9"/>
-      <c r="C48" s="9"/>
-      <c r="D48" s="9"/>
-      <c r="F48" s="1"/>
-      <c r="G48" s="2"/>
-      <c r="H48" s="1"/>
-      <c r="I48" s="1"/>
-      <c r="K48" s="1"/>
-      <c r="L48" s="1"/>
-      <c r="M48" s="1"/>
-      <c r="N48" s="1"/>
-      <c r="P48" s="2"/>
-      <c r="Q48" s="2"/>
-      <c r="R48" s="2"/>
-      <c r="S48" s="1"/>
-      <c r="T48" s="8"/>
-      <c r="U48" s="2"/>
-      <c r="V48" s="1"/>
-    </row>
-    <row r="49" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="9"/>
-      <c r="B49" s="9"/>
-      <c r="C49" s="9"/>
-      <c r="D49" s="9"/>
-      <c r="F49" s="1"/>
-      <c r="G49" s="2"/>
-      <c r="H49" s="1"/>
-      <c r="I49" s="1"/>
-      <c r="K49" s="1"/>
-      <c r="L49" s="1"/>
-      <c r="M49" s="1"/>
-      <c r="N49" s="1"/>
-      <c r="P49" s="2"/>
-      <c r="Q49" s="2"/>
-      <c r="R49" s="2"/>
-      <c r="S49" s="1"/>
-      <c r="T49" s="8"/>
-      <c r="U49" s="2"/>
-      <c r="V49" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8824,7 +11371,7 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="34" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="B28" s="31"/>
       <c r="C28" s="32"/>
@@ -8832,43 +11379,43 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B29" s="32" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="C29" s="35" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="D29" s="9"/>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B30" s="32" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="C30" s="36" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="D30" s="9"/>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B31" s="32" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="C31" s="36" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="D31" s="9"/>
     </row>
     <row r="32" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B32" s="32" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="C32" s="36" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="D32" s="9"/>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="20" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="C33" s="9" t="s">
         <v>45</v>
@@ -8957,7 +11504,7 @@
       </c>
       <c r="C44" s="13"/>
       <c r="D44" s="26" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
@@ -8970,56 +11517,56 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="28" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="D46" s="27" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B47" s="19" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="C47" s="19" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B48" s="19" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="C48" s="19" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="29" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="D49" s="27" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="C50" s="19" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="29" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="D51" s="26" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C52" s="19" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="D46" r:id="rId1" location=":~:text=%D0%A1%D0%BE%D0%B7%D0%B4%D0%B0%D0%BD%D0%B8%D0%B5%20%D0%B1%D0%B0%D0%B7%D1%8B%20%D0%B4%D0%B0%D0%BD%D0%BD%D1%8B%D1%85" xr:uid="{FDFE2116-2B22-4A87-B37D-3DFA9E8F9FE0}"/>
     <hyperlink ref="D44" r:id="rId2" location=":~:text=%D0%A1%D0%BE%D0%B7%D0%B4%D0%B0%D0%BD%D0%B8%D0%B5%20%D0%B1%D0%B0%D0%B7%D1%8B%20%D0%B4%D0%B0%D0%BD%D0%BD%D1%8B%D1%85%20%D0%B2%20SQL%20Management%20Studio" xr:uid="{5B701F02-CEF7-44EA-83C6-0E21D7145608}"/>
@@ -9095,7 +11642,7 @@
       </c>
       <c r="C3" s="9"/>
       <c r="D3" s="26" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="P3" s="1"/>
       <c r="U3" s="1"/>
@@ -9103,7 +11650,7 @@
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A4" s="20" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="B4" s="9"/>
       <c r="C4" s="9"/>
@@ -9112,32 +11659,32 @@
     <row r="5" spans="1:22" ht="72" x14ac:dyDescent="0.3">
       <c r="A5" s="9"/>
       <c r="B5" s="19" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="D5" s="9"/>
     </row>
     <row r="6" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="21" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="D6" s="9"/>
     </row>
     <row r="7" spans="1:22" ht="72" x14ac:dyDescent="0.3">
       <c r="A7" s="9"/>
       <c r="B7" s="19" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="D7" s="9"/>
     </row>
     <row r="8" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="21" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="B8" s="19"/>
       <c r="C8" s="1"/>
@@ -9147,7 +11694,7 @@
       <c r="A9" s="9"/>
       <c r="B9" s="19"/>
       <c r="C9" s="19" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="D9" s="9"/>
     </row>
@@ -9159,7 +11706,7 @@
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A11" s="21" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="B11" s="9"/>
       <c r="C11" s="9"/>
@@ -9168,14 +11715,14 @@
     <row r="12" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A12" s="9"/>
       <c r="B12" s="19" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A13" s="21" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="B13" s="9"/>
       <c r="C13" s="9"/>
@@ -9184,13 +11731,13 @@
     <row r="14" spans="1:22" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A14" s="9"/>
       <c r="B14" s="19" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="D14" s="19" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.3">
@@ -9977,7 +12524,7 @@
       </c>
       <c r="B4" s="9"/>
       <c r="C4" s="37" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="D4" s="9"/>
     </row>
@@ -10008,7 +12555,9 @@
       <c r="D6" s="1"/>
     </row>
     <row r="7" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="9"/>
+      <c r="A7" s="45" t="s">
+        <v>227</v>
+      </c>
       <c r="B7" s="9"/>
       <c r="C7" s="9"/>
       <c r="D7" s="9"/>
@@ -10028,10 +12577,14 @@
       <c r="U7" s="2"/>
       <c r="V7" s="1"/>
     </row>
-    <row r="8" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:22" s="7" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A8" s="9"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
+      <c r="B8" s="43" t="s">
+        <v>228</v>
+      </c>
+      <c r="C8" s="43" t="s">
+        <v>230</v>
+      </c>
       <c r="D8" s="9"/>
       <c r="F8" s="1"/>
       <c r="G8" s="2"/>
@@ -10050,9 +12603,11 @@
       <c r="V8" s="1"/>
     </row>
     <row r="9" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="9"/>
+      <c r="A9" s="45" t="s">
+        <v>229</v>
+      </c>
       <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
+      <c r="C9" s="46"/>
       <c r="D9" s="9"/>
       <c r="F9" s="1"/>
       <c r="G9" s="2"/>
@@ -10070,10 +12625,14 @@
       <c r="U9" s="2"/>
       <c r="V9" s="1"/>
     </row>
-    <row r="10" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:22" s="7" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A10" s="9"/>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
+      <c r="B10" s="43" t="s">
+        <v>228</v>
+      </c>
+      <c r="C10" s="43" t="s">
+        <v>231</v>
+      </c>
       <c r="D10" s="9"/>
       <c r="F10" s="1"/>
       <c r="G10" s="2"/>
@@ -10523,7 +13082,7 @@
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A4" s="25" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="B4" s="9"/>
       <c r="D4" s="9"/>
@@ -10533,22 +13092,24 @@
     </row>
     <row r="5" spans="1:22" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A5" s="19" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>109</v>
-      </c>
-      <c r="D5" s="9"/>
+        <v>102</v>
+      </c>
+      <c r="D5" s="42" t="s">
+        <v>207</v>
+      </c>
       <c r="P5" s="1"/>
       <c r="U5" s="1"/>
       <c r="V5" s="2"/>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A6" s="24" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
@@ -10556,19 +13117,21 @@
     </row>
     <row r="7" spans="1:22" ht="72" x14ac:dyDescent="0.3">
       <c r="A7" s="19" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="B7" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="C7" s="19" t="s">
         <v>111</v>
       </c>
-      <c r="C7" s="19" t="s">
-        <v>118</v>
-      </c>
-      <c r="D7" s="9"/>
+      <c r="D7" s="42" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="8" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A8" s="24" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="B8" s="9"/>
       <c r="C8" s="9"/>
@@ -10576,122 +13139,126 @@
     </row>
     <row r="9" spans="1:22" ht="216" x14ac:dyDescent="0.3">
       <c r="A9" s="19" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="D9" s="19" t="s">
-        <v>107</v>
+        <v>101</v>
+      </c>
+      <c r="D9" s="42" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A10" s="25" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="C10" s="19"/>
       <c r="D10" s="4"/>
     </row>
     <row r="11" spans="1:22" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A11" s="32" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="B11" s="32" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="C11" s="32" t="s">
-        <v>153</v>
-      </c>
-      <c r="D11" s="33"/>
+        <v>146</v>
+      </c>
+      <c r="D11" s="33" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="12" spans="1:22" ht="72" x14ac:dyDescent="0.3">
       <c r="A12" s="32" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="B12" s="31"/>
       <c r="C12" s="32" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="D12" s="33"/>
     </row>
     <row r="13" spans="1:22" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A13" s="32" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="B13" s="32" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="C13" s="32" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="D13" s="33"/>
     </row>
     <row r="14" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A14" s="32" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="B14" s="31"/>
       <c r="C14" s="32" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="D14" s="33"/>
     </row>
     <row r="15" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A15" s="32" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="B15" s="31" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="C15" s="32" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="D15" s="33"/>
     </row>
     <row r="16" spans="1:22" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A16" s="32" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="B16" s="31" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="C16" s="32" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="D16" s="33"/>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A17" s="38" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="B17" s="31" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="C17" s="32"/>
       <c r="D17" s="33"/>
     </row>
     <row r="18" spans="1:22" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A18" s="32" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="B18" s="32" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="C18" s="32" t="s">
-        <v>172</v>
-      </c>
-      <c r="D18" s="33"/>
+        <v>165</v>
+      </c>
+      <c r="D18" s="33" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="19" spans="1:22" s="7" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A19" s="32" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="B19" s="31"/>
       <c r="C19" s="32" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="D19" s="33"/>
       <c r="F19" s="1"/>
@@ -10712,11 +13279,11 @@
     </row>
     <row r="20" spans="1:22" s="7" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A20" s="32" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="B20" s="31"/>
       <c r="C20" s="32" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="D20" s="33"/>
       <c r="F20" s="1"/>
@@ -10737,11 +13304,11 @@
     </row>
     <row r="21" spans="1:22" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A21" s="32" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="B21" s="31"/>
       <c r="C21" s="32" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="D21" s="33"/>
       <c r="F21" s="1"/>
@@ -10762,11 +13329,11 @@
     </row>
     <row r="22" spans="1:22" s="7" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A22" s="32" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="B22" s="31"/>
       <c r="C22" s="32" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="D22" s="33"/>
       <c r="F22" s="1"/>
@@ -10787,11 +13354,11 @@
     </row>
     <row r="23" spans="1:22" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A23" s="32" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="B23" s="31"/>
       <c r="C23" s="32" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="D23" s="33"/>
       <c r="F23" s="1"/>
@@ -10812,11 +13379,11 @@
     </row>
     <row r="24" spans="1:22" s="7" customFormat="1" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A24" s="32" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="B24" s="31"/>
       <c r="C24" s="32" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="D24" s="33"/>
       <c r="F24" s="1"/>
@@ -10837,13 +13404,13 @@
     </row>
     <row r="25" spans="1:22" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A25" s="32" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="B25" s="31" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="C25" s="32" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="D25" s="33"/>
       <c r="F25" s="1"/>
@@ -10864,11 +13431,11 @@
     </row>
     <row r="26" spans="1:22" s="7" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A26" s="32" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="B26" s="31"/>
       <c r="C26" s="32" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="D26" s="33"/>
       <c r="F26" s="1"/>
@@ -10889,13 +13456,13 @@
     </row>
     <row r="27" spans="1:22" s="7" customFormat="1" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A27" s="32" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="B27" s="31" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="C27" s="32" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="D27" s="33"/>
       <c r="F27" s="1"/>
@@ -10916,13 +13483,13 @@
     </row>
     <row r="28" spans="1:22" s="7" customFormat="1" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A28" s="32" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="B28" s="39" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="C28" s="32" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="D28" s="33"/>
       <c r="F28" s="1"/>
@@ -10943,13 +13510,13 @@
     </row>
     <row r="29" spans="1:22" s="7" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A29" s="32" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="B29" s="39" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="C29" s="32" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="D29" s="33"/>
       <c r="F29" s="1"/>
@@ -10970,11 +13537,11 @@
     </row>
     <row r="30" spans="1:22" s="7" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A30" s="32" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="B30" s="31"/>
       <c r="C30" s="32" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="D30" s="33"/>
       <c r="F30" s="1"/>
@@ -10995,13 +13562,13 @@
     </row>
     <row r="31" spans="1:22" s="7" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A31" s="32" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="B31" s="39" t="s">
+        <v>187</v>
+      </c>
+      <c r="C31" s="32" t="s">
         <v>194</v>
-      </c>
-      <c r="C31" s="32" t="s">
-        <v>201</v>
       </c>
       <c r="D31" s="33"/>
       <c r="F31" s="1"/>
@@ -11427,6 +13994,838 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4794FD93-B283-45AF-BCD9-82490C321ADD}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A2:V48"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="36" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.5546875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="71.21875" style="4" customWidth="1"/>
+    <col min="4" max="4" width="56.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="6.21875" style="7" customWidth="1"/>
+    <col min="6" max="6" width="43.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="55.109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="67.88671875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="64.33203125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="7.77734375" style="7" customWidth="1"/>
+    <col min="11" max="11" width="39.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="48.88671875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="72.6640625" style="1" customWidth="1"/>
+    <col min="14" max="14" width="43.88671875" style="1" customWidth="1"/>
+    <col min="15" max="15" width="7.77734375" style="7" customWidth="1"/>
+    <col min="16" max="16" width="56.77734375" style="2" customWidth="1"/>
+    <col min="17" max="17" width="46.77734375" style="2" customWidth="1"/>
+    <col min="18" max="18" width="62.88671875" style="2" customWidth="1"/>
+    <col min="19" max="19" width="49.21875" style="1" customWidth="1"/>
+    <col min="20" max="20" width="8.77734375" style="8"/>
+    <col min="21" max="21" width="67.77734375" style="2" customWidth="1"/>
+    <col min="22" max="22" width="68.33203125" style="1" customWidth="1"/>
+    <col min="23" max="24" width="59.33203125" style="1" customWidth="1"/>
+    <col min="25" max="25" width="59.6640625" style="1" customWidth="1"/>
+    <col min="26" max="26" width="99.44140625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="41.21875" style="1" customWidth="1"/>
+    <col min="28" max="16384" width="8.77734375" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A2" s="3"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="P2" s="5"/>
+      <c r="Q2" s="5"/>
+      <c r="R2" s="5"/>
+      <c r="S2" s="5"/>
+      <c r="U2" s="5"/>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="9"/>
+      <c r="P3" s="1"/>
+      <c r="U3" s="1"/>
+      <c r="V3" s="2"/>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A4" s="45" t="s">
+        <v>224</v>
+      </c>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A5" s="9"/>
+      <c r="B5" s="43" t="s">
+        <v>226</v>
+      </c>
+      <c r="C5" s="43" t="s">
+        <v>225</v>
+      </c>
+      <c r="D5" s="9"/>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A6" s="45" t="s">
+        <v>223</v>
+      </c>
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+    </row>
+    <row r="7" spans="1:22" ht="230.4" x14ac:dyDescent="0.3">
+      <c r="A7" s="9"/>
+      <c r="B7" s="9"/>
+      <c r="C7" s="43" t="s">
+        <v>235</v>
+      </c>
+      <c r="D7" s="9"/>
+    </row>
+    <row r="8" spans="1:22" ht="331.2" x14ac:dyDescent="0.3">
+      <c r="A8" s="9"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="43" t="s">
+        <v>236</v>
+      </c>
+      <c r="D8" s="9"/>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A9" s="9"/>
+      <c r="B9" s="9"/>
+      <c r="D9" s="9"/>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A10" s="9"/>
+      <c r="B10" s="9"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A11" s="9"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="9"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A12" s="9"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A13" s="9"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A14" s="9"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A15" s="9"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A16" s="9"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
+    </row>
+    <row r="17" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="9"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="K17" s="1"/>
+      <c r="L17" s="1"/>
+      <c r="M17" s="1"/>
+      <c r="N17" s="1"/>
+      <c r="P17" s="2"/>
+      <c r="Q17" s="2"/>
+      <c r="R17" s="2"/>
+      <c r="S17" s="1"/>
+      <c r="T17" s="8"/>
+      <c r="U17" s="2"/>
+      <c r="V17" s="1"/>
+    </row>
+    <row r="18" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="9"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="K18" s="1"/>
+      <c r="L18" s="1"/>
+      <c r="M18" s="1"/>
+      <c r="N18" s="1"/>
+      <c r="P18" s="2"/>
+      <c r="Q18" s="2"/>
+      <c r="R18" s="2"/>
+      <c r="S18" s="1"/>
+      <c r="T18" s="8"/>
+      <c r="U18" s="2"/>
+      <c r="V18" s="1"/>
+    </row>
+    <row r="19" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="9"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="1"/>
+      <c r="P19" s="2"/>
+      <c r="Q19" s="2"/>
+      <c r="R19" s="2"/>
+      <c r="S19" s="1"/>
+      <c r="T19" s="8"/>
+      <c r="U19" s="2"/>
+      <c r="V19" s="1"/>
+    </row>
+    <row r="20" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="9"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1"/>
+      <c r="M20" s="1"/>
+      <c r="N20" s="1"/>
+      <c r="P20" s="2"/>
+      <c r="Q20" s="2"/>
+      <c r="R20" s="2"/>
+      <c r="S20" s="1"/>
+      <c r="T20" s="8"/>
+      <c r="U20" s="2"/>
+      <c r="V20" s="1"/>
+    </row>
+    <row r="21" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="9"/>
+      <c r="B21" s="9"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="9"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1"/>
+      <c r="M21" s="1"/>
+      <c r="N21" s="1"/>
+      <c r="P21" s="2"/>
+      <c r="Q21" s="2"/>
+      <c r="R21" s="2"/>
+      <c r="S21" s="1"/>
+      <c r="T21" s="8"/>
+      <c r="U21" s="2"/>
+      <c r="V21" s="1"/>
+    </row>
+    <row r="22" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="9"/>
+      <c r="B22" s="9"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+      <c r="K22" s="1"/>
+      <c r="L22" s="1"/>
+      <c r="M22" s="1"/>
+      <c r="N22" s="1"/>
+      <c r="P22" s="2"/>
+      <c r="Q22" s="2"/>
+      <c r="R22" s="2"/>
+      <c r="S22" s="1"/>
+      <c r="T22" s="8"/>
+      <c r="U22" s="2"/>
+      <c r="V22" s="1"/>
+    </row>
+    <row r="23" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="9"/>
+      <c r="B23" s="9"/>
+      <c r="C23" s="9"/>
+      <c r="D23" s="9"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+      <c r="K23" s="1"/>
+      <c r="L23" s="1"/>
+      <c r="M23" s="1"/>
+      <c r="N23" s="1"/>
+      <c r="P23" s="2"/>
+      <c r="Q23" s="2"/>
+      <c r="R23" s="2"/>
+      <c r="S23" s="1"/>
+      <c r="T23" s="8"/>
+      <c r="U23" s="2"/>
+      <c r="V23" s="1"/>
+    </row>
+    <row r="24" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="9"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="9"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
+      <c r="K24" s="1"/>
+      <c r="L24" s="1"/>
+      <c r="M24" s="1"/>
+      <c r="N24" s="1"/>
+      <c r="P24" s="2"/>
+      <c r="Q24" s="2"/>
+      <c r="R24" s="2"/>
+      <c r="S24" s="1"/>
+      <c r="T24" s="8"/>
+      <c r="U24" s="2"/>
+      <c r="V24" s="1"/>
+    </row>
+    <row r="25" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="9"/>
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
+      <c r="K25" s="1"/>
+      <c r="L25" s="1"/>
+      <c r="M25" s="1"/>
+      <c r="N25" s="1"/>
+      <c r="P25" s="2"/>
+      <c r="Q25" s="2"/>
+      <c r="R25" s="2"/>
+      <c r="S25" s="1"/>
+      <c r="T25" s="8"/>
+      <c r="U25" s="2"/>
+      <c r="V25" s="1"/>
+    </row>
+    <row r="26" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="9"/>
+      <c r="B26" s="9"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+      <c r="K26" s="1"/>
+      <c r="L26" s="1"/>
+      <c r="M26" s="1"/>
+      <c r="N26" s="1"/>
+      <c r="P26" s="2"/>
+      <c r="Q26" s="2"/>
+      <c r="R26" s="2"/>
+      <c r="S26" s="1"/>
+      <c r="T26" s="8"/>
+      <c r="U26" s="2"/>
+      <c r="V26" s="1"/>
+    </row>
+    <row r="27" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="9"/>
+      <c r="B27" s="9"/>
+      <c r="C27" s="9"/>
+      <c r="D27" s="9"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+      <c r="K27" s="1"/>
+      <c r="L27" s="1"/>
+      <c r="M27" s="1"/>
+      <c r="N27" s="1"/>
+      <c r="P27" s="2"/>
+      <c r="Q27" s="2"/>
+      <c r="R27" s="2"/>
+      <c r="S27" s="1"/>
+      <c r="T27" s="8"/>
+      <c r="U27" s="2"/>
+      <c r="V27" s="1"/>
+    </row>
+    <row r="28" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="9"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="9"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+      <c r="K28" s="1"/>
+      <c r="L28" s="1"/>
+      <c r="M28" s="1"/>
+      <c r="N28" s="1"/>
+      <c r="P28" s="2"/>
+      <c r="Q28" s="2"/>
+      <c r="R28" s="2"/>
+      <c r="S28" s="1"/>
+      <c r="T28" s="8"/>
+      <c r="U28" s="2"/>
+      <c r="V28" s="1"/>
+    </row>
+    <row r="29" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="9"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="9"/>
+      <c r="D29" s="9"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+      <c r="K29" s="1"/>
+      <c r="L29" s="1"/>
+      <c r="M29" s="1"/>
+      <c r="N29" s="1"/>
+      <c r="P29" s="2"/>
+      <c r="Q29" s="2"/>
+      <c r="R29" s="2"/>
+      <c r="S29" s="1"/>
+      <c r="T29" s="8"/>
+      <c r="U29" s="2"/>
+      <c r="V29" s="1"/>
+    </row>
+    <row r="30" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="9"/>
+      <c r="B30" s="9"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="9"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
+      <c r="K30" s="1"/>
+      <c r="L30" s="1"/>
+      <c r="M30" s="1"/>
+      <c r="N30" s="1"/>
+      <c r="P30" s="2"/>
+      <c r="Q30" s="2"/>
+      <c r="R30" s="2"/>
+      <c r="S30" s="1"/>
+      <c r="T30" s="8"/>
+      <c r="U30" s="2"/>
+      <c r="V30" s="1"/>
+    </row>
+    <row r="31" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="9"/>
+      <c r="B31" s="9"/>
+      <c r="C31" s="9"/>
+      <c r="D31" s="9"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+      <c r="K31" s="1"/>
+      <c r="L31" s="1"/>
+      <c r="M31" s="1"/>
+      <c r="N31" s="1"/>
+      <c r="P31" s="2"/>
+      <c r="Q31" s="2"/>
+      <c r="R31" s="2"/>
+      <c r="S31" s="1"/>
+      <c r="T31" s="8"/>
+      <c r="U31" s="2"/>
+      <c r="V31" s="1"/>
+    </row>
+    <row r="32" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="9"/>
+      <c r="B32" s="9"/>
+      <c r="C32" s="9"/>
+      <c r="D32" s="9"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+      <c r="K32" s="1"/>
+      <c r="L32" s="1"/>
+      <c r="M32" s="1"/>
+      <c r="N32" s="1"/>
+      <c r="P32" s="2"/>
+      <c r="Q32" s="2"/>
+      <c r="R32" s="2"/>
+      <c r="S32" s="1"/>
+      <c r="T32" s="8"/>
+      <c r="U32" s="2"/>
+      <c r="V32" s="1"/>
+    </row>
+    <row r="33" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="9"/>
+      <c r="B33" s="9"/>
+      <c r="C33" s="9"/>
+      <c r="D33" s="9"/>
+      <c r="F33" s="1"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
+      <c r="K33" s="1"/>
+      <c r="L33" s="1"/>
+      <c r="M33" s="1"/>
+      <c r="N33" s="1"/>
+      <c r="P33" s="2"/>
+      <c r="Q33" s="2"/>
+      <c r="R33" s="2"/>
+      <c r="S33" s="1"/>
+      <c r="T33" s="8"/>
+      <c r="U33" s="2"/>
+      <c r="V33" s="1"/>
+    </row>
+    <row r="34" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="9"/>
+      <c r="B34" s="9"/>
+      <c r="C34" s="9"/>
+      <c r="D34" s="9"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
+      <c r="K34" s="1"/>
+      <c r="L34" s="1"/>
+      <c r="M34" s="1"/>
+      <c r="N34" s="1"/>
+      <c r="P34" s="2"/>
+      <c r="Q34" s="2"/>
+      <c r="R34" s="2"/>
+      <c r="S34" s="1"/>
+      <c r="T34" s="8"/>
+      <c r="U34" s="2"/>
+      <c r="V34" s="1"/>
+    </row>
+    <row r="35" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="9"/>
+      <c r="B35" s="9"/>
+      <c r="C35" s="9"/>
+      <c r="D35" s="9"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="2"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
+      <c r="K35" s="1"/>
+      <c r="L35" s="1"/>
+      <c r="M35" s="1"/>
+      <c r="N35" s="1"/>
+      <c r="P35" s="2"/>
+      <c r="Q35" s="2"/>
+      <c r="R35" s="2"/>
+      <c r="S35" s="1"/>
+      <c r="T35" s="8"/>
+      <c r="U35" s="2"/>
+      <c r="V35" s="1"/>
+    </row>
+    <row r="36" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="9"/>
+      <c r="B36" s="9"/>
+      <c r="C36" s="9"/>
+      <c r="D36" s="9"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="1"/>
+      <c r="I36" s="1"/>
+      <c r="K36" s="1"/>
+      <c r="L36" s="1"/>
+      <c r="M36" s="1"/>
+      <c r="N36" s="1"/>
+      <c r="P36" s="2"/>
+      <c r="Q36" s="2"/>
+      <c r="R36" s="2"/>
+      <c r="S36" s="1"/>
+      <c r="T36" s="8"/>
+      <c r="U36" s="2"/>
+      <c r="V36" s="1"/>
+    </row>
+    <row r="37" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="9"/>
+      <c r="B37" s="9"/>
+      <c r="C37" s="9"/>
+      <c r="D37" s="9"/>
+      <c r="F37" s="1"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="1"/>
+      <c r="I37" s="1"/>
+      <c r="K37" s="1"/>
+      <c r="L37" s="1"/>
+      <c r="M37" s="1"/>
+      <c r="N37" s="1"/>
+      <c r="P37" s="2"/>
+      <c r="Q37" s="2"/>
+      <c r="R37" s="2"/>
+      <c r="S37" s="1"/>
+      <c r="T37" s="8"/>
+      <c r="U37" s="2"/>
+      <c r="V37" s="1"/>
+    </row>
+    <row r="38" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="9"/>
+      <c r="B38" s="9"/>
+      <c r="C38" s="9"/>
+      <c r="D38" s="9"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="1"/>
+      <c r="I38" s="1"/>
+      <c r="K38" s="1"/>
+      <c r="L38" s="1"/>
+      <c r="M38" s="1"/>
+      <c r="N38" s="1"/>
+      <c r="P38" s="2"/>
+      <c r="Q38" s="2"/>
+      <c r="R38" s="2"/>
+      <c r="S38" s="1"/>
+      <c r="T38" s="8"/>
+      <c r="U38" s="2"/>
+      <c r="V38" s="1"/>
+    </row>
+    <row r="39" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="9"/>
+      <c r="B39" s="9"/>
+      <c r="C39" s="9"/>
+      <c r="D39" s="9"/>
+      <c r="F39" s="1"/>
+      <c r="G39" s="2"/>
+      <c r="H39" s="1"/>
+      <c r="I39" s="1"/>
+      <c r="K39" s="1"/>
+      <c r="L39" s="1"/>
+      <c r="M39" s="1"/>
+      <c r="N39" s="1"/>
+      <c r="P39" s="2"/>
+      <c r="Q39" s="2"/>
+      <c r="R39" s="2"/>
+      <c r="S39" s="1"/>
+      <c r="T39" s="8"/>
+      <c r="U39" s="2"/>
+      <c r="V39" s="1"/>
+    </row>
+    <row r="40" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="9"/>
+      <c r="B40" s="9"/>
+      <c r="C40" s="9"/>
+      <c r="D40" s="9"/>
+      <c r="F40" s="1"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="1"/>
+      <c r="I40" s="1"/>
+      <c r="K40" s="1"/>
+      <c r="L40" s="1"/>
+      <c r="M40" s="1"/>
+      <c r="N40" s="1"/>
+      <c r="P40" s="2"/>
+      <c r="Q40" s="2"/>
+      <c r="R40" s="2"/>
+      <c r="S40" s="1"/>
+      <c r="T40" s="8"/>
+      <c r="U40" s="2"/>
+      <c r="V40" s="1"/>
+    </row>
+    <row r="41" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="9"/>
+      <c r="B41" s="9"/>
+      <c r="C41" s="9"/>
+      <c r="D41" s="9"/>
+      <c r="F41" s="1"/>
+      <c r="G41" s="2"/>
+      <c r="H41" s="1"/>
+      <c r="I41" s="1"/>
+      <c r="K41" s="1"/>
+      <c r="L41" s="1"/>
+      <c r="M41" s="1"/>
+      <c r="N41" s="1"/>
+      <c r="P41" s="2"/>
+      <c r="Q41" s="2"/>
+      <c r="R41" s="2"/>
+      <c r="S41" s="1"/>
+      <c r="T41" s="8"/>
+      <c r="U41" s="2"/>
+      <c r="V41" s="1"/>
+    </row>
+    <row r="42" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="9"/>
+      <c r="B42" s="9"/>
+      <c r="C42" s="9"/>
+      <c r="D42" s="9"/>
+      <c r="F42" s="1"/>
+      <c r="G42" s="2"/>
+      <c r="H42" s="1"/>
+      <c r="I42" s="1"/>
+      <c r="K42" s="1"/>
+      <c r="L42" s="1"/>
+      <c r="M42" s="1"/>
+      <c r="N42" s="1"/>
+      <c r="P42" s="2"/>
+      <c r="Q42" s="2"/>
+      <c r="R42" s="2"/>
+      <c r="S42" s="1"/>
+      <c r="T42" s="8"/>
+      <c r="U42" s="2"/>
+      <c r="V42" s="1"/>
+    </row>
+    <row r="43" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="9"/>
+      <c r="B43" s="9"/>
+      <c r="C43" s="9"/>
+      <c r="D43" s="9"/>
+      <c r="F43" s="1"/>
+      <c r="G43" s="2"/>
+      <c r="H43" s="1"/>
+      <c r="I43" s="1"/>
+      <c r="K43" s="1"/>
+      <c r="L43" s="1"/>
+      <c r="M43" s="1"/>
+      <c r="N43" s="1"/>
+      <c r="P43" s="2"/>
+      <c r="Q43" s="2"/>
+      <c r="R43" s="2"/>
+      <c r="S43" s="1"/>
+      <c r="T43" s="8"/>
+      <c r="U43" s="2"/>
+      <c r="V43" s="1"/>
+    </row>
+    <row r="44" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="9"/>
+      <c r="B44" s="9"/>
+      <c r="C44" s="9"/>
+      <c r="D44" s="9"/>
+      <c r="F44" s="1"/>
+      <c r="G44" s="2"/>
+      <c r="H44" s="1"/>
+      <c r="I44" s="1"/>
+      <c r="K44" s="1"/>
+      <c r="L44" s="1"/>
+      <c r="M44" s="1"/>
+      <c r="N44" s="1"/>
+      <c r="P44" s="2"/>
+      <c r="Q44" s="2"/>
+      <c r="R44" s="2"/>
+      <c r="S44" s="1"/>
+      <c r="T44" s="8"/>
+      <c r="U44" s="2"/>
+      <c r="V44" s="1"/>
+    </row>
+    <row r="45" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="9"/>
+      <c r="B45" s="9"/>
+      <c r="C45" s="9"/>
+      <c r="D45" s="9"/>
+      <c r="F45" s="1"/>
+      <c r="G45" s="2"/>
+      <c r="H45" s="1"/>
+      <c r="I45" s="1"/>
+      <c r="K45" s="1"/>
+      <c r="L45" s="1"/>
+      <c r="M45" s="1"/>
+      <c r="N45" s="1"/>
+      <c r="P45" s="2"/>
+      <c r="Q45" s="2"/>
+      <c r="R45" s="2"/>
+      <c r="S45" s="1"/>
+      <c r="T45" s="8"/>
+      <c r="U45" s="2"/>
+      <c r="V45" s="1"/>
+    </row>
+    <row r="46" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="9"/>
+      <c r="B46" s="9"/>
+      <c r="C46" s="9"/>
+      <c r="D46" s="9"/>
+      <c r="F46" s="1"/>
+      <c r="G46" s="2"/>
+      <c r="H46" s="1"/>
+      <c r="I46" s="1"/>
+      <c r="K46" s="1"/>
+      <c r="L46" s="1"/>
+      <c r="M46" s="1"/>
+      <c r="N46" s="1"/>
+      <c r="P46" s="2"/>
+      <c r="Q46" s="2"/>
+      <c r="R46" s="2"/>
+      <c r="S46" s="1"/>
+      <c r="T46" s="8"/>
+      <c r="U46" s="2"/>
+      <c r="V46" s="1"/>
+    </row>
+    <row r="47" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="9"/>
+      <c r="B47" s="9"/>
+      <c r="C47" s="9"/>
+      <c r="D47" s="9"/>
+      <c r="F47" s="1"/>
+      <c r="G47" s="2"/>
+      <c r="H47" s="1"/>
+      <c r="I47" s="1"/>
+      <c r="K47" s="1"/>
+      <c r="L47" s="1"/>
+      <c r="M47" s="1"/>
+      <c r="N47" s="1"/>
+      <c r="P47" s="2"/>
+      <c r="Q47" s="2"/>
+      <c r="R47" s="2"/>
+      <c r="S47" s="1"/>
+      <c r="T47" s="8"/>
+      <c r="U47" s="2"/>
+      <c r="V47" s="1"/>
+    </row>
+    <row r="48" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="9"/>
+      <c r="B48" s="9"/>
+      <c r="C48" s="9"/>
+      <c r="D48" s="9"/>
+      <c r="F48" s="1"/>
+      <c r="G48" s="2"/>
+      <c r="H48" s="1"/>
+      <c r="I48" s="1"/>
+      <c r="K48" s="1"/>
+      <c r="L48" s="1"/>
+      <c r="M48" s="1"/>
+      <c r="N48" s="1"/>
+      <c r="P48" s="2"/>
+      <c r="Q48" s="2"/>
+      <c r="R48" s="2"/>
+      <c r="S48" s="1"/>
+      <c r="T48" s="8"/>
+      <c r="U48" s="2"/>
+      <c r="V48" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DB01197-FE1C-4ED1-B3B4-7B774B71A2A6}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -11767,7 +15166,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8347859-D7B0-40A5-9B17-0069AC1E92BB}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -12130,341 +15529,4 @@
   <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16AAE27B-B1A5-470A-8C56-1AC981AA4A71}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A2:V44"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="36" style="1" customWidth="1"/>
-    <col min="2" max="2" width="50.5546875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="71.21875" style="4" customWidth="1"/>
-    <col min="4" max="4" width="56.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="6.21875" style="7" customWidth="1"/>
-    <col min="6" max="6" width="43.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="55.109375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="67.88671875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="64.33203125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="7.77734375" style="7" customWidth="1"/>
-    <col min="11" max="11" width="39.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="48.88671875" style="1" customWidth="1"/>
-    <col min="13" max="13" width="72.6640625" style="1" customWidth="1"/>
-    <col min="14" max="14" width="43.88671875" style="1" customWidth="1"/>
-    <col min="15" max="15" width="7.77734375" style="7" customWidth="1"/>
-    <col min="16" max="16" width="56.77734375" style="2" customWidth="1"/>
-    <col min="17" max="17" width="46.77734375" style="2" customWidth="1"/>
-    <col min="18" max="18" width="62.88671875" style="2" customWidth="1"/>
-    <col min="19" max="19" width="49.21875" style="1" customWidth="1"/>
-    <col min="20" max="20" width="8.77734375" style="8"/>
-    <col min="21" max="21" width="67.77734375" style="2" customWidth="1"/>
-    <col min="22" max="22" width="68.33203125" style="1" customWidth="1"/>
-    <col min="23" max="24" width="59.33203125" style="1" customWidth="1"/>
-    <col min="25" max="25" width="59.6640625" style="1" customWidth="1"/>
-    <col min="26" max="26" width="99.44140625" style="1" customWidth="1"/>
-    <col min="27" max="27" width="41.21875" style="1" customWidth="1"/>
-    <col min="28" max="16384" width="8.77734375" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A2" s="3"/>
-      <c r="B2" s="5"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
-      <c r="N2" s="3"/>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="5"/>
-      <c r="R2" s="5"/>
-      <c r="S2" s="5"/>
-      <c r="U2" s="5"/>
-    </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="9"/>
-      <c r="P3" s="1"/>
-      <c r="U3" s="1"/>
-      <c r="V3" s="2"/>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A4" s="20" t="s">
-        <v>142</v>
-      </c>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A5" s="9"/>
-      <c r="B5" s="32" t="s">
-        <v>143</v>
-      </c>
-      <c r="C5" s="35" t="s">
-        <v>147</v>
-      </c>
-      <c r="D5" s="9"/>
-    </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A6" s="9"/>
-      <c r="B6" s="32" t="s">
-        <v>144</v>
-      </c>
-      <c r="C6" s="36" t="s">
-        <v>148</v>
-      </c>
-      <c r="D6" s="9"/>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A7" s="9"/>
-      <c r="B7" s="32" t="s">
-        <v>145</v>
-      </c>
-      <c r="C7" s="36" t="s">
-        <v>149</v>
-      </c>
-      <c r="D7" s="9"/>
-    </row>
-    <row r="8" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A8" s="9"/>
-      <c r="B8" s="32" t="s">
-        <v>146</v>
-      </c>
-      <c r="C8" s="36" t="s">
-        <v>150</v>
-      </c>
-      <c r="D8" s="9"/>
-    </row>
-    <row r="9" spans="1:22" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="9"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="19" t="s">
-        <v>90</v>
-      </c>
-      <c r="D9" s="9"/>
-    </row>
-    <row r="10" spans="1:22" ht="144" x14ac:dyDescent="0.3">
-      <c r="A10" s="9"/>
-      <c r="B10" s="22" t="s">
-        <v>89</v>
-      </c>
-      <c r="C10" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="D10" s="9"/>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A11" s="9"/>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A12" s="9"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A13" s="9"/>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A14" s="9"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A15" s="9"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A16" s="9"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="9"/>
-      <c r="B17" s="31"/>
-      <c r="C17" s="32"/>
-      <c r="D17" s="9"/>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="9"/>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="9"/>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
-      <c r="D20" s="9"/>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="9"/>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="9"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="9"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" s="9"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="9"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" s="9"/>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="9"/>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" s="9"/>
-      <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="9"/>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28" s="9"/>
-      <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
-      <c r="D28" s="9"/>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" s="9"/>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A30" s="9"/>
-      <c r="B30" s="9"/>
-      <c r="C30" s="9"/>
-      <c r="D30" s="9"/>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A31" s="9"/>
-      <c r="B31" s="9"/>
-      <c r="C31" s="9"/>
-      <c r="D31" s="9"/>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A32" s="9"/>
-      <c r="B32" s="9"/>
-      <c r="C32" s="9"/>
-      <c r="D32" s="9"/>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33" s="9"/>
-      <c r="B33" s="9"/>
-      <c r="C33" s="9"/>
-      <c r="D33" s="9"/>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A34" s="9"/>
-      <c r="B34" s="9"/>
-      <c r="C34" s="9"/>
-      <c r="D34" s="9"/>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A35" s="9"/>
-      <c r="B35" s="9"/>
-      <c r="C35" s="9"/>
-      <c r="D35" s="9"/>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A36" s="9"/>
-      <c r="B36" s="9"/>
-      <c r="C36" s="9"/>
-      <c r="D36" s="9"/>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A37" s="9"/>
-      <c r="B37" s="9"/>
-      <c r="C37" s="9"/>
-      <c r="D37" s="9"/>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A38" s="9"/>
-      <c r="B38" s="9"/>
-      <c r="C38" s="9"/>
-      <c r="D38" s="9"/>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A39" s="9"/>
-      <c r="B39" s="9"/>
-      <c r="C39" s="9"/>
-      <c r="D39" s="9"/>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A40" s="9"/>
-      <c r="B40" s="9"/>
-      <c r="C40" s="9"/>
-      <c r="D40" s="9"/>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A41" s="9"/>
-      <c r="B41" s="9"/>
-      <c r="C41" s="9"/>
-      <c r="D41" s="9"/>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A42" s="9"/>
-      <c r="B42" s="9"/>
-      <c r="C42" s="9"/>
-      <c r="D42" s="9"/>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A43" s="9"/>
-      <c r="B43" s="9"/>
-      <c r="C43" s="9"/>
-      <c r="D43" s="9"/>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A44" s="9"/>
-      <c r="B44" s="9"/>
-      <c r="C44" s="9"/>
-      <c r="D44" s="9"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
-</worksheet>
 </file>
--- a/4 четверть_MSSQL.xlsx
+++ b/4 четверть_MSSQL.xlsx
@@ -8,23 +8,24 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlexServHW\Desktop\GB_Developer_Workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7571CD00-1A0F-4A75-BC93-5EE2E6C2C7B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD93E8F1-59D3-462E-856B-62EC12DDECB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-5190" yWindow="-19365" windowWidth="29085" windowHeight="15270" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-13140" yWindow="-21600" windowWidth="23250" windowHeight="12450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Изучить" sheetId="21" r:id="rId1"/>
     <sheet name="Установка" sheetId="13" r:id="rId2"/>
     <sheet name="DATABASE" sheetId="12" r:id="rId3"/>
-    <sheet name="TABLE" sheetId="20" r:id="rId4"/>
-    <sheet name="SELECT" sheetId="15" r:id="rId5"/>
-    <sheet name="WHERE" sheetId="19" r:id="rId6"/>
-    <sheet name="IF" sheetId="23" r:id="rId7"/>
-    <sheet name="template" sheetId="14" r:id="rId8"/>
-    <sheet name="Каскадное удаление" sheetId="16" r:id="rId9"/>
-    <sheet name="Транзакции" sheetId="17" r:id="rId10"/>
-    <sheet name="bc Массивы" sheetId="18" r:id="rId11"/>
-    <sheet name="bc JSON" sheetId="22" r:id="rId12"/>
+    <sheet name="Типы данных" sheetId="24" r:id="rId4"/>
+    <sheet name="TABLE" sheetId="20" r:id="rId5"/>
+    <sheet name="SELECT" sheetId="15" r:id="rId6"/>
+    <sheet name="WHERE" sheetId="19" r:id="rId7"/>
+    <sheet name="IF" sheetId="23" r:id="rId8"/>
+    <sheet name="template" sheetId="14" r:id="rId9"/>
+    <sheet name="Каскадное удаление" sheetId="16" r:id="rId10"/>
+    <sheet name="Транзакции" sheetId="17" r:id="rId11"/>
+    <sheet name="bc Массивы" sheetId="18" r:id="rId12"/>
+    <sheet name="bc JSON" sheetId="22" r:id="rId13"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="351">
   <si>
     <t>Урок 1 часть 1</t>
   </si>
@@ -3748,97 +3749,7 @@
     <t>Примеры корректных идентификаторов</t>
   </si>
   <si>
-    <t>Настройки столбцов и таблицы</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Атрибуты столбцов и атрибуты таблицы являются </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>необязательными</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>компонентами</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>, и их можно не указывать.</t>
-    </r>
-  </si>
-  <si>
     <t>В самом просто виде команда CREATE TABLE должна содержать как минимум имя таблицы, имена и типы столбцов.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Самый минимальный CREATE TABLE </t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>CREATE TABLE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Customers
-(
-    Id INT,
-    Age INT,
-    FirstName NVARCHAR(20),
-    LastName NVARCHAR(20),
-    Email VARCHAR(30),
-    Phone VARCHAR(20)
-)</t>
-    </r>
   </si>
   <si>
     <r>
@@ -5734,42 +5645,6 @@
   <si>
     <t>Идентификаторы и имена. Осмысленные и в едином стиле.
 2 четверть_6_Тестировщик_SQLxls</t>
-  </si>
-  <si>
-    <t>`https://metanit.com/sql/sqlserver/3.2.php#:~:text=%D0%A1%D0%BE%D0%B7%D0%B4%D0%B0%D0%BD%D0%B8%D0%B5%20%D1%82%D0%B0%D0%B1%D0%BB%D0%B8%D1%86%D1%8B%20%D0%B2%20SQL%20Management%20Studio</t>
-  </si>
-  <si>
-    <t>`-- Парсим JSON в табличное представление
-DECLARE @ParsedReceivers TABLE (
-    UserMail NVARCHAR(255),
-    CompanyName NVARCHAR(255)
-);
-INSERT INTO @ParsedReceivers (UserMail, CompanyName)
-SELECT UserMail, CompanyName
-FROM OPENJSON(@mailReceiversJson)
-WITH (
-    UserMail NVARCHAR(255) '$.UserMail',
-    CompanyName NVARCHAR(255) '$.CompanyName'
-);
--- 1. Добавляем новых пользователей, которых ещё нет в таблице пользователей
-INSERT INTO LK_DATA.dbo.site_UserMails (UserMail, CompanyName, StatusOrigin)
-SELECT pr.UserMail, pr.CompanyName, 'CompanyContacts'
-FROM @ParsedReceivers pr
-WHERE NOT EXISTS (
-    SELECT 1 
-    FROM LK_DATA.dbo.site_UserMails existing
-    WHERE existing.UserMail = pr.UserMail
-);
--- 2. Добавляем связи пользователей с группой рассылки (если ещё нет)
-INSERT INTO LK_DATA.dbo.site_MailGroupsCrossUserMail (idMailGroup, UserMail)
-SELECT @idMailGroup, pr.UserMail
-FROM @ParsedReceivers pr
-WHERE NOT EXISTS (
-    SELECT 1 
-    FROM LK_DATA.dbo.site_MailGroupsCrossUserMail existing
-    WHERE existing.idMailGroup = @idMailGroup
-      AND existing.UserMail = pr.UserMail
-);</t>
   </si>
   <si>
     <t>Для чего?</t>
@@ -7432,17 +7307,1417 @@
       <t>END</t>
     </r>
   </si>
+  <si>
+    <t>COUNT</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">SELECT 
+ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[IdCompany]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, 
+ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>COUNT(*)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> AS [UserCount]
+FROM 
+ [LK_DATA].[dbo].[usr_Users]
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>GROUP BY 
+ [IdCompany]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Основной случай 
+Пояснение!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Любые сосендие колоник должны быть сгруппированы по количеству, посчитанному в COUNT</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">SELECT  
+    </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>uc.[CompanyName],</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+   </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ISNULL(u_stats.[UserCount], 0) AS [CompanyHeadcount],</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+FROM 
+ [LK_DATA].[dbo].[usr_Companys] uc
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">LEFT JOIN </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(
+ SELECT 
+   [IdCompany], 
+   COUNT(*) AS [UserCount]
+ FROM 
+   [LK_DATA].[dbo].[usr_Users]
+ GROUP BY 
+  [IdCompany]
+) AS u_stats ON u_stats.[IdCompany] = uc.[IdCompany]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Когда нужно добавить в другую таблицу значения из COUNT другой таблицы 
+Пояснение!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Важно, чтобы принцип группировки таблицы, где был использован COUNT, был соответствующе выдержан в таблице, в которой эти данные надобились. В данном примере </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>uc.[CompanyName]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> подходит, так как соответствует принципу группировки по</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> [IdCompany]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">USE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>usersdb;</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+CREATE TABLE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Customers
+(
+    Id INT,
+    Age INT,
+    FirstName NVARCHAR(20),
+    LastName NVARCHAR(20),
+    Email VARCHAR(30),
+    Phone VARCHAR(20)
+)</t>
+    </r>
+  </si>
+  <si>
+    <t>Синтаксис названий таблиц</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Минимальный</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> набор параметров для создания! </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">В самом просто виде команда CREATE TABLE должна содержать как минимум 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">(1) имя таблицы, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">(2) имена и типы столбцов.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Атрибуты столбцов и атрибуты таблицы являются </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>необязательными компонентами</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, и их можно не указывать.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">CREATE TABLE </t>
+  </si>
+  <si>
+    <t>DROP TABLE</t>
+  </si>
+  <si>
+    <t>DROP TABLE table1 [, table2, ...]</t>
+  </si>
+  <si>
+    <t>Rename Table</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>USE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> usersdb;
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>EXEC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>sp_rename</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 'Users', 'UserAccounts';</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>DROP TABLE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Customers</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Пояснение!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Для переименования таблиц применяется </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>системная хранимая процедура "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>sp_rename</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>".</t>
+    </r>
+  </si>
+  <si>
+    <t>Числовые типы</t>
+  </si>
+  <si>
+    <t>BIT</t>
+  </si>
+  <si>
+    <t>TINYINT</t>
+  </si>
+  <si>
+    <t>SMALLINT</t>
+  </si>
+  <si>
+    <t>INT</t>
+  </si>
+  <si>
+    <t>BIGINT</t>
+  </si>
+  <si>
+    <t>DECIMAL(p,s)</t>
+  </si>
+  <si>
+    <t>NUMERIC</t>
+  </si>
+  <si>
+    <t>SMALLMONEY</t>
+  </si>
+  <si>
+    <t>MONEY</t>
+  </si>
+  <si>
+    <t>FLOAT(n)</t>
+  </si>
+  <si>
+    <t>REAL</t>
+  </si>
+  <si>
+    <t>До 8 знач. — 1 байт, 9-16 — 2 байта.</t>
+  </si>
+  <si>
+    <t>32 768 до 32 767</t>
+  </si>
+  <si>
+    <t>–2 147 483 648 до 2 147 483 647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 до 255. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 до 16 (аналог boolean: 1 = true, 0 = false). </t>
+  </si>
+  <si>
+    <t>-9 223 372 036 854 775 808 до 9 223 372 036 854 775 807</t>
+  </si>
+  <si>
+    <t>аналог DECIMAL</t>
+  </si>
+  <si>
+    <t>денежные величины от -214 748.3648 до 214 748.3647</t>
+  </si>
+  <si>
+    <t>денежные величины от -922 337 203 685 477.5808 до 922 337 203 685 477.5807</t>
+  </si>
+  <si>
+    <t>8 байт (DECIMAL(19,4))</t>
+  </si>
+  <si>
+    <t>1 байт</t>
+  </si>
+  <si>
+    <t>2 байта</t>
+  </si>
+  <si>
+    <t>4 байта</t>
+  </si>
+  <si>
+    <t>8 байт</t>
+  </si>
+  <si>
+    <t>5-17 байт</t>
+  </si>
+  <si>
+    <t>4 байта (DECIMAL(10,4))</t>
+  </si>
+  <si>
+    <t>числа от –1.79E+308 до 1.79E+308. n — бит для мантиссы (по умолч. 53)</t>
+  </si>
+  <si>
+    <t>4-8 байт</t>
+  </si>
+  <si>
+    <t>числа от –340E+38 до 3.40E+38</t>
+  </si>
+  <si>
+    <t>4 байта (FLOAT(24))</t>
+  </si>
+  <si>
+    <t>Дата и время</t>
+  </si>
+  <si>
+    <t>DATE</t>
+  </si>
+  <si>
+    <t>TIME(n)</t>
+  </si>
+  <si>
+    <t>DATETIME</t>
+  </si>
+  <si>
+    <t>DATETIME2(n)</t>
+  </si>
+  <si>
+    <t>SMALLDATETIME</t>
+  </si>
+  <si>
+    <t>DATETIMEOFFSET</t>
+  </si>
+  <si>
+    <t>Строковые типы</t>
+  </si>
+  <si>
+    <t>CHAR(n)</t>
+  </si>
+  <si>
+    <t>VARCHAR(n | MAX)</t>
+  </si>
+  <si>
+    <t>NCHAR(n)</t>
+  </si>
+  <si>
+    <t>NVARCHAR(n | MAX)</t>
+  </si>
+  <si>
+    <t>BINARY(n)</t>
+  </si>
+  <si>
+    <t>VARBINARY(n | MAX)</t>
+  </si>
+  <si>
+    <t>UNIQUEIDENTIFIER</t>
+  </si>
+  <si>
+    <t>TIMESTAMP</t>
+  </si>
+  <si>
+    <t>CURSOR</t>
+  </si>
+  <si>
+    <t>HIERARCHYID</t>
+  </si>
+  <si>
+    <t>SQL_VARIANT</t>
+  </si>
+  <si>
+    <t>XML</t>
+  </si>
+  <si>
+    <t>TABLE</t>
+  </si>
+  <si>
+    <t>GEOGRAPHY</t>
+  </si>
+  <si>
+    <t>GEOMETRY</t>
+  </si>
+  <si>
+    <t>даты от 0001-01-01 до 9999-12-31</t>
+  </si>
+  <si>
+    <t>3 байта</t>
+  </si>
+  <si>
+    <t>время 00:00:00.0000000 до 23:59:59.9999999. n — цифр в секундах (0-7)</t>
+  </si>
+  <si>
+    <t>3-5 байт</t>
+  </si>
+  <si>
+    <t>дата и время от 01/01/1753 до 31/12/9999</t>
+  </si>
+  <si>
+    <t>дата и время от 0001-01-01 до 9999-12-31 с точностью до 100 нс. n (0-7)</t>
+  </si>
+  <si>
+    <t>6-8 байт</t>
+  </si>
+  <si>
+    <t>дата и время от 01/01/1900 до 06/06/2079</t>
+  </si>
+  <si>
+    <t>дата и время с точностью до 100 нс + смещение</t>
+  </si>
+  <si>
+    <t>10 байт</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>не Unicode</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. 1 байт/символ. Дополняется пробелами.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>не Unicode</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. 1 байт/символ. Без дополнения пробелами.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Unicode</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, 2 байта/символ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. Дополняется пробелами.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">1 073 741 824 символов — до 2 ГБ. </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Unicode</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, 2 байта/символ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. Без дополнения пробелами.</t>
+    </r>
+  </si>
+  <si>
+    <t>2 147 483 648 символов — до 2 ГБ</t>
+  </si>
+  <si>
+    <t>8 000 символов — до 0,00000745 ГБ</t>
+  </si>
+  <si>
+    <t>16 байт</t>
+  </si>
+  <si>
+    <t>GUID (глобальный уникальный идентификатор) 
+Часто используется для создания уникальных первичных ключей, особенно в распределённых системах</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Уникальное двоичное число, автоматически генерируемое SQL Server. Это </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>НЕ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> тип для хранения </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>даты/времени</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, а </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>механизм отслеживания изменений строк</t>
+    </r>
+  </si>
+  <si>
+    <t>тип данных для хранения ссылки на курсор (используется для построчной обработки результатов запроса)</t>
+  </si>
+  <si>
+    <t>переменный тип данных для представления позиции в иерархической структуре. Позволяет эффективно работать с древовидными данными и отслеживать положение записей в иерархии</t>
+  </si>
+  <si>
+    <t>данные любого другого типа T-SQL. универсальный тип, который может хранить значения различных типов данных SQL Server (кроме некоторых ограничений). Используется внутренне системой и не является частью SQL стандарт</t>
+  </si>
+  <si>
+    <t>XML-документы или фрагменты до 2 ГБ. редназначен для хранения и обработки XML-документов. Поддерживает методы XPath и XQuery для работы с XML-данными</t>
+  </si>
+  <si>
+    <t>до 2 ГБ</t>
+  </si>
+  <si>
+    <t>тип данных для хранения результирующего набора строк. Часто используется в табличных переменных и возвращаемых табличных значениях функций</t>
+  </si>
+  <si>
+    <t>географические данные (широта, долгота). ространственный тип данных для хранения географических координат на поверхности Земли (сферическая система координат). Поддерживает точки, линии, многоугольники и другие геометрические фигуры</t>
+  </si>
+  <si>
+    <t>координаты на плоскости. пространственный тип данных для хранения геометрических фигур в плоской (евклидовой) системе координат. Также поддерживает точки, линии, полигоны и т.д.</t>
+  </si>
+  <si>
+    <t>1 до 8000 байт или до 2 ГБ (MAX)</t>
+  </si>
+  <si>
+    <t>бинарные данные</t>
+  </si>
+  <si>
+    <t>Изображения (JPEG, PNG, GIF)
+PDF документы
+Word/Excel файлы
+ZIP архивы</t>
+  </si>
+  <si>
+    <t>Хранение файлов и документов</t>
+  </si>
+  <si>
+    <t>Хранение зашифрованных данных</t>
+  </si>
+  <si>
+    <t>Хэши паролей
+Зашифрованная информация
+Криптографические ключи</t>
+  </si>
+  <si>
+    <t>Сериализованные объекты</t>
+  </si>
+  <si>
+    <t>Объекты приложений
+Состояния программ</t>
+  </si>
+  <si>
+    <t>Иконки, логотипы
+Аудио/видео файлы (небольшие)
+Резервные копии данных</t>
+  </si>
+  <si>
+    <t>Двоичные данные приложений</t>
+  </si>
+  <si>
+    <t>1 до 8000 байт</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Важно!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Современная практика рекомендует хранить большие файлы вне базы данных (в файловой системе или облачном хранилище), а в БД сохранять только ссылки на них, так как это:
+Уменьшает размер БД
+Улучшает производительность
+Упрощает резервное копирование</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Бинарные типы (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>хранения хэшей и сериализованных данных</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Прочие типы (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>больше системные</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>4 000 символов — до 0,00000745 ГБ</t>
+  </si>
+  <si>
+    <t>ANSI (однобайтовая, например, CP1251 для кириллицы)</t>
+  </si>
+  <si>
+    <t>UTF-16 (в SQL Server)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Используется для хранения текста на </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>латинице</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Используется для хранения текста на </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>русском</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">числа с фиксированной точностью. 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>p precision</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (1-38) — всего цифр, s (0-</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>p</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>) — после запятой</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Важно! </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Параметр </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>precision</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> представляет максимальное количество цифр, которые может хранить число. Это значение должно находиться в диапазоне </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>от 1 до 38</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>По умолчанию оно равно 18</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Параметр </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>scale</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> представляет максимальное количество цифр, которые может содержать число после запятой. Это значение должно находиться в диапазоне от</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 0 до значения параметра precision</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>По умолчанию оно равно 0.</t>
+    </r>
+  </si>
+  <si>
+    <t>`https://metanit.com/sql/sqlserver/3.4.php</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="31" x14ac:knownFonts="1">
+  <fonts count="32" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -7695,7 +8970,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -7762,6 +9037,24 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF002060"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -7774,9 +9067,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -7787,42 +9080,48 @@
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -7830,87 +9129,111 @@
     <xf numFmtId="49" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="16" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="15" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="14" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="24" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="25" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="16" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="27" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="28" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="16" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="16" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="28" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="49" fontId="16" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -8549,7 +9872,7 @@
       <c r="B4" s="9"/>
       <c r="C4" s="40"/>
       <c r="D4" s="22" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
     </row>
     <row r="5" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
@@ -8557,7 +9880,7 @@
       <c r="B5" s="9"/>
       <c r="C5" s="40"/>
       <c r="D5" s="22" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
     </row>
     <row r="6" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
@@ -8565,17 +9888,17 @@
       <c r="B6" s="9"/>
       <c r="C6" s="40"/>
       <c r="D6" s="22" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A7" s="9"/>
       <c r="B7" s="9"/>
       <c r="C7" s="22" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="D7" s="40" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.3">
@@ -8583,7 +9906,7 @@
       <c r="B8" s="9"/>
       <c r="C8" s="40"/>
       <c r="D8" s="40" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.3">
@@ -8591,26 +9914,23 @@
       <c r="B9" s="9"/>
       <c r="C9" s="40"/>
       <c r="D9" s="40" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
     </row>
     <row r="10" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="9"/>
       <c r="B10" s="9"/>
       <c r="C10" s="22" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="D10" s="22" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="11" spans="1:22" ht="57.6" x14ac:dyDescent="0.3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A11" s="9"/>
       <c r="B11" s="9"/>
       <c r="C11" s="40"/>
-      <c r="D11" s="22" t="s">
-        <v>205</v>
-      </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A12" s="9"/>
@@ -8630,13 +9950,13 @@
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
     </row>
-    <row r="15" spans="1:22" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A15" s="9"/>
-      <c r="B15" s="41" t="s">
-        <v>206</v>
-      </c>
+      <c r="B15" s="48"/>
       <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
+      <c r="D15" s="49" t="s">
+        <v>350</v>
+      </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A16" s="9"/>
@@ -8843,6 +10163,371 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8347859-D7B0-40A5-9B17-0069AC1E92BB}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A2:V49"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="36" style="1" customWidth="1"/>
+    <col min="2" max="2" width="36.21875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="71.21875" style="4" customWidth="1"/>
+    <col min="4" max="4" width="56.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="6.21875" style="7" customWidth="1"/>
+    <col min="6" max="6" width="43.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="55.109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="67.88671875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="64.33203125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="7.77734375" style="7" customWidth="1"/>
+    <col min="11" max="11" width="39.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="48.88671875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="72.6640625" style="1" customWidth="1"/>
+    <col min="14" max="14" width="43.88671875" style="1" customWidth="1"/>
+    <col min="15" max="15" width="7.77734375" style="7" customWidth="1"/>
+    <col min="16" max="16" width="56.77734375" style="2" customWidth="1"/>
+    <col min="17" max="17" width="46.77734375" style="2" customWidth="1"/>
+    <col min="18" max="18" width="62.88671875" style="2" customWidth="1"/>
+    <col min="19" max="19" width="49.21875" style="1" customWidth="1"/>
+    <col min="20" max="20" width="8.77734375" style="8"/>
+    <col min="21" max="21" width="67.77734375" style="2" customWidth="1"/>
+    <col min="22" max="22" width="68.33203125" style="1" customWidth="1"/>
+    <col min="23" max="24" width="59.33203125" style="1" customWidth="1"/>
+    <col min="25" max="25" width="59.6640625" style="1" customWidth="1"/>
+    <col min="26" max="26" width="99.44140625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="41.21875" style="1" customWidth="1"/>
+    <col min="28" max="16384" width="8.77734375" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A2" s="3"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="P2" s="5"/>
+      <c r="Q2" s="5"/>
+      <c r="R2" s="5"/>
+      <c r="S2" s="5"/>
+      <c r="U2" s="5"/>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="9"/>
+      <c r="P3" s="1"/>
+      <c r="U3" s="1"/>
+      <c r="V3" s="2"/>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A4" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="B4" s="9"/>
+      <c r="D4" s="9"/>
+    </row>
+    <row r="5" spans="1:22" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A5" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="C5" s="9"/>
+      <c r="D5" s="19" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A6" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="B6" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+    </row>
+    <row r="7" spans="1:22" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="B7" s="9"/>
+      <c r="C7" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="D7" s="9"/>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A8" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+    </row>
+    <row r="9" spans="1:22" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="B9" s="9"/>
+      <c r="C9" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="D9" s="9"/>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A10" s="9"/>
+      <c r="B10" s="9"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A11" s="9"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="9"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A12" s="9"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A13" s="9"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A14" s="9"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A15" s="9"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A16" s="9"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="9"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" s="9"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" s="9"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" s="9"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" s="9"/>
+      <c r="B21" s="9"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="9"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" s="9"/>
+      <c r="B22" s="9"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" s="9"/>
+      <c r="B23" s="9"/>
+      <c r="C23" s="9"/>
+      <c r="D23" s="9"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" s="9"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="9"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" s="9"/>
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" s="9"/>
+      <c r="B26" s="9"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" s="9"/>
+      <c r="B27" s="9"/>
+      <c r="C27" s="9"/>
+      <c r="D27" s="9"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" s="9"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="9"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" s="9"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="9"/>
+      <c r="D29" s="9"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30" s="9"/>
+      <c r="B30" s="9"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="9"/>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31" s="9"/>
+      <c r="B31" s="9"/>
+      <c r="C31" s="9"/>
+      <c r="D31" s="9"/>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A32" s="9"/>
+      <c r="B32" s="9"/>
+      <c r="C32" s="9"/>
+      <c r="D32" s="9"/>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33" s="9"/>
+      <c r="B33" s="9"/>
+      <c r="C33" s="9"/>
+      <c r="D33" s="9"/>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A34" s="9"/>
+      <c r="B34" s="9"/>
+      <c r="C34" s="9"/>
+      <c r="D34" s="9"/>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A35" s="9"/>
+      <c r="B35" s="9"/>
+      <c r="C35" s="9"/>
+      <c r="D35" s="9"/>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A36" s="9"/>
+      <c r="B36" s="9"/>
+      <c r="C36" s="9"/>
+      <c r="D36" s="9"/>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A37" s="9"/>
+      <c r="B37" s="9"/>
+      <c r="C37" s="9"/>
+      <c r="D37" s="9"/>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A38" s="9"/>
+      <c r="B38" s="9"/>
+      <c r="C38" s="9"/>
+      <c r="D38" s="9"/>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A39" s="9"/>
+      <c r="B39" s="9"/>
+      <c r="C39" s="9"/>
+      <c r="D39" s="9"/>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A40" s="9"/>
+      <c r="B40" s="9"/>
+      <c r="C40" s="9"/>
+      <c r="D40" s="9"/>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A41" s="9"/>
+      <c r="B41" s="9"/>
+      <c r="C41" s="9"/>
+      <c r="D41" s="9"/>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A42" s="9"/>
+      <c r="B42" s="9"/>
+      <c r="C42" s="9"/>
+      <c r="D42" s="9"/>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A43" s="9"/>
+      <c r="B43" s="9"/>
+      <c r="C43" s="9"/>
+      <c r="D43" s="9"/>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A44" s="9"/>
+      <c r="B44" s="9"/>
+      <c r="C44" s="9"/>
+      <c r="D44" s="9"/>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A45" s="9"/>
+      <c r="B45" s="9"/>
+      <c r="C45" s="9"/>
+      <c r="D45" s="9"/>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A46" s="9"/>
+      <c r="B46" s="9"/>
+      <c r="C46" s="9"/>
+      <c r="D46" s="9"/>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A47" s="9"/>
+      <c r="B47" s="9"/>
+      <c r="C47" s="9"/>
+      <c r="D47" s="9"/>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A48" s="9"/>
+      <c r="B48" s="9"/>
+      <c r="C48" s="9"/>
+      <c r="D48" s="9"/>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A49" s="9"/>
+      <c r="B49" s="9"/>
+      <c r="C49" s="9"/>
+      <c r="D49" s="9"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16AAE27B-B1A5-470A-8C56-1AC981AA4A71}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -8909,7 +10594,7 @@
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A4" s="20" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B4" s="9"/>
       <c r="C4" s="9"/>
@@ -8918,40 +10603,40 @@
     <row r="5" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A5" s="9"/>
       <c r="B5" s="32" t="s">
+        <v>132</v>
+      </c>
+      <c r="C5" s="35" t="s">
         <v>136</v>
-      </c>
-      <c r="C5" s="35" t="s">
-        <v>140</v>
       </c>
       <c r="D5" s="9"/>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A6" s="9"/>
       <c r="B6" s="32" t="s">
+        <v>133</v>
+      </c>
+      <c r="C6" s="36" t="s">
         <v>137</v>
-      </c>
-      <c r="C6" s="36" t="s">
-        <v>141</v>
       </c>
       <c r="D6" s="9"/>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A7" s="9"/>
       <c r="B7" s="32" t="s">
+        <v>134</v>
+      </c>
+      <c r="C7" s="36" t="s">
         <v>138</v>
-      </c>
-      <c r="C7" s="36" t="s">
-        <v>142</v>
       </c>
       <c r="D7" s="9"/>
     </row>
     <row r="8" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="9"/>
       <c r="B8" s="32" t="s">
+        <v>135</v>
+      </c>
+      <c r="C8" s="36" t="s">
         <v>139</v>
-      </c>
-      <c r="C8" s="36" t="s">
-        <v>143</v>
       </c>
       <c r="D8" s="9"/>
     </row>
@@ -9179,7 +10864,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B13A24C-6305-48F4-A1E6-55B31CAA1F4A}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -9275,24 +10960,24 @@
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A8" s="9"/>
-      <c r="B8" s="44" t="s">
+      <c r="B8" s="43" t="s">
+        <v>206</v>
+      </c>
+      <c r="C8" s="42" t="s">
         <v>212</v>
       </c>
-      <c r="C8" s="43" t="s">
-        <v>218</v>
-      </c>
-      <c r="D8" s="43" t="s">
-        <v>215</v>
+      <c r="D8" s="42" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="9" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="9"/>
       <c r="B9" s="9"/>
-      <c r="C9" s="43" t="s">
-        <v>234</v>
-      </c>
-      <c r="D9" s="43" t="s">
-        <v>216</v>
+      <c r="C9" s="42" t="s">
+        <v>228</v>
+      </c>
+      <c r="D9" s="42" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.3">
@@ -9304,19 +10989,19 @@
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A11" s="9"/>
-      <c r="B11" s="44" t="s">
-        <v>212</v>
-      </c>
-      <c r="C11" s="43" t="s">
-        <v>217</v>
+      <c r="B11" s="43" t="s">
+        <v>206</v>
+      </c>
+      <c r="C11" s="42" t="s">
+        <v>211</v>
       </c>
       <c r="D11" s="19"/>
     </row>
     <row r="12" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="9"/>
       <c r="B12" s="9"/>
-      <c r="C12" s="43" t="s">
-        <v>233</v>
+      <c r="C12" s="42" t="s">
+        <v>227</v>
       </c>
       <c r="D12" s="19"/>
     </row>
@@ -10052,7 +11737,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA83B601-5B0E-4344-A36B-7DD0432A3007}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -10135,31 +11820,31 @@
     </row>
     <row r="6" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="9"/>
-      <c r="C6" s="43" t="s">
-        <v>209</v>
+      <c r="C6" s="42" t="s">
+        <v>203</v>
       </c>
       <c r="D6" s="9"/>
     </row>
     <row r="7" spans="1:22" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A7" s="9"/>
-      <c r="B7" s="44" t="s">
-        <v>211</v>
-      </c>
-      <c r="C7" s="43" t="s">
-        <v>210</v>
-      </c>
-      <c r="D7" s="43" t="s">
-        <v>214</v>
+      <c r="B7" s="43" t="s">
+        <v>205</v>
+      </c>
+      <c r="C7" s="42" t="s">
+        <v>204</v>
+      </c>
+      <c r="D7" s="42" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="8" spans="1:22" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A8" s="9"/>
       <c r="B8" s="9"/>
-      <c r="C8" s="43" t="s">
-        <v>232</v>
-      </c>
-      <c r="D8" s="43" t="s">
-        <v>213</v>
+      <c r="C8" s="42" t="s">
+        <v>226</v>
+      </c>
+      <c r="D8" s="42" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.3">
@@ -10175,21 +11860,21 @@
       <c r="B10" s="19" t="s">
         <v>97</v>
       </c>
-      <c r="C10" s="43" t="s">
-        <v>221</v>
-      </c>
-      <c r="D10" s="43" t="s">
-        <v>219</v>
+      <c r="C10" s="42" t="s">
+        <v>215</v>
+      </c>
+      <c r="D10" s="42" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="11" spans="1:22" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A11" s="9"/>
       <c r="B11" s="9"/>
-      <c r="C11" s="43" t="s">
-        <v>222</v>
-      </c>
-      <c r="D11" s="43" t="s">
-        <v>220</v>
+      <c r="C11" s="42" t="s">
+        <v>216</v>
+      </c>
+      <c r="D11" s="42" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.3">
@@ -11371,7 +13056,7 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="34" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B28" s="31"/>
       <c r="C28" s="32"/>
@@ -11379,43 +13064,43 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B29" s="32" t="s">
+        <v>132</v>
+      </c>
+      <c r="C29" s="35" t="s">
         <v>136</v>
-      </c>
-      <c r="C29" s="35" t="s">
-        <v>140</v>
       </c>
       <c r="D29" s="9"/>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B30" s="32" t="s">
+        <v>133</v>
+      </c>
+      <c r="C30" s="36" t="s">
         <v>137</v>
-      </c>
-      <c r="C30" s="36" t="s">
-        <v>141</v>
       </c>
       <c r="D30" s="9"/>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B31" s="32" t="s">
+        <v>134</v>
+      </c>
+      <c r="C31" s="36" t="s">
         <v>138</v>
-      </c>
-      <c r="C31" s="36" t="s">
-        <v>142</v>
       </c>
       <c r="D31" s="9"/>
     </row>
     <row r="32" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B32" s="32" t="s">
+        <v>135</v>
+      </c>
+      <c r="C32" s="36" t="s">
         <v>139</v>
-      </c>
-      <c r="C32" s="36" t="s">
-        <v>143</v>
       </c>
       <c r="D32" s="9"/>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="20" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C33" s="9" t="s">
         <v>45</v>
@@ -11566,7 +13251,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
+  <phoneticPr fontId="9" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="D46" r:id="rId1" location=":~:text=%D0%A1%D0%BE%D0%B7%D0%B4%D0%B0%D0%BD%D0%B8%D0%B5%20%D0%B1%D0%B0%D0%B7%D1%8B%20%D0%B4%D0%B0%D0%BD%D0%BD%D1%8B%D1%85" xr:uid="{FDFE2116-2B22-4A87-B37D-3DFA9E8F9FE0}"/>
     <hyperlink ref="D44" r:id="rId2" location=":~:text=%D0%A1%D0%BE%D0%B7%D0%B4%D0%B0%D0%BD%D0%B8%D0%B5%20%D0%B1%D0%B0%D0%B7%D1%8B%20%D0%B4%D0%B0%D0%BD%D0%BD%D1%8B%D1%85%20%D0%B2%20SQL%20Management%20Studio" xr:uid="{5B701F02-CEF7-44EA-83C6-0E21D7145608}"/>
@@ -11580,12 +13265,478 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EE7095F-8B4B-470C-B9E5-197B8CFF3B58}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A2:E48"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="36" style="2" customWidth="1"/>
+    <col min="2" max="2" width="50.5546875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="71.21875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="56.44140625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="6.21875" style="53" customWidth="1"/>
+    <col min="6" max="6" width="43.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="55.109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="67.88671875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="64.33203125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="7.77734375" style="2" customWidth="1"/>
+    <col min="11" max="11" width="39.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="48.88671875" style="2" customWidth="1"/>
+    <col min="13" max="13" width="72.6640625" style="2" customWidth="1"/>
+    <col min="14" max="14" width="43.88671875" style="2" customWidth="1"/>
+    <col min="15" max="15" width="7.77734375" style="2" customWidth="1"/>
+    <col min="16" max="16" width="56.77734375" style="2" customWidth="1"/>
+    <col min="17" max="17" width="46.77734375" style="2" customWidth="1"/>
+    <col min="18" max="18" width="62.88671875" style="2" customWidth="1"/>
+    <col min="19" max="19" width="49.21875" style="2" customWidth="1"/>
+    <col min="20" max="20" width="8.77734375" style="2"/>
+    <col min="21" max="21" width="67.77734375" style="2" customWidth="1"/>
+    <col min="22" max="22" width="68.33203125" style="2" customWidth="1"/>
+    <col min="23" max="24" width="59.33203125" style="2" customWidth="1"/>
+    <col min="25" max="25" width="59.6640625" style="2" customWidth="1"/>
+    <col min="26" max="26" width="99.44140625" style="2" customWidth="1"/>
+    <col min="27" max="27" width="41.21875" style="2" customWidth="1"/>
+    <col min="28" max="16384" width="8.77734375" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:5" s="52" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="E2" s="53"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="54" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="D10" s="48" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="54" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" s="54" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A28" s="54" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31" s="55" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="B32" s="48" t="s">
+        <v>340</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" s="56" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="C34" s="2" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" s="56" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="C36" s="2" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" s="56" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="C38" s="2" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" s="54" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A40" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A41" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A42" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A43" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A44" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A45" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A46" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A47" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A48" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>328</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="9" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1138C089-CDC1-4142-9299-EE469CB775F6}">
   <sheetPr>
     <tabColor theme="4" tint="0.79998168889431442"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:V51"/>
+  <dimension ref="A2:V48"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="36" style="1" customWidth="1"/>
@@ -11659,16 +13810,19 @@
     <row r="5" spans="1:22" ht="72" x14ac:dyDescent="0.3">
       <c r="A5" s="9"/>
       <c r="B5" s="19" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="D5" s="9"/>
     </row>
     <row r="6" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="21" t="s">
-        <v>134</v>
+        <v>130</v>
+      </c>
+      <c r="B6" s="50" t="s">
+        <v>237</v>
       </c>
       <c r="D6" s="9"/>
     </row>
@@ -11684,9 +13838,11 @@
     </row>
     <row r="8" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="21" t="s">
-        <v>133</v>
-      </c>
-      <c r="B8" s="19"/>
+        <v>129</v>
+      </c>
+      <c r="B8" s="50" t="s">
+        <v>237</v>
+      </c>
       <c r="C8" s="1"/>
       <c r="D8" s="9"/>
     </row>
@@ -11694,56 +13850,64 @@
       <c r="A9" s="9"/>
       <c r="B9" s="19"/>
       <c r="C9" s="19" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="D9" s="9"/>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A10" s="9"/>
-      <c r="B10" s="19"/>
-      <c r="C10" s="19"/>
+      <c r="A10" s="30" t="s">
+        <v>239</v>
+      </c>
+      <c r="B10" s="9"/>
+      <c r="C10" s="9"/>
       <c r="D10" s="9"/>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A11" s="21" t="s">
-        <v>125</v>
-      </c>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-    </row>
-    <row r="12" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A12" s="9"/>
-      <c r="B12" s="19" t="s">
-        <v>126</v>
-      </c>
+    <row r="11" spans="1:22" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A11" s="9"/>
+      <c r="B11" s="48" t="s">
+        <v>238</v>
+      </c>
+      <c r="C11" s="48" t="s">
+        <v>236</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A12" s="37" t="s">
+        <v>240</v>
+      </c>
+      <c r="B12" s="9"/>
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A13" s="21" t="s">
-        <v>128</v>
-      </c>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
+      <c r="A13" s="9"/>
+      <c r="B13" s="48" t="s">
+        <v>241</v>
+      </c>
+      <c r="C13" s="48" t="s">
+        <v>244</v>
+      </c>
       <c r="D13" s="9"/>
     </row>
-    <row r="14" spans="1:22" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="9"/>
-      <c r="B14" s="19" t="s">
-        <v>127</v>
-      </c>
-      <c r="C14" s="19" t="s">
-        <v>129</v>
-      </c>
-      <c r="D14" s="19" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A14" s="51" t="s">
+        <v>242</v>
+      </c>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
+    </row>
+    <row r="15" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15" s="9"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
+      <c r="B15" s="48" t="s">
+        <v>245</v>
+      </c>
+      <c r="C15" s="48" t="s">
+        <v>243</v>
+      </c>
       <c r="D15" s="9"/>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.3">
@@ -11752,23 +13916,68 @@
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
     </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="9"/>
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
-    </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="F17" s="1"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="K17" s="1"/>
+      <c r="L17" s="1"/>
+      <c r="M17" s="1"/>
+      <c r="N17" s="1"/>
+      <c r="P17" s="2"/>
+      <c r="Q17" s="2"/>
+      <c r="R17" s="2"/>
+      <c r="S17" s="1"/>
+      <c r="T17" s="8"/>
+      <c r="U17" s="2"/>
+      <c r="V17" s="1"/>
+    </row>
+    <row r="18" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" s="9"/>
       <c r="B18" s="9"/>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
-    </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="F18" s="1"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="K18" s="1"/>
+      <c r="L18" s="1"/>
+      <c r="M18" s="1"/>
+      <c r="N18" s="1"/>
+      <c r="P18" s="2"/>
+      <c r="Q18" s="2"/>
+      <c r="R18" s="2"/>
+      <c r="S18" s="1"/>
+      <c r="T18" s="8"/>
+      <c r="U18" s="2"/>
+      <c r="V18" s="1"/>
+    </row>
+    <row r="19" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A19" s="9"/>
       <c r="B19" s="9"/>
       <c r="C19" s="9"/>
       <c r="D19" s="9"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="1"/>
+      <c r="P19" s="2"/>
+      <c r="Q19" s="2"/>
+      <c r="R19" s="2"/>
+      <c r="S19" s="1"/>
+      <c r="T19" s="8"/>
+      <c r="U19" s="2"/>
+      <c r="V19" s="1"/>
     </row>
     <row r="20" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A20" s="9"/>
@@ -12379,69 +14588,6 @@
       <c r="U48" s="2"/>
       <c r="V48" s="1"/>
     </row>
-    <row r="49" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="9"/>
-      <c r="B49" s="9"/>
-      <c r="C49" s="9"/>
-      <c r="D49" s="9"/>
-      <c r="F49" s="1"/>
-      <c r="G49" s="2"/>
-      <c r="H49" s="1"/>
-      <c r="I49" s="1"/>
-      <c r="K49" s="1"/>
-      <c r="L49" s="1"/>
-      <c r="M49" s="1"/>
-      <c r="N49" s="1"/>
-      <c r="P49" s="2"/>
-      <c r="Q49" s="2"/>
-      <c r="R49" s="2"/>
-      <c r="S49" s="1"/>
-      <c r="T49" s="8"/>
-      <c r="U49" s="2"/>
-      <c r="V49" s="1"/>
-    </row>
-    <row r="50" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="9"/>
-      <c r="B50" s="9"/>
-      <c r="C50" s="9"/>
-      <c r="D50" s="9"/>
-      <c r="F50" s="1"/>
-      <c r="G50" s="2"/>
-      <c r="H50" s="1"/>
-      <c r="I50" s="1"/>
-      <c r="K50" s="1"/>
-      <c r="L50" s="1"/>
-      <c r="M50" s="1"/>
-      <c r="N50" s="1"/>
-      <c r="P50" s="2"/>
-      <c r="Q50" s="2"/>
-      <c r="R50" s="2"/>
-      <c r="S50" s="1"/>
-      <c r="T50" s="8"/>
-      <c r="U50" s="2"/>
-      <c r="V50" s="1"/>
-    </row>
-    <row r="51" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="9"/>
-      <c r="B51" s="9"/>
-      <c r="C51" s="9"/>
-      <c r="D51" s="9"/>
-      <c r="F51" s="1"/>
-      <c r="G51" s="2"/>
-      <c r="H51" s="1"/>
-      <c r="I51" s="1"/>
-      <c r="K51" s="1"/>
-      <c r="L51" s="1"/>
-      <c r="M51" s="1"/>
-      <c r="N51" s="1"/>
-      <c r="P51" s="2"/>
-      <c r="Q51" s="2"/>
-      <c r="R51" s="2"/>
-      <c r="S51" s="1"/>
-      <c r="T51" s="8"/>
-      <c r="U51" s="2"/>
-      <c r="V51" s="1"/>
-    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="D3" r:id="rId1" location=":~:text=%D0%A1%D0%BE%D0%B7%D0%B4%D0%B0%D0%BD%D0%B8%D0%B5%20%D0%B8%20%D1%83%D0%B4%D0%B0%D0%BB%D0%B5%D0%BD%D0%B8%D0%B5%20%D1%82%D0%B0%D0%B1%D0%BB%D0%B8%D1%86" xr:uid="{EBAD4F4A-49BC-45EE-B388-4866E40CC60C}"/>
@@ -12451,13 +14597,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1F646E2-B598-4143-89B5-75F807CE8970}">
   <sheetPr>
     <tabColor rgb="FF00B050"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:V27"/>
+  <dimension ref="A2:V26"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="36" style="1" customWidth="1"/>
@@ -12524,7 +14670,7 @@
       </c>
       <c r="B4" s="9"/>
       <c r="C4" s="37" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="D4" s="9"/>
     </row>
@@ -12555,8 +14701,8 @@
       <c r="D6" s="1"/>
     </row>
     <row r="7" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="45" t="s">
-        <v>227</v>
+      <c r="A7" s="44" t="s">
+        <v>221</v>
       </c>
       <c r="B7" s="9"/>
       <c r="C7" s="9"/>
@@ -12579,11 +14725,11 @@
     </row>
     <row r="8" spans="1:22" s="7" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A8" s="9"/>
-      <c r="B8" s="43" t="s">
-        <v>228</v>
-      </c>
-      <c r="C8" s="43" t="s">
-        <v>230</v>
+      <c r="B8" s="42" t="s">
+        <v>222</v>
+      </c>
+      <c r="C8" s="42" t="s">
+        <v>224</v>
       </c>
       <c r="D8" s="9"/>
       <c r="F8" s="1"/>
@@ -12603,11 +14749,11 @@
       <c r="V8" s="1"/>
     </row>
     <row r="9" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="45" t="s">
-        <v>229</v>
+      <c r="A9" s="44" t="s">
+        <v>223</v>
       </c>
       <c r="B9" s="9"/>
-      <c r="C9" s="46"/>
+      <c r="C9" s="45"/>
       <c r="D9" s="9"/>
       <c r="F9" s="1"/>
       <c r="G9" s="2"/>
@@ -12627,11 +14773,11 @@
     </row>
     <row r="10" spans="1:22" s="7" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A10" s="9"/>
-      <c r="B10" s="43" t="s">
-        <v>228</v>
-      </c>
-      <c r="C10" s="43" t="s">
-        <v>231</v>
+      <c r="B10" s="42" t="s">
+        <v>222</v>
+      </c>
+      <c r="C10" s="42" t="s">
+        <v>225</v>
       </c>
       <c r="D10" s="9"/>
       <c r="F10" s="1"/>
@@ -12651,7 +14797,9 @@
       <c r="V10" s="1"/>
     </row>
     <row r="11" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="9"/>
+      <c r="A11" s="47" t="s">
+        <v>231</v>
+      </c>
       <c r="B11" s="9"/>
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
@@ -12671,10 +14819,14 @@
       <c r="U11" s="2"/>
       <c r="V11" s="1"/>
     </row>
-    <row r="12" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:22" s="7" customFormat="1" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A12" s="9"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
+      <c r="B12" s="46" t="s">
+        <v>233</v>
+      </c>
+      <c r="C12" s="46" t="s">
+        <v>232</v>
+      </c>
       <c r="D12" s="9"/>
       <c r="F12" s="1"/>
       <c r="G12" s="2"/>
@@ -12692,10 +14844,14 @@
       <c r="U12" s="2"/>
       <c r="V12" s="1"/>
     </row>
-    <row r="13" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:22" s="7" customFormat="1" ht="216" x14ac:dyDescent="0.3">
       <c r="A13" s="9"/>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
+      <c r="B13" s="46" t="s">
+        <v>235</v>
+      </c>
+      <c r="C13" s="46" t="s">
+        <v>234</v>
+      </c>
       <c r="D13" s="9"/>
       <c r="F13" s="1"/>
       <c r="G13" s="2"/>
@@ -12986,27 +15142,6 @@
       <c r="U26" s="2"/>
       <c r="V26" s="1"/>
     </row>
-    <row r="27" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="9"/>
-      <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="9"/>
-      <c r="F27" s="1"/>
-      <c r="G27" s="2"/>
-      <c r="H27" s="1"/>
-      <c r="I27" s="1"/>
-      <c r="K27" s="1"/>
-      <c r="L27" s="1"/>
-      <c r="M27" s="1"/>
-      <c r="N27" s="1"/>
-      <c r="P27" s="2"/>
-      <c r="Q27" s="2"/>
-      <c r="R27" s="2"/>
-      <c r="S27" s="1"/>
-      <c r="T27" s="8"/>
-      <c r="U27" s="2"/>
-      <c r="V27" s="1"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
@@ -13014,7 +15149,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87C455FF-42A2-4363-8055-67FDFE85198A}">
   <sheetPr>
     <tabColor rgb="FF00B050"/>
@@ -13100,8 +15235,8 @@
       <c r="C5" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="D5" s="42" t="s">
-        <v>207</v>
+      <c r="D5" s="41" t="s">
+        <v>201</v>
       </c>
       <c r="P5" s="1"/>
       <c r="U5" s="1"/>
@@ -13125,8 +15260,8 @@
       <c r="C7" s="19" t="s">
         <v>111</v>
       </c>
-      <c r="D7" s="42" t="s">
-        <v>207</v>
+      <c r="D7" s="41" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="8" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
@@ -13147,118 +15282,118 @@
       <c r="C9" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="D9" s="42" t="s">
-        <v>208</v>
+      <c r="D9" s="41" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A10" s="25" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="C10" s="19"/>
       <c r="D10" s="4"/>
     </row>
     <row r="11" spans="1:22" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A11" s="32" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="B11" s="32" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="C11" s="32" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="D11" s="33" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12" spans="1:22" ht="72" x14ac:dyDescent="0.3">
       <c r="A12" s="32" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="B12" s="31"/>
       <c r="C12" s="32" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="D12" s="33"/>
     </row>
     <row r="13" spans="1:22" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A13" s="32" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B13" s="32" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C13" s="32" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="D13" s="33"/>
     </row>
     <row r="14" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A14" s="32" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="B14" s="31"/>
       <c r="C14" s="32" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="D14" s="33"/>
     </row>
     <row r="15" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A15" s="32" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="B15" s="31" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C15" s="32" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D15" s="33"/>
     </row>
     <row r="16" spans="1:22" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A16" s="32" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B16" s="31" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C16" s="32" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="D16" s="33"/>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A17" s="38" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="B17" s="31" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C17" s="32"/>
       <c r="D17" s="33"/>
     </row>
     <row r="18" spans="1:22" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A18" s="32" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="B18" s="32" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C18" s="32" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D18" s="33" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
     </row>
     <row r="19" spans="1:22" s="7" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A19" s="32" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B19" s="31"/>
       <c r="C19" s="32" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="D19" s="33"/>
       <c r="F19" s="1"/>
@@ -13279,11 +15414,11 @@
     </row>
     <row r="20" spans="1:22" s="7" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A20" s="32" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="B20" s="31"/>
       <c r="C20" s="32" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="D20" s="33"/>
       <c r="F20" s="1"/>
@@ -13304,11 +15439,11 @@
     </row>
     <row r="21" spans="1:22" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A21" s="32" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="B21" s="31"/>
       <c r="C21" s="32" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="D21" s="33"/>
       <c r="F21" s="1"/>
@@ -13329,11 +15464,11 @@
     </row>
     <row r="22" spans="1:22" s="7" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A22" s="32" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="B22" s="31"/>
       <c r="C22" s="32" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="D22" s="33"/>
       <c r="F22" s="1"/>
@@ -13354,11 +15489,11 @@
     </row>
     <row r="23" spans="1:22" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A23" s="32" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="B23" s="31"/>
       <c r="C23" s="32" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D23" s="33"/>
       <c r="F23" s="1"/>
@@ -13379,11 +15514,11 @@
     </row>
     <row r="24" spans="1:22" s="7" customFormat="1" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A24" s="32" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="B24" s="31"/>
       <c r="C24" s="32" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="D24" s="33"/>
       <c r="F24" s="1"/>
@@ -13404,13 +15539,13 @@
     </row>
     <row r="25" spans="1:22" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A25" s="32" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B25" s="31" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="C25" s="32" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="D25" s="33"/>
       <c r="F25" s="1"/>
@@ -13431,11 +15566,11 @@
     </row>
     <row r="26" spans="1:22" s="7" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A26" s="32" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="B26" s="31"/>
       <c r="C26" s="32" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="D26" s="33"/>
       <c r="F26" s="1"/>
@@ -13456,13 +15591,13 @@
     </row>
     <row r="27" spans="1:22" s="7" customFormat="1" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A27" s="32" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="B27" s="31" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C27" s="32" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="D27" s="33"/>
       <c r="F27" s="1"/>
@@ -13483,13 +15618,13 @@
     </row>
     <row r="28" spans="1:22" s="7" customFormat="1" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A28" s="32" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="B28" s="39" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C28" s="32" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="D28" s="33"/>
       <c r="F28" s="1"/>
@@ -13510,13 +15645,13 @@
     </row>
     <row r="29" spans="1:22" s="7" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A29" s="32" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B29" s="39" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C29" s="32" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="D29" s="33"/>
       <c r="F29" s="1"/>
@@ -13537,11 +15672,11 @@
     </row>
     <row r="30" spans="1:22" s="7" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A30" s="32" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="B30" s="31"/>
       <c r="C30" s="32" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="D30" s="33"/>
       <c r="F30" s="1"/>
@@ -13562,13 +15697,13 @@
     </row>
     <row r="31" spans="1:22" s="7" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A31" s="32" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="B31" s="39" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C31" s="32" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D31" s="33"/>
       <c r="F31" s="1"/>
@@ -13993,7 +16128,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4794FD93-B283-45AF-BCD9-82490C321ADD}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -14059,8 +16194,8 @@
       <c r="V3" s="2"/>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A4" s="45" t="s">
-        <v>224</v>
+      <c r="A4" s="44" t="s">
+        <v>218</v>
       </c>
       <c r="B4" s="9"/>
       <c r="C4" s="9"/>
@@ -14068,17 +16203,17 @@
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A5" s="9"/>
-      <c r="B5" s="43" t="s">
-        <v>226</v>
-      </c>
-      <c r="C5" s="43" t="s">
-        <v>225</v>
+      <c r="B5" s="42" t="s">
+        <v>220</v>
+      </c>
+      <c r="C5" s="42" t="s">
+        <v>219</v>
       </c>
       <c r="D5" s="9"/>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A6" s="45" t="s">
-        <v>223</v>
+      <c r="A6" s="44" t="s">
+        <v>217</v>
       </c>
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
@@ -14087,16 +16222,16 @@
     <row r="7" spans="1:22" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A7" s="9"/>
       <c r="B7" s="9"/>
-      <c r="C7" s="43" t="s">
-        <v>235</v>
+      <c r="C7" s="42" t="s">
+        <v>229</v>
       </c>
       <c r="D7" s="9"/>
     </row>
     <row r="8" spans="1:22" ht="331.2" x14ac:dyDescent="0.3">
       <c r="A8" s="9"/>
       <c r="B8" s="9"/>
-      <c r="C8" s="43" t="s">
-        <v>236</v>
+      <c r="C8" s="42" t="s">
+        <v>230</v>
       </c>
       <c r="D8" s="9"/>
     </row>
@@ -14825,708 +16960,53 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DB01197-FE1C-4ED1-B3B4-7B774B71A2A6}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:V48"/>
+  <dimension ref="A2:E3"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="36" style="1" customWidth="1"/>
+    <col min="1" max="1" width="36" style="2" customWidth="1"/>
     <col min="2" max="2" width="50.5546875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="71.21875" style="4" customWidth="1"/>
-    <col min="4" max="4" width="56.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="6.21875" style="7" customWidth="1"/>
-    <col min="6" max="6" width="43.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="71.21875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="56.44140625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="6.21875" style="53" customWidth="1"/>
+    <col min="6" max="6" width="43.21875" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="55.109375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="67.88671875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="64.33203125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="7.77734375" style="7" customWidth="1"/>
-    <col min="11" max="11" width="39.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="48.88671875" style="1" customWidth="1"/>
-    <col min="13" max="13" width="72.6640625" style="1" customWidth="1"/>
-    <col min="14" max="14" width="43.88671875" style="1" customWidth="1"/>
-    <col min="15" max="15" width="7.77734375" style="7" customWidth="1"/>
+    <col min="8" max="8" width="67.88671875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="64.33203125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="7.77734375" style="2" customWidth="1"/>
+    <col min="11" max="11" width="39.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="48.88671875" style="2" customWidth="1"/>
+    <col min="13" max="13" width="72.6640625" style="2" customWidth="1"/>
+    <col min="14" max="14" width="43.88671875" style="2" customWidth="1"/>
+    <col min="15" max="15" width="7.77734375" style="2" customWidth="1"/>
     <col min="16" max="16" width="56.77734375" style="2" customWidth="1"/>
     <col min="17" max="17" width="46.77734375" style="2" customWidth="1"/>
     <col min="18" max="18" width="62.88671875" style="2" customWidth="1"/>
-    <col min="19" max="19" width="49.21875" style="1" customWidth="1"/>
-    <col min="20" max="20" width="8.77734375" style="8"/>
+    <col min="19" max="19" width="49.21875" style="2" customWidth="1"/>
+    <col min="20" max="20" width="8.77734375" style="2"/>
     <col min="21" max="21" width="67.77734375" style="2" customWidth="1"/>
-    <col min="22" max="22" width="68.33203125" style="1" customWidth="1"/>
-    <col min="23" max="24" width="59.33203125" style="1" customWidth="1"/>
-    <col min="25" max="25" width="59.6640625" style="1" customWidth="1"/>
-    <col min="26" max="26" width="99.44140625" style="1" customWidth="1"/>
-    <col min="27" max="27" width="41.21875" style="1" customWidth="1"/>
-    <col min="28" max="16384" width="8.77734375" style="1"/>
+    <col min="22" max="22" width="68.33203125" style="2" customWidth="1"/>
+    <col min="23" max="24" width="59.33203125" style="2" customWidth="1"/>
+    <col min="25" max="25" width="59.6640625" style="2" customWidth="1"/>
+    <col min="26" max="26" width="99.44140625" style="2" customWidth="1"/>
+    <col min="27" max="27" width="41.21875" style="2" customWidth="1"/>
+    <col min="28" max="16384" width="8.77734375" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A2" s="3"/>
-      <c r="B2" s="5"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
-      <c r="N2" s="3"/>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="5"/>
-      <c r="R2" s="5"/>
-      <c r="S2" s="5"/>
-      <c r="U2" s="5"/>
-    </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+    <row r="2" spans="1:5" s="52" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="E2" s="53"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="9"/>
-      <c r="P3" s="1"/>
-      <c r="U3" s="1"/>
-      <c r="V3" s="2"/>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A4" s="9"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A5" s="9"/>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-    </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A6" s="9"/>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A7" s="9"/>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A8" s="9"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A9" s="9"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A10" s="9"/>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A11" s="9"/>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A12" s="9"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A13" s="9"/>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A14" s="9"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A15" s="9"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A16" s="9"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="9"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="9"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="9"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="9"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="9"/>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="9"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="9"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" s="9"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="9"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" s="9"/>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="9"/>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" s="9"/>
-      <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="9"/>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28" s="9"/>
-      <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
-      <c r="D28" s="9"/>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" s="9"/>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A30" s="9"/>
-      <c r="B30" s="9"/>
-      <c r="C30" s="9"/>
-      <c r="D30" s="9"/>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A31" s="9"/>
-      <c r="B31" s="9"/>
-      <c r="C31" s="9"/>
-      <c r="D31" s="9"/>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A32" s="9"/>
-      <c r="B32" s="9"/>
-      <c r="C32" s="9"/>
-      <c r="D32" s="9"/>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33" s="9"/>
-      <c r="B33" s="9"/>
-      <c r="C33" s="9"/>
-      <c r="D33" s="9"/>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A34" s="9"/>
-      <c r="B34" s="9"/>
-      <c r="C34" s="9"/>
-      <c r="D34" s="9"/>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A35" s="9"/>
-      <c r="B35" s="9"/>
-      <c r="C35" s="9"/>
-      <c r="D35" s="9"/>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A36" s="9"/>
-      <c r="B36" s="9"/>
-      <c r="C36" s="9"/>
-      <c r="D36" s="9"/>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A37" s="9"/>
-      <c r="B37" s="9"/>
-      <c r="C37" s="9"/>
-      <c r="D37" s="9"/>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A38" s="9"/>
-      <c r="B38" s="9"/>
-      <c r="C38" s="9"/>
-      <c r="D38" s="9"/>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A39" s="9"/>
-      <c r="B39" s="9"/>
-      <c r="C39" s="9"/>
-      <c r="D39" s="9"/>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A40" s="9"/>
-      <c r="B40" s="9"/>
-      <c r="C40" s="9"/>
-      <c r="D40" s="9"/>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A41" s="9"/>
-      <c r="B41" s="9"/>
-      <c r="C41" s="9"/>
-      <c r="D41" s="9"/>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A42" s="9"/>
-      <c r="B42" s="9"/>
-      <c r="C42" s="9"/>
-      <c r="D42" s="9"/>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A43" s="9"/>
-      <c r="B43" s="9"/>
-      <c r="C43" s="9"/>
-      <c r="D43" s="9"/>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A44" s="9"/>
-      <c r="B44" s="9"/>
-      <c r="C44" s="9"/>
-      <c r="D44" s="9"/>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A45" s="9"/>
-      <c r="B45" s="9"/>
-      <c r="C45" s="9"/>
-      <c r="D45" s="9"/>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A46" s="9"/>
-      <c r="B46" s="9"/>
-      <c r="C46" s="9"/>
-      <c r="D46" s="9"/>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A47" s="9"/>
-      <c r="B47" s="9"/>
-      <c r="C47" s="9"/>
-      <c r="D47" s="9"/>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A48" s="9"/>
-      <c r="B48" s="9"/>
-      <c r="C48" s="9"/>
-      <c r="D48" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8347859-D7B0-40A5-9B17-0069AC1E92BB}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A2:V49"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="36" style="1" customWidth="1"/>
-    <col min="2" max="2" width="36.21875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="71.21875" style="4" customWidth="1"/>
-    <col min="4" max="4" width="56.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="6.21875" style="7" customWidth="1"/>
-    <col min="6" max="6" width="43.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="55.109375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="67.88671875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="64.33203125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="7.77734375" style="7" customWidth="1"/>
-    <col min="11" max="11" width="39.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="48.88671875" style="1" customWidth="1"/>
-    <col min="13" max="13" width="72.6640625" style="1" customWidth="1"/>
-    <col min="14" max="14" width="43.88671875" style="1" customWidth="1"/>
-    <col min="15" max="15" width="7.77734375" style="7" customWidth="1"/>
-    <col min="16" max="16" width="56.77734375" style="2" customWidth="1"/>
-    <col min="17" max="17" width="46.77734375" style="2" customWidth="1"/>
-    <col min="18" max="18" width="62.88671875" style="2" customWidth="1"/>
-    <col min="19" max="19" width="49.21875" style="1" customWidth="1"/>
-    <col min="20" max="20" width="8.77734375" style="8"/>
-    <col min="21" max="21" width="67.77734375" style="2" customWidth="1"/>
-    <col min="22" max="22" width="68.33203125" style="1" customWidth="1"/>
-    <col min="23" max="24" width="59.33203125" style="1" customWidth="1"/>
-    <col min="25" max="25" width="59.6640625" style="1" customWidth="1"/>
-    <col min="26" max="26" width="99.44140625" style="1" customWidth="1"/>
-    <col min="27" max="27" width="41.21875" style="1" customWidth="1"/>
-    <col min="28" max="16384" width="8.77734375" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A2" s="3"/>
-      <c r="B2" s="5"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
-      <c r="N2" s="3"/>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="5"/>
-      <c r="R2" s="5"/>
-      <c r="S2" s="5"/>
-      <c r="U2" s="5"/>
-    </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="9"/>
-      <c r="P3" s="1"/>
-      <c r="U3" s="1"/>
-      <c r="V3" s="2"/>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A4" s="20" t="s">
-        <v>75</v>
-      </c>
-      <c r="B4" s="9"/>
-      <c r="D4" s="9"/>
-    </row>
-    <row r="5" spans="1:22" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A5" s="19" t="s">
-        <v>76</v>
-      </c>
-      <c r="B5" s="19" t="s">
-        <v>84</v>
-      </c>
-      <c r="C5" s="9"/>
-      <c r="D5" s="19" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A6" s="21" t="s">
-        <v>79</v>
-      </c>
-      <c r="B6" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-    </row>
-    <row r="7" spans="1:22" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="B7" s="9"/>
-      <c r="C7" s="19" t="s">
-        <v>77</v>
-      </c>
-      <c r="D7" s="9"/>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A8" s="21" t="s">
-        <v>80</v>
-      </c>
-      <c r="B8" s="19" t="s">
-        <v>83</v>
-      </c>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-    </row>
-    <row r="9" spans="1:22" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="B9" s="9"/>
-      <c r="C9" s="19" t="s">
-        <v>78</v>
-      </c>
-      <c r="D9" s="9"/>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A10" s="9"/>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A11" s="9"/>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A12" s="9"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A13" s="9"/>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A14" s="9"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A15" s="9"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A16" s="9"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="9"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="9"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="9"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="9"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="9"/>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="9"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="9"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" s="9"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="9"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" s="9"/>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="9"/>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" s="9"/>
-      <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="9"/>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28" s="9"/>
-      <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
-      <c r="D28" s="9"/>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" s="9"/>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A30" s="9"/>
-      <c r="B30" s="9"/>
-      <c r="C30" s="9"/>
-      <c r="D30" s="9"/>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A31" s="9"/>
-      <c r="B31" s="9"/>
-      <c r="C31" s="9"/>
-      <c r="D31" s="9"/>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A32" s="9"/>
-      <c r="B32" s="9"/>
-      <c r="C32" s="9"/>
-      <c r="D32" s="9"/>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33" s="9"/>
-      <c r="B33" s="9"/>
-      <c r="C33" s="9"/>
-      <c r="D33" s="9"/>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A34" s="9"/>
-      <c r="B34" s="9"/>
-      <c r="C34" s="9"/>
-      <c r="D34" s="9"/>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A35" s="9"/>
-      <c r="B35" s="9"/>
-      <c r="C35" s="9"/>
-      <c r="D35" s="9"/>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A36" s="9"/>
-      <c r="B36" s="9"/>
-      <c r="C36" s="9"/>
-      <c r="D36" s="9"/>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A37" s="9"/>
-      <c r="B37" s="9"/>
-      <c r="C37" s="9"/>
-      <c r="D37" s="9"/>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A38" s="9"/>
-      <c r="B38" s="9"/>
-      <c r="C38" s="9"/>
-      <c r="D38" s="9"/>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A39" s="9"/>
-      <c r="B39" s="9"/>
-      <c r="C39" s="9"/>
-      <c r="D39" s="9"/>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A40" s="9"/>
-      <c r="B40" s="9"/>
-      <c r="C40" s="9"/>
-      <c r="D40" s="9"/>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A41" s="9"/>
-      <c r="B41" s="9"/>
-      <c r="C41" s="9"/>
-      <c r="D41" s="9"/>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A42" s="9"/>
-      <c r="B42" s="9"/>
-      <c r="C42" s="9"/>
-      <c r="D42" s="9"/>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A43" s="9"/>
-      <c r="B43" s="9"/>
-      <c r="C43" s="9"/>
-      <c r="D43" s="9"/>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A44" s="9"/>
-      <c r="B44" s="9"/>
-      <c r="C44" s="9"/>
-      <c r="D44" s="9"/>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A45" s="9"/>
-      <c r="B45" s="9"/>
-      <c r="C45" s="9"/>
-      <c r="D45" s="9"/>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A46" s="9"/>
-      <c r="B46" s="9"/>
-      <c r="C46" s="9"/>
-      <c r="D46" s="9"/>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A47" s="9"/>
-      <c r="B47" s="9"/>
-      <c r="C47" s="9"/>
-      <c r="D47" s="9"/>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A48" s="9"/>
-      <c r="B48" s="9"/>
-      <c r="C48" s="9"/>
-      <c r="D48" s="9"/>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A49" s="9"/>
-      <c r="B49" s="9"/>
-      <c r="C49" s="9"/>
-      <c r="D49" s="9"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
-  <drawing r:id="rId2"/>
-</worksheet>
 </file>
--- a/4 четверть_MSSQL.xlsx
+++ b/4 четверть_MSSQL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlexServHW\Desktop\GB_Developer_Workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD93E8F1-59D3-462E-856B-62EC12DDECB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98D284CF-6637-443E-A04A-7DC48A933A5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-13140" yWindow="-21600" windowWidth="23250" windowHeight="12450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-13875" yWindow="-21720" windowWidth="51840" windowHeight="21120" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Изучить" sheetId="21" r:id="rId1"/>
@@ -24,8 +24,9 @@
     <sheet name="template" sheetId="14" r:id="rId9"/>
     <sheet name="Каскадное удаление" sheetId="16" r:id="rId10"/>
     <sheet name="Транзакции" sheetId="17" r:id="rId11"/>
-    <sheet name="bc Массивы" sheetId="18" r:id="rId12"/>
-    <sheet name="bc JSON" sheetId="22" r:id="rId13"/>
+    <sheet name="VIEW" sheetId="25" r:id="rId12"/>
+    <sheet name="bc Массивы" sheetId="18" r:id="rId13"/>
+    <sheet name="bc JSON" sheetId="22" r:id="rId14"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="351">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="352">
   <si>
     <t>Урок 1 часть 1</t>
   </si>
@@ -8699,17 +8700,28 @@
   <si>
     <t>`https://metanit.com/sql/sqlserver/3.4.php</t>
   </si>
+  <si>
+    <t>Аналог SELECT, но работает быстрее обычного SELECT, так как хранит конечный результат SELECT непосредственно в базе без необходимости обращения к каждому под-запросу каждый раз</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="32" x14ac:knownFonts="1">
+  <fonts count="33" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -9067,7 +9079,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -9080,42 +9092,48 @@
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -9123,101 +9141,95 @@
     <xf numFmtId="49" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="17" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="16" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="25" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="26" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="17" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="28" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="29" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="17" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="17" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="29" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="28" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="17" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -10865,6 +10877,62 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C506E3D-0255-4B93-95A3-63E2CE874713}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A2:E4"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="36" style="2" customWidth="1"/>
+    <col min="2" max="2" width="50.5546875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="71.21875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="56.44140625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="6.21875" style="53" customWidth="1"/>
+    <col min="6" max="6" width="43.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="55.109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="67.88671875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="64.33203125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="7.77734375" style="2" customWidth="1"/>
+    <col min="11" max="11" width="39.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="48.88671875" style="2" customWidth="1"/>
+    <col min="13" max="13" width="72.6640625" style="2" customWidth="1"/>
+    <col min="14" max="14" width="43.88671875" style="2" customWidth="1"/>
+    <col min="15" max="15" width="7.77734375" style="2" customWidth="1"/>
+    <col min="16" max="16" width="56.77734375" style="2" customWidth="1"/>
+    <col min="17" max="17" width="46.77734375" style="2" customWidth="1"/>
+    <col min="18" max="18" width="62.88671875" style="2" customWidth="1"/>
+    <col min="19" max="19" width="49.21875" style="2" customWidth="1"/>
+    <col min="20" max="20" width="8.77734375" style="2"/>
+    <col min="21" max="21" width="67.77734375" style="2" customWidth="1"/>
+    <col min="22" max="22" width="68.33203125" style="2" customWidth="1"/>
+    <col min="23" max="24" width="59.33203125" style="2" customWidth="1"/>
+    <col min="25" max="25" width="59.6640625" style="2" customWidth="1"/>
+    <col min="26" max="26" width="99.44140625" style="2" customWidth="1"/>
+    <col min="27" max="27" width="41.21875" style="2" customWidth="1"/>
+    <col min="28" max="16384" width="8.77734375" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:5" s="52" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="E2" s="53"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="C4" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B13A24C-6305-48F4-A1E6-55B31CAA1F4A}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -11737,7 +11805,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA83B601-5B0E-4344-A36B-7DD0432A3007}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -13251,7 +13319,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="9" type="noConversion"/>
+  <phoneticPr fontId="10" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="D46" r:id="rId1" location=":~:text=%D0%A1%D0%BE%D0%B7%D0%B4%D0%B0%D0%BD%D0%B8%D0%B5%20%D0%B1%D0%B0%D0%B7%D1%8B%20%D0%B4%D0%B0%D0%BD%D0%BD%D1%8B%D1%85" xr:uid="{FDFE2116-2B22-4A87-B37D-3DFA9E8F9FE0}"/>
     <hyperlink ref="D44" r:id="rId2" location=":~:text=%D0%A1%D0%BE%D0%B7%D0%B4%D0%B0%D0%BD%D0%B8%D0%B5%20%D0%B1%D0%B0%D0%B7%D1%8B%20%D0%B4%D0%B0%D0%BD%D0%BD%D1%8B%D1%85%20%D0%B2%20SQL%20Management%20Studio" xr:uid="{5B701F02-CEF7-44EA-83C6-0E21D7145608}"/>
@@ -13724,7 +13792,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="9" type="noConversion"/>
+  <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>

--- a/4 четверть_MSSQL.xlsx
+++ b/4 четверть_MSSQL.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlexServHW\Desktop\GB_Developer_Workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98D284CF-6637-443E-A04A-7DC48A933A5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2C1AC8B-F84B-406A-B377-3B25079CC0B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-13875" yWindow="-21720" windowWidth="51840" windowHeight="21120" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="180" yWindow="-18390" windowWidth="18930" windowHeight="15885" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Изучить" sheetId="21" r:id="rId1"/>
     <sheet name="Установка" sheetId="13" r:id="rId2"/>
     <sheet name="DATABASE" sheetId="12" r:id="rId3"/>
     <sheet name="Типы данных" sheetId="24" r:id="rId4"/>
-    <sheet name="TABLE" sheetId="20" r:id="rId5"/>
+    <sheet name="TABLE" sheetId="26" r:id="rId5"/>
     <sheet name="SELECT" sheetId="15" r:id="rId6"/>
     <sheet name="WHERE" sheetId="19" r:id="rId7"/>
     <sheet name="IF" sheetId="23" r:id="rId8"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="352">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="430">
   <si>
     <t>Урок 1 часть 1</t>
   </si>
@@ -8698,22 +8698,3000 @@
     </r>
   </si>
   <si>
-    <t>`https://metanit.com/sql/sqlserver/3.4.php</t>
-  </si>
-  <si>
     <t>Аналог SELECT, но работает быстрее обычного SELECT, так как хранит конечный результат SELECT непосредственно в базе без необходимости обращения к каждому под-запросу каждый раз</t>
+  </si>
+  <si>
+    <t>Максимальный набор</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">С помощью выражения </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PRIMARY KEY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> столбец можно сделать первичным ключом.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Пояснение! </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Первичный ключ уникально идентифицирует строку в таблице. В качестве первичного ключа необязательно должны выступать столбцы с типом int, они могут представлять любой другой тип.</t>
+    </r>
+  </si>
+  <si>
+    <t>Вариант 1</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">CREATE TABLE Customers
+(
+    Id INT,
+    Age INT,
+    FirstName NVARCHAR(20),
+    LastName NVARCHAR(20),
+    Email VARCHAR(30),
+    Phone VARCHAR(20),
+    </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PRIMARY KEY(Id)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+)</t>
+    </r>
+  </si>
+  <si>
+    <t>PRIMARY KEY</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">CREATE TABLE OrderLines
+(
+    OrderId INT,
+    ProductId INT,
+    Quantity INT,
+    Price MONEY,
+    </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PRIMARY KEY(OrderId, ProductId)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+)</t>
+    </r>
+  </si>
+  <si>
+    <t>Вариант 2 (простой)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Пояснение!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Первичный ключ может быть составным (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>compound key</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">). Такой ключ может потребоваться, если у нас сразу два столбца должны уникально идентифицировать строку в таблице.
+Здесь поля OrderId и ProductId вместе выступают как составной первичный ключ. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Важно!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> То есть в таблице OrderLines </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>не может быть двух строк, где для обоих из этих полей одновременно были бы одни и те же значения.</t>
+    </r>
+  </si>
+  <si>
+    <t>IDENTITY</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">`https://metanit.com/sql/sqlserver/3.4.php#:~:text=PRIMARY%20KEY
+CREATE TABLE Customers
+(
+    Id INT </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PRIMARY KEY,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    Age INT,
+    FirstName NVARCHAR(20),
+    LastName NVARCHAR(20),
+    Email VARCHAR(30),
+    Phone VARCHAR(20)
+)</t>
+    </r>
+  </si>
+  <si>
+    <t>`https://metanit.com/sql/sqlserver/3.4.php#:~:text=IDENTITY</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">CREATE TABLE Customers
+(
+    Id INT PRIMARY KEY </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>IDENTITY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>,
+    Age INT,
+    FirstName NVARCHAR(20),
+    LastName NVARCHAR(20),
+    Email VARCHAR(30),
+    Phone VARCHAR(20)
+)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">CREATE TABLE Customers
+(
+    Id INT PRIMARY KEY </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>IDENTITY(1, 1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>,
+    Age INT,
+    FirstName NVARCHAR(20),
+    LastName NVARCHAR(20),
+    Email VARCHAR(30),
+    Phone VARCHAR(20)
+)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Ограничение!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Этот атрибут может назначаться </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ТОЛЬКО</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> для столбцов числовых типов </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>INT, SMALLINT, BIGINT, TYNIINT, DECIMAL и NUMERIC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Ограничение!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> в таблице только один столбец должен иметь такой атрибут.</t>
+    </r>
+  </si>
+  <si>
+    <t>Атрибут IDENTITY позволяет сделать столбец идентификатором. 
+При добавлении новых данных в таблицу SQL Server будет инкрементировать на единицу значение этого столбца у последней записи. Как правило, в роли идентификатора выступает тот же столбец, который является первичным ключом, хотя в принципе это необязательно.</t>
+  </si>
+  <si>
+    <t>`https://metanit.com/sql/sqlserver/3.4.php#:~:text=UNIQUE</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PRIMARY KEY</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> IDENTITY</t>
+  </si>
+  <si>
+    <t>UNIQUE</t>
+  </si>
+  <si>
+    <t>Ограничения!</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">CREATE TABLE Customers
+(
+    Id INT PRIMARY KEY IDENTITY,
+    Age INT,
+    FirstName NVARCHAR(20),
+    LastName NVARCHAR(20),
+    Email VARCHAR(30) </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>UNIQUE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">,
+    Phone VARCHAR(20) </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>UNIQUE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Дополнительная возможность!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Если мы хотим, чтобы столбец имел только уникальные значения, то для него можно определить атрибут UNIQUE.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Пояснение!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">1 Одинаковые Email → </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>❌ запрещено</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+2 Одинаковые Phone → </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>❌ запрещено</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+3 Одинаковые Email И Phone одновременно → </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>тоже запрещено</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (потому что каждое из них уже нарушает своё отдельное ограничение)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Пояснение!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">1 (a@b.ru, 111) и (a@b.ru, 222) → </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>✅ можно</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+2 (a@b.ru, 111) и (c@d.ru, 111) → </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>✅ можно</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+3 (a@b.ru, 111) и (a@b.ru, 111) → </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>❌ нельзя</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">CREATE TABLE Customers
+(
+    Id INT PRIMARY KEY IDENTITY,
+    Age INT,
+    FirstName NVARCHAR(20),
+    LastName NVARCHAR(20),
+    Email VARCHAR(30),
+    Phone VARCHAR(20),
+    </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>UNIQUE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">(Email, Phone) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> -- только пара Email+Phone уникальна
+)</t>
+    </r>
+  </si>
+  <si>
+    <t>UNIQUE (Email, Phone)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Дополнительная возможность!
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>UNIQUE</t>
+    </r>
+  </si>
+  <si>
+    <t>NULL и NOT NULL</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Дополнительная возможность!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Чтобы указать, может ли столбец принимать значение NULL, при определении столбца ему можно задать атрибут NULL или NOT NULL.</t>
+    </r>
+  </si>
+  <si>
+    <t>PRIMARY KEY(Id)</t>
+  </si>
+  <si>
+    <t>PRIMARY KEY(OrderId, ProductId)</t>
+  </si>
+  <si>
+    <t>IDENTITY(seed, increment)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">CREATE TABLE Customers
+(
+    Id INT PRIMARY KEY IDENTITY,
+    Age INT,
+    FirstName NVARCHAR(20) </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>NOT NULL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">,
+    LastName NVARCHAR(20) </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>NOT NULL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>,
+    Email VARCHAR(30) UNIQUE,
+    Phone VARCHAR(20) UNIQUE
+)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>По умолчанию:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">IDENTITY(1, 1)
+Пояснение! </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>отсчет начинается с 1, а последующие значения увеличиваются на 1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Можем переопределить:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">IDENTITY (2, 3)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Пояснение! </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>отсчет начнется с 2, а значение каждой последующей записи будет увеличиваться на 3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>По умолчанию</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: NULL
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Ограничение! </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>По умолчанию для первичного ключа NOT NULL</t>
+    </r>
+  </si>
+  <si>
+    <t>`https://metanit.com/sql/sqlserver/3.4.php#:~:text=NULL и NOT NULL</t>
+  </si>
+  <si>
+    <t>`https://metanit.com/sql/sqlserver/3.4.php#:~:text=DEFAULT</t>
+  </si>
+  <si>
+    <t>DEFAULT</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">CREATE TABLE Customers
+(
+    Id INT PRIMARY KEY IDENTITY,
+    Age INT </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>DEFAULT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 18,
+    FirstName NVARCHAR(20) NOT NULL,
+    LastName NVARCHAR(20) NOT NULL,
+    Email VARCHAR(30) UNIQUE,
+    Phone VARCHAR(20) UNIQUE
+);</t>
+    </r>
+  </si>
+  <si>
+    <t>CHECK</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Дополнительная возможность!
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>NOT NULL</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">CREATE TABLE Customers
+(
+    Id INT PRIMARY KEY IDENTITY,
+    Age INT DEFAULT 18 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CHECK(Age &gt;0 AND Age &lt; 100)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">,
+    FirstName NVARCHAR(20) NOT NULL,
+    LastName NVARCHAR(20) NOT NULL,
+    Email VARCHAR(30) UNIQUE </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CHECK(Email !='')</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">,
+    Phone VARCHAR(20) UNIQUE </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CHECK(Phone !='')</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Дополнительная возможность!</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+DEFAULT</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Дополнительная возможность!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Атрибут DEFAULT определяет значение по умолчанию для столбца.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">CREATE TABLE Customers
+(
+    Id INT PRIMARY KEY IDENTITY,
+    Age INT DEFAULT 18,
+    FirstName NVARCHAR(20) NOT NULL,
+    LastName NVARCHAR(20) NOT NULL,
+    Email VARCHAR(30) UNIQUE,
+    Phone VARCHAR(20) UNIQUE,
+    </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CHECK((Age &gt;0 AND Age&lt;100) AND (Email !='') AND (Phone !=''))</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+)</t>
+    </r>
+  </si>
+  <si>
+    <t>CHECK(
+ (Age &gt;0 AND Age&lt;100) 
+  AND (Email !='') 
+  AND (Phone !='')
+)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Дополнительная возможность!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CHECK(Age &gt;0 AND Age &lt; 100)
+CHECK(Email !='')
+CHECK(Phone !='')</t>
+    </r>
+  </si>
+  <si>
+    <t>CONSTRAINT</t>
+  </si>
+  <si>
+    <t>`https://metanit.com/sql/sqlserver/3.4.php#:~:text=CHECK</t>
+  </si>
+  <si>
+    <t>`https://metanit.com/sql/sqlserver/3.4.php#:~:text=CONSTRAINT</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Дополнительная возможность! 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">CONSTRAINT DF_Customer_Age DEFAULT 18 </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">CREATE TABLE Customers
+(
+    Id INT CONSTRAINT PK_Customer_Id PRIMARY KEY IDENTITY,
+    Age INT
+        </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CONSTRAINT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> DF_Customer_Age </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">DEFAULT 18 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+        </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CONSTRAINT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> CK_Customer_Age </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CHECK(Age &gt;0 AND Age &lt; 100)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">,
+    FirstName NVARCHAR(20) NOT NULL,
+    LastName NVARCHAR(20) NOT NULL,
+    Email VARCHAR(30) </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CONSTRAINT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> UQ_Customer_Email </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>UNIQUE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">,
+    Phone VARCHAR(20) </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CONSTRAINT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> UQ_Customer_Phone </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>UNIQUE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">CREATE TABLE Customers
+(
+    Id INT CONSTRAINT PK_Customers PRIMARY KEY IDENTITY,
+    Age INT CONSTRAINT CHK_Customers_Age CHECK (Age &gt; 0 AND Age &lt; 100),
+    FirstName NVARCHAR(20) CONSTRAINT NN_Customers_FirstName NOT NULL,
+    LastName NVARCHAR(20) NOT NULL,  -- без имени (сгенерируется автоматически)
+    Email VARCHAR(30) CONSTRAINT UQ_Customers_Email UNIQUE,
+    Phone VARCHAR(20) CONSTRAINT UQ_Customers_Phone UNIQUE,
+    CountryId INT,
+    </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CONSTRAINT FK_Customers_Countries FOREIGN KEY (CountryId) REFERENCES Countries(Id)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">2 При удалении таблицы с внешними ключами нужно знать имена:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ALTER TABLE Orders DROP CONSTRAINT FK_Orders_Customers;  -- понятно</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ALTER TABLE Orders DROP CONSTRAINT FK__Orders__Cust__123; -- что это?</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">CREATE TABLE Orders
+(
+    OrderId INT,
+    CustomerId INT,
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">    CONSTRAINT PK_Orders PRIMARY KEY (OrderId),
+    CONSTRAINT FK_Orders_Customers FOREIGN KEY (CustomerId) REFERENCES Customers(Id),
+    CONSTRAINT UQ_Orders_Number UNIQUE (OrderId)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Удалить </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CONSTRAINT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> по имени</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Переименовать </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CONSTRAINT</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>EXEC sp_rename</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 'Customers.CHK_Customers_Age', 'CHK_Customers_Age_New', 'OBJECT';</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ALTER TABLE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Customers </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>DROP CONSTRAINT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> CHK_Customers_Age;
+</t>
+    </r>
+  </si>
+  <si>
+    <t>DELETE</t>
+  </si>
+  <si>
+    <t>UPDATE</t>
+  </si>
+  <si>
+    <t>FOREIGN KEY</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">CREATE TABLE </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RIghts</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+(
+    Id INT PRIMARY KEY,
+    </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Right</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> NVARCHAR(50)
+);
+-- Таблица с внешним ключом (дочерняя)
+CREATE TABLE </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>usr_Users</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+(
+    Id INT PRIMARY KEY,
+    Name NVARCHAR(50),
+    </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RightId</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> INT,
+    </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>FOREIGN KEY (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RightId</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>) REFERENCES</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Rights</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(Id)  -- внешний ключ
+);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Пояснение!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> это ограничение, которое обеспечивает ссылочную целостность между двумя таблицами. Оно гарантирует, что значение в одной таблице существует в другой таблице.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Дополнительная возможность!  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">✅ Нельзя </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">вставить продукт с CategoryId = 999, если нет категории с Id = 999
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>✅ Нельзя</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> удалить категорию, если на неё ссылаются продукты
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">✅ Нельзя </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>изменить Id категории, если на неё ссылаются</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">    CONSTRAINT PK_Orders PRIMARY KEY (OrderId),
+    CONSTRAINT FK_Orders_Customers FOREIGN KEY (CustomerId) REFERENCES Customers(Id),
+    CONSTRAINT UQ_Orders_Number UNIQUE (OrderId)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Вариант записи 1</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Дополнительная возможность!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Ключевое слово CHECK задает ограничение для диапазона значений, которые могут храниться в столбце.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Вариант записи 2
+Также с помощью CHECK можно создать ограничение в целом для таблицы
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Примечание по знаку неравенства!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Может быть &lt;&gt; и !=</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Вариант записи 1</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="8"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Дополнительная возможность! </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+1 Понятные сообщения об ошибках
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>-- Без имени:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+-- "Violation of CHECK constraint </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CK__Customers__Age__12345678</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">"
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>-- С именем:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+-- "Violation of CHECK constraint </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CHK_Age_Range</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"  ← сразу понятно, что не так</t>
+    </r>
+  </si>
+  <si>
+    <t>Вариант записи 2</t>
+  </si>
+  <si>
+    <t>"PK_" - для PRIMARY KEY
+"FK_" - для FOREIGN KEY
+"CK_" - для CHECK
+"UQ_" - для UNIQUE
+"DF_" - для DEFAULT</t>
+  </si>
+  <si>
+    <t>Синтаксис</t>
+  </si>
+  <si>
+    <t>`https://metanit.com/sql/sqlserver/3.5.php</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">CREATE TABLE Customers (
+    Id INT PRIMARY KEY,
+    Name NVARCHAR(100)
+);
+CREATE TABLE Orders (
+    Id INT PRIMARY KEY,
+    CustomerId INT,
+    OrderDate DATE,
+    </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">FOREIGN KEY (CustomerId) REFERENCES Customers(Id) </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">связь </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>один клиент - много заказов</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+);
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">-- ❌ Не сработает
+INSERT INTO Orders VALUES (1, 999, '2024-01-01');
+-- Сообщение: FOREIGN KEY constraint failed
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>-- ✅ Правильно
+INSERT INTO Customers VALUES (1, 'Иван');
+INSERT INTO Orders VALUES (1, 1, '2024-01-01');  -- Ok</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Дополнительно! </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Здесь связь one-to-many (один ко многим)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">:
+Один клиент → много заказов
+Один заказ → принадлежит одному клиенту
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Важно!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Внешний ключ устанавливается для столбцов из </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>зависимой (one)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>подчиненной таблицы</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, и указывает на один из столбцов из </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>главной таблицы (many)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Ограничение!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Хотя, как правило, внешний ключ указывает на первичный ключ из связанной главной таблицы, но это необязательно должно быть непременным условием. Внешний ключ также может указывать на какой-то другой столбец, который имеет уникальное значение.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Ограничение!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Хотя, как правило, внешний ключ указывает на первичный ключ из связанной главной таблицы, но это необязательно должно быть непременным условием. Внешний ключ также может указывать на какой-то другой столбец, который имеет уникальное значение.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">CREATE TABLE </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Categories</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+(
+    Id INT PRIMARY KEY,
+    Name NVARCHAR(50)
+);
+-- Таблица с внешним ключом (дочерняя)
+CREATE TABLE </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Products</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+(
+    Id INT PRIMARY KEY,
+    Name NVARCHAR(50),
+    </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CategoryId</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> INT,
+    </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>FOREIGN KEY (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CategoryId</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">) REFERENCES </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Categories</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(Id)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  -- внешний ключ
+);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ON DELETE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> {</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CASCADE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>|</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>NO ACTION</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>}]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> [</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ON UPDATE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> {</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CASCADE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>|</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>NO ACTION</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>}]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>FOREIGN KEY (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>стобец1, столбец2, ... столбецN</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>) 
+    REFERENCES</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> главная_таблица</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(столбец_главной_таблицы1, столбец_главной_таблицы2, ... столбец_главной_таблицыN)</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    [ON DELETE {CASCADE|NO ACTION}]
+    [ON UPDATE {CASCADE|NO ACTION}]</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="33" x14ac:knownFonts="1">
+  <fonts count="37" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -8981,8 +11959,26 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF0070C0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="15">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -9067,6 +12063,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -9079,9 +12081,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -9092,144 +12094,141 @@
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="8" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="8" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="8" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    <xf numFmtId="49" fontId="19" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    <xf numFmtId="49" fontId="18" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="28" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    <xf numFmtId="49" fontId="8" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="31" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="26" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="29" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="31" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="29" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="19" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -9245,6 +12244,48 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="35" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="36" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="31" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="31" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -9966,8 +13007,8 @@
       <c r="A15" s="9"/>
       <c r="B15" s="48"/>
       <c r="C15" s="9"/>
-      <c r="D15" s="49" t="s">
-        <v>350</v>
+      <c r="D15" s="59" t="s">
+        <v>422</v>
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.3">
@@ -10888,7 +13929,7 @@
     <col min="2" max="2" width="50.5546875" style="2" customWidth="1"/>
     <col min="3" max="3" width="71.21875" style="2" customWidth="1"/>
     <col min="4" max="4" width="56.44140625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="6.21875" style="53" customWidth="1"/>
+    <col min="5" max="5" width="6.21875" style="52" customWidth="1"/>
     <col min="6" max="6" width="43.21875" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="55.109375" style="2" customWidth="1"/>
     <col min="8" max="8" width="67.88671875" style="2" customWidth="1"/>
@@ -10913,8 +13954,8 @@
     <col min="28" max="16384" width="8.77734375" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:5" s="52" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="E2" s="53"/>
+    <row r="2" spans="1:5" s="51" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="E2" s="52"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
@@ -10923,7 +13964,7 @@
     </row>
     <row r="4" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="C4" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
   </sheetData>
@@ -13319,7 +16360,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="10" type="noConversion"/>
+  <phoneticPr fontId="12" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="D46" r:id="rId1" location=":~:text=%D0%A1%D0%BE%D0%B7%D0%B4%D0%B0%D0%BD%D0%B8%D0%B5%20%D0%B1%D0%B0%D0%B7%D1%8B%20%D0%B4%D0%B0%D0%BD%D0%BD%D1%8B%D1%85" xr:uid="{FDFE2116-2B22-4A87-B37D-3DFA9E8F9FE0}"/>
     <hyperlink ref="D44" r:id="rId2" location=":~:text=%D0%A1%D0%BE%D0%B7%D0%B4%D0%B0%D0%BD%D0%B8%D0%B5%20%D0%B1%D0%B0%D0%B7%D1%8B%20%D0%B4%D0%B0%D0%BD%D0%BD%D1%8B%D1%85%20%D0%B2%20SQL%20Management%20Studio" xr:uid="{5B701F02-CEF7-44EA-83C6-0E21D7145608}"/>
@@ -13344,7 +16385,7 @@
     <col min="2" max="2" width="50.5546875" style="2" customWidth="1"/>
     <col min="3" max="3" width="71.21875" style="2" customWidth="1"/>
     <col min="4" max="4" width="56.44140625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="6.21875" style="53" customWidth="1"/>
+    <col min="5" max="5" width="6.21875" style="52" customWidth="1"/>
     <col min="6" max="6" width="43.21875" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="55.109375" style="2" customWidth="1"/>
     <col min="8" max="8" width="67.88671875" style="2" customWidth="1"/>
@@ -13369,8 +16410,8 @@
     <col min="28" max="16384" width="8.77734375" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:5" s="52" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="E2" s="53"/>
+    <row r="2" spans="1:5" s="51" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="E2" s="52"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
@@ -13378,7 +16419,7 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="54" t="s">
+      <c r="A4" s="53" t="s">
         <v>246</v>
       </c>
     </row>
@@ -13504,7 +16545,7 @@
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="54" t="s">
+      <c r="A16" s="53" t="s">
         <v>278</v>
       </c>
     </row>
@@ -13575,7 +16616,7 @@
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="54" t="s">
+      <c r="A23" s="53" t="s">
         <v>285</v>
       </c>
     </row>
@@ -13636,7 +16677,7 @@
       </c>
     </row>
     <row r="28" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A28" s="54" t="s">
+      <c r="A28" s="53" t="s">
         <v>341</v>
       </c>
     </row>
@@ -13663,7 +16704,7 @@
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A31" s="55" t="s">
+      <c r="A31" s="54" t="s">
         <v>332</v>
       </c>
     </row>
@@ -13676,7 +16717,7 @@
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33" s="56" t="s">
+      <c r="A33" s="55" t="s">
         <v>333</v>
       </c>
     </row>
@@ -13686,7 +16727,7 @@
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A35" s="56" t="s">
+      <c r="A35" s="55" t="s">
         <v>335</v>
       </c>
     </row>
@@ -13696,7 +16737,7 @@
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A37" s="56" t="s">
+      <c r="A37" s="55" t="s">
         <v>338</v>
       </c>
     </row>
@@ -13706,7 +16747,7 @@
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A39" s="54" t="s">
+      <c r="A39" s="53" t="s">
         <v>342</v>
       </c>
     </row>
@@ -13792,873 +16833,504 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="10" type="noConversion"/>
+  <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1138C089-CDC1-4142-9299-EE469CB775F6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{167F5111-19C3-403C-BD83-02EC5AD53664}">
   <sheetPr>
-    <tabColor theme="4" tint="0.79998168889431442"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:V48"/>
+  <dimension ref="A2:E59"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="36" style="1" customWidth="1"/>
+    <col min="1" max="1" width="36" style="2" customWidth="1"/>
     <col min="2" max="2" width="50.5546875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="71.21875" style="4" customWidth="1"/>
-    <col min="4" max="4" width="56.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="6.21875" style="7" customWidth="1"/>
-    <col min="6" max="6" width="43.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="71.21875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="56.44140625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="6.21875" style="52" customWidth="1"/>
+    <col min="6" max="6" width="43.21875" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="55.109375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="67.88671875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="64.33203125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="7.77734375" style="7" customWidth="1"/>
-    <col min="11" max="11" width="39.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="48.88671875" style="1" customWidth="1"/>
-    <col min="13" max="13" width="72.6640625" style="1" customWidth="1"/>
-    <col min="14" max="14" width="43.88671875" style="1" customWidth="1"/>
-    <col min="15" max="15" width="7.77734375" style="7" customWidth="1"/>
+    <col min="8" max="8" width="67.88671875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="64.33203125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="7.77734375" style="2" customWidth="1"/>
+    <col min="11" max="11" width="39.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="48.88671875" style="2" customWidth="1"/>
+    <col min="13" max="13" width="72.6640625" style="2" customWidth="1"/>
+    <col min="14" max="14" width="43.88671875" style="2" customWidth="1"/>
+    <col min="15" max="15" width="7.77734375" style="2" customWidth="1"/>
     <col min="16" max="16" width="56.77734375" style="2" customWidth="1"/>
     <col min="17" max="17" width="46.77734375" style="2" customWidth="1"/>
     <col min="18" max="18" width="62.88671875" style="2" customWidth="1"/>
-    <col min="19" max="19" width="49.21875" style="1" customWidth="1"/>
-    <col min="20" max="20" width="8.77734375" style="8"/>
+    <col min="19" max="19" width="49.21875" style="2" customWidth="1"/>
+    <col min="20" max="20" width="8.77734375" style="2"/>
     <col min="21" max="21" width="67.77734375" style="2" customWidth="1"/>
-    <col min="22" max="22" width="68.33203125" style="1" customWidth="1"/>
-    <col min="23" max="24" width="59.33203125" style="1" customWidth="1"/>
-    <col min="25" max="25" width="59.6640625" style="1" customWidth="1"/>
-    <col min="26" max="26" width="99.44140625" style="1" customWidth="1"/>
-    <col min="27" max="27" width="41.21875" style="1" customWidth="1"/>
-    <col min="28" max="16384" width="8.77734375" style="1"/>
+    <col min="22" max="22" width="68.33203125" style="2" customWidth="1"/>
+    <col min="23" max="24" width="59.33203125" style="2" customWidth="1"/>
+    <col min="25" max="25" width="59.6640625" style="2" customWidth="1"/>
+    <col min="26" max="26" width="99.44140625" style="2" customWidth="1"/>
+    <col min="27" max="27" width="41.21875" style="2" customWidth="1"/>
+    <col min="28" max="16384" width="8.77734375" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A2" s="3"/>
-      <c r="B2" s="5"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
-      <c r="N2" s="3"/>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="5"/>
-      <c r="R2" s="5"/>
-      <c r="S2" s="5"/>
-      <c r="U2" s="5"/>
-    </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="61" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="53" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="53" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="53" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="53" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="53" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" s="51" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="E16" s="52"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="9"/>
-      <c r="D3" s="26" t="s">
+      <c r="C17" s="9"/>
+      <c r="D17" s="26" t="s">
         <v>113</v>
       </c>
-      <c r="P3" s="1"/>
-      <c r="U3" s="1"/>
-      <c r="V3" s="2"/>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A4" s="20" t="s">
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-    </row>
-    <row r="5" spans="1:22" ht="72" x14ac:dyDescent="0.3">
-      <c r="A5" s="9"/>
-      <c r="B5" s="19" t="s">
-        <v>125</v>
-      </c>
-      <c r="C5" s="19" t="s">
-        <v>126</v>
-      </c>
-      <c r="D5" s="9"/>
-    </row>
-    <row r="6" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A6" s="21" t="s">
-        <v>130</v>
-      </c>
-      <c r="B6" s="50" t="s">
-        <v>237</v>
-      </c>
-      <c r="D6" s="9"/>
-    </row>
-    <row r="7" spans="1:22" ht="72" x14ac:dyDescent="0.3">
-      <c r="A7" s="9"/>
-      <c r="B7" s="19" t="s">
-        <v>124</v>
-      </c>
-      <c r="C7" s="19" t="s">
-        <v>123</v>
-      </c>
-      <c r="D7" s="9"/>
-    </row>
-    <row r="8" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A8" s="21" t="s">
-        <v>129</v>
-      </c>
-      <c r="B8" s="50" t="s">
-        <v>237</v>
-      </c>
-      <c r="C8" s="1"/>
-      <c r="D8" s="9"/>
-    </row>
-    <row r="9" spans="1:22" ht="144" x14ac:dyDescent="0.3">
-      <c r="A9" s="9"/>
-      <c r="B9" s="19"/>
-      <c r="C9" s="19" t="s">
-        <v>128</v>
-      </c>
-      <c r="D9" s="9"/>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A10" s="30" t="s">
-        <v>239</v>
-      </c>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-    </row>
-    <row r="11" spans="1:22" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A11" s="9"/>
-      <c r="B11" s="48" t="s">
-        <v>238</v>
-      </c>
-      <c r="C11" s="48" t="s">
-        <v>236</v>
-      </c>
-      <c r="D11" s="19" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A12" s="37" t="s">
-        <v>240</v>
-      </c>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A13" s="9"/>
-      <c r="B13" s="48" t="s">
-        <v>241</v>
-      </c>
-      <c r="C13" s="48" t="s">
-        <v>244</v>
-      </c>
-      <c r="D13" s="9"/>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A14" s="51" t="s">
-        <v>242</v>
-      </c>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-    </row>
-    <row r="15" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A15" s="9"/>
-      <c r="B15" s="48" t="s">
-        <v>245</v>
-      </c>
-      <c r="C15" s="48" t="s">
-        <v>243</v>
-      </c>
-      <c r="D15" s="9"/>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A16" s="9"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-    </row>
-    <row r="17" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="9"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
-      <c r="K17" s="1"/>
-      <c r="L17" s="1"/>
-      <c r="M17" s="1"/>
-      <c r="N17" s="1"/>
-      <c r="P17" s="2"/>
-      <c r="Q17" s="2"/>
-      <c r="R17" s="2"/>
-      <c r="S17" s="1"/>
-      <c r="T17" s="8"/>
-      <c r="U17" s="2"/>
-      <c r="V17" s="1"/>
-    </row>
-    <row r="18" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="9"/>
       <c r="B18" s="9"/>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
-      <c r="K18" s="1"/>
-      <c r="L18" s="1"/>
-      <c r="M18" s="1"/>
-      <c r="N18" s="1"/>
-      <c r="P18" s="2"/>
-      <c r="Q18" s="2"/>
-      <c r="R18" s="2"/>
-      <c r="S18" s="1"/>
-      <c r="T18" s="8"/>
-      <c r="U18" s="2"/>
-      <c r="V18" s="1"/>
-    </row>
-    <row r="19" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="A19" s="9"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
+      <c r="B19" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="C19" s="19" t="s">
+        <v>126</v>
+      </c>
       <c r="D19" s="9"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
-      <c r="K19" s="1"/>
-      <c r="L19" s="1"/>
-      <c r="M19" s="1"/>
-      <c r="N19" s="1"/>
-      <c r="P19" s="2"/>
-      <c r="Q19" s="2"/>
-      <c r="R19" s="2"/>
-      <c r="S19" s="1"/>
-      <c r="T19" s="8"/>
-      <c r="U19" s="2"/>
-      <c r="V19" s="1"/>
-    </row>
-    <row r="20" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="9"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
+    </row>
+    <row r="20" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A20" s="60" t="s">
+        <v>130</v>
+      </c>
+      <c r="B20" s="49" t="s">
+        <v>237</v>
+      </c>
+      <c r="C20" s="4"/>
       <c r="D20" s="9"/>
-      <c r="F20" s="1"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
-      <c r="K20" s="1"/>
-      <c r="L20" s="1"/>
-      <c r="M20" s="1"/>
-      <c r="N20" s="1"/>
-      <c r="P20" s="2"/>
-      <c r="Q20" s="2"/>
-      <c r="R20" s="2"/>
-      <c r="S20" s="1"/>
-      <c r="T20" s="8"/>
-      <c r="U20" s="2"/>
-      <c r="V20" s="1"/>
-    </row>
-    <row r="21" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="A21" s="9"/>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
+      <c r="B21" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="C21" s="19" t="s">
+        <v>123</v>
+      </c>
       <c r="D21" s="9"/>
-      <c r="F21" s="1"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="1"/>
-      <c r="I21" s="1"/>
-      <c r="K21" s="1"/>
-      <c r="L21" s="1"/>
-      <c r="M21" s="1"/>
-      <c r="N21" s="1"/>
-      <c r="P21" s="2"/>
-      <c r="Q21" s="2"/>
-      <c r="R21" s="2"/>
-      <c r="S21" s="1"/>
-      <c r="T21" s="8"/>
-      <c r="U21" s="2"/>
-      <c r="V21" s="1"/>
-    </row>
-    <row r="22" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="9"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
+    </row>
+    <row r="22" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A22" s="21" t="s">
+        <v>129</v>
+      </c>
+      <c r="B22" s="49" t="s">
+        <v>237</v>
+      </c>
+      <c r="C22" s="1"/>
       <c r="D22" s="9"/>
-      <c r="F22" s="1"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="1"/>
-      <c r="I22" s="1"/>
-      <c r="K22" s="1"/>
-      <c r="L22" s="1"/>
-      <c r="M22" s="1"/>
-      <c r="N22" s="1"/>
-      <c r="P22" s="2"/>
-      <c r="Q22" s="2"/>
-      <c r="R22" s="2"/>
-      <c r="S22" s="1"/>
-      <c r="T22" s="8"/>
-      <c r="U22" s="2"/>
-      <c r="V22" s="1"/>
-    </row>
-    <row r="23" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="23" spans="1:4" ht="144" x14ac:dyDescent="0.3">
       <c r="A23" s="9"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
+      <c r="B23" s="19"/>
+      <c r="C23" s="19" t="s">
+        <v>128</v>
+      </c>
       <c r="D23" s="9"/>
-      <c r="F23" s="1"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="1"/>
-      <c r="I23" s="1"/>
-      <c r="K23" s="1"/>
-      <c r="L23" s="1"/>
-      <c r="M23" s="1"/>
-      <c r="N23" s="1"/>
-      <c r="P23" s="2"/>
-      <c r="Q23" s="2"/>
-      <c r="R23" s="2"/>
-      <c r="S23" s="1"/>
-      <c r="T23" s="8"/>
-      <c r="U23" s="2"/>
-      <c r="V23" s="1"/>
-    </row>
-    <row r="24" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="9"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" s="37" t="s">
+        <v>240</v>
+      </c>
       <c r="B24" s="9"/>
       <c r="C24" s="9"/>
       <c r="D24" s="9"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="1"/>
-      <c r="I24" s="1"/>
-      <c r="K24" s="1"/>
-      <c r="L24" s="1"/>
-      <c r="M24" s="1"/>
-      <c r="N24" s="1"/>
-      <c r="P24" s="2"/>
-      <c r="Q24" s="2"/>
-      <c r="R24" s="2"/>
-      <c r="S24" s="1"/>
-      <c r="T24" s="8"/>
-      <c r="U24" s="2"/>
-      <c r="V24" s="1"/>
-    </row>
-    <row r="25" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="9"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
+      <c r="B25" s="48" t="s">
+        <v>241</v>
+      </c>
+      <c r="C25" s="48" t="s">
+        <v>244</v>
+      </c>
       <c r="D25" s="9"/>
-      <c r="F25" s="1"/>
-      <c r="G25" s="2"/>
-      <c r="H25" s="1"/>
-      <c r="I25" s="1"/>
-      <c r="K25" s="1"/>
-      <c r="L25" s="1"/>
-      <c r="M25" s="1"/>
-      <c r="N25" s="1"/>
-      <c r="P25" s="2"/>
-      <c r="Q25" s="2"/>
-      <c r="R25" s="2"/>
-      <c r="S25" s="1"/>
-      <c r="T25" s="8"/>
-      <c r="U25" s="2"/>
-      <c r="V25" s="1"/>
-    </row>
-    <row r="26" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="9"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" s="50" t="s">
+        <v>242</v>
+      </c>
       <c r="B26" s="9"/>
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
-      <c r="F26" s="1"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="1"/>
-      <c r="I26" s="1"/>
-      <c r="K26" s="1"/>
-      <c r="L26" s="1"/>
-      <c r="M26" s="1"/>
-      <c r="N26" s="1"/>
-      <c r="P26" s="2"/>
-      <c r="Q26" s="2"/>
-      <c r="R26" s="2"/>
-      <c r="S26" s="1"/>
-      <c r="T26" s="8"/>
-      <c r="U26" s="2"/>
-      <c r="V26" s="1"/>
-    </row>
-    <row r="27" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="27" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A27" s="9"/>
-      <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
+      <c r="B27" s="48" t="s">
+        <v>245</v>
+      </c>
+      <c r="C27" s="48" t="s">
+        <v>243</v>
+      </c>
       <c r="D27" s="9"/>
-      <c r="F27" s="1"/>
-      <c r="G27" s="2"/>
-      <c r="H27" s="1"/>
-      <c r="I27" s="1"/>
-      <c r="K27" s="1"/>
-      <c r="L27" s="1"/>
-      <c r="M27" s="1"/>
-      <c r="N27" s="1"/>
-      <c r="P27" s="2"/>
-      <c r="Q27" s="2"/>
-      <c r="R27" s="2"/>
-      <c r="S27" s="1"/>
-      <c r="T27" s="8"/>
-      <c r="U27" s="2"/>
-      <c r="V27" s="1"/>
-    </row>
-    <row r="28" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="9"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" s="30" t="s">
+        <v>239</v>
+      </c>
       <c r="B28" s="9"/>
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
-      <c r="F28" s="1"/>
-      <c r="G28" s="2"/>
-      <c r="H28" s="1"/>
-      <c r="I28" s="1"/>
-      <c r="K28" s="1"/>
-      <c r="L28" s="1"/>
-      <c r="M28" s="1"/>
-      <c r="N28" s="1"/>
-      <c r="P28" s="2"/>
-      <c r="Q28" s="2"/>
-      <c r="R28" s="2"/>
-      <c r="S28" s="1"/>
-      <c r="T28" s="8"/>
-      <c r="U28" s="2"/>
-      <c r="V28" s="1"/>
-    </row>
-    <row r="29" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="29" spans="1:4" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A29" s="9"/>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-      <c r="F29" s="1"/>
-      <c r="G29" s="2"/>
-      <c r="H29" s="1"/>
-      <c r="I29" s="1"/>
-      <c r="K29" s="1"/>
-      <c r="L29" s="1"/>
-      <c r="M29" s="1"/>
-      <c r="N29" s="1"/>
-      <c r="P29" s="2"/>
-      <c r="Q29" s="2"/>
-      <c r="R29" s="2"/>
-      <c r="S29" s="1"/>
-      <c r="T29" s="8"/>
-      <c r="U29" s="2"/>
-      <c r="V29" s="1"/>
-    </row>
-    <row r="30" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="9"/>
-      <c r="B30" s="9"/>
-      <c r="C30" s="9"/>
-      <c r="D30" s="9"/>
-      <c r="F30" s="1"/>
-      <c r="G30" s="2"/>
-      <c r="H30" s="1"/>
-      <c r="I30" s="1"/>
-      <c r="K30" s="1"/>
-      <c r="L30" s="1"/>
-      <c r="M30" s="1"/>
-      <c r="N30" s="1"/>
-      <c r="P30" s="2"/>
-      <c r="Q30" s="2"/>
-      <c r="R30" s="2"/>
-      <c r="S30" s="1"/>
-      <c r="T30" s="8"/>
-      <c r="U30" s="2"/>
-      <c r="V30" s="1"/>
-    </row>
-    <row r="31" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="9"/>
-      <c r="B31" s="9"/>
-      <c r="C31" s="9"/>
-      <c r="D31" s="9"/>
-      <c r="F31" s="1"/>
-      <c r="G31" s="2"/>
-      <c r="H31" s="1"/>
-      <c r="I31" s="1"/>
-      <c r="K31" s="1"/>
-      <c r="L31" s="1"/>
-      <c r="M31" s="1"/>
-      <c r="N31" s="1"/>
-      <c r="P31" s="2"/>
-      <c r="Q31" s="2"/>
-      <c r="R31" s="2"/>
-      <c r="S31" s="1"/>
-      <c r="T31" s="8"/>
-      <c r="U31" s="2"/>
-      <c r="V31" s="1"/>
-    </row>
-    <row r="32" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="9"/>
-      <c r="B32" s="9"/>
-      <c r="C32" s="9"/>
+      <c r="B29" s="48" t="s">
+        <v>238</v>
+      </c>
+      <c r="C29" s="48" t="s">
+        <v>236</v>
+      </c>
+      <c r="D29" s="19" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30" s="60" t="s">
+        <v>355</v>
+      </c>
+      <c r="B30" s="57" t="s">
+        <v>351</v>
+      </c>
+      <c r="C30" s="58" t="s">
+        <v>353</v>
+      </c>
+      <c r="D30" s="58" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A31" s="64" t="s">
+        <v>379</v>
+      </c>
+      <c r="B31" s="56" t="s">
+        <v>352</v>
+      </c>
+      <c r="C31" s="56" t="s">
+        <v>354</v>
+      </c>
+      <c r="D31" s="56" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="144" x14ac:dyDescent="0.3">
+      <c r="A32" s="64" t="s">
+        <v>380</v>
+      </c>
+      <c r="B32" s="56" t="s">
+        <v>358</v>
+      </c>
+      <c r="C32" s="56" t="s">
+        <v>356</v>
+      </c>
       <c r="D32" s="9"/>
-      <c r="F32" s="1"/>
-      <c r="G32" s="2"/>
-      <c r="H32" s="1"/>
-      <c r="I32" s="1"/>
-      <c r="K32" s="1"/>
-      <c r="L32" s="1"/>
-      <c r="M32" s="1"/>
-      <c r="N32" s="1"/>
-      <c r="P32" s="2"/>
-      <c r="Q32" s="2"/>
-      <c r="R32" s="2"/>
-      <c r="S32" s="1"/>
-      <c r="T32" s="8"/>
-      <c r="U32" s="2"/>
-      <c r="V32" s="1"/>
-    </row>
-    <row r="33" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="9"/>
-      <c r="B33" s="9"/>
-      <c r="C33" s="9"/>
-      <c r="D33" s="9"/>
-      <c r="F33" s="1"/>
-      <c r="G33" s="2"/>
-      <c r="H33" s="1"/>
-      <c r="I33" s="1"/>
-      <c r="K33" s="1"/>
-      <c r="L33" s="1"/>
-      <c r="M33" s="1"/>
-      <c r="N33" s="1"/>
-      <c r="P33" s="2"/>
-      <c r="Q33" s="2"/>
-      <c r="R33" s="2"/>
-      <c r="S33" s="1"/>
-      <c r="T33" s="8"/>
-      <c r="U33" s="2"/>
-      <c r="V33" s="1"/>
-    </row>
-    <row r="34" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="9"/>
-      <c r="B34" s="9"/>
-      <c r="C34" s="9"/>
-      <c r="D34" s="9"/>
-      <c r="F34" s="1"/>
-      <c r="G34" s="2"/>
-      <c r="H34" s="1"/>
-      <c r="I34" s="1"/>
-      <c r="K34" s="1"/>
-      <c r="L34" s="1"/>
-      <c r="M34" s="1"/>
-      <c r="N34" s="1"/>
-      <c r="P34" s="2"/>
-      <c r="Q34" s="2"/>
-      <c r="R34" s="2"/>
-      <c r="S34" s="1"/>
-      <c r="T34" s="8"/>
-      <c r="U34" s="2"/>
-      <c r="V34" s="1"/>
-    </row>
-    <row r="35" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="9"/>
-      <c r="B35" s="9"/>
-      <c r="C35" s="9"/>
-      <c r="D35" s="9"/>
-      <c r="F35" s="1"/>
-      <c r="G35" s="2"/>
-      <c r="H35" s="1"/>
-      <c r="I35" s="1"/>
-      <c r="K35" s="1"/>
-      <c r="L35" s="1"/>
-      <c r="M35" s="1"/>
-      <c r="N35" s="1"/>
-      <c r="P35" s="2"/>
-      <c r="Q35" s="2"/>
-      <c r="R35" s="2"/>
-      <c r="S35" s="1"/>
-      <c r="T35" s="8"/>
-      <c r="U35" s="2"/>
-      <c r="V35" s="1"/>
-    </row>
-    <row r="36" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="9"/>
-      <c r="B36" s="9"/>
-      <c r="C36" s="9"/>
-      <c r="D36" s="9"/>
-      <c r="F36" s="1"/>
-      <c r="G36" s="2"/>
-      <c r="H36" s="1"/>
-      <c r="I36" s="1"/>
-      <c r="K36" s="1"/>
-      <c r="L36" s="1"/>
-      <c r="M36" s="1"/>
-      <c r="N36" s="1"/>
-      <c r="P36" s="2"/>
-      <c r="Q36" s="2"/>
-      <c r="R36" s="2"/>
-      <c r="S36" s="1"/>
-      <c r="T36" s="8"/>
-      <c r="U36" s="2"/>
-      <c r="V36" s="1"/>
-    </row>
-    <row r="37" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="9"/>
-      <c r="B37" s="9"/>
-      <c r="C37" s="9"/>
-      <c r="D37" s="9"/>
-      <c r="F37" s="1"/>
-      <c r="G37" s="2"/>
-      <c r="H37" s="1"/>
-      <c r="I37" s="1"/>
-      <c r="K37" s="1"/>
-      <c r="L37" s="1"/>
-      <c r="M37" s="1"/>
-      <c r="N37" s="1"/>
-      <c r="P37" s="2"/>
-      <c r="Q37" s="2"/>
-      <c r="R37" s="2"/>
-      <c r="S37" s="1"/>
-      <c r="T37" s="8"/>
-      <c r="U37" s="2"/>
-      <c r="V37" s="1"/>
-    </row>
-    <row r="38" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="9"/>
-      <c r="B38" s="9"/>
-      <c r="C38" s="9"/>
-      <c r="D38" s="9"/>
-      <c r="F38" s="1"/>
-      <c r="G38" s="2"/>
-      <c r="H38" s="1"/>
-      <c r="I38" s="1"/>
-      <c r="K38" s="1"/>
-      <c r="L38" s="1"/>
-      <c r="M38" s="1"/>
-      <c r="N38" s="1"/>
-      <c r="P38" s="2"/>
-      <c r="Q38" s="2"/>
-      <c r="R38" s="2"/>
-      <c r="S38" s="1"/>
-      <c r="T38" s="8"/>
-      <c r="U38" s="2"/>
-      <c r="V38" s="1"/>
-    </row>
-    <row r="39" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="9"/>
-      <c r="B39" s="9"/>
-      <c r="C39" s="9"/>
-      <c r="D39" s="9"/>
-      <c r="F39" s="1"/>
-      <c r="G39" s="2"/>
-      <c r="H39" s="1"/>
-      <c r="I39" s="1"/>
-      <c r="K39" s="1"/>
-      <c r="L39" s="1"/>
-      <c r="M39" s="1"/>
-      <c r="N39" s="1"/>
-      <c r="P39" s="2"/>
-      <c r="Q39" s="2"/>
-      <c r="R39" s="2"/>
-      <c r="S39" s="1"/>
-      <c r="T39" s="8"/>
-      <c r="U39" s="2"/>
-      <c r="V39" s="1"/>
-    </row>
-    <row r="40" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="9"/>
-      <c r="B40" s="9"/>
-      <c r="C40" s="9"/>
-      <c r="D40" s="9"/>
-      <c r="F40" s="1"/>
-      <c r="G40" s="2"/>
-      <c r="H40" s="1"/>
-      <c r="I40" s="1"/>
-      <c r="K40" s="1"/>
-      <c r="L40" s="1"/>
-      <c r="M40" s="1"/>
-      <c r="N40" s="1"/>
-      <c r="P40" s="2"/>
-      <c r="Q40" s="2"/>
-      <c r="R40" s="2"/>
-      <c r="S40" s="1"/>
-      <c r="T40" s="8"/>
-      <c r="U40" s="2"/>
-      <c r="V40" s="1"/>
-    </row>
-    <row r="41" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="9"/>
-      <c r="B41" s="9"/>
-      <c r="C41" s="9"/>
-      <c r="D41" s="9"/>
-      <c r="F41" s="1"/>
-      <c r="G41" s="2"/>
-      <c r="H41" s="1"/>
-      <c r="I41" s="1"/>
-      <c r="K41" s="1"/>
-      <c r="L41" s="1"/>
-      <c r="M41" s="1"/>
-      <c r="N41" s="1"/>
-      <c r="P41" s="2"/>
-      <c r="Q41" s="2"/>
-      <c r="R41" s="2"/>
-      <c r="S41" s="1"/>
-      <c r="T41" s="8"/>
-      <c r="U41" s="2"/>
-      <c r="V41" s="1"/>
-    </row>
-    <row r="42" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="9"/>
-      <c r="B42" s="9"/>
-      <c r="C42" s="9"/>
-      <c r="D42" s="9"/>
-      <c r="F42" s="1"/>
-      <c r="G42" s="2"/>
-      <c r="H42" s="1"/>
-      <c r="I42" s="1"/>
-      <c r="K42" s="1"/>
-      <c r="L42" s="1"/>
-      <c r="M42" s="1"/>
-      <c r="N42" s="1"/>
-      <c r="P42" s="2"/>
-      <c r="Q42" s="2"/>
-      <c r="R42" s="2"/>
-      <c r="S42" s="1"/>
-      <c r="T42" s="8"/>
-      <c r="U42" s="2"/>
-      <c r="V42" s="1"/>
-    </row>
-    <row r="43" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="9"/>
-      <c r="B43" s="9"/>
-      <c r="C43" s="9"/>
-      <c r="D43" s="9"/>
-      <c r="F43" s="1"/>
-      <c r="G43" s="2"/>
-      <c r="H43" s="1"/>
-      <c r="I43" s="1"/>
-      <c r="K43" s="1"/>
-      <c r="L43" s="1"/>
-      <c r="M43" s="1"/>
-      <c r="N43" s="1"/>
-      <c r="P43" s="2"/>
-      <c r="Q43" s="2"/>
-      <c r="R43" s="2"/>
-      <c r="S43" s="1"/>
-      <c r="T43" s="8"/>
-      <c r="U43" s="2"/>
-      <c r="V43" s="1"/>
-    </row>
-    <row r="44" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="9"/>
-      <c r="B44" s="9"/>
-      <c r="C44" s="9"/>
-      <c r="D44" s="9"/>
-      <c r="F44" s="1"/>
-      <c r="G44" s="2"/>
-      <c r="H44" s="1"/>
-      <c r="I44" s="1"/>
-      <c r="K44" s="1"/>
-      <c r="L44" s="1"/>
-      <c r="M44" s="1"/>
-      <c r="N44" s="1"/>
-      <c r="P44" s="2"/>
-      <c r="Q44" s="2"/>
-      <c r="R44" s="2"/>
-      <c r="S44" s="1"/>
-      <c r="T44" s="8"/>
-      <c r="U44" s="2"/>
-      <c r="V44" s="1"/>
-    </row>
-    <row r="45" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="9"/>
-      <c r="B45" s="9"/>
-      <c r="C45" s="9"/>
-      <c r="D45" s="9"/>
-      <c r="F45" s="1"/>
-      <c r="G45" s="2"/>
-      <c r="H45" s="1"/>
-      <c r="I45" s="1"/>
-      <c r="K45" s="1"/>
-      <c r="L45" s="1"/>
-      <c r="M45" s="1"/>
-      <c r="N45" s="1"/>
-      <c r="P45" s="2"/>
-      <c r="Q45" s="2"/>
-      <c r="R45" s="2"/>
-      <c r="S45" s="1"/>
-      <c r="T45" s="8"/>
-      <c r="U45" s="2"/>
-      <c r="V45" s="1"/>
-    </row>
-    <row r="46" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="9"/>
-      <c r="B46" s="9"/>
-      <c r="C46" s="9"/>
-      <c r="D46" s="9"/>
-      <c r="F46" s="1"/>
-      <c r="G46" s="2"/>
-      <c r="H46" s="1"/>
-      <c r="I46" s="1"/>
-      <c r="K46" s="1"/>
-      <c r="L46" s="1"/>
-      <c r="M46" s="1"/>
-      <c r="N46" s="1"/>
-      <c r="P46" s="2"/>
-      <c r="Q46" s="2"/>
-      <c r="R46" s="2"/>
-      <c r="S46" s="1"/>
-      <c r="T46" s="8"/>
-      <c r="U46" s="2"/>
-      <c r="V46" s="1"/>
-    </row>
-    <row r="47" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="9"/>
-      <c r="B47" s="9"/>
-      <c r="C47" s="9"/>
-      <c r="D47" s="9"/>
-      <c r="F47" s="1"/>
-      <c r="G47" s="2"/>
-      <c r="H47" s="1"/>
-      <c r="I47" s="1"/>
-      <c r="K47" s="1"/>
-      <c r="L47" s="1"/>
-      <c r="M47" s="1"/>
-      <c r="N47" s="1"/>
-      <c r="P47" s="2"/>
-      <c r="Q47" s="2"/>
-      <c r="R47" s="2"/>
-      <c r="S47" s="1"/>
-      <c r="T47" s="8"/>
-      <c r="U47" s="2"/>
-      <c r="V47" s="1"/>
-    </row>
-    <row r="48" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="9"/>
-      <c r="B48" s="9"/>
-      <c r="C48" s="9"/>
-      <c r="D48" s="9"/>
-      <c r="F48" s="1"/>
-      <c r="G48" s="2"/>
-      <c r="H48" s="1"/>
-      <c r="I48" s="1"/>
-      <c r="K48" s="1"/>
-      <c r="L48" s="1"/>
-      <c r="M48" s="1"/>
-      <c r="N48" s="1"/>
-      <c r="P48" s="2"/>
-      <c r="Q48" s="2"/>
-      <c r="R48" s="2"/>
-      <c r="S48" s="1"/>
-      <c r="T48" s="8"/>
-      <c r="U48" s="2"/>
-      <c r="V48" s="1"/>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33" s="60" t="s">
+        <v>359</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A34" s="57" t="s">
+        <v>370</v>
+      </c>
+      <c r="B34" s="62" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A35" s="64" t="s">
+        <v>359</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="D35" s="62" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A36" s="64" t="s">
+        <v>381</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="D36" s="62" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A37" s="55" t="s">
+        <v>369</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="144" x14ac:dyDescent="0.3">
+      <c r="A38" s="63" t="s">
+        <v>376</v>
+      </c>
+      <c r="B38" s="62" t="s">
+        <v>372</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="144" x14ac:dyDescent="0.3">
+      <c r="A39" s="64" t="s">
+        <v>375</v>
+      </c>
+      <c r="B39" s="62" t="s">
+        <v>373</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A40" s="55" t="s">
+        <v>377</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A41" s="63" t="s">
+        <v>391</v>
+      </c>
+      <c r="B41" s="62" t="s">
+        <v>378</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="D41" s="62" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A42" s="55" t="s">
+        <v>388</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A43" s="64" t="s">
+        <v>393</v>
+      </c>
+      <c r="B43" s="62" t="s">
+        <v>394</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A44" s="55" t="s">
+        <v>390</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A45" s="62" t="s">
+        <v>397</v>
+      </c>
+      <c r="B45" s="62" t="s">
+        <v>416</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="144" x14ac:dyDescent="0.3">
+      <c r="A46" s="64" t="s">
+        <v>396</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A47" s="55" t="s">
+        <v>398</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A48" s="65" t="s">
+        <v>401</v>
+      </c>
+      <c r="B48" s="62" t="s">
+        <v>418</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A49" s="64" t="s">
+        <v>415</v>
+      </c>
+      <c r="B49" s="62" t="s">
+        <v>419</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="A50" s="64" t="s">
+        <v>421</v>
+      </c>
+      <c r="B50" s="68" t="s">
+        <v>421</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A51" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="B51" s="66" t="s">
+        <v>410</v>
+      </c>
+      <c r="C51" s="62" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="B52" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A53" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="B53" s="67" t="s">
+        <v>411</v>
+      </c>
+      <c r="C53" s="62" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A54" s="55" t="s">
+        <v>412</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="B55" s="62" t="s">
+        <v>425</v>
+      </c>
+      <c r="C55" s="64" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" ht="216" x14ac:dyDescent="0.3">
+      <c r="B56" s="62" t="s">
+        <v>414</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" ht="288" x14ac:dyDescent="0.3">
+      <c r="B57" s="62" t="s">
+        <v>424</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A58" s="2" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A59" s="2" t="s">
+        <v>428</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="D3" r:id="rId1" location=":~:text=%D0%A1%D0%BE%D0%B7%D0%B4%D0%B0%D0%BD%D0%B8%D0%B5%20%D0%B8%20%D1%83%D0%B4%D0%B0%D0%BB%D0%B5%D0%BD%D0%B8%D0%B5%20%D1%82%D0%B0%D0%B1%D0%BB%D0%B8%D1%86" xr:uid="{EBAD4F4A-49BC-45EE-B388-4866E40CC60C}"/>
+    <hyperlink ref="D17" r:id="rId1" location=":~:text=%D0%A1%D0%BE%D0%B7%D0%B4%D0%B0%D0%BD%D0%B8%D0%B5%20%D0%B8%20%D1%83%D0%B4%D0%B0%D0%BB%D0%B5%D0%BD%D0%B8%D0%B5%20%D1%82%D0%B0%D0%B1%D0%BB%D0%B8%D1%86" xr:uid="{99C85CF6-B702-4857-9551-C40F16D93FED}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId2"/>
@@ -14796,7 +17468,7 @@
       <c r="B8" s="42" t="s">
         <v>222</v>
       </c>
-      <c r="C8" s="42" t="s">
+      <c r="C8" s="69" t="s">
         <v>224</v>
       </c>
       <c r="D8" s="9"/>
@@ -17040,7 +19712,7 @@
     <col min="2" max="2" width="50.5546875" style="2" customWidth="1"/>
     <col min="3" max="3" width="71.21875" style="2" customWidth="1"/>
     <col min="4" max="4" width="56.44140625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="6.21875" style="53" customWidth="1"/>
+    <col min="5" max="5" width="6.21875" style="52" customWidth="1"/>
     <col min="6" max="6" width="43.21875" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="55.109375" style="2" customWidth="1"/>
     <col min="8" max="8" width="67.88671875" style="2" customWidth="1"/>
@@ -17065,8 +19737,8 @@
     <col min="28" max="16384" width="8.77734375" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:5" s="52" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="E2" s="53"/>
+    <row r="2" spans="1:5" s="51" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="E2" s="52"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">

--- a/4 четверть_MSSQL.xlsx
+++ b/4 четверть_MSSQL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlexServHW\Desktop\GB_Developer_Workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2C1AC8B-F84B-406A-B377-3B25079CC0B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08754BB9-4733-4EB6-BE8D-E42F108A8146}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="180" yWindow="-18390" windowWidth="18930" windowHeight="15885" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Изучить" sheetId="21" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="450">
   <si>
     <t>Урок 1 часть 1</t>
   </si>
@@ -9984,52 +9984,6 @@
     </r>
   </si>
   <si>
-    <t>CHECK(
- (Age &gt;0 AND Age&lt;100) 
-  AND (Email !='') 
-  AND (Phone !='')
-)</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Дополнительная возможность!</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>CHECK(Age &gt;0 AND Age &lt; 100)
-CHECK(Email !='')
-CHECK(Phone !='')</t>
-    </r>
-  </si>
-  <si>
     <t>CONSTRAINT</t>
   </si>
   <si>
@@ -10037,24 +9991,6 @@
   </si>
   <si>
     <t>`https://metanit.com/sql/sqlserver/3.4.php#:~:text=CONSTRAINT</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Дополнительная возможность! 
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">CONSTRAINT DF_Customer_Age DEFAULT 18 </t>
-    </r>
   </si>
   <si>
     <r>
@@ -10484,6 +10420,282 @@
     <t>FOREIGN KEY</t>
   </si>
   <si>
+    <t>Вариант записи 2</t>
+  </si>
+  <si>
+    <t>"PK_" - для PRIMARY KEY
+"FK_" - для FOREIGN KEY
+"CK_" - для CHECK
+"UQ_" - для UNIQUE
+"DF_" - для DEFAULT</t>
+  </si>
+  <si>
+    <t>Синтаксис</t>
+  </si>
+  <si>
+    <t>`https://metanit.com/sql/sqlserver/3.5.php</t>
+  </si>
+  <si>
+    <r>
+      <t>FOREIGN KEY (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>стобец1, столбец2, ... столбецN</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>) 
+    REFERENCES</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> главная_таблица</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(столбец_главной_таблицы1, столбец_главной_таблицы2, ... столбец_главной_таблицыN)</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    [ON DELETE {CASCADE|NO ACTION}]
+    [ON UPDATE {CASCADE|NO ACTION}]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Ограничение!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Хотя, как правило, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>внешний ключ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> указывает на </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>первичный ключ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> из связанной главной таблицы, но это </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>необязательно</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> должно быть непременным условием. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Внешний ключ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> также может указывать на какой-то другой столбец, который имеет </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(2)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>уникальное значение</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">CREATE TABLE </t>
     </r>
@@ -10491,7 +10703,7 @@
       <rPr>
         <b/>
         <sz val="11"/>
-        <color rgb="FF00B050"/>
+        <color rgb="FF7030A0"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="204"/>
@@ -10509,14 +10721,34 @@
       </rPr>
       <t xml:space="preserve">
 (
-    Id INT PRIMARY KEY,
     </t>
     </r>
     <r>
       <rPr>
         <b/>
         <sz val="11"/>
-        <color rgb="FFC00000"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Id</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> INT PRIMARY KEY,
+    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="204"/>
@@ -10636,669 +10868,35 @@
       <rPr>
         <b/>
         <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Rights</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(Id)  -- внешний ключ
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Rights(Id)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  -- внешний ключ
 );</t>
     </r>
   </si>
   <si>
     <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Пояснение!</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> это ограничение, которое обеспечивает ссылочную целостность между двумя таблицами. Оно гарантирует, что значение в одной таблице существует в другой таблице.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Дополнительная возможность!  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">✅ Нельзя </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">вставить продукт с CategoryId = 999, если нет категории с Id = 999
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>✅ Нельзя</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> удалить категорию, если на неё ссылаются продукты
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">✅ Нельзя </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>изменить Id категории, если на неё ссылаются</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">    CONSTRAINT PK_Orders PRIMARY KEY (OrderId),
-    CONSTRAINT FK_Orders_Customers FOREIGN KEY (CustomerId) REFERENCES Customers(Id),
-    CONSTRAINT UQ_Orders_Number UNIQUE (OrderId)</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Вариант записи 1</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Дополнительная возможность!</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Ключевое слово CHECK задает ограничение для диапазона значений, которые могут храниться в столбце.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Вариант записи 2
-Также с помощью CHECK можно создать ограничение в целом для таблицы
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Примечание по знаку неравенства!</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Может быть &lt;&gt; и !=</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Вариант записи 1</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="8"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Дополнительная возможность! </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-1 Понятные сообщения об ошибках
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>-- Без имени:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
--- "Violation of CHECK constraint </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>CK__Customers__Age__12345678</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">"
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>-- С именем:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
--- "Violation of CHECK constraint </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>CHK_Age_Range</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>"  ← сразу понятно, что не так</t>
-    </r>
-  </si>
-  <si>
-    <t>Вариант записи 2</t>
-  </si>
-  <si>
-    <t>"PK_" - для PRIMARY KEY
-"FK_" - для FOREIGN KEY
-"CK_" - для CHECK
-"UQ_" - для UNIQUE
-"DF_" - для DEFAULT</t>
-  </si>
-  <si>
-    <t>Синтаксис</t>
-  </si>
-  <si>
-    <t>`https://metanit.com/sql/sqlserver/3.5.php</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">CREATE TABLE Customers (
-    Id INT PRIMARY KEY,
-    Name NVARCHAR(100)
-);
-CREATE TABLE Orders (
-    Id INT PRIMARY KEY,
-    CustomerId INT,
-    OrderDate DATE,
-    </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">FOREIGN KEY (CustomerId) REFERENCES Customers(Id) </t>
+      <t xml:space="preserve">CREATE TABLE </t>
     </r>
     <r>
       <rPr>
         <b/>
         <sz val="11"/>
         <color rgb="FF7030A0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">связь </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF7030A0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>один клиент - много заказов</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-);
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">-- ❌ Не сработает
-INSERT INTO Orders VALUES (1, 999, '2024-01-01');
--- Сообщение: FOREIGN KEY constraint failed
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>-- ✅ Правильно
-INSERT INTO Customers VALUES (1, 'Иван');
-INSERT INTO Orders VALUES (1, 1, '2024-01-01');  -- Ok</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Дополнительно! </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Здесь связь one-to-many (один ко многим)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">:
-Один клиент → много заказов
-Один заказ → принадлежит одному клиенту
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Важно!</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Внешний ключ устанавливается для столбцов из </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF7030A0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>зависимой (one)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>подчиненной таблицы</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, и указывает на один из столбцов из </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>главной таблицы (many)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Ограничение!</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Хотя, как правило, внешний ключ указывает на первичный ключ из связанной главной таблицы, но это необязательно должно быть непременным условием. Внешний ключ также может указывать на какой-то другой столбец, который имеет уникальное значение.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Ограничение!</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Хотя, как правило, внешний ключ указывает на первичный ключ из связанной главной таблицы, но это необязательно должно быть непременным условием. Внешний ключ также может указывать на какой-то другой столбец, который имеет уникальное значение.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">CREATE TABLE </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="204"/>
@@ -11316,7 +10914,29 @@
       </rPr>
       <t xml:space="preserve">
 (
-    Id INT PRIMARY KEY,
+    </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Id</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> INT PRIMARY KEY,
     Name NVARCHAR(50)
 );
 -- Таблица с внешним ключом (дочерняя)
@@ -11411,25 +11031,13 @@
       <rPr>
         <b/>
         <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Categories</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(Id)</t>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Categories(Id)</t>
     </r>
     <r>
       <rPr>
@@ -11445,7 +11053,162 @@
   </si>
   <si>
     <r>
-      <t>[</t>
+      <t>Вариант записи 2</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Зачем нужен внешний ключ!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> это ограничение, которое обеспечивает ссылочную целостность между двумя таблицами. Оно гарантирует, что значение в одной таблице существует в другой таблице.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Дополнительная возможность!  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">✅ Нельзя </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">вставить продукт с CategoryId = 999, если нет категории с Id = 999
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>✅ Нельзя</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> удалить категорию, если на неё ссылаются продукты
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">✅ Нельзя </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>изменить Id категории, если на неё ссылаются</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Дополнительно! </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
     </r>
     <r>
       <rPr>
@@ -11457,6 +11220,1281 @@
         <charset val="204"/>
         <scheme val="minor"/>
       </rPr>
+      <t>Здесь связь one-to-many (один ко многим)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">:
+Один клиент → много заказов
+Один заказ → принадлежит одному клиенту
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Важно!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Внешний ключ устанавливается для столбцов из </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>зависимой (one)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>подчиненной таблицы</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, и указывает на один из столбцов из </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>главной таблицы (many)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Пояснение к примеру слева!</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+-- ❌ Не сработает
+INSERT INTO Orders VALUES (1, 999, '2024-01-01');
+-- Сообщение: FOREIGN KEY constraint failed
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">-- ✅ Правильно
+INSERT INTO Customers VALUES </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1, 'Иван'</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">;
+INSERT INTO Orders VALUES </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1, 1, '2024-01-01'</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>;  -- Ok</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">CREATE TABLE </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Customers</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (
+    Id INT PRIMARY KEY,
+    Name NVARCHAR(100)
+);
+CREATE TABLE </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Orders</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (
+    Id INT PRIMARY KEY,
+    OrderDate DATE,
+    </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CustomerId INT,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>FOREIGN KEY (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CustomerId</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">) REFERENCES </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Customers(Id)</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">связь </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>один Customer - много Orders</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">CREATE TABLE </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Customers</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+(
+    </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Id</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> INT PRIMARY KEY IDENTITY,
+    Age INT DEFAULT 18, 
+    FirstName NVARCHAR(20) NOT NULL,
+    LastName NVARCHAR(20) NOT NULL,
+    Email VARCHAR(30) UNIQUE,
+    Phone VARCHAR(20) UNIQUE
+);
+CREATE TABLE </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Orders</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+(
+    Id INT PRIMARY KEY IDENTITY,
+    </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CustomerId</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> INT REFERENCES </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Customers (Id)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>,
+    CreatedAt Date
+);</t>
+    </r>
+  </si>
+  <si>
+    <t>С помощью оператора CONSTRAINT можно задать имя для ограничения внешнего ключа. Обычно это имя начинается с префикса "FK_":</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">CREATE TABLE Orders
+(
+    Id INT PRIMARY KEY IDENTITY,
+    </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CustomerId</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> INT,
+    CreatedAt Date,
+    CONSTRAINT FK_Orders_To_Customers</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> FOREIGN KEY (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CustomerId</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">)  REFERENCES </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Customers (Id)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Вариант записи 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+CREATE TABLE </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Orders</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+(
+    Id INT PRIMARY KEY IDENTITY,
+    </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CustomerId</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>INT REFERENCES</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Customers (Id)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>,
+    CreatedAt Date
+);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Пояснение к примеру справа!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Здесь определены таблицы Customers и Orders. Customers является главной и представляет клиента. Orders является зависимой и представляет заказ, сделанный клиентом. Эта таблица через столбец CustomerId связана с таблицей Customers и ее столбцом Id. То есть столбец CustomerId является внешним ключом, который указывает на столбец Id из таблицы Customers.</t>
+    </r>
+  </si>
+  <si>
+    <t>Определение внешнего ключа на уровне таблицы выглядело бы следующим образом</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Вариант записи 2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+CREATE TABLE </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Products</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+(
+    Id INT PRIMARY KEY,
+    Name NVARCHAR(50),
+    </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CategoryId</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> INT,
+    </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>FOREIGN KEY (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CategoryId</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">) REFERENCES </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Categories(Id)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  -- внешний ключ
+);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Вариант записи 3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+CREATE TABLE Orders
+(
+    Id INT PRIMARY KEY IDENTITY,
+    </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CustomerId</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> INT,
+    CreatedAt Date,
+    </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CONSTRAINT FK_Orders_To_Customers FOREIGN KEY (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CustomerId</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">)  REFERENCES </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Customers (Id)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="8"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Дополнительная возможность! </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+1 Понятные сообщения об ошибках
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>-- Без имени:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+-- "Violation of CHECK constraint </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CK__Customers__Age__12345678</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">"
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>-- С именем:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+-- "Violation of CHECK constraint </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CHK_Age_Range</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"  ← сразу понятно, что не так</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Дополнительная возможность! 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Вариант записи 1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Дополнительная возможность!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Ключевое слово CHECK задает ограничение для диапазона значений, которые могут храниться в столбце.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Дополнительная возможность!
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Вариант записи 1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Также с помощью CHECK можно создать ограничение в целом для таблицы
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Примечание по знаку неравенства!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Может быть &lt;&gt; и !=</t>
+    </r>
+  </si>
+  <si>
+    <t>ON DELETE и ON UPDATE</t>
+  </si>
+  <si>
+    <t>С помощью выражений ON DELETE и ON UPDATE можно установить действия, которые выполняться соответственно при удалении и изменении связанной строки из главной таблицы. И для определения действия мы можем использовать следующие опции:</t>
+  </si>
+  <si>
+    <t>CASCADE</t>
+  </si>
+  <si>
+    <t>NO ACTION</t>
+  </si>
+  <si>
+    <t>SET NULL</t>
+  </si>
+  <si>
+    <t>SET DEFAULT</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>ON DELETE</t>
     </r>
     <r>
@@ -11467,13 +12505,680 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> {</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>при удалении</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> связанных строк </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>в главной таблице</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, предотвращает какие-либо действия</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> в зависимой таблице </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ON UPDATE</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> при изменении</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> связанных строк </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>в главной таблице</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, предотвращает какие-либо действия </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>в зависимой таблице</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> .</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ON DELETE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>при</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>удалении</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> связанных строк </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>в главной таблице</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> DELETE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>удаляет</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> строки из </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>зависимой таблицы</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ON UPDATE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>при</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>изменении</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> связанных строк </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>в главной таблице</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> UPDATE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>изменяет</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> строки из </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>зависимой таблицы</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">ON DELETE </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>при</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>удалении</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> связанной строки </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>из главной таблицы</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> устанавливает для столбца внешнего ключа </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>значение NULL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ON DELETE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>при</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>удалении</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> связанной строки </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>из главной таблицы</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> устанавливает для столбца внешнего ключа </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>значение по умолчанию</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, которое задается с помощью атрибуты DEFAULT. Если для столбца не задано значение по умолчанию, то в качестве него применяется значение NULL.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">CREATE TABLE Orders
+(
+    Id INT PRIMARY KEY IDENTITY,
+    CustomerId INT,
+    CreatedAt Date,
+    FOREIGN KEY (CustomerId) REFERENCES Customers (Id) </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">ON DELETE </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="204"/>
@@ -11489,105 +13194,18 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>|</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>NO ACTION</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>}]</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve"> [</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>ON UPDATE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> {</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>CASCADE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>|</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>NO ACTION</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>}]</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>FOREIGN KEY (</t>
+      <t xml:space="preserve">
+)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">CREATE TABLE Orders
+(
+    Id INT PRIMARY KEY IDENTITY,
+    CustomerId INT,
+    CreatedAt Date,
+    FOREIGN KEY (CustomerId) REFERENCES Customers (Id) </t>
     </r>
     <r>
       <rPr>
@@ -11599,41 +13217,122 @@
         <charset val="204"/>
         <scheme val="minor"/>
       </rPr>
-      <t>стобец1, столбец2, ... столбецN</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>) 
-    REFERENCES</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> главная_таблица</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
+      <t xml:space="preserve">ON DELETE </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SET NULL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Обязательно!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Чтобы</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> SET DEFAULT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> сработал, необходимо, чтобы </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>DEFAULT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> был объявлен в настройках таблицы
+CREATE TABLE Orders
+(
+    Id INT PRIMARY KEY IDENTITY,
+    CreatedAt Date,
+    </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CustomerId INT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -11642,40 +13341,128 @@
       <rPr>
         <b/>
         <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(столбец_главной_таблицы1, столбец_главной_таблицы2, ... столбец_главной_таблицыN)</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>DEFAULT 0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>,
+    FOREIGN KEY (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CustomerId</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">) REFERENCES Customers (Id) </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ON DELETE</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SET DEFAULT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-    [ON DELETE {CASCADE|NO ACTION}]
-    [ON UPDATE {CASCADE|NO ACTION}]</t>
-    </r>
+)</t>
+    </r>
+  </si>
+  <si>
+    <t>`https://metanit.com/sql/sqlserver/3.6.php</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALTER TABLE </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="37" x14ac:knownFonts="1">
+  <fonts count="39" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -11978,7 +13765,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="16">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -12069,6 +13856,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0070C0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -12081,9 +13880,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -12094,141 +13893,141 @@
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="13" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="10" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="10" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    <xf numFmtId="49" fontId="21" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    <xf numFmtId="49" fontId="20" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="30" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    <xf numFmtId="49" fontId="10" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="33" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="8" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="18" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="28" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="31" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="33" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="31" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="21" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -12246,43 +14045,55 @@
     <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="37" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="38" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="33" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="33" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="35" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="36" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="31" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="31" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="21" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -13007,8 +14818,8 @@
       <c r="A15" s="9"/>
       <c r="B15" s="48"/>
       <c r="C15" s="9"/>
-      <c r="D15" s="59" t="s">
-        <v>422</v>
+      <c r="D15" s="69" t="s">
+        <v>448</v>
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.3">
@@ -14939,7 +16750,7 @@
       <c r="B7" s="43" t="s">
         <v>205</v>
       </c>
-      <c r="C7" s="42" t="s">
+      <c r="C7" s="73" t="s">
         <v>204</v>
       </c>
       <c r="D7" s="42" t="s">
@@ -14949,7 +16760,7 @@
     <row r="8" spans="1:22" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A8" s="9"/>
       <c r="B8" s="9"/>
-      <c r="C8" s="42" t="s">
+      <c r="C8" s="73" t="s">
         <v>226</v>
       </c>
       <c r="D8" s="42" t="s">
@@ -16360,7 +18171,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="12" type="noConversion"/>
+  <phoneticPr fontId="14" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="D46" r:id="rId1" location=":~:text=%D0%A1%D0%BE%D0%B7%D0%B4%D0%B0%D0%BD%D0%B8%D0%B5%20%D0%B1%D0%B0%D0%B7%D1%8B%20%D0%B4%D0%B0%D0%BD%D0%BD%D1%8B%D1%85" xr:uid="{FDFE2116-2B22-4A87-B37D-3DFA9E8F9FE0}"/>
     <hyperlink ref="D44" r:id="rId2" location=":~:text=%D0%A1%D0%BE%D0%B7%D0%B4%D0%B0%D0%BD%D0%B8%D0%B5%20%D0%B1%D0%B0%D0%B7%D1%8B%20%D0%B4%D0%B0%D0%BD%D0%BD%D1%8B%D1%85%20%D0%B2%20SQL%20Management%20Studio" xr:uid="{5B701F02-CEF7-44EA-83C6-0E21D7145608}"/>
@@ -16833,7 +18644,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="12" type="noConversion"/>
+  <phoneticPr fontId="14" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
@@ -16844,7 +18655,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:E59"/>
+  <dimension ref="A2:E77"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="36" style="2" customWidth="1"/>
@@ -16877,7 +18688,7 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="61" t="s">
+      <c r="A2" s="60" t="s">
         <v>237</v>
       </c>
     </row>
@@ -16937,7 +18748,7 @@
       <c r="D19" s="9"/>
     </row>
     <row r="20" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A20" s="60" t="s">
+      <c r="A20" s="59" t="s">
         <v>130</v>
       </c>
       <c r="B20" s="49" t="s">
@@ -17011,321 +18822,465 @@
       <c r="D27" s="9"/>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28" s="30" t="s">
+      <c r="A28" s="72" t="s">
+        <v>449</v>
+      </c>
+      <c r="B28" s="48"/>
+      <c r="C28" s="48"/>
+      <c r="D28" s="9"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" s="9"/>
+      <c r="B29" s="48"/>
+      <c r="C29" s="48"/>
+      <c r="D29" s="9"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30" s="9"/>
+      <c r="B30" s="48"/>
+      <c r="C30" s="48"/>
+      <c r="D30" s="9"/>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31" s="9"/>
+      <c r="B31" s="48"/>
+      <c r="C31" s="48"/>
+      <c r="D31" s="9"/>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A32" s="9"/>
+      <c r="B32" s="48"/>
+      <c r="C32" s="48"/>
+      <c r="D32" s="9"/>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33" s="9"/>
+      <c r="B33" s="48"/>
+      <c r="C33" s="48"/>
+      <c r="D33" s="9"/>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A34" s="9"/>
+      <c r="B34" s="48"/>
+      <c r="C34" s="48"/>
+      <c r="D34" s="9"/>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A35" s="9"/>
+      <c r="B35" s="48"/>
+      <c r="C35" s="48"/>
+      <c r="D35" s="9"/>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A36" s="9"/>
+      <c r="B36" s="48"/>
+      <c r="C36" s="48"/>
+      <c r="D36" s="9"/>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A37" s="9"/>
+      <c r="B37" s="48"/>
+      <c r="C37" s="48"/>
+      <c r="D37" s="9"/>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A38" s="9"/>
+      <c r="B38" s="48"/>
+      <c r="C38" s="48"/>
+      <c r="D38" s="9"/>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A39" s="9"/>
+      <c r="B39" s="48"/>
+      <c r="C39" s="48"/>
+      <c r="D39" s="9"/>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A40" s="30" t="s">
         <v>239</v>
       </c>
-      <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
-      <c r="D28" s="9"/>
-    </row>
-    <row r="29" spans="1:4" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A29" s="9"/>
-      <c r="B29" s="48" t="s">
+      <c r="B40" s="9"/>
+      <c r="C40" s="9"/>
+      <c r="D40" s="9"/>
+    </row>
+    <row r="41" spans="1:4" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A41" s="9"/>
+      <c r="B41" s="48" t="s">
         <v>238</v>
       </c>
-      <c r="C29" s="48" t="s">
+      <c r="C41" s="48" t="s">
         <v>236</v>
       </c>
-      <c r="D29" s="19" t="s">
+      <c r="D41" s="19" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A30" s="60" t="s">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A42" s="59" t="s">
         <v>355</v>
       </c>
-      <c r="B30" s="57" t="s">
+      <c r="B42" s="57" t="s">
         <v>351</v>
       </c>
-      <c r="C30" s="58" t="s">
+      <c r="C42" s="58" t="s">
         <v>353</v>
       </c>
-      <c r="D30" s="58" t="s">
+      <c r="D42" s="58" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="172.8" x14ac:dyDescent="0.3">
-      <c r="A31" s="64" t="s">
+    <row r="43" spans="1:4" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A43" s="63" t="s">
         <v>379</v>
       </c>
-      <c r="B31" s="56" t="s">
+      <c r="B43" s="56" t="s">
         <v>352</v>
       </c>
-      <c r="C31" s="56" t="s">
+      <c r="C43" s="56" t="s">
         <v>354</v>
       </c>
-      <c r="D31" s="56" t="s">
+      <c r="D43" s="56" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="144" x14ac:dyDescent="0.3">
-      <c r="A32" s="64" t="s">
+    <row r="44" spans="1:4" ht="144" x14ac:dyDescent="0.3">
+      <c r="A44" s="63" t="s">
         <v>380</v>
       </c>
-      <c r="B32" s="56" t="s">
+      <c r="B44" s="56" t="s">
         <v>358</v>
       </c>
-      <c r="C32" s="56" t="s">
+      <c r="C44" s="56" t="s">
         <v>356</v>
       </c>
-      <c r="D32" s="9"/>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33" s="60" t="s">
+      <c r="D44" s="9"/>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A45" s="59" t="s">
         <v>359</v>
       </c>
-      <c r="D33" s="2" t="s">
+      <c r="D45" s="2" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A34" s="57" t="s">
+    <row r="46" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A46" s="57" t="s">
         <v>370</v>
       </c>
-      <c r="B34" s="62" t="s">
+      <c r="B46" s="61" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A35" s="64" t="s">
+    <row r="47" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A47" s="63" t="s">
         <v>359</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="B47" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="C47" s="2" t="s">
         <v>362</v>
       </c>
-      <c r="D35" s="62" t="s">
+      <c r="D47" s="61" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A36" s="64" t="s">
+    <row r="48" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A48" s="63" t="s">
         <v>381</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="C48" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="D36" s="62" t="s">
+      <c r="D48" s="61" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A37" s="55" t="s">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A49" s="55" t="s">
         <v>369</v>
       </c>
-      <c r="D37" s="2" t="s">
+      <c r="D49" s="2" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="144" x14ac:dyDescent="0.3">
-      <c r="A38" s="63" t="s">
+    <row r="50" spans="1:4" ht="144" x14ac:dyDescent="0.3">
+      <c r="A50" s="62" t="s">
         <v>376</v>
       </c>
-      <c r="B38" s="62" t="s">
+      <c r="B50" s="61" t="s">
         <v>372</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="C50" s="2" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="144" x14ac:dyDescent="0.3">
-      <c r="A39" s="64" t="s">
+    <row r="51" spans="1:4" ht="144" x14ac:dyDescent="0.3">
+      <c r="A51" s="63" t="s">
         <v>375</v>
       </c>
-      <c r="B39" s="62" t="s">
+      <c r="B51" s="61" t="s">
         <v>373</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="C51" s="2" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A40" s="55" t="s">
+    <row r="52" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A52" s="55" t="s">
         <v>377</v>
       </c>
-      <c r="D40" s="2" t="s">
+      <c r="D52" s="2" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A41" s="63" t="s">
+    <row r="53" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A53" s="62" t="s">
         <v>391</v>
       </c>
-      <c r="B41" s="62" t="s">
+      <c r="B53" s="61" t="s">
         <v>378</v>
       </c>
-      <c r="C41" s="2" t="s">
+      <c r="C53" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="D41" s="62" t="s">
+      <c r="D53" s="61" t="s">
         <v>385</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A42" s="55" t="s">
-        <v>388</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A43" s="64" t="s">
-        <v>393</v>
-      </c>
-      <c r="B43" s="62" t="s">
-        <v>394</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A44" s="55" t="s">
-        <v>390</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A45" s="62" t="s">
-        <v>397</v>
-      </c>
-      <c r="B45" s="62" t="s">
-        <v>416</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" ht="144" x14ac:dyDescent="0.3">
-      <c r="A46" s="64" t="s">
-        <v>396</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A47" s="55" t="s">
-        <v>398</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A48" s="65" t="s">
-        <v>401</v>
-      </c>
-      <c r="B48" s="62" t="s">
-        <v>418</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A49" s="64" t="s">
-        <v>415</v>
-      </c>
-      <c r="B49" s="62" t="s">
-        <v>419</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" ht="72" x14ac:dyDescent="0.3">
-      <c r="A50" s="64" t="s">
-        <v>421</v>
-      </c>
-      <c r="B50" s="68" t="s">
-        <v>421</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A51" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="B51" s="66" t="s">
-        <v>410</v>
-      </c>
-      <c r="C51" s="62" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" ht="187.2" x14ac:dyDescent="0.3">
-      <c r="B52" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A53" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="B53" s="67" t="s">
-        <v>411</v>
-      </c>
-      <c r="C53" s="62" t="s">
-        <v>408</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="55" t="s">
+        <v>388</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A55" s="63" t="s">
+        <v>393</v>
+      </c>
+      <c r="B55" s="61" t="s">
+        <v>394</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A56" s="55" t="s">
+        <v>390</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A57" s="62" t="s">
+        <v>433</v>
+      </c>
+      <c r="B57" s="70" t="s">
+        <v>432</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" ht="144" x14ac:dyDescent="0.3">
+      <c r="A58" s="67" t="s">
+        <v>410</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A59" s="55" t="s">
+        <v>396</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A60" s="64" t="s">
+        <v>431</v>
+      </c>
+      <c r="B60" s="70" t="s">
+        <v>430</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A61" s="67" t="s">
+        <v>410</v>
+      </c>
+      <c r="B61" s="70"/>
+      <c r="C61" s="2" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="A62" s="63" t="s">
         <v>412</v>
       </c>
-      <c r="D54" s="2" t="s">
+      <c r="B62" s="67" t="s">
+        <v>412</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A63" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="B63" s="65" t="s">
+        <v>407</v>
+      </c>
+      <c r="C63" s="61" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="B64" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A65" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="B65" s="66" t="s">
+        <v>408</v>
+      </c>
+      <c r="C65" s="61" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A66" s="55" t="s">
+        <v>409</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="B67" s="70" t="s">
+        <v>415</v>
+      </c>
+      <c r="C67" s="63" t="s">
+        <v>414</v>
+      </c>
+      <c r="D67" s="70" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" ht="230.4" x14ac:dyDescent="0.3">
+      <c r="A68" s="70" t="s">
+        <v>425</v>
+      </c>
+      <c r="B68" s="70" t="s">
+        <v>426</v>
+      </c>
+      <c r="C68" s="2" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="B55" s="62" t="s">
-        <v>425</v>
-      </c>
-      <c r="C55" s="64" t="s">
+    <row r="69" spans="1:4" ht="216" x14ac:dyDescent="0.3">
+      <c r="A69" s="70" t="s">
+        <v>428</v>
+      </c>
+      <c r="B69" s="70" t="s">
+        <v>427</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="B70" s="70" t="s">
+        <v>419</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="D70" s="70" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A71" s="70" t="s">
         <v>429</v>
       </c>
-    </row>
-    <row r="56" spans="1:4" ht="216" x14ac:dyDescent="0.3">
-      <c r="B56" s="62" t="s">
-        <v>414</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>426</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" ht="288" x14ac:dyDescent="0.3">
-      <c r="B57" s="62" t="s">
+      <c r="B71" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="C71" s="2" t="s">
         <v>424</v>
       </c>
-      <c r="C57" s="2" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A58" s="2" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A59" s="2" t="s">
-        <v>428</v>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A72" s="71" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="C73" s="2" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A74" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="C74" s="70" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A75" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="C75" s="70" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A76" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="C76" s="70" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A77" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="B77" s="70" t="s">
+        <v>447</v>
+      </c>
+      <c r="C77" s="70" t="s">
+        <v>444</v>
       </c>
     </row>
   </sheetData>
@@ -17468,7 +19423,7 @@
       <c r="B8" s="42" t="s">
         <v>222</v>
       </c>
-      <c r="C8" s="69" t="s">
+      <c r="C8" s="68" t="s">
         <v>224</v>
       </c>
       <c r="D8" s="9"/>

--- a/4 четверть_MSSQL.xlsx
+++ b/4 четверть_MSSQL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlexServHW\Desktop\GB_Developer_Workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08754BB9-4733-4EB6-BE8D-E42F108A8146}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78B4ABF1-7AE0-46FE-91C3-FF7AA36C1CF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3660" yWindow="-16440" windowWidth="23250" windowHeight="12450" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Изучить" sheetId="21" r:id="rId1"/>
@@ -18,15 +18,17 @@
     <sheet name="DATABASE" sheetId="12" r:id="rId3"/>
     <sheet name="Типы данных" sheetId="24" r:id="rId4"/>
     <sheet name="TABLE" sheetId="26" r:id="rId5"/>
-    <sheet name="SELECT" sheetId="15" r:id="rId6"/>
-    <sheet name="WHERE" sheetId="19" r:id="rId7"/>
-    <sheet name="IF" sheetId="23" r:id="rId8"/>
-    <sheet name="template" sheetId="14" r:id="rId9"/>
-    <sheet name="Каскадное удаление" sheetId="16" r:id="rId10"/>
-    <sheet name="Транзакции" sheetId="17" r:id="rId11"/>
-    <sheet name="VIEW" sheetId="25" r:id="rId12"/>
-    <sheet name="bc Массивы" sheetId="18" r:id="rId13"/>
-    <sheet name="bc JSON" sheetId="22" r:id="rId14"/>
+    <sheet name="CREATE" sheetId="27" r:id="rId6"/>
+    <sheet name="ALTER" sheetId="28" r:id="rId7"/>
+    <sheet name="SELECT" sheetId="15" r:id="rId8"/>
+    <sheet name="WHERE" sheetId="19" r:id="rId9"/>
+    <sheet name="IF" sheetId="23" r:id="rId10"/>
+    <sheet name="template" sheetId="14" r:id="rId11"/>
+    <sheet name="Каскадное удаление" sheetId="16" r:id="rId12"/>
+    <sheet name="Транзакции" sheetId="17" r:id="rId13"/>
+    <sheet name="VIEW" sheetId="25" r:id="rId14"/>
+    <sheet name="bc Массивы" sheetId="18" r:id="rId15"/>
+    <sheet name="bc JSON" sheetId="22" r:id="rId16"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -41,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="450">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="454">
   <si>
     <t>Урок 1 часть 1</t>
   </si>
@@ -13436,17 +13438,114 @@
   <si>
     <t xml:space="preserve">ALTER TABLE </t>
   </si>
+  <si>
+    <t>ALTER TABLE название_таблицы [WITH CHECK | WITH NOCHECK]
+{ ADD название_столбца тип_данных_столбца [атрибуты_столбца] | 
+  DROP COLUMN название_столбца |
+  ALTER COLUMN название_столбца тип_данных_столбца [NULL|NOT NULL] |
+  ADD [CONSTRAINT] определение_ограничения |
+  DROP [CONSTRAINT] имя_ограничения}</t>
+  </si>
+  <si>
+    <t>Добавление нового столбца</t>
+  </si>
+  <si>
+    <t>Добавим в таблицу Customers новый столбец Address</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">ALTER TABLE Customers
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ADD</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Address </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>NVARCHAR(50)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>NULL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="39" x14ac:knownFonts="1">
+  <fonts count="40" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -13880,9 +13979,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -13893,42 +13992,48 @@
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="14" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -13936,98 +14041,92 @@
     <xf numFmtId="49" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="22" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="21" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="20" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="30" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="31" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="21" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="22" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="33" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="34" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="21" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="22" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="21" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="22" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="13" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="8" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="34" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="33" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="22" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -14045,58 +14144,64 @@
     <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="37" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="38" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="33" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="33" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="39" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="34" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="34" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -14818,7 +14923,7 @@
       <c r="A15" s="9"/>
       <c r="B15" s="48"/>
       <c r="C15" s="9"/>
-      <c r="D15" s="69" t="s">
+      <c r="D15" s="73" t="s">
         <v>448</v>
       </c>
     </row>
@@ -15027,6 +15132,889 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4794FD93-B283-45AF-BCD9-82490C321ADD}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A2:V48"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="36" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.5546875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="71.21875" style="4" customWidth="1"/>
+    <col min="4" max="4" width="56.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="6.21875" style="7" customWidth="1"/>
+    <col min="6" max="6" width="43.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="55.109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="67.88671875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="64.33203125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="7.77734375" style="7" customWidth="1"/>
+    <col min="11" max="11" width="39.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="48.88671875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="72.6640625" style="1" customWidth="1"/>
+    <col min="14" max="14" width="43.88671875" style="1" customWidth="1"/>
+    <col min="15" max="15" width="7.77734375" style="7" customWidth="1"/>
+    <col min="16" max="16" width="56.77734375" style="2" customWidth="1"/>
+    <col min="17" max="17" width="46.77734375" style="2" customWidth="1"/>
+    <col min="18" max="18" width="62.88671875" style="2" customWidth="1"/>
+    <col min="19" max="19" width="49.21875" style="1" customWidth="1"/>
+    <col min="20" max="20" width="8.77734375" style="8"/>
+    <col min="21" max="21" width="67.77734375" style="2" customWidth="1"/>
+    <col min="22" max="22" width="68.33203125" style="1" customWidth="1"/>
+    <col min="23" max="24" width="59.33203125" style="1" customWidth="1"/>
+    <col min="25" max="25" width="59.6640625" style="1" customWidth="1"/>
+    <col min="26" max="26" width="99.44140625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="41.21875" style="1" customWidth="1"/>
+    <col min="28" max="16384" width="8.77734375" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A2" s="3"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="P2" s="5"/>
+      <c r="Q2" s="5"/>
+      <c r="R2" s="5"/>
+      <c r="S2" s="5"/>
+      <c r="U2" s="5"/>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="9"/>
+      <c r="P3" s="1"/>
+      <c r="U3" s="1"/>
+      <c r="V3" s="2"/>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A4" s="44" t="s">
+        <v>218</v>
+      </c>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A5" s="9"/>
+      <c r="B5" s="42" t="s">
+        <v>220</v>
+      </c>
+      <c r="C5" s="42" t="s">
+        <v>219</v>
+      </c>
+      <c r="D5" s="9"/>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A6" s="44" t="s">
+        <v>217</v>
+      </c>
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+    </row>
+    <row r="7" spans="1:22" ht="230.4" x14ac:dyDescent="0.3">
+      <c r="A7" s="9"/>
+      <c r="B7" s="9"/>
+      <c r="C7" s="42" t="s">
+        <v>229</v>
+      </c>
+      <c r="D7" s="9"/>
+    </row>
+    <row r="8" spans="1:22" ht="331.2" x14ac:dyDescent="0.3">
+      <c r="A8" s="9"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="42" t="s">
+        <v>230</v>
+      </c>
+      <c r="D8" s="9"/>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A9" s="9"/>
+      <c r="B9" s="9"/>
+      <c r="D9" s="9"/>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A10" s="9"/>
+      <c r="B10" s="9"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A11" s="9"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="9"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A12" s="9"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A13" s="9"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A14" s="9"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A15" s="9"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A16" s="9"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
+    </row>
+    <row r="17" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="9"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="K17" s="1"/>
+      <c r="L17" s="1"/>
+      <c r="M17" s="1"/>
+      <c r="N17" s="1"/>
+      <c r="P17" s="2"/>
+      <c r="Q17" s="2"/>
+      <c r="R17" s="2"/>
+      <c r="S17" s="1"/>
+      <c r="T17" s="8"/>
+      <c r="U17" s="2"/>
+      <c r="V17" s="1"/>
+    </row>
+    <row r="18" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="9"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="K18" s="1"/>
+      <c r="L18" s="1"/>
+      <c r="M18" s="1"/>
+      <c r="N18" s="1"/>
+      <c r="P18" s="2"/>
+      <c r="Q18" s="2"/>
+      <c r="R18" s="2"/>
+      <c r="S18" s="1"/>
+      <c r="T18" s="8"/>
+      <c r="U18" s="2"/>
+      <c r="V18" s="1"/>
+    </row>
+    <row r="19" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="9"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="1"/>
+      <c r="P19" s="2"/>
+      <c r="Q19" s="2"/>
+      <c r="R19" s="2"/>
+      <c r="S19" s="1"/>
+      <c r="T19" s="8"/>
+      <c r="U19" s="2"/>
+      <c r="V19" s="1"/>
+    </row>
+    <row r="20" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="9"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1"/>
+      <c r="M20" s="1"/>
+      <c r="N20" s="1"/>
+      <c r="P20" s="2"/>
+      <c r="Q20" s="2"/>
+      <c r="R20" s="2"/>
+      <c r="S20" s="1"/>
+      <c r="T20" s="8"/>
+      <c r="U20" s="2"/>
+      <c r="V20" s="1"/>
+    </row>
+    <row r="21" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="9"/>
+      <c r="B21" s="9"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="9"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1"/>
+      <c r="M21" s="1"/>
+      <c r="N21" s="1"/>
+      <c r="P21" s="2"/>
+      <c r="Q21" s="2"/>
+      <c r="R21" s="2"/>
+      <c r="S21" s="1"/>
+      <c r="T21" s="8"/>
+      <c r="U21" s="2"/>
+      <c r="V21" s="1"/>
+    </row>
+    <row r="22" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="9"/>
+      <c r="B22" s="9"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+      <c r="K22" s="1"/>
+      <c r="L22" s="1"/>
+      <c r="M22" s="1"/>
+      <c r="N22" s="1"/>
+      <c r="P22" s="2"/>
+      <c r="Q22" s="2"/>
+      <c r="R22" s="2"/>
+      <c r="S22" s="1"/>
+      <c r="T22" s="8"/>
+      <c r="U22" s="2"/>
+      <c r="V22" s="1"/>
+    </row>
+    <row r="23" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="9"/>
+      <c r="B23" s="9"/>
+      <c r="C23" s="9"/>
+      <c r="D23" s="9"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+      <c r="K23" s="1"/>
+      <c r="L23" s="1"/>
+      <c r="M23" s="1"/>
+      <c r="N23" s="1"/>
+      <c r="P23" s="2"/>
+      <c r="Q23" s="2"/>
+      <c r="R23" s="2"/>
+      <c r="S23" s="1"/>
+      <c r="T23" s="8"/>
+      <c r="U23" s="2"/>
+      <c r="V23" s="1"/>
+    </row>
+    <row r="24" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="9"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="9"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
+      <c r="K24" s="1"/>
+      <c r="L24" s="1"/>
+      <c r="M24" s="1"/>
+      <c r="N24" s="1"/>
+      <c r="P24" s="2"/>
+      <c r="Q24" s="2"/>
+      <c r="R24" s="2"/>
+      <c r="S24" s="1"/>
+      <c r="T24" s="8"/>
+      <c r="U24" s="2"/>
+      <c r="V24" s="1"/>
+    </row>
+    <row r="25" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="9"/>
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
+      <c r="K25" s="1"/>
+      <c r="L25" s="1"/>
+      <c r="M25" s="1"/>
+      <c r="N25" s="1"/>
+      <c r="P25" s="2"/>
+      <c r="Q25" s="2"/>
+      <c r="R25" s="2"/>
+      <c r="S25" s="1"/>
+      <c r="T25" s="8"/>
+      <c r="U25" s="2"/>
+      <c r="V25" s="1"/>
+    </row>
+    <row r="26" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="9"/>
+      <c r="B26" s="9"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+      <c r="K26" s="1"/>
+      <c r="L26" s="1"/>
+      <c r="M26" s="1"/>
+      <c r="N26" s="1"/>
+      <c r="P26" s="2"/>
+      <c r="Q26" s="2"/>
+      <c r="R26" s="2"/>
+      <c r="S26" s="1"/>
+      <c r="T26" s="8"/>
+      <c r="U26" s="2"/>
+      <c r="V26" s="1"/>
+    </row>
+    <row r="27" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="9"/>
+      <c r="B27" s="9"/>
+      <c r="C27" s="9"/>
+      <c r="D27" s="9"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+      <c r="K27" s="1"/>
+      <c r="L27" s="1"/>
+      <c r="M27" s="1"/>
+      <c r="N27" s="1"/>
+      <c r="P27" s="2"/>
+      <c r="Q27" s="2"/>
+      <c r="R27" s="2"/>
+      <c r="S27" s="1"/>
+      <c r="T27" s="8"/>
+      <c r="U27" s="2"/>
+      <c r="V27" s="1"/>
+    </row>
+    <row r="28" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="9"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="9"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+      <c r="K28" s="1"/>
+      <c r="L28" s="1"/>
+      <c r="M28" s="1"/>
+      <c r="N28" s="1"/>
+      <c r="P28" s="2"/>
+      <c r="Q28" s="2"/>
+      <c r="R28" s="2"/>
+      <c r="S28" s="1"/>
+      <c r="T28" s="8"/>
+      <c r="U28" s="2"/>
+      <c r="V28" s="1"/>
+    </row>
+    <row r="29" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="9"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="9"/>
+      <c r="D29" s="9"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+      <c r="K29" s="1"/>
+      <c r="L29" s="1"/>
+      <c r="M29" s="1"/>
+      <c r="N29" s="1"/>
+      <c r="P29" s="2"/>
+      <c r="Q29" s="2"/>
+      <c r="R29" s="2"/>
+      <c r="S29" s="1"/>
+      <c r="T29" s="8"/>
+      <c r="U29" s="2"/>
+      <c r="V29" s="1"/>
+    </row>
+    <row r="30" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="9"/>
+      <c r="B30" s="9"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="9"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
+      <c r="K30" s="1"/>
+      <c r="L30" s="1"/>
+      <c r="M30" s="1"/>
+      <c r="N30" s="1"/>
+      <c r="P30" s="2"/>
+      <c r="Q30" s="2"/>
+      <c r="R30" s="2"/>
+      <c r="S30" s="1"/>
+      <c r="T30" s="8"/>
+      <c r="U30" s="2"/>
+      <c r="V30" s="1"/>
+    </row>
+    <row r="31" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="9"/>
+      <c r="B31" s="9"/>
+      <c r="C31" s="9"/>
+      <c r="D31" s="9"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+      <c r="K31" s="1"/>
+      <c r="L31" s="1"/>
+      <c r="M31" s="1"/>
+      <c r="N31" s="1"/>
+      <c r="P31" s="2"/>
+      <c r="Q31" s="2"/>
+      <c r="R31" s="2"/>
+      <c r="S31" s="1"/>
+      <c r="T31" s="8"/>
+      <c r="U31" s="2"/>
+      <c r="V31" s="1"/>
+    </row>
+    <row r="32" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="9"/>
+      <c r="B32" s="9"/>
+      <c r="C32" s="9"/>
+      <c r="D32" s="9"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+      <c r="K32" s="1"/>
+      <c r="L32" s="1"/>
+      <c r="M32" s="1"/>
+      <c r="N32" s="1"/>
+      <c r="P32" s="2"/>
+      <c r="Q32" s="2"/>
+      <c r="R32" s="2"/>
+      <c r="S32" s="1"/>
+      <c r="T32" s="8"/>
+      <c r="U32" s="2"/>
+      <c r="V32" s="1"/>
+    </row>
+    <row r="33" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="9"/>
+      <c r="B33" s="9"/>
+      <c r="C33" s="9"/>
+      <c r="D33" s="9"/>
+      <c r="F33" s="1"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
+      <c r="K33" s="1"/>
+      <c r="L33" s="1"/>
+      <c r="M33" s="1"/>
+      <c r="N33" s="1"/>
+      <c r="P33" s="2"/>
+      <c r="Q33" s="2"/>
+      <c r="R33" s="2"/>
+      <c r="S33" s="1"/>
+      <c r="T33" s="8"/>
+      <c r="U33" s="2"/>
+      <c r="V33" s="1"/>
+    </row>
+    <row r="34" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="9"/>
+      <c r="B34" s="9"/>
+      <c r="C34" s="9"/>
+      <c r="D34" s="9"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
+      <c r="K34" s="1"/>
+      <c r="L34" s="1"/>
+      <c r="M34" s="1"/>
+      <c r="N34" s="1"/>
+      <c r="P34" s="2"/>
+      <c r="Q34" s="2"/>
+      <c r="R34" s="2"/>
+      <c r="S34" s="1"/>
+      <c r="T34" s="8"/>
+      <c r="U34" s="2"/>
+      <c r="V34" s="1"/>
+    </row>
+    <row r="35" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="9"/>
+      <c r="B35" s="9"/>
+      <c r="C35" s="9"/>
+      <c r="D35" s="9"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="2"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
+      <c r="K35" s="1"/>
+      <c r="L35" s="1"/>
+      <c r="M35" s="1"/>
+      <c r="N35" s="1"/>
+      <c r="P35" s="2"/>
+      <c r="Q35" s="2"/>
+      <c r="R35" s="2"/>
+      <c r="S35" s="1"/>
+      <c r="T35" s="8"/>
+      <c r="U35" s="2"/>
+      <c r="V35" s="1"/>
+    </row>
+    <row r="36" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="9"/>
+      <c r="B36" s="9"/>
+      <c r="C36" s="9"/>
+      <c r="D36" s="9"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="1"/>
+      <c r="I36" s="1"/>
+      <c r="K36" s="1"/>
+      <c r="L36" s="1"/>
+      <c r="M36" s="1"/>
+      <c r="N36" s="1"/>
+      <c r="P36" s="2"/>
+      <c r="Q36" s="2"/>
+      <c r="R36" s="2"/>
+      <c r="S36" s="1"/>
+      <c r="T36" s="8"/>
+      <c r="U36" s="2"/>
+      <c r="V36" s="1"/>
+    </row>
+    <row r="37" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="9"/>
+      <c r="B37" s="9"/>
+      <c r="C37" s="9"/>
+      <c r="D37" s="9"/>
+      <c r="F37" s="1"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="1"/>
+      <c r="I37" s="1"/>
+      <c r="K37" s="1"/>
+      <c r="L37" s="1"/>
+      <c r="M37" s="1"/>
+      <c r="N37" s="1"/>
+      <c r="P37" s="2"/>
+      <c r="Q37" s="2"/>
+      <c r="R37" s="2"/>
+      <c r="S37" s="1"/>
+      <c r="T37" s="8"/>
+      <c r="U37" s="2"/>
+      <c r="V37" s="1"/>
+    </row>
+    <row r="38" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="9"/>
+      <c r="B38" s="9"/>
+      <c r="C38" s="9"/>
+      <c r="D38" s="9"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="1"/>
+      <c r="I38" s="1"/>
+      <c r="K38" s="1"/>
+      <c r="L38" s="1"/>
+      <c r="M38" s="1"/>
+      <c r="N38" s="1"/>
+      <c r="P38" s="2"/>
+      <c r="Q38" s="2"/>
+      <c r="R38" s="2"/>
+      <c r="S38" s="1"/>
+      <c r="T38" s="8"/>
+      <c r="U38" s="2"/>
+      <c r="V38" s="1"/>
+    </row>
+    <row r="39" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="9"/>
+      <c r="B39" s="9"/>
+      <c r="C39" s="9"/>
+      <c r="D39" s="9"/>
+      <c r="F39" s="1"/>
+      <c r="G39" s="2"/>
+      <c r="H39" s="1"/>
+      <c r="I39" s="1"/>
+      <c r="K39" s="1"/>
+      <c r="L39" s="1"/>
+      <c r="M39" s="1"/>
+      <c r="N39" s="1"/>
+      <c r="P39" s="2"/>
+      <c r="Q39" s="2"/>
+      <c r="R39" s="2"/>
+      <c r="S39" s="1"/>
+      <c r="T39" s="8"/>
+      <c r="U39" s="2"/>
+      <c r="V39" s="1"/>
+    </row>
+    <row r="40" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="9"/>
+      <c r="B40" s="9"/>
+      <c r="C40" s="9"/>
+      <c r="D40" s="9"/>
+      <c r="F40" s="1"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="1"/>
+      <c r="I40" s="1"/>
+      <c r="K40" s="1"/>
+      <c r="L40" s="1"/>
+      <c r="M40" s="1"/>
+      <c r="N40" s="1"/>
+      <c r="P40" s="2"/>
+      <c r="Q40" s="2"/>
+      <c r="R40" s="2"/>
+      <c r="S40" s="1"/>
+      <c r="T40" s="8"/>
+      <c r="U40" s="2"/>
+      <c r="V40" s="1"/>
+    </row>
+    <row r="41" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="9"/>
+      <c r="B41" s="9"/>
+      <c r="C41" s="9"/>
+      <c r="D41" s="9"/>
+      <c r="F41" s="1"/>
+      <c r="G41" s="2"/>
+      <c r="H41" s="1"/>
+      <c r="I41" s="1"/>
+      <c r="K41" s="1"/>
+      <c r="L41" s="1"/>
+      <c r="M41" s="1"/>
+      <c r="N41" s="1"/>
+      <c r="P41" s="2"/>
+      <c r="Q41" s="2"/>
+      <c r="R41" s="2"/>
+      <c r="S41" s="1"/>
+      <c r="T41" s="8"/>
+      <c r="U41" s="2"/>
+      <c r="V41" s="1"/>
+    </row>
+    <row r="42" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="9"/>
+      <c r="B42" s="9"/>
+      <c r="C42" s="9"/>
+      <c r="D42" s="9"/>
+      <c r="F42" s="1"/>
+      <c r="G42" s="2"/>
+      <c r="H42" s="1"/>
+      <c r="I42" s="1"/>
+      <c r="K42" s="1"/>
+      <c r="L42" s="1"/>
+      <c r="M42" s="1"/>
+      <c r="N42" s="1"/>
+      <c r="P42" s="2"/>
+      <c r="Q42" s="2"/>
+      <c r="R42" s="2"/>
+      <c r="S42" s="1"/>
+      <c r="T42" s="8"/>
+      <c r="U42" s="2"/>
+      <c r="V42" s="1"/>
+    </row>
+    <row r="43" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="9"/>
+      <c r="B43" s="9"/>
+      <c r="C43" s="9"/>
+      <c r="D43" s="9"/>
+      <c r="F43" s="1"/>
+      <c r="G43" s="2"/>
+      <c r="H43" s="1"/>
+      <c r="I43" s="1"/>
+      <c r="K43" s="1"/>
+      <c r="L43" s="1"/>
+      <c r="M43" s="1"/>
+      <c r="N43" s="1"/>
+      <c r="P43" s="2"/>
+      <c r="Q43" s="2"/>
+      <c r="R43" s="2"/>
+      <c r="S43" s="1"/>
+      <c r="T43" s="8"/>
+      <c r="U43" s="2"/>
+      <c r="V43" s="1"/>
+    </row>
+    <row r="44" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="9"/>
+      <c r="B44" s="9"/>
+      <c r="C44" s="9"/>
+      <c r="D44" s="9"/>
+      <c r="F44" s="1"/>
+      <c r="G44" s="2"/>
+      <c r="H44" s="1"/>
+      <c r="I44" s="1"/>
+      <c r="K44" s="1"/>
+      <c r="L44" s="1"/>
+      <c r="M44" s="1"/>
+      <c r="N44" s="1"/>
+      <c r="P44" s="2"/>
+      <c r="Q44" s="2"/>
+      <c r="R44" s="2"/>
+      <c r="S44" s="1"/>
+      <c r="T44" s="8"/>
+      <c r="U44" s="2"/>
+      <c r="V44" s="1"/>
+    </row>
+    <row r="45" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="9"/>
+      <c r="B45" s="9"/>
+      <c r="C45" s="9"/>
+      <c r="D45" s="9"/>
+      <c r="F45" s="1"/>
+      <c r="G45" s="2"/>
+      <c r="H45" s="1"/>
+      <c r="I45" s="1"/>
+      <c r="K45" s="1"/>
+      <c r="L45" s="1"/>
+      <c r="M45" s="1"/>
+      <c r="N45" s="1"/>
+      <c r="P45" s="2"/>
+      <c r="Q45" s="2"/>
+      <c r="R45" s="2"/>
+      <c r="S45" s="1"/>
+      <c r="T45" s="8"/>
+      <c r="U45" s="2"/>
+      <c r="V45" s="1"/>
+    </row>
+    <row r="46" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="9"/>
+      <c r="B46" s="9"/>
+      <c r="C46" s="9"/>
+      <c r="D46" s="9"/>
+      <c r="F46" s="1"/>
+      <c r="G46" s="2"/>
+      <c r="H46" s="1"/>
+      <c r="I46" s="1"/>
+      <c r="K46" s="1"/>
+      <c r="L46" s="1"/>
+      <c r="M46" s="1"/>
+      <c r="N46" s="1"/>
+      <c r="P46" s="2"/>
+      <c r="Q46" s="2"/>
+      <c r="R46" s="2"/>
+      <c r="S46" s="1"/>
+      <c r="T46" s="8"/>
+      <c r="U46" s="2"/>
+      <c r="V46" s="1"/>
+    </row>
+    <row r="47" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="9"/>
+      <c r="B47" s="9"/>
+      <c r="C47" s="9"/>
+      <c r="D47" s="9"/>
+      <c r="F47" s="1"/>
+      <c r="G47" s="2"/>
+      <c r="H47" s="1"/>
+      <c r="I47" s="1"/>
+      <c r="K47" s="1"/>
+      <c r="L47" s="1"/>
+      <c r="M47" s="1"/>
+      <c r="N47" s="1"/>
+      <c r="P47" s="2"/>
+      <c r="Q47" s="2"/>
+      <c r="R47" s="2"/>
+      <c r="S47" s="1"/>
+      <c r="T47" s="8"/>
+      <c r="U47" s="2"/>
+      <c r="V47" s="1"/>
+    </row>
+    <row r="48" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="9"/>
+      <c r="B48" s="9"/>
+      <c r="C48" s="9"/>
+      <c r="D48" s="9"/>
+      <c r="F48" s="1"/>
+      <c r="G48" s="2"/>
+      <c r="H48" s="1"/>
+      <c r="I48" s="1"/>
+      <c r="K48" s="1"/>
+      <c r="L48" s="1"/>
+      <c r="M48" s="1"/>
+      <c r="N48" s="1"/>
+      <c r="P48" s="2"/>
+      <c r="Q48" s="2"/>
+      <c r="R48" s="2"/>
+      <c r="S48" s="1"/>
+      <c r="T48" s="8"/>
+      <c r="U48" s="2"/>
+      <c r="V48" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DB01197-FE1C-4ED1-B3B4-7B774B71A2A6}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A2:E3"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="36" style="2" customWidth="1"/>
+    <col min="2" max="2" width="50.5546875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="71.21875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="56.44140625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="6.21875" style="52" customWidth="1"/>
+    <col min="6" max="6" width="43.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="55.109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="67.88671875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="64.33203125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="7.77734375" style="2" customWidth="1"/>
+    <col min="11" max="11" width="39.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="48.88671875" style="2" customWidth="1"/>
+    <col min="13" max="13" width="72.6640625" style="2" customWidth="1"/>
+    <col min="14" max="14" width="43.88671875" style="2" customWidth="1"/>
+    <col min="15" max="15" width="7.77734375" style="2" customWidth="1"/>
+    <col min="16" max="16" width="56.77734375" style="2" customWidth="1"/>
+    <col min="17" max="17" width="46.77734375" style="2" customWidth="1"/>
+    <col min="18" max="18" width="62.88671875" style="2" customWidth="1"/>
+    <col min="19" max="19" width="49.21875" style="2" customWidth="1"/>
+    <col min="20" max="20" width="8.77734375" style="2"/>
+    <col min="21" max="21" width="67.77734375" style="2" customWidth="1"/>
+    <col min="22" max="22" width="68.33203125" style="2" customWidth="1"/>
+    <col min="23" max="24" width="59.33203125" style="2" customWidth="1"/>
+    <col min="25" max="25" width="59.6640625" style="2" customWidth="1"/>
+    <col min="26" max="26" width="99.44140625" style="2" customWidth="1"/>
+    <col min="27" max="27" width="41.21875" style="2" customWidth="1"/>
+    <col min="28" max="16384" width="8.77734375" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:5" s="51" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="E2" s="52"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8347859-D7B0-40A5-9B17-0069AC1E92BB}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -15391,7 +16379,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16AAE27B-B1A5-470A-8C56-1AC981AA4A71}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -15728,7 +16716,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C506E3D-0255-4B93-95A3-63E2CE874713}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -15784,7 +16772,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B13A24C-6305-48F4-A1E6-55B31CAA1F4A}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -16657,7 +17645,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA83B601-5B0E-4344-A36B-7DD0432A3007}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -16750,7 +17738,7 @@
       <c r="B7" s="43" t="s">
         <v>205</v>
       </c>
-      <c r="C7" s="73" t="s">
+      <c r="C7" s="72" t="s">
         <v>204</v>
       </c>
       <c r="D7" s="42" t="s">
@@ -16760,7 +17748,7 @@
     <row r="8" spans="1:22" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A8" s="9"/>
       <c r="B8" s="9"/>
-      <c r="C8" s="73" t="s">
+      <c r="C8" s="72" t="s">
         <v>226</v>
       </c>
       <c r="D8" s="42" t="s">
@@ -18171,7 +19159,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="14" type="noConversion"/>
+  <phoneticPr fontId="15" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="D46" r:id="rId1" location=":~:text=%D0%A1%D0%BE%D0%B7%D0%B4%D0%B0%D0%BD%D0%B8%D0%B5%20%D0%B1%D0%B0%D0%B7%D1%8B%20%D0%B4%D0%B0%D0%BD%D0%BD%D1%8B%D1%85" xr:uid="{FDFE2116-2B22-4A87-B37D-3DFA9E8F9FE0}"/>
     <hyperlink ref="D44" r:id="rId2" location=":~:text=%D0%A1%D0%BE%D0%B7%D0%B4%D0%B0%D0%BD%D0%B8%D0%B5%20%D0%B1%D0%B0%D0%B7%D1%8B%20%D0%B4%D0%B0%D0%BD%D0%BD%D1%8B%D1%85%20%D0%B2%20SQL%20Management%20Studio" xr:uid="{5B701F02-CEF7-44EA-83C6-0E21D7145608}"/>
@@ -18644,7 +19632,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="14" type="noConversion"/>
+  <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
@@ -18653,9 +19641,10 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{167F5111-19C3-403C-BD83-02EC5AD53664}">
   <sheetPr>
+    <tabColor theme="9" tint="0.39997558519241921"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:E77"/>
+  <dimension ref="A2:E39"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="36" style="2" customWidth="1"/>
@@ -18822,7 +19811,7 @@
       <c r="D27" s="9"/>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28" s="72" t="s">
+      <c r="A28" s="71" t="s">
         <v>449</v>
       </c>
       <c r="B28" s="48"/>
@@ -18894,394 +19883,6 @@
       <c r="B39" s="48"/>
       <c r="C39" s="48"/>
       <c r="D39" s="9"/>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A40" s="30" t="s">
-        <v>239</v>
-      </c>
-      <c r="B40" s="9"/>
-      <c r="C40" s="9"/>
-      <c r="D40" s="9"/>
-    </row>
-    <row r="41" spans="1:4" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A41" s="9"/>
-      <c r="B41" s="48" t="s">
-        <v>238</v>
-      </c>
-      <c r="C41" s="48" t="s">
-        <v>236</v>
-      </c>
-      <c r="D41" s="19" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A42" s="59" t="s">
-        <v>355</v>
-      </c>
-      <c r="B42" s="57" t="s">
-        <v>351</v>
-      </c>
-      <c r="C42" s="58" t="s">
-        <v>353</v>
-      </c>
-      <c r="D42" s="58" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" ht="172.8" x14ac:dyDescent="0.3">
-      <c r="A43" s="63" t="s">
-        <v>379</v>
-      </c>
-      <c r="B43" s="56" t="s">
-        <v>352</v>
-      </c>
-      <c r="C43" s="56" t="s">
-        <v>354</v>
-      </c>
-      <c r="D43" s="56" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" ht="144" x14ac:dyDescent="0.3">
-      <c r="A44" s="63" t="s">
-        <v>380</v>
-      </c>
-      <c r="B44" s="56" t="s">
-        <v>358</v>
-      </c>
-      <c r="C44" s="56" t="s">
-        <v>356</v>
-      </c>
-      <c r="D44" s="9"/>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A45" s="59" t="s">
-        <v>359</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A46" s="57" t="s">
-        <v>370</v>
-      </c>
-      <c r="B46" s="61" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A47" s="63" t="s">
-        <v>359</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="D47" s="61" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A48" s="63" t="s">
-        <v>381</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="D48" s="61" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A49" s="55" t="s">
-        <v>369</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" ht="144" x14ac:dyDescent="0.3">
-      <c r="A50" s="62" t="s">
-        <v>376</v>
-      </c>
-      <c r="B50" s="61" t="s">
-        <v>372</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" ht="144" x14ac:dyDescent="0.3">
-      <c r="A51" s="63" t="s">
-        <v>375</v>
-      </c>
-      <c r="B51" s="61" t="s">
-        <v>373</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A52" s="55" t="s">
-        <v>377</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A53" s="62" t="s">
-        <v>391</v>
-      </c>
-      <c r="B53" s="61" t="s">
-        <v>378</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="D53" s="61" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A54" s="55" t="s">
-        <v>388</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A55" s="63" t="s">
-        <v>393</v>
-      </c>
-      <c r="B55" s="61" t="s">
-        <v>394</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A56" s="55" t="s">
-        <v>390</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A57" s="62" t="s">
-        <v>433</v>
-      </c>
-      <c r="B57" s="70" t="s">
-        <v>432</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" ht="144" x14ac:dyDescent="0.3">
-      <c r="A58" s="67" t="s">
-        <v>410</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A59" s="55" t="s">
-        <v>396</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A60" s="64" t="s">
-        <v>431</v>
-      </c>
-      <c r="B60" s="70" t="s">
-        <v>430</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A61" s="67" t="s">
-        <v>410</v>
-      </c>
-      <c r="B61" s="70"/>
-      <c r="C61" s="2" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" ht="72" x14ac:dyDescent="0.3">
-      <c r="A62" s="63" t="s">
-        <v>412</v>
-      </c>
-      <c r="B62" s="67" t="s">
-        <v>412</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A63" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="B63" s="65" t="s">
-        <v>407</v>
-      </c>
-      <c r="C63" s="61" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" ht="187.2" x14ac:dyDescent="0.3">
-      <c r="B64" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A65" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="B65" s="66" t="s">
-        <v>408</v>
-      </c>
-      <c r="C65" s="61" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A66" s="55" t="s">
-        <v>409</v>
-      </c>
-      <c r="D66" s="2" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" ht="172.8" x14ac:dyDescent="0.3">
-      <c r="B67" s="70" t="s">
-        <v>415</v>
-      </c>
-      <c r="C67" s="63" t="s">
-        <v>414</v>
-      </c>
-      <c r="D67" s="70" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" ht="230.4" x14ac:dyDescent="0.3">
-      <c r="A68" s="70" t="s">
-        <v>425</v>
-      </c>
-      <c r="B68" s="70" t="s">
-        <v>426</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" ht="216" x14ac:dyDescent="0.3">
-      <c r="A69" s="70" t="s">
-        <v>428</v>
-      </c>
-      <c r="B69" s="70" t="s">
-        <v>427</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="D69" s="2" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" ht="172.8" x14ac:dyDescent="0.3">
-      <c r="B70" s="70" t="s">
-        <v>419</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="D70" s="70" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" ht="172.8" x14ac:dyDescent="0.3">
-      <c r="A71" s="70" t="s">
-        <v>429</v>
-      </c>
-      <c r="B71" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A72" s="71" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="C73" s="2" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A74" s="2" t="s">
-        <v>437</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>445</v>
-      </c>
-      <c r="C74" s="70" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A75" s="2" t="s">
-        <v>438</v>
-      </c>
-      <c r="C75" s="70" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A76" s="2" t="s">
-        <v>439</v>
-      </c>
-      <c r="B76" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="C76" s="70" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" ht="172.8" x14ac:dyDescent="0.3">
-      <c r="A77" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="B77" s="70" t="s">
-        <v>447</v>
-      </c>
-      <c r="C77" s="70" t="s">
-        <v>444</v>
-      </c>
     </row>
   </sheetData>
   <hyperlinks>
@@ -19293,6 +19894,1498 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{287FFDAD-91BC-4E68-B2BE-D025A8EC0BE3}">
+  <sheetPr>
+    <tabColor theme="9" tint="0.39997558519241921"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A3:AA42"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="36" style="2" customWidth="1"/>
+    <col min="2" max="2" width="50.5546875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="71.21875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="56.44140625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="6.21875" style="52" customWidth="1"/>
+    <col min="6" max="6" width="43.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="55.109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="67.88671875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="64.33203125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="7.77734375" style="2" customWidth="1"/>
+    <col min="11" max="11" width="39.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="48.88671875" style="2" customWidth="1"/>
+    <col min="13" max="13" width="72.6640625" style="2" customWidth="1"/>
+    <col min="14" max="14" width="43.88671875" style="2" customWidth="1"/>
+    <col min="15" max="15" width="7.77734375" style="2" customWidth="1"/>
+    <col min="16" max="16" width="56.77734375" style="2" customWidth="1"/>
+    <col min="17" max="17" width="46.77734375" style="2" customWidth="1"/>
+    <col min="18" max="18" width="62.88671875" style="2" customWidth="1"/>
+    <col min="19" max="19" width="49.21875" style="2" customWidth="1"/>
+    <col min="20" max="20" width="8.77734375" style="2"/>
+    <col min="21" max="21" width="67.77734375" style="2" customWidth="1"/>
+    <col min="22" max="22" width="68.33203125" style="2" customWidth="1"/>
+    <col min="23" max="24" width="59.33203125" style="2" customWidth="1"/>
+    <col min="25" max="25" width="59.6640625" style="2" customWidth="1"/>
+    <col min="26" max="26" width="99.44140625" style="2" customWidth="1"/>
+    <col min="27" max="27" width="41.21875" style="2" customWidth="1"/>
+    <col min="28" max="16384" width="8.77734375" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:27" s="51" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="E3" s="52"/>
+    </row>
+    <row r="4" spans="1:27" s="52" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="26" t="s">
+        <v>113</v>
+      </c>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
+      <c r="S4" s="2"/>
+      <c r="T4" s="2"/>
+      <c r="U4" s="2"/>
+      <c r="V4" s="2"/>
+      <c r="W4" s="2"/>
+      <c r="X4" s="2"/>
+      <c r="Y4" s="2"/>
+      <c r="Z4" s="2"/>
+      <c r="AA4" s="2"/>
+    </row>
+    <row r="5" spans="1:27" s="52" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="30" t="s">
+        <v>239</v>
+      </c>
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2"/>
+      <c r="P5" s="2"/>
+      <c r="Q5" s="2"/>
+      <c r="R5" s="2"/>
+      <c r="S5" s="2"/>
+      <c r="T5" s="2"/>
+      <c r="U5" s="2"/>
+      <c r="V5" s="2"/>
+      <c r="W5" s="2"/>
+      <c r="X5" s="2"/>
+      <c r="Y5" s="2"/>
+      <c r="Z5" s="2"/>
+      <c r="AA5" s="2"/>
+    </row>
+    <row r="6" spans="1:27" s="52" customFormat="1" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A6" s="9"/>
+      <c r="B6" s="48" t="s">
+        <v>238</v>
+      </c>
+      <c r="C6" s="48" t="s">
+        <v>236</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="2"/>
+      <c r="O6" s="2"/>
+      <c r="P6" s="2"/>
+      <c r="Q6" s="2"/>
+      <c r="R6" s="2"/>
+      <c r="S6" s="2"/>
+      <c r="T6" s="2"/>
+      <c r="U6" s="2"/>
+      <c r="V6" s="2"/>
+      <c r="W6" s="2"/>
+      <c r="X6" s="2"/>
+      <c r="Y6" s="2"/>
+      <c r="Z6" s="2"/>
+      <c r="AA6" s="2"/>
+    </row>
+    <row r="7" spans="1:27" s="52" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="59" t="s">
+        <v>355</v>
+      </c>
+      <c r="B7" s="57" t="s">
+        <v>351</v>
+      </c>
+      <c r="C7" s="58" t="s">
+        <v>353</v>
+      </c>
+      <c r="D7" s="58" t="s">
+        <v>357</v>
+      </c>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
+      <c r="N7" s="2"/>
+      <c r="O7" s="2"/>
+      <c r="P7" s="2"/>
+      <c r="Q7" s="2"/>
+      <c r="R7" s="2"/>
+      <c r="S7" s="2"/>
+      <c r="T7" s="2"/>
+      <c r="U7" s="2"/>
+      <c r="V7" s="2"/>
+      <c r="W7" s="2"/>
+      <c r="X7" s="2"/>
+      <c r="Y7" s="2"/>
+      <c r="Z7" s="2"/>
+      <c r="AA7" s="2"/>
+    </row>
+    <row r="8" spans="1:27" s="52" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="63" t="s">
+        <v>379</v>
+      </c>
+      <c r="B8" s="56" t="s">
+        <v>352</v>
+      </c>
+      <c r="C8" s="56" t="s">
+        <v>354</v>
+      </c>
+      <c r="D8" s="56" t="s">
+        <v>360</v>
+      </c>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
+      <c r="N8" s="2"/>
+      <c r="O8" s="2"/>
+      <c r="P8" s="2"/>
+      <c r="Q8" s="2"/>
+      <c r="R8" s="2"/>
+      <c r="S8" s="2"/>
+      <c r="T8" s="2"/>
+      <c r="U8" s="2"/>
+      <c r="V8" s="2"/>
+      <c r="W8" s="2"/>
+      <c r="X8" s="2"/>
+      <c r="Y8" s="2"/>
+      <c r="Z8" s="2"/>
+      <c r="AA8" s="2"/>
+    </row>
+    <row r="9" spans="1:27" s="52" customFormat="1" ht="144" x14ac:dyDescent="0.3">
+      <c r="A9" s="63" t="s">
+        <v>380</v>
+      </c>
+      <c r="B9" s="56" t="s">
+        <v>358</v>
+      </c>
+      <c r="C9" s="56" t="s">
+        <v>356</v>
+      </c>
+      <c r="D9" s="9"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
+      <c r="N9" s="2"/>
+      <c r="O9" s="2"/>
+      <c r="P9" s="2"/>
+      <c r="Q9" s="2"/>
+      <c r="R9" s="2"/>
+      <c r="S9" s="2"/>
+      <c r="T9" s="2"/>
+      <c r="U9" s="2"/>
+      <c r="V9" s="2"/>
+      <c r="W9" s="2"/>
+      <c r="X9" s="2"/>
+      <c r="Y9" s="2"/>
+      <c r="Z9" s="2"/>
+      <c r="AA9" s="2"/>
+    </row>
+    <row r="10" spans="1:27" s="52" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="59" t="s">
+        <v>359</v>
+      </c>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="2"/>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
+      <c r="P10" s="2"/>
+      <c r="Q10" s="2"/>
+      <c r="R10" s="2"/>
+      <c r="S10" s="2"/>
+      <c r="T10" s="2"/>
+      <c r="U10" s="2"/>
+      <c r="V10" s="2"/>
+      <c r="W10" s="2"/>
+      <c r="X10" s="2"/>
+      <c r="Y10" s="2"/>
+      <c r="Z10" s="2"/>
+      <c r="AA10" s="2"/>
+    </row>
+    <row r="11" spans="1:27" s="52" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A11" s="57" t="s">
+        <v>370</v>
+      </c>
+      <c r="B11" s="61" t="s">
+        <v>364</v>
+      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
+      <c r="M11" s="2"/>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
+      <c r="P11" s="2"/>
+      <c r="Q11" s="2"/>
+      <c r="R11" s="2"/>
+      <c r="S11" s="2"/>
+      <c r="T11" s="2"/>
+      <c r="U11" s="2"/>
+      <c r="V11" s="2"/>
+      <c r="W11" s="2"/>
+      <c r="X11" s="2"/>
+      <c r="Y11" s="2"/>
+      <c r="Z11" s="2"/>
+      <c r="AA11" s="2"/>
+    </row>
+    <row r="12" spans="1:27" s="52" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="63" t="s">
+        <v>359</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="D12" s="61" t="s">
+        <v>383</v>
+      </c>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
+      <c r="P12" s="2"/>
+      <c r="Q12" s="2"/>
+      <c r="R12" s="2"/>
+      <c r="S12" s="2"/>
+      <c r="T12" s="2"/>
+      <c r="U12" s="2"/>
+      <c r="V12" s="2"/>
+      <c r="W12" s="2"/>
+      <c r="X12" s="2"/>
+      <c r="Y12" s="2"/>
+      <c r="Z12" s="2"/>
+      <c r="AA12" s="2"/>
+    </row>
+    <row r="13" spans="1:27" s="52" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="63" t="s">
+        <v>381</v>
+      </c>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="D13" s="61" t="s">
+        <v>384</v>
+      </c>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="2"/>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2"/>
+      <c r="P13" s="2"/>
+      <c r="Q13" s="2"/>
+      <c r="R13" s="2"/>
+      <c r="S13" s="2"/>
+      <c r="T13" s="2"/>
+      <c r="U13" s="2"/>
+      <c r="V13" s="2"/>
+      <c r="W13" s="2"/>
+      <c r="X13" s="2"/>
+      <c r="Y13" s="2"/>
+      <c r="Z13" s="2"/>
+      <c r="AA13" s="2"/>
+    </row>
+    <row r="14" spans="1:27" s="52" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="55" t="s">
+        <v>369</v>
+      </c>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2"/>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
+      <c r="P14" s="2"/>
+      <c r="Q14" s="2"/>
+      <c r="R14" s="2"/>
+      <c r="S14" s="2"/>
+      <c r="T14" s="2"/>
+      <c r="U14" s="2"/>
+      <c r="V14" s="2"/>
+      <c r="W14" s="2"/>
+      <c r="X14" s="2"/>
+      <c r="Y14" s="2"/>
+      <c r="Z14" s="2"/>
+      <c r="AA14" s="2"/>
+    </row>
+    <row r="15" spans="1:27" s="52" customFormat="1" ht="144" x14ac:dyDescent="0.3">
+      <c r="A15" s="62" t="s">
+        <v>376</v>
+      </c>
+      <c r="B15" s="61" t="s">
+        <v>372</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="D15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2"/>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
+      <c r="P15" s="2"/>
+      <c r="Q15" s="2"/>
+      <c r="R15" s="2"/>
+      <c r="S15" s="2"/>
+      <c r="T15" s="2"/>
+      <c r="U15" s="2"/>
+      <c r="V15" s="2"/>
+      <c r="W15" s="2"/>
+      <c r="X15" s="2"/>
+      <c r="Y15" s="2"/>
+      <c r="Z15" s="2"/>
+      <c r="AA15" s="2"/>
+    </row>
+    <row r="16" spans="1:27" s="52" customFormat="1" ht="144" x14ac:dyDescent="0.3">
+      <c r="A16" s="63" t="s">
+        <v>375</v>
+      </c>
+      <c r="B16" s="61" t="s">
+        <v>373</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="D16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2"/>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
+      <c r="P16" s="2"/>
+      <c r="Q16" s="2"/>
+      <c r="R16" s="2"/>
+      <c r="S16" s="2"/>
+      <c r="T16" s="2"/>
+      <c r="U16" s="2"/>
+      <c r="V16" s="2"/>
+      <c r="W16" s="2"/>
+      <c r="X16" s="2"/>
+      <c r="Y16" s="2"/>
+      <c r="Z16" s="2"/>
+      <c r="AA16" s="2"/>
+    </row>
+    <row r="17" spans="1:27" s="52" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A17" s="55" t="s">
+        <v>377</v>
+      </c>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
+      <c r="L17" s="2"/>
+      <c r="M17" s="2"/>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
+      <c r="P17" s="2"/>
+      <c r="Q17" s="2"/>
+      <c r="R17" s="2"/>
+      <c r="S17" s="2"/>
+      <c r="T17" s="2"/>
+      <c r="U17" s="2"/>
+      <c r="V17" s="2"/>
+      <c r="W17" s="2"/>
+      <c r="X17" s="2"/>
+      <c r="Y17" s="2"/>
+      <c r="Z17" s="2"/>
+      <c r="AA17" s="2"/>
+    </row>
+    <row r="18" spans="1:27" s="52" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A18" s="62" t="s">
+        <v>391</v>
+      </c>
+      <c r="B18" s="61" t="s">
+        <v>378</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="D18" s="61" t="s">
+        <v>385</v>
+      </c>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
+      <c r="L18" s="2"/>
+      <c r="M18" s="2"/>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
+      <c r="P18" s="2"/>
+      <c r="Q18" s="2"/>
+      <c r="R18" s="2"/>
+      <c r="S18" s="2"/>
+      <c r="T18" s="2"/>
+      <c r="U18" s="2"/>
+      <c r="V18" s="2"/>
+      <c r="W18" s="2"/>
+      <c r="X18" s="2"/>
+      <c r="Y18" s="2"/>
+      <c r="Z18" s="2"/>
+      <c r="AA18" s="2"/>
+    </row>
+    <row r="19" spans="1:27" s="52" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="55" t="s">
+        <v>388</v>
+      </c>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="2"/>
+      <c r="M19" s="2"/>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
+      <c r="P19" s="2"/>
+      <c r="Q19" s="2"/>
+      <c r="R19" s="2"/>
+      <c r="S19" s="2"/>
+      <c r="T19" s="2"/>
+      <c r="U19" s="2"/>
+      <c r="V19" s="2"/>
+      <c r="W19" s="2"/>
+      <c r="X19" s="2"/>
+      <c r="Y19" s="2"/>
+      <c r="Z19" s="2"/>
+      <c r="AA19" s="2"/>
+    </row>
+    <row r="20" spans="1:27" s="52" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A20" s="63" t="s">
+        <v>393</v>
+      </c>
+      <c r="B20" s="61" t="s">
+        <v>394</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="D20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
+      <c r="L20" s="2"/>
+      <c r="M20" s="2"/>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
+      <c r="P20" s="2"/>
+      <c r="Q20" s="2"/>
+      <c r="R20" s="2"/>
+      <c r="S20" s="2"/>
+      <c r="T20" s="2"/>
+      <c r="U20" s="2"/>
+      <c r="V20" s="2"/>
+      <c r="W20" s="2"/>
+      <c r="X20" s="2"/>
+      <c r="Y20" s="2"/>
+      <c r="Z20" s="2"/>
+      <c r="AA20" s="2"/>
+    </row>
+    <row r="21" spans="1:27" s="52" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="55" t="s">
+        <v>390</v>
+      </c>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2"/>
+      <c r="L21" s="2"/>
+      <c r="M21" s="2"/>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
+      <c r="P21" s="2"/>
+      <c r="Q21" s="2"/>
+      <c r="R21" s="2"/>
+      <c r="S21" s="2"/>
+      <c r="T21" s="2"/>
+      <c r="U21" s="2"/>
+      <c r="V21" s="2"/>
+      <c r="W21" s="2"/>
+      <c r="X21" s="2"/>
+      <c r="Y21" s="2"/>
+      <c r="Z21" s="2"/>
+      <c r="AA21" s="2"/>
+    </row>
+    <row r="22" spans="1:27" s="52" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A22" s="62" t="s">
+        <v>433</v>
+      </c>
+      <c r="B22" s="69" t="s">
+        <v>432</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="D22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2"/>
+      <c r="L22" s="2"/>
+      <c r="M22" s="2"/>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
+      <c r="P22" s="2"/>
+      <c r="Q22" s="2"/>
+      <c r="R22" s="2"/>
+      <c r="S22" s="2"/>
+      <c r="T22" s="2"/>
+      <c r="U22" s="2"/>
+      <c r="V22" s="2"/>
+      <c r="W22" s="2"/>
+      <c r="X22" s="2"/>
+      <c r="Y22" s="2"/>
+      <c r="Z22" s="2"/>
+      <c r="AA22" s="2"/>
+    </row>
+    <row r="23" spans="1:27" s="52" customFormat="1" ht="144" x14ac:dyDescent="0.3">
+      <c r="A23" s="67" t="s">
+        <v>410</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="D23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2"/>
+      <c r="L23" s="2"/>
+      <c r="M23" s="2"/>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
+      <c r="P23" s="2"/>
+      <c r="Q23" s="2"/>
+      <c r="R23" s="2"/>
+      <c r="S23" s="2"/>
+      <c r="T23" s="2"/>
+      <c r="U23" s="2"/>
+      <c r="V23" s="2"/>
+      <c r="W23" s="2"/>
+      <c r="X23" s="2"/>
+      <c r="Y23" s="2"/>
+      <c r="Z23" s="2"/>
+      <c r="AA23" s="2"/>
+    </row>
+    <row r="24" spans="1:27" s="52" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="55" t="s">
+        <v>396</v>
+      </c>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2"/>
+      <c r="L24" s="2"/>
+      <c r="M24" s="2"/>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
+      <c r="P24" s="2"/>
+      <c r="Q24" s="2"/>
+      <c r="R24" s="2"/>
+      <c r="S24" s="2"/>
+      <c r="T24" s="2"/>
+      <c r="U24" s="2"/>
+      <c r="V24" s="2"/>
+      <c r="W24" s="2"/>
+      <c r="X24" s="2"/>
+      <c r="Y24" s="2"/>
+      <c r="Z24" s="2"/>
+      <c r="AA24" s="2"/>
+    </row>
+    <row r="25" spans="1:27" s="52" customFormat="1" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A25" s="64" t="s">
+        <v>431</v>
+      </c>
+      <c r="B25" s="69" t="s">
+        <v>430</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="D25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2"/>
+      <c r="L25" s="2"/>
+      <c r="M25" s="2"/>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
+      <c r="P25" s="2"/>
+      <c r="Q25" s="2"/>
+      <c r="R25" s="2"/>
+      <c r="S25" s="2"/>
+      <c r="T25" s="2"/>
+      <c r="U25" s="2"/>
+      <c r="V25" s="2"/>
+      <c r="W25" s="2"/>
+      <c r="X25" s="2"/>
+      <c r="Y25" s="2"/>
+      <c r="Z25" s="2"/>
+      <c r="AA25" s="2"/>
+    </row>
+    <row r="26" spans="1:27" s="52" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A26" s="67" t="s">
+        <v>410</v>
+      </c>
+      <c r="B26" s="69"/>
+      <c r="C26" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="D26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+      <c r="K26" s="2"/>
+      <c r="L26" s="2"/>
+      <c r="M26" s="2"/>
+      <c r="N26" s="2"/>
+      <c r="O26" s="2"/>
+      <c r="P26" s="2"/>
+      <c r="Q26" s="2"/>
+      <c r="R26" s="2"/>
+      <c r="S26" s="2"/>
+      <c r="T26" s="2"/>
+      <c r="U26" s="2"/>
+      <c r="V26" s="2"/>
+      <c r="W26" s="2"/>
+      <c r="X26" s="2"/>
+      <c r="Y26" s="2"/>
+      <c r="Z26" s="2"/>
+      <c r="AA26" s="2"/>
+    </row>
+    <row r="27" spans="1:27" s="52" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+      <c r="A27" s="63" t="s">
+        <v>412</v>
+      </c>
+      <c r="B27" s="67" t="s">
+        <v>412</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="D27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
+      <c r="K27" s="2"/>
+      <c r="L27" s="2"/>
+      <c r="M27" s="2"/>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
+      <c r="P27" s="2"/>
+      <c r="Q27" s="2"/>
+      <c r="R27" s="2"/>
+      <c r="S27" s="2"/>
+      <c r="T27" s="2"/>
+      <c r="U27" s="2"/>
+      <c r="V27" s="2"/>
+      <c r="W27" s="2"/>
+      <c r="X27" s="2"/>
+      <c r="Y27" s="2"/>
+      <c r="Z27" s="2"/>
+      <c r="AA27" s="2"/>
+    </row>
+    <row r="28" spans="1:27" s="52" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="B28" s="65" t="s">
+        <v>407</v>
+      </c>
+      <c r="C28" s="61" t="s">
+        <v>406</v>
+      </c>
+      <c r="D28" s="2"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
+      <c r="K28" s="2"/>
+      <c r="L28" s="2"/>
+      <c r="M28" s="2"/>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
+      <c r="P28" s="2"/>
+      <c r="Q28" s="2"/>
+      <c r="R28" s="2"/>
+      <c r="S28" s="2"/>
+      <c r="T28" s="2"/>
+      <c r="U28" s="2"/>
+      <c r="V28" s="2"/>
+      <c r="W28" s="2"/>
+      <c r="X28" s="2"/>
+      <c r="Y28" s="2"/>
+      <c r="Z28" s="2"/>
+      <c r="AA28" s="2"/>
+    </row>
+    <row r="29" spans="1:27" s="52" customFormat="1" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="A29" s="2"/>
+      <c r="B29" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="D29" s="2"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="2"/>
+      <c r="K29" s="2"/>
+      <c r="L29" s="2"/>
+      <c r="M29" s="2"/>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
+      <c r="P29" s="2"/>
+      <c r="Q29" s="2"/>
+      <c r="R29" s="2"/>
+      <c r="S29" s="2"/>
+      <c r="T29" s="2"/>
+      <c r="U29" s="2"/>
+      <c r="V29" s="2"/>
+      <c r="W29" s="2"/>
+      <c r="X29" s="2"/>
+      <c r="Y29" s="2"/>
+      <c r="Z29" s="2"/>
+      <c r="AA29" s="2"/>
+    </row>
+    <row r="30" spans="1:27" s="52" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="B30" s="66" t="s">
+        <v>408</v>
+      </c>
+      <c r="C30" s="61" t="s">
+        <v>405</v>
+      </c>
+      <c r="D30" s="2"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="2"/>
+      <c r="K30" s="2"/>
+      <c r="L30" s="2"/>
+      <c r="M30" s="2"/>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
+      <c r="P30" s="2"/>
+      <c r="Q30" s="2"/>
+      <c r="R30" s="2"/>
+      <c r="S30" s="2"/>
+      <c r="T30" s="2"/>
+      <c r="U30" s="2"/>
+      <c r="V30" s="2"/>
+      <c r="W30" s="2"/>
+      <c r="X30" s="2"/>
+      <c r="Y30" s="2"/>
+      <c r="Z30" s="2"/>
+      <c r="AA30" s="2"/>
+    </row>
+    <row r="31" spans="1:27" s="52" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="55" t="s">
+        <v>409</v>
+      </c>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="2"/>
+      <c r="K31" s="2"/>
+      <c r="L31" s="2"/>
+      <c r="M31" s="2"/>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
+      <c r="P31" s="2"/>
+      <c r="Q31" s="2"/>
+      <c r="R31" s="2"/>
+      <c r="S31" s="2"/>
+      <c r="T31" s="2"/>
+      <c r="U31" s="2"/>
+      <c r="V31" s="2"/>
+      <c r="W31" s="2"/>
+      <c r="X31" s="2"/>
+      <c r="Y31" s="2"/>
+      <c r="Z31" s="2"/>
+      <c r="AA31" s="2"/>
+    </row>
+    <row r="32" spans="1:27" s="52" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A32" s="2"/>
+      <c r="B32" s="69" t="s">
+        <v>415</v>
+      </c>
+      <c r="C32" s="63" t="s">
+        <v>414</v>
+      </c>
+      <c r="D32" s="69" t="s">
+        <v>418</v>
+      </c>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="2"/>
+      <c r="K32" s="2"/>
+      <c r="L32" s="2"/>
+      <c r="M32" s="2"/>
+      <c r="N32" s="2"/>
+      <c r="O32" s="2"/>
+      <c r="P32" s="2"/>
+      <c r="Q32" s="2"/>
+      <c r="R32" s="2"/>
+      <c r="S32" s="2"/>
+      <c r="T32" s="2"/>
+      <c r="U32" s="2"/>
+      <c r="V32" s="2"/>
+      <c r="W32" s="2"/>
+      <c r="X32" s="2"/>
+      <c r="Y32" s="2"/>
+      <c r="Z32" s="2"/>
+      <c r="AA32" s="2"/>
+    </row>
+    <row r="33" spans="1:27" s="52" customFormat="1" ht="230.4" x14ac:dyDescent="0.3">
+      <c r="A33" s="69" t="s">
+        <v>425</v>
+      </c>
+      <c r="B33" s="69" t="s">
+        <v>426</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="D33" s="2"/>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
+      <c r="J33" s="2"/>
+      <c r="K33" s="2"/>
+      <c r="L33" s="2"/>
+      <c r="M33" s="2"/>
+      <c r="N33" s="2"/>
+      <c r="O33" s="2"/>
+      <c r="P33" s="2"/>
+      <c r="Q33" s="2"/>
+      <c r="R33" s="2"/>
+      <c r="S33" s="2"/>
+      <c r="T33" s="2"/>
+      <c r="U33" s="2"/>
+      <c r="V33" s="2"/>
+      <c r="W33" s="2"/>
+      <c r="X33" s="2"/>
+      <c r="Y33" s="2"/>
+      <c r="Z33" s="2"/>
+      <c r="AA33" s="2"/>
+    </row>
+    <row r="34" spans="1:27" s="52" customFormat="1" ht="216" x14ac:dyDescent="0.3">
+      <c r="A34" s="69" t="s">
+        <v>428</v>
+      </c>
+      <c r="B34" s="69" t="s">
+        <v>427</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
+      <c r="J34" s="2"/>
+      <c r="K34" s="2"/>
+      <c r="L34" s="2"/>
+      <c r="M34" s="2"/>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
+      <c r="P34" s="2"/>
+      <c r="Q34" s="2"/>
+      <c r="R34" s="2"/>
+      <c r="S34" s="2"/>
+      <c r="T34" s="2"/>
+      <c r="U34" s="2"/>
+      <c r="V34" s="2"/>
+      <c r="W34" s="2"/>
+      <c r="X34" s="2"/>
+      <c r="Y34" s="2"/>
+      <c r="Z34" s="2"/>
+      <c r="AA34" s="2"/>
+    </row>
+    <row r="35" spans="1:27" s="52" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A35" s="2"/>
+      <c r="B35" s="69" t="s">
+        <v>419</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="D35" s="69" t="s">
+        <v>420</v>
+      </c>
+      <c r="F35" s="2"/>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+      <c r="I35" s="2"/>
+      <c r="J35" s="2"/>
+      <c r="K35" s="2"/>
+      <c r="L35" s="2"/>
+      <c r="M35" s="2"/>
+      <c r="N35" s="2"/>
+      <c r="O35" s="2"/>
+      <c r="P35" s="2"/>
+      <c r="Q35" s="2"/>
+      <c r="R35" s="2"/>
+      <c r="S35" s="2"/>
+      <c r="T35" s="2"/>
+      <c r="U35" s="2"/>
+      <c r="V35" s="2"/>
+      <c r="W35" s="2"/>
+      <c r="X35" s="2"/>
+      <c r="Y35" s="2"/>
+      <c r="Z35" s="2"/>
+      <c r="AA35" s="2"/>
+    </row>
+    <row r="36" spans="1:27" s="52" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A36" s="69" t="s">
+        <v>429</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="D36" s="2"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+      <c r="J36" s="2"/>
+      <c r="K36" s="2"/>
+      <c r="L36" s="2"/>
+      <c r="M36" s="2"/>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
+      <c r="P36" s="2"/>
+      <c r="Q36" s="2"/>
+      <c r="R36" s="2"/>
+      <c r="S36" s="2"/>
+      <c r="T36" s="2"/>
+      <c r="U36" s="2"/>
+      <c r="V36" s="2"/>
+      <c r="W36" s="2"/>
+      <c r="X36" s="2"/>
+      <c r="Y36" s="2"/>
+      <c r="Z36" s="2"/>
+      <c r="AA36" s="2"/>
+    </row>
+    <row r="37" spans="1:27" s="52" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="70" t="s">
+        <v>435</v>
+      </c>
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="F37" s="2"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+      <c r="I37" s="2"/>
+      <c r="J37" s="2"/>
+      <c r="K37" s="2"/>
+      <c r="L37" s="2"/>
+      <c r="M37" s="2"/>
+      <c r="N37" s="2"/>
+      <c r="O37" s="2"/>
+      <c r="P37" s="2"/>
+      <c r="Q37" s="2"/>
+      <c r="R37" s="2"/>
+      <c r="S37" s="2"/>
+      <c r="T37" s="2"/>
+      <c r="U37" s="2"/>
+      <c r="V37" s="2"/>
+      <c r="W37" s="2"/>
+      <c r="X37" s="2"/>
+      <c r="Y37" s="2"/>
+      <c r="Z37" s="2"/>
+      <c r="AA37" s="2"/>
+    </row>
+    <row r="38" spans="1:27" s="52" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A38" s="2"/>
+      <c r="B38" s="2"/>
+      <c r="C38" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="D38" s="2"/>
+      <c r="F38" s="2"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+      <c r="I38" s="2"/>
+      <c r="J38" s="2"/>
+      <c r="K38" s="2"/>
+      <c r="L38" s="2"/>
+      <c r="M38" s="2"/>
+      <c r="N38" s="2"/>
+      <c r="O38" s="2"/>
+      <c r="P38" s="2"/>
+      <c r="Q38" s="2"/>
+      <c r="R38" s="2"/>
+      <c r="S38" s="2"/>
+      <c r="T38" s="2"/>
+      <c r="U38" s="2"/>
+      <c r="V38" s="2"/>
+      <c r="W38" s="2"/>
+      <c r="X38" s="2"/>
+      <c r="Y38" s="2"/>
+      <c r="Z38" s="2"/>
+      <c r="AA38" s="2"/>
+    </row>
+    <row r="39" spans="1:27" s="52" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A39" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="C39" s="69" t="s">
+        <v>442</v>
+      </c>
+      <c r="D39" s="2"/>
+      <c r="F39" s="2"/>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
+      <c r="I39" s="2"/>
+      <c r="J39" s="2"/>
+      <c r="K39" s="2"/>
+      <c r="L39" s="2"/>
+      <c r="M39" s="2"/>
+      <c r="N39" s="2"/>
+      <c r="O39" s="2"/>
+      <c r="P39" s="2"/>
+      <c r="Q39" s="2"/>
+      <c r="R39" s="2"/>
+      <c r="S39" s="2"/>
+      <c r="T39" s="2"/>
+      <c r="U39" s="2"/>
+      <c r="V39" s="2"/>
+      <c r="W39" s="2"/>
+      <c r="X39" s="2"/>
+      <c r="Y39" s="2"/>
+      <c r="Z39" s="2"/>
+      <c r="AA39" s="2"/>
+    </row>
+    <row r="40" spans="1:27" s="52" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A40" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="B40" s="2"/>
+      <c r="C40" s="69" t="s">
+        <v>441</v>
+      </c>
+      <c r="D40" s="2"/>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+      <c r="I40" s="2"/>
+      <c r="J40" s="2"/>
+      <c r="K40" s="2"/>
+      <c r="L40" s="2"/>
+      <c r="M40" s="2"/>
+      <c r="N40" s="2"/>
+      <c r="O40" s="2"/>
+      <c r="P40" s="2"/>
+      <c r="Q40" s="2"/>
+      <c r="R40" s="2"/>
+      <c r="S40" s="2"/>
+      <c r="T40" s="2"/>
+      <c r="U40" s="2"/>
+      <c r="V40" s="2"/>
+      <c r="W40" s="2"/>
+      <c r="X40" s="2"/>
+      <c r="Y40" s="2"/>
+      <c r="Z40" s="2"/>
+      <c r="AA40" s="2"/>
+    </row>
+    <row r="41" spans="1:27" s="52" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A41" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="C41" s="69" t="s">
+        <v>443</v>
+      </c>
+      <c r="D41" s="2"/>
+      <c r="F41" s="2"/>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
+      <c r="I41" s="2"/>
+      <c r="J41" s="2"/>
+      <c r="K41" s="2"/>
+      <c r="L41" s="2"/>
+      <c r="M41" s="2"/>
+      <c r="N41" s="2"/>
+      <c r="O41" s="2"/>
+      <c r="P41" s="2"/>
+      <c r="Q41" s="2"/>
+      <c r="R41" s="2"/>
+      <c r="S41" s="2"/>
+      <c r="T41" s="2"/>
+      <c r="U41" s="2"/>
+      <c r="V41" s="2"/>
+      <c r="W41" s="2"/>
+      <c r="X41" s="2"/>
+      <c r="Y41" s="2"/>
+      <c r="Z41" s="2"/>
+      <c r="AA41" s="2"/>
+    </row>
+    <row r="42" spans="1:27" s="52" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A42" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="B42" s="69" t="s">
+        <v>447</v>
+      </c>
+      <c r="C42" s="69" t="s">
+        <v>444</v>
+      </c>
+      <c r="D42" s="2"/>
+      <c r="F42" s="2"/>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2"/>
+      <c r="I42" s="2"/>
+      <c r="J42" s="2"/>
+      <c r="K42" s="2"/>
+      <c r="L42" s="2"/>
+      <c r="M42" s="2"/>
+      <c r="N42" s="2"/>
+      <c r="O42" s="2"/>
+      <c r="P42" s="2"/>
+      <c r="Q42" s="2"/>
+      <c r="R42" s="2"/>
+      <c r="S42" s="2"/>
+      <c r="T42" s="2"/>
+      <c r="U42" s="2"/>
+      <c r="V42" s="2"/>
+      <c r="W42" s="2"/>
+      <c r="X42" s="2"/>
+      <c r="Y42" s="2"/>
+      <c r="Z42" s="2"/>
+      <c r="AA42" s="2"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D4" r:id="rId1" location=":~:text=%D0%A1%D0%BE%D0%B7%D0%B4%D0%B0%D0%BD%D0%B8%D0%B5%20%D0%B8%20%D1%83%D0%B4%D0%B0%D0%BB%D0%B5%D0%BD%D0%B8%D0%B5%20%D1%82%D0%B0%D0%B1%D0%BB%D0%B8%D1%86" xr:uid="{410137C7-8009-4D89-AC4A-85676062AE90}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5E68B7E-90B4-48CB-8941-663F5884FA9B}">
+  <sheetPr>
+    <tabColor theme="9" tint="0.39997558519241921"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A2:E15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="36" style="2" customWidth="1"/>
+    <col min="2" max="2" width="50.5546875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="71.21875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="56.44140625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="6.21875" style="52" customWidth="1"/>
+    <col min="6" max="6" width="43.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="55.109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="67.88671875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="64.33203125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="7.77734375" style="2" customWidth="1"/>
+    <col min="11" max="11" width="39.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="48.88671875" style="2" customWidth="1"/>
+    <col min="13" max="13" width="72.6640625" style="2" customWidth="1"/>
+    <col min="14" max="14" width="43.88671875" style="2" customWidth="1"/>
+    <col min="15" max="15" width="7.77734375" style="2" customWidth="1"/>
+    <col min="16" max="16" width="56.77734375" style="2" customWidth="1"/>
+    <col min="17" max="17" width="46.77734375" style="2" customWidth="1"/>
+    <col min="18" max="18" width="62.88671875" style="2" customWidth="1"/>
+    <col min="19" max="19" width="49.21875" style="2" customWidth="1"/>
+    <col min="20" max="20" width="8.77734375" style="2"/>
+    <col min="21" max="21" width="67.77734375" style="2" customWidth="1"/>
+    <col min="22" max="22" width="68.33203125" style="2" customWidth="1"/>
+    <col min="23" max="24" width="59.33203125" style="2" customWidth="1"/>
+    <col min="25" max="25" width="59.6640625" style="2" customWidth="1"/>
+    <col min="26" max="26" width="99.44140625" style="2" customWidth="1"/>
+    <col min="27" max="27" width="41.21875" style="2" customWidth="1"/>
+    <col min="28" max="16384" width="8.77734375" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:5" s="51" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="E2" s="52"/>
+    </row>
+    <row r="3" spans="1:5" s="52" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="26" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" s="52" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="71" t="s">
+        <v>449</v>
+      </c>
+      <c r="B4" s="48"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="9"/>
+    </row>
+    <row r="5" spans="1:5" s="52" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A5" s="9"/>
+      <c r="B5" s="48"/>
+      <c r="C5" s="74" t="s">
+        <v>450</v>
+      </c>
+      <c r="D5" s="9"/>
+    </row>
+    <row r="6" spans="1:5" s="52" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="75" t="s">
+        <v>451</v>
+      </c>
+      <c r="B6" s="48"/>
+      <c r="C6" s="48"/>
+      <c r="D6" s="9"/>
+    </row>
+    <row r="7" spans="1:5" s="52" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="9"/>
+      <c r="B7" s="48"/>
+      <c r="C7" s="74" t="s">
+        <v>452</v>
+      </c>
+      <c r="D7" s="9"/>
+    </row>
+    <row r="8" spans="1:5" s="52" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="9"/>
+      <c r="B8" s="48"/>
+      <c r="C8" s="74" t="s">
+        <v>453</v>
+      </c>
+      <c r="D8" s="9"/>
+    </row>
+    <row r="9" spans="1:5" s="52" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="9"/>
+      <c r="B9" s="48"/>
+      <c r="C9" s="48"/>
+      <c r="D9" s="9"/>
+    </row>
+    <row r="10" spans="1:5" s="52" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="9"/>
+      <c r="B10" s="48"/>
+      <c r="C10" s="48"/>
+      <c r="D10" s="9"/>
+    </row>
+    <row r="11" spans="1:5" s="52" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="9"/>
+      <c r="B11" s="48"/>
+      <c r="C11" s="48"/>
+      <c r="D11" s="9"/>
+    </row>
+    <row r="12" spans="1:5" s="52" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="9"/>
+      <c r="B12" s="48"/>
+      <c r="C12" s="48"/>
+      <c r="D12" s="9"/>
+    </row>
+    <row r="13" spans="1:5" s="52" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="9"/>
+      <c r="B13" s="48"/>
+      <c r="C13" s="48"/>
+      <c r="D13" s="9"/>
+    </row>
+    <row r="14" spans="1:5" s="52" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="9"/>
+      <c r="B14" s="48"/>
+      <c r="C14" s="48"/>
+      <c r="D14" s="9"/>
+    </row>
+    <row r="15" spans="1:5" s="52" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="9"/>
+      <c r="B15" s="48"/>
+      <c r="C15" s="48"/>
+      <c r="D15" s="9"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D3" r:id="rId1" location=":~:text=%D0%A1%D0%BE%D0%B7%D0%B4%D0%B0%D0%BD%D0%B8%D0%B5%20%D0%B8%20%D1%83%D0%B4%D0%B0%D0%BB%D0%B5%D0%BD%D0%B8%D0%B5%20%D1%82%D0%B0%D0%B1%D0%BB%D0%B8%D1%86" xr:uid="{00C82B12-02C8-4568-A693-2C76F456F5E9}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1F646E2-B598-4143-89B5-75F807CE8970}">
   <sheetPr>
     <tabColor rgb="FF00B050"/>
@@ -19844,7 +21937,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87C455FF-42A2-4363-8055-67FDFE85198A}">
   <sheetPr>
     <tabColor rgb="FF00B050"/>
@@ -20821,887 +22914,4 @@
   <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4794FD93-B283-45AF-BCD9-82490C321ADD}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A2:V48"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="36" style="1" customWidth="1"/>
-    <col min="2" max="2" width="50.5546875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="71.21875" style="4" customWidth="1"/>
-    <col min="4" max="4" width="56.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="6.21875" style="7" customWidth="1"/>
-    <col min="6" max="6" width="43.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="55.109375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="67.88671875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="64.33203125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="7.77734375" style="7" customWidth="1"/>
-    <col min="11" max="11" width="39.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="48.88671875" style="1" customWidth="1"/>
-    <col min="13" max="13" width="72.6640625" style="1" customWidth="1"/>
-    <col min="14" max="14" width="43.88671875" style="1" customWidth="1"/>
-    <col min="15" max="15" width="7.77734375" style="7" customWidth="1"/>
-    <col min="16" max="16" width="56.77734375" style="2" customWidth="1"/>
-    <col min="17" max="17" width="46.77734375" style="2" customWidth="1"/>
-    <col min="18" max="18" width="62.88671875" style="2" customWidth="1"/>
-    <col min="19" max="19" width="49.21875" style="1" customWidth="1"/>
-    <col min="20" max="20" width="8.77734375" style="8"/>
-    <col min="21" max="21" width="67.77734375" style="2" customWidth="1"/>
-    <col min="22" max="22" width="68.33203125" style="1" customWidth="1"/>
-    <col min="23" max="24" width="59.33203125" style="1" customWidth="1"/>
-    <col min="25" max="25" width="59.6640625" style="1" customWidth="1"/>
-    <col min="26" max="26" width="99.44140625" style="1" customWidth="1"/>
-    <col min="27" max="27" width="41.21875" style="1" customWidth="1"/>
-    <col min="28" max="16384" width="8.77734375" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A2" s="3"/>
-      <c r="B2" s="5"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
-      <c r="N2" s="3"/>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="5"/>
-      <c r="R2" s="5"/>
-      <c r="S2" s="5"/>
-      <c r="U2" s="5"/>
-    </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="9"/>
-      <c r="P3" s="1"/>
-      <c r="U3" s="1"/>
-      <c r="V3" s="2"/>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A4" s="44" t="s">
-        <v>218</v>
-      </c>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A5" s="9"/>
-      <c r="B5" s="42" t="s">
-        <v>220</v>
-      </c>
-      <c r="C5" s="42" t="s">
-        <v>219</v>
-      </c>
-      <c r="D5" s="9"/>
-    </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A6" s="44" t="s">
-        <v>217</v>
-      </c>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-    </row>
-    <row r="7" spans="1:22" ht="230.4" x14ac:dyDescent="0.3">
-      <c r="A7" s="9"/>
-      <c r="B7" s="9"/>
-      <c r="C7" s="42" t="s">
-        <v>229</v>
-      </c>
-      <c r="D7" s="9"/>
-    </row>
-    <row r="8" spans="1:22" ht="331.2" x14ac:dyDescent="0.3">
-      <c r="A8" s="9"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="42" t="s">
-        <v>230</v>
-      </c>
-      <c r="D8" s="9"/>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A9" s="9"/>
-      <c r="B9" s="9"/>
-      <c r="D9" s="9"/>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A10" s="9"/>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A11" s="9"/>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A12" s="9"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A13" s="9"/>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A14" s="9"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A15" s="9"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A16" s="9"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-    </row>
-    <row r="17" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="9"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
-      <c r="K17" s="1"/>
-      <c r="L17" s="1"/>
-      <c r="M17" s="1"/>
-      <c r="N17" s="1"/>
-      <c r="P17" s="2"/>
-      <c r="Q17" s="2"/>
-      <c r="R17" s="2"/>
-      <c r="S17" s="1"/>
-      <c r="T17" s="8"/>
-      <c r="U17" s="2"/>
-      <c r="V17" s="1"/>
-    </row>
-    <row r="18" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="9"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
-      <c r="K18" s="1"/>
-      <c r="L18" s="1"/>
-      <c r="M18" s="1"/>
-      <c r="N18" s="1"/>
-      <c r="P18" s="2"/>
-      <c r="Q18" s="2"/>
-      <c r="R18" s="2"/>
-      <c r="S18" s="1"/>
-      <c r="T18" s="8"/>
-      <c r="U18" s="2"/>
-      <c r="V18" s="1"/>
-    </row>
-    <row r="19" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="9"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
-      <c r="K19" s="1"/>
-      <c r="L19" s="1"/>
-      <c r="M19" s="1"/>
-      <c r="N19" s="1"/>
-      <c r="P19" s="2"/>
-      <c r="Q19" s="2"/>
-      <c r="R19" s="2"/>
-      <c r="S19" s="1"/>
-      <c r="T19" s="8"/>
-      <c r="U19" s="2"/>
-      <c r="V19" s="1"/>
-    </row>
-    <row r="20" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="9"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="F20" s="1"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
-      <c r="K20" s="1"/>
-      <c r="L20" s="1"/>
-      <c r="M20" s="1"/>
-      <c r="N20" s="1"/>
-      <c r="P20" s="2"/>
-      <c r="Q20" s="2"/>
-      <c r="R20" s="2"/>
-      <c r="S20" s="1"/>
-      <c r="T20" s="8"/>
-      <c r="U20" s="2"/>
-      <c r="V20" s="1"/>
-    </row>
-    <row r="21" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="9"/>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
-      <c r="F21" s="1"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="1"/>
-      <c r="I21" s="1"/>
-      <c r="K21" s="1"/>
-      <c r="L21" s="1"/>
-      <c r="M21" s="1"/>
-      <c r="N21" s="1"/>
-      <c r="P21" s="2"/>
-      <c r="Q21" s="2"/>
-      <c r="R21" s="2"/>
-      <c r="S21" s="1"/>
-      <c r="T21" s="8"/>
-      <c r="U21" s="2"/>
-      <c r="V21" s="1"/>
-    </row>
-    <row r="22" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="9"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
-      <c r="F22" s="1"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="1"/>
-      <c r="I22" s="1"/>
-      <c r="K22" s="1"/>
-      <c r="L22" s="1"/>
-      <c r="M22" s="1"/>
-      <c r="N22" s="1"/>
-      <c r="P22" s="2"/>
-      <c r="Q22" s="2"/>
-      <c r="R22" s="2"/>
-      <c r="S22" s="1"/>
-      <c r="T22" s="8"/>
-      <c r="U22" s="2"/>
-      <c r="V22" s="1"/>
-    </row>
-    <row r="23" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="9"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-      <c r="F23" s="1"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="1"/>
-      <c r="I23" s="1"/>
-      <c r="K23" s="1"/>
-      <c r="L23" s="1"/>
-      <c r="M23" s="1"/>
-      <c r="N23" s="1"/>
-      <c r="P23" s="2"/>
-      <c r="Q23" s="2"/>
-      <c r="R23" s="2"/>
-      <c r="S23" s="1"/>
-      <c r="T23" s="8"/>
-      <c r="U23" s="2"/>
-      <c r="V23" s="1"/>
-    </row>
-    <row r="24" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="9"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="1"/>
-      <c r="I24" s="1"/>
-      <c r="K24" s="1"/>
-      <c r="L24" s="1"/>
-      <c r="M24" s="1"/>
-      <c r="N24" s="1"/>
-      <c r="P24" s="2"/>
-      <c r="Q24" s="2"/>
-      <c r="R24" s="2"/>
-      <c r="S24" s="1"/>
-      <c r="T24" s="8"/>
-      <c r="U24" s="2"/>
-      <c r="V24" s="1"/>
-    </row>
-    <row r="25" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="9"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
-      <c r="F25" s="1"/>
-      <c r="G25" s="2"/>
-      <c r="H25" s="1"/>
-      <c r="I25" s="1"/>
-      <c r="K25" s="1"/>
-      <c r="L25" s="1"/>
-      <c r="M25" s="1"/>
-      <c r="N25" s="1"/>
-      <c r="P25" s="2"/>
-      <c r="Q25" s="2"/>
-      <c r="R25" s="2"/>
-      <c r="S25" s="1"/>
-      <c r="T25" s="8"/>
-      <c r="U25" s="2"/>
-      <c r="V25" s="1"/>
-    </row>
-    <row r="26" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="9"/>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="9"/>
-      <c r="F26" s="1"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="1"/>
-      <c r="I26" s="1"/>
-      <c r="K26" s="1"/>
-      <c r="L26" s="1"/>
-      <c r="M26" s="1"/>
-      <c r="N26" s="1"/>
-      <c r="P26" s="2"/>
-      <c r="Q26" s="2"/>
-      <c r="R26" s="2"/>
-      <c r="S26" s="1"/>
-      <c r="T26" s="8"/>
-      <c r="U26" s="2"/>
-      <c r="V26" s="1"/>
-    </row>
-    <row r="27" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="9"/>
-      <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="9"/>
-      <c r="F27" s="1"/>
-      <c r="G27" s="2"/>
-      <c r="H27" s="1"/>
-      <c r="I27" s="1"/>
-      <c r="K27" s="1"/>
-      <c r="L27" s="1"/>
-      <c r="M27" s="1"/>
-      <c r="N27" s="1"/>
-      <c r="P27" s="2"/>
-      <c r="Q27" s="2"/>
-      <c r="R27" s="2"/>
-      <c r="S27" s="1"/>
-      <c r="T27" s="8"/>
-      <c r="U27" s="2"/>
-      <c r="V27" s="1"/>
-    </row>
-    <row r="28" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="9"/>
-      <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
-      <c r="D28" s="9"/>
-      <c r="F28" s="1"/>
-      <c r="G28" s="2"/>
-      <c r="H28" s="1"/>
-      <c r="I28" s="1"/>
-      <c r="K28" s="1"/>
-      <c r="L28" s="1"/>
-      <c r="M28" s="1"/>
-      <c r="N28" s="1"/>
-      <c r="P28" s="2"/>
-      <c r="Q28" s="2"/>
-      <c r="R28" s="2"/>
-      <c r="S28" s="1"/>
-      <c r="T28" s="8"/>
-      <c r="U28" s="2"/>
-      <c r="V28" s="1"/>
-    </row>
-    <row r="29" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="9"/>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-      <c r="F29" s="1"/>
-      <c r="G29" s="2"/>
-      <c r="H29" s="1"/>
-      <c r="I29" s="1"/>
-      <c r="K29" s="1"/>
-      <c r="L29" s="1"/>
-      <c r="M29" s="1"/>
-      <c r="N29" s="1"/>
-      <c r="P29" s="2"/>
-      <c r="Q29" s="2"/>
-      <c r="R29" s="2"/>
-      <c r="S29" s="1"/>
-      <c r="T29" s="8"/>
-      <c r="U29" s="2"/>
-      <c r="V29" s="1"/>
-    </row>
-    <row r="30" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="9"/>
-      <c r="B30" s="9"/>
-      <c r="C30" s="9"/>
-      <c r="D30" s="9"/>
-      <c r="F30" s="1"/>
-      <c r="G30" s="2"/>
-      <c r="H30" s="1"/>
-      <c r="I30" s="1"/>
-      <c r="K30" s="1"/>
-      <c r="L30" s="1"/>
-      <c r="M30" s="1"/>
-      <c r="N30" s="1"/>
-      <c r="P30" s="2"/>
-      <c r="Q30" s="2"/>
-      <c r="R30" s="2"/>
-      <c r="S30" s="1"/>
-      <c r="T30" s="8"/>
-      <c r="U30" s="2"/>
-      <c r="V30" s="1"/>
-    </row>
-    <row r="31" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="9"/>
-      <c r="B31" s="9"/>
-      <c r="C31" s="9"/>
-      <c r="D31" s="9"/>
-      <c r="F31" s="1"/>
-      <c r="G31" s="2"/>
-      <c r="H31" s="1"/>
-      <c r="I31" s="1"/>
-      <c r="K31" s="1"/>
-      <c r="L31" s="1"/>
-      <c r="M31" s="1"/>
-      <c r="N31" s="1"/>
-      <c r="P31" s="2"/>
-      <c r="Q31" s="2"/>
-      <c r="R31" s="2"/>
-      <c r="S31" s="1"/>
-      <c r="T31" s="8"/>
-      <c r="U31" s="2"/>
-      <c r="V31" s="1"/>
-    </row>
-    <row r="32" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="9"/>
-      <c r="B32" s="9"/>
-      <c r="C32" s="9"/>
-      <c r="D32" s="9"/>
-      <c r="F32" s="1"/>
-      <c r="G32" s="2"/>
-      <c r="H32" s="1"/>
-      <c r="I32" s="1"/>
-      <c r="K32" s="1"/>
-      <c r="L32" s="1"/>
-      <c r="M32" s="1"/>
-      <c r="N32" s="1"/>
-      <c r="P32" s="2"/>
-      <c r="Q32" s="2"/>
-      <c r="R32" s="2"/>
-      <c r="S32" s="1"/>
-      <c r="T32" s="8"/>
-      <c r="U32" s="2"/>
-      <c r="V32" s="1"/>
-    </row>
-    <row r="33" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="9"/>
-      <c r="B33" s="9"/>
-      <c r="C33" s="9"/>
-      <c r="D33" s="9"/>
-      <c r="F33" s="1"/>
-      <c r="G33" s="2"/>
-      <c r="H33" s="1"/>
-      <c r="I33" s="1"/>
-      <c r="K33" s="1"/>
-      <c r="L33" s="1"/>
-      <c r="M33" s="1"/>
-      <c r="N33" s="1"/>
-      <c r="P33" s="2"/>
-      <c r="Q33" s="2"/>
-      <c r="R33" s="2"/>
-      <c r="S33" s="1"/>
-      <c r="T33" s="8"/>
-      <c r="U33" s="2"/>
-      <c r="V33" s="1"/>
-    </row>
-    <row r="34" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="9"/>
-      <c r="B34" s="9"/>
-      <c r="C34" s="9"/>
-      <c r="D34" s="9"/>
-      <c r="F34" s="1"/>
-      <c r="G34" s="2"/>
-      <c r="H34" s="1"/>
-      <c r="I34" s="1"/>
-      <c r="K34" s="1"/>
-      <c r="L34" s="1"/>
-      <c r="M34" s="1"/>
-      <c r="N34" s="1"/>
-      <c r="P34" s="2"/>
-      <c r="Q34" s="2"/>
-      <c r="R34" s="2"/>
-      <c r="S34" s="1"/>
-      <c r="T34" s="8"/>
-      <c r="U34" s="2"/>
-      <c r="V34" s="1"/>
-    </row>
-    <row r="35" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="9"/>
-      <c r="B35" s="9"/>
-      <c r="C35" s="9"/>
-      <c r="D35" s="9"/>
-      <c r="F35" s="1"/>
-      <c r="G35" s="2"/>
-      <c r="H35" s="1"/>
-      <c r="I35" s="1"/>
-      <c r="K35" s="1"/>
-      <c r="L35" s="1"/>
-      <c r="M35" s="1"/>
-      <c r="N35" s="1"/>
-      <c r="P35" s="2"/>
-      <c r="Q35" s="2"/>
-      <c r="R35" s="2"/>
-      <c r="S35" s="1"/>
-      <c r="T35" s="8"/>
-      <c r="U35" s="2"/>
-      <c r="V35" s="1"/>
-    </row>
-    <row r="36" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="9"/>
-      <c r="B36" s="9"/>
-      <c r="C36" s="9"/>
-      <c r="D36" s="9"/>
-      <c r="F36" s="1"/>
-      <c r="G36" s="2"/>
-      <c r="H36" s="1"/>
-      <c r="I36" s="1"/>
-      <c r="K36" s="1"/>
-      <c r="L36" s="1"/>
-      <c r="M36" s="1"/>
-      <c r="N36" s="1"/>
-      <c r="P36" s="2"/>
-      <c r="Q36" s="2"/>
-      <c r="R36" s="2"/>
-      <c r="S36" s="1"/>
-      <c r="T36" s="8"/>
-      <c r="U36" s="2"/>
-      <c r="V36" s="1"/>
-    </row>
-    <row r="37" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="9"/>
-      <c r="B37" s="9"/>
-      <c r="C37" s="9"/>
-      <c r="D37" s="9"/>
-      <c r="F37" s="1"/>
-      <c r="G37" s="2"/>
-      <c r="H37" s="1"/>
-      <c r="I37" s="1"/>
-      <c r="K37" s="1"/>
-      <c r="L37" s="1"/>
-      <c r="M37" s="1"/>
-      <c r="N37" s="1"/>
-      <c r="P37" s="2"/>
-      <c r="Q37" s="2"/>
-      <c r="R37" s="2"/>
-      <c r="S37" s="1"/>
-      <c r="T37" s="8"/>
-      <c r="U37" s="2"/>
-      <c r="V37" s="1"/>
-    </row>
-    <row r="38" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="9"/>
-      <c r="B38" s="9"/>
-      <c r="C38" s="9"/>
-      <c r="D38" s="9"/>
-      <c r="F38" s="1"/>
-      <c r="G38" s="2"/>
-      <c r="H38" s="1"/>
-      <c r="I38" s="1"/>
-      <c r="K38" s="1"/>
-      <c r="L38" s="1"/>
-      <c r="M38" s="1"/>
-      <c r="N38" s="1"/>
-      <c r="P38" s="2"/>
-      <c r="Q38" s="2"/>
-      <c r="R38" s="2"/>
-      <c r="S38" s="1"/>
-      <c r="T38" s="8"/>
-      <c r="U38" s="2"/>
-      <c r="V38" s="1"/>
-    </row>
-    <row r="39" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="9"/>
-      <c r="B39" s="9"/>
-      <c r="C39" s="9"/>
-      <c r="D39" s="9"/>
-      <c r="F39" s="1"/>
-      <c r="G39" s="2"/>
-      <c r="H39" s="1"/>
-      <c r="I39" s="1"/>
-      <c r="K39" s="1"/>
-      <c r="L39" s="1"/>
-      <c r="M39" s="1"/>
-      <c r="N39" s="1"/>
-      <c r="P39" s="2"/>
-      <c r="Q39" s="2"/>
-      <c r="R39" s="2"/>
-      <c r="S39" s="1"/>
-      <c r="T39" s="8"/>
-      <c r="U39" s="2"/>
-      <c r="V39" s="1"/>
-    </row>
-    <row r="40" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="9"/>
-      <c r="B40" s="9"/>
-      <c r="C40" s="9"/>
-      <c r="D40" s="9"/>
-      <c r="F40" s="1"/>
-      <c r="G40" s="2"/>
-      <c r="H40" s="1"/>
-      <c r="I40" s="1"/>
-      <c r="K40" s="1"/>
-      <c r="L40" s="1"/>
-      <c r="M40" s="1"/>
-      <c r="N40" s="1"/>
-      <c r="P40" s="2"/>
-      <c r="Q40" s="2"/>
-      <c r="R40" s="2"/>
-      <c r="S40" s="1"/>
-      <c r="T40" s="8"/>
-      <c r="U40" s="2"/>
-      <c r="V40" s="1"/>
-    </row>
-    <row r="41" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="9"/>
-      <c r="B41" s="9"/>
-      <c r="C41" s="9"/>
-      <c r="D41" s="9"/>
-      <c r="F41" s="1"/>
-      <c r="G41" s="2"/>
-      <c r="H41" s="1"/>
-      <c r="I41" s="1"/>
-      <c r="K41" s="1"/>
-      <c r="L41" s="1"/>
-      <c r="M41" s="1"/>
-      <c r="N41" s="1"/>
-      <c r="P41" s="2"/>
-      <c r="Q41" s="2"/>
-      <c r="R41" s="2"/>
-      <c r="S41" s="1"/>
-      <c r="T41" s="8"/>
-      <c r="U41" s="2"/>
-      <c r="V41" s="1"/>
-    </row>
-    <row r="42" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="9"/>
-      <c r="B42" s="9"/>
-      <c r="C42" s="9"/>
-      <c r="D42" s="9"/>
-      <c r="F42" s="1"/>
-      <c r="G42" s="2"/>
-      <c r="H42" s="1"/>
-      <c r="I42" s="1"/>
-      <c r="K42" s="1"/>
-      <c r="L42" s="1"/>
-      <c r="M42" s="1"/>
-      <c r="N42" s="1"/>
-      <c r="P42" s="2"/>
-      <c r="Q42" s="2"/>
-      <c r="R42" s="2"/>
-      <c r="S42" s="1"/>
-      <c r="T42" s="8"/>
-      <c r="U42" s="2"/>
-      <c r="V42" s="1"/>
-    </row>
-    <row r="43" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="9"/>
-      <c r="B43" s="9"/>
-      <c r="C43" s="9"/>
-      <c r="D43" s="9"/>
-      <c r="F43" s="1"/>
-      <c r="G43" s="2"/>
-      <c r="H43" s="1"/>
-      <c r="I43" s="1"/>
-      <c r="K43" s="1"/>
-      <c r="L43" s="1"/>
-      <c r="M43" s="1"/>
-      <c r="N43" s="1"/>
-      <c r="P43" s="2"/>
-      <c r="Q43" s="2"/>
-      <c r="R43" s="2"/>
-      <c r="S43" s="1"/>
-      <c r="T43" s="8"/>
-      <c r="U43" s="2"/>
-      <c r="V43" s="1"/>
-    </row>
-    <row r="44" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="9"/>
-      <c r="B44" s="9"/>
-      <c r="C44" s="9"/>
-      <c r="D44" s="9"/>
-      <c r="F44" s="1"/>
-      <c r="G44" s="2"/>
-      <c r="H44" s="1"/>
-      <c r="I44" s="1"/>
-      <c r="K44" s="1"/>
-      <c r="L44" s="1"/>
-      <c r="M44" s="1"/>
-      <c r="N44" s="1"/>
-      <c r="P44" s="2"/>
-      <c r="Q44" s="2"/>
-      <c r="R44" s="2"/>
-      <c r="S44" s="1"/>
-      <c r="T44" s="8"/>
-      <c r="U44" s="2"/>
-      <c r="V44" s="1"/>
-    </row>
-    <row r="45" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="9"/>
-      <c r="B45" s="9"/>
-      <c r="C45" s="9"/>
-      <c r="D45" s="9"/>
-      <c r="F45" s="1"/>
-      <c r="G45" s="2"/>
-      <c r="H45" s="1"/>
-      <c r="I45" s="1"/>
-      <c r="K45" s="1"/>
-      <c r="L45" s="1"/>
-      <c r="M45" s="1"/>
-      <c r="N45" s="1"/>
-      <c r="P45" s="2"/>
-      <c r="Q45" s="2"/>
-      <c r="R45" s="2"/>
-      <c r="S45" s="1"/>
-      <c r="T45" s="8"/>
-      <c r="U45" s="2"/>
-      <c r="V45" s="1"/>
-    </row>
-    <row r="46" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="9"/>
-      <c r="B46" s="9"/>
-      <c r="C46" s="9"/>
-      <c r="D46" s="9"/>
-      <c r="F46" s="1"/>
-      <c r="G46" s="2"/>
-      <c r="H46" s="1"/>
-      <c r="I46" s="1"/>
-      <c r="K46" s="1"/>
-      <c r="L46" s="1"/>
-      <c r="M46" s="1"/>
-      <c r="N46" s="1"/>
-      <c r="P46" s="2"/>
-      <c r="Q46" s="2"/>
-      <c r="R46" s="2"/>
-      <c r="S46" s="1"/>
-      <c r="T46" s="8"/>
-      <c r="U46" s="2"/>
-      <c r="V46" s="1"/>
-    </row>
-    <row r="47" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="9"/>
-      <c r="B47" s="9"/>
-      <c r="C47" s="9"/>
-      <c r="D47" s="9"/>
-      <c r="F47" s="1"/>
-      <c r="G47" s="2"/>
-      <c r="H47" s="1"/>
-      <c r="I47" s="1"/>
-      <c r="K47" s="1"/>
-      <c r="L47" s="1"/>
-      <c r="M47" s="1"/>
-      <c r="N47" s="1"/>
-      <c r="P47" s="2"/>
-      <c r="Q47" s="2"/>
-      <c r="R47" s="2"/>
-      <c r="S47" s="1"/>
-      <c r="T47" s="8"/>
-      <c r="U47" s="2"/>
-      <c r="V47" s="1"/>
-    </row>
-    <row r="48" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="9"/>
-      <c r="B48" s="9"/>
-      <c r="C48" s="9"/>
-      <c r="D48" s="9"/>
-      <c r="F48" s="1"/>
-      <c r="G48" s="2"/>
-      <c r="H48" s="1"/>
-      <c r="I48" s="1"/>
-      <c r="K48" s="1"/>
-      <c r="L48" s="1"/>
-      <c r="M48" s="1"/>
-      <c r="N48" s="1"/>
-      <c r="P48" s="2"/>
-      <c r="Q48" s="2"/>
-      <c r="R48" s="2"/>
-      <c r="S48" s="1"/>
-      <c r="T48" s="8"/>
-      <c r="U48" s="2"/>
-      <c r="V48" s="1"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DB01197-FE1C-4ED1-B3B4-7B774B71A2A6}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A2:E3"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="36" style="2" customWidth="1"/>
-    <col min="2" max="2" width="50.5546875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="71.21875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="56.44140625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="6.21875" style="52" customWidth="1"/>
-    <col min="6" max="6" width="43.21875" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="55.109375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="67.88671875" style="2" customWidth="1"/>
-    <col min="9" max="9" width="64.33203125" style="2" customWidth="1"/>
-    <col min="10" max="10" width="7.77734375" style="2" customWidth="1"/>
-    <col min="11" max="11" width="39.21875" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="48.88671875" style="2" customWidth="1"/>
-    <col min="13" max="13" width="72.6640625" style="2" customWidth="1"/>
-    <col min="14" max="14" width="43.88671875" style="2" customWidth="1"/>
-    <col min="15" max="15" width="7.77734375" style="2" customWidth="1"/>
-    <col min="16" max="16" width="56.77734375" style="2" customWidth="1"/>
-    <col min="17" max="17" width="46.77734375" style="2" customWidth="1"/>
-    <col min="18" max="18" width="62.88671875" style="2" customWidth="1"/>
-    <col min="19" max="19" width="49.21875" style="2" customWidth="1"/>
-    <col min="20" max="20" width="8.77734375" style="2"/>
-    <col min="21" max="21" width="67.77734375" style="2" customWidth="1"/>
-    <col min="22" max="22" width="68.33203125" style="2" customWidth="1"/>
-    <col min="23" max="24" width="59.33203125" style="2" customWidth="1"/>
-    <col min="25" max="25" width="59.6640625" style="2" customWidth="1"/>
-    <col min="26" max="26" width="99.44140625" style="2" customWidth="1"/>
-    <col min="27" max="27" width="41.21875" style="2" customWidth="1"/>
-    <col min="28" max="16384" width="8.77734375" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="1:5" s="51" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="E2" s="52"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
-</worksheet>
 </file>
--- a/4 четверть_MSSQL.xlsx
+++ b/4 четверть_MSSQL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlexServHW\Desktop\GB_Developer_Workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78B4ABF1-7AE0-46FE-91C3-FF7AA36C1CF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35FD2CDE-DDC5-4F79-94D9-842A5D1A03D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3660" yWindow="-16440" windowWidth="23250" windowHeight="12450" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="6" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Изучить" sheetId="21" r:id="rId1"/>
@@ -1500,44 +1500,6 @@
         <charset val="204"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> MSSQL может работать с массивами, переведенными в строки, соединенные через запятую.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[1,2,3,4].join()</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Правило!</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
       <t xml:space="preserve"> THROW может быть настроена только для хранимых процедур (изучить)</t>
     </r>
   </si>
@@ -13527,17 +13489,133 @@
       <t>;</t>
     </r>
   </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Правило!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> MSSQL может работать с </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ARRAY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>переведенными</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>в STRING (ВАЖНО)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, соединенные через запятую.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[1,2,3,4].join()</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="40" x14ac:knownFonts="1">
+  <fonts count="42" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -13863,6 +13941,16 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="18">
     <fill>
@@ -13979,9 +14067,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -13992,42 +14080,48 @@
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="14" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="15" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="13" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -14035,98 +14129,92 @@
     <xf numFmtId="49" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="23" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="22" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="21" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="31" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="32" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="22" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="23" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="34" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="35" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="22" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="23" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="22" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="23" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="14" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="35" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="34" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="22" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="23" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -14144,64 +14232,67 @@
     <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="38" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="39" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="34" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="34" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="40" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="35" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="35" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="23" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="22" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -14841,7 +14932,7 @@
       <c r="B4" s="9"/>
       <c r="C4" s="40"/>
       <c r="D4" s="22" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="5" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
@@ -14849,7 +14940,7 @@
       <c r="B5" s="9"/>
       <c r="C5" s="40"/>
       <c r="D5" s="22" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="6" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
@@ -14857,17 +14948,17 @@
       <c r="B6" s="9"/>
       <c r="C6" s="40"/>
       <c r="D6" s="22" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A7" s="9"/>
       <c r="B7" s="9"/>
       <c r="C7" s="22" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D7" s="40" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.3">
@@ -14875,7 +14966,7 @@
       <c r="B8" s="9"/>
       <c r="C8" s="40"/>
       <c r="D8" s="40" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.3">
@@ -14883,17 +14974,17 @@
       <c r="B9" s="9"/>
       <c r="C9" s="40"/>
       <c r="D9" s="40" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="10" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="9"/>
       <c r="B10" s="9"/>
       <c r="C10" s="22" t="s">
+        <v>198</v>
+      </c>
+      <c r="D10" s="22" t="s">
         <v>199</v>
-      </c>
-      <c r="D10" s="22" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.3">
@@ -14924,7 +15015,7 @@
       <c r="B15" s="48"/>
       <c r="C15" s="9"/>
       <c r="D15" s="73" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.3">
@@ -15198,7 +15289,7 @@
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A4" s="44" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B4" s="9"/>
       <c r="C4" s="9"/>
@@ -15207,16 +15298,16 @@
     <row r="5" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A5" s="9"/>
       <c r="B5" s="42" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C5" s="42" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D5" s="9"/>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A6" s="44" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
@@ -15226,7 +15317,7 @@
       <c r="A7" s="9"/>
       <c r="B7" s="9"/>
       <c r="C7" s="42" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D7" s="9"/>
     </row>
@@ -15234,7 +15325,7 @@
       <c r="A8" s="9"/>
       <c r="B8" s="9"/>
       <c r="C8" s="42" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D8" s="9"/>
     </row>
@@ -16446,7 +16537,7 @@
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A4" s="20" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B4" s="9"/>
       <c r="C4" s="9"/>
@@ -16455,40 +16546,40 @@
     <row r="5" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A5" s="9"/>
       <c r="B5" s="32" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C5" s="35" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D5" s="9"/>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A6" s="9"/>
       <c r="B6" s="32" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C6" s="36" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D6" s="9"/>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A7" s="9"/>
       <c r="B7" s="32" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C7" s="36" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D7" s="9"/>
     </row>
     <row r="8" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="9"/>
       <c r="B8" s="32" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C8" s="36" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D8" s="9"/>
     </row>
@@ -16496,17 +16587,17 @@
       <c r="A9" s="9"/>
       <c r="B9" s="9"/>
       <c r="C9" s="19" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D9" s="9"/>
     </row>
     <row r="10" spans="1:22" ht="144" x14ac:dyDescent="0.3">
       <c r="A10" s="9"/>
       <c r="B10" s="22" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D10" s="9"/>
     </row>
@@ -16763,7 +16854,7 @@
     </row>
     <row r="4" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="C4" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
   </sheetData>
@@ -16847,7 +16938,7 @@
     </row>
     <row r="5" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="23" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B5" s="9"/>
       <c r="C5" s="9"/>
@@ -16855,8 +16946,8 @@
     </row>
     <row r="6" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A6" s="9"/>
-      <c r="C6" s="19" t="s">
-        <v>88</v>
+      <c r="C6" s="76" t="s">
+        <v>453</v>
       </c>
       <c r="D6" s="9"/>
     </row>
@@ -16869,28 +16960,28 @@
     <row r="8" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A8" s="9"/>
       <c r="B8" s="43" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C8" s="42" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D8" s="42" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="9" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="9"/>
       <c r="B9" s="9"/>
       <c r="C9" s="42" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D9" s="42" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A10" s="19" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="19"/>
@@ -16898,10 +16989,10 @@
     <row r="11" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A11" s="9"/>
       <c r="B11" s="43" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C11" s="42" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D11" s="19"/>
     </row>
@@ -16909,13 +17000,13 @@
       <c r="A12" s="9"/>
       <c r="B12" s="9"/>
       <c r="C12" s="42" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D12" s="19"/>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A13" s="23" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B13" s="9"/>
       <c r="C13" s="9"/>
@@ -16924,23 +17015,23 @@
     <row r="14" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A14" s="9"/>
       <c r="B14" s="19" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D14" s="19" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="15" spans="1:22" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A15" s="9"/>
       <c r="B15" s="9"/>
       <c r="C15" s="19" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D15" s="19" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.3">
@@ -17720,7 +17811,7 @@
     </row>
     <row r="5" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="23" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B5" s="9"/>
       <c r="C5" s="9"/>
@@ -17729,35 +17820,35 @@
     <row r="6" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="9"/>
       <c r="C6" s="42" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D6" s="9"/>
     </row>
     <row r="7" spans="1:22" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A7" s="9"/>
       <c r="B7" s="43" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C7" s="72" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D7" s="42" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="8" spans="1:22" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A8" s="9"/>
       <c r="B8" s="9"/>
       <c r="C8" s="72" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D8" s="42" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A9" s="23" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
@@ -17766,23 +17857,23 @@
     <row r="10" spans="1:22" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A10" s="9"/>
       <c r="B10" s="19" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C10" s="42" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D10" s="42" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11" spans="1:22" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A11" s="9"/>
       <c r="B11" s="9"/>
       <c r="C11" s="42" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D11" s="42" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.3">
@@ -18964,7 +19055,7 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="34" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B28" s="31"/>
       <c r="C28" s="32"/>
@@ -18972,43 +19063,43 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B29" s="32" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C29" s="35" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D29" s="9"/>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B30" s="32" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C30" s="36" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D30" s="9"/>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B31" s="32" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C31" s="36" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D31" s="9"/>
     </row>
     <row r="32" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B32" s="32" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C32" s="36" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D32" s="9"/>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="20" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C33" s="9" t="s">
         <v>45</v>
@@ -19097,7 +19188,7 @@
       </c>
       <c r="C44" s="13"/>
       <c r="D44" s="26" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
@@ -19110,56 +19201,56 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="28" t="s">
+        <v>111</v>
+      </c>
+      <c r="D46" s="27" t="s">
         <v>112</v>
-      </c>
-      <c r="D46" s="27" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B47" s="19" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C47" s="19" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B48" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="C48" s="19" t="s">
         <v>116</v>
-      </c>
-      <c r="C48" s="19" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="29" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D49" s="27" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="C50" s="19" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="29" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D51" s="26" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C52" s="19" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="15" type="noConversion"/>
+  <phoneticPr fontId="16" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="D46" r:id="rId1" location=":~:text=%D0%A1%D0%BE%D0%B7%D0%B4%D0%B0%D0%BD%D0%B8%D0%B5%20%D0%B1%D0%B0%D0%B7%D1%8B%20%D0%B4%D0%B0%D0%BD%D0%BD%D1%8B%D1%85" xr:uid="{FDFE2116-2B22-4A87-B37D-3DFA9E8F9FE0}"/>
     <hyperlink ref="D44" r:id="rId2" location=":~:text=%D0%A1%D0%BE%D0%B7%D0%B4%D0%B0%D0%BD%D0%B8%D0%B5%20%D0%B1%D0%B0%D0%B7%D1%8B%20%D0%B4%D0%B0%D0%BD%D0%BD%D1%8B%D1%85%20%D0%B2%20SQL%20Management%20Studio" xr:uid="{5B701F02-CEF7-44EA-83C6-0E21D7145608}"/>
@@ -19219,420 +19310,420 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="53" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="D10" s="48" t="s">
         <v>348</v>
-      </c>
-      <c r="D10" s="48" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="53" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="53" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A28" s="53" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B30" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>329</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="54" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
       <c r="B32" s="48" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" s="55" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
       <c r="C34" s="2" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" s="55" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C36" s="2" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" s="55" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
       <c r="C38" s="2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" s="53" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B40" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="C40" s="2" t="s">
         <v>318</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="15" type="noConversion"/>
+  <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
@@ -19678,32 +19769,32 @@
   <sheetData>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="60" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="53" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="53" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="53" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="53" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="53" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="16" spans="1:5" s="51" customFormat="1" x14ac:dyDescent="0.3">
@@ -19715,12 +19806,12 @@
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="26" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="20" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B18" s="9"/>
       <c r="C18" s="9"/>
@@ -19729,19 +19820,19 @@
     <row r="19" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="A19" s="9"/>
       <c r="B19" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="C19" s="19" t="s">
         <v>125</v>
-      </c>
-      <c r="C19" s="19" t="s">
-        <v>126</v>
       </c>
       <c r="D19" s="9"/>
     </row>
     <row r="20" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A20" s="59" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B20" s="49" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C20" s="4"/>
       <c r="D20" s="9"/>
@@ -19749,19 +19840,19 @@
     <row r="21" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="A21" s="9"/>
       <c r="B21" s="19" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D21" s="9"/>
     </row>
     <row r="22" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A22" s="21" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B22" s="49" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C22" s="1"/>
       <c r="D22" s="9"/>
@@ -19770,13 +19861,13 @@
       <c r="A23" s="9"/>
       <c r="B23" s="19"/>
       <c r="C23" s="19" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D23" s="9"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="37" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B24" s="9"/>
       <c r="C24" s="9"/>
@@ -19785,16 +19876,16 @@
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="9"/>
       <c r="B25" s="48" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C25" s="48" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D25" s="9"/>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="50" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B26" s="9"/>
       <c r="C26" s="9"/>
@@ -19803,16 +19894,16 @@
     <row r="27" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A27" s="9"/>
       <c r="B27" s="48" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C27" s="48" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D27" s="9"/>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="71" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B28" s="48"/>
       <c r="C28" s="48"/>
@@ -19941,7 +20032,7 @@
       <c r="B4" s="2"/>
       <c r="C4" s="9"/>
       <c r="D4" s="26" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
@@ -19968,7 +20059,7 @@
     </row>
     <row r="5" spans="1:27" s="52" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="30" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B5" s="9"/>
       <c r="C5" s="9"/>
@@ -19999,13 +20090,13 @@
     <row r="6" spans="1:27" s="52" customFormat="1" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A6" s="9"/>
       <c r="B6" s="48" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C6" s="48" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
@@ -20032,16 +20123,16 @@
     </row>
     <row r="7" spans="1:27" s="52" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="59" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B7" s="57" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C7" s="58" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D7" s="58" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
@@ -20068,16 +20159,16 @@
     </row>
     <row r="8" spans="1:27" s="52" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A8" s="63" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B8" s="56" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C8" s="56" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D8" s="56" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
@@ -20104,13 +20195,13 @@
     </row>
     <row r="9" spans="1:27" s="52" customFormat="1" ht="144" x14ac:dyDescent="0.3">
       <c r="A9" s="63" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B9" s="56" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C9" s="56" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D9" s="9"/>
       <c r="F9" s="2"/>
@@ -20138,12 +20229,12 @@
     </row>
     <row r="10" spans="1:27" s="52" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" s="59" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
       <c r="D10" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
@@ -20170,10 +20261,10 @@
     </row>
     <row r="11" spans="1:27" s="52" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A11" s="57" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B11" s="61" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
@@ -20202,16 +20293,16 @@
     </row>
     <row r="12" spans="1:27" s="52" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A12" s="63" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D12" s="61" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
@@ -20238,14 +20329,14 @@
     </row>
     <row r="13" spans="1:27" s="52" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A13" s="63" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D13" s="61" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
@@ -20272,12 +20363,12 @@
     </row>
     <row r="14" spans="1:27" s="52" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="55" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
@@ -20304,13 +20395,13 @@
     </row>
     <row r="15" spans="1:27" s="52" customFormat="1" ht="144" x14ac:dyDescent="0.3">
       <c r="A15" s="62" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B15" s="61" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D15" s="2"/>
       <c r="F15" s="2"/>
@@ -20338,13 +20429,13 @@
     </row>
     <row r="16" spans="1:27" s="52" customFormat="1" ht="144" x14ac:dyDescent="0.3">
       <c r="A16" s="63" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B16" s="61" t="s">
+        <v>372</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>373</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>374</v>
       </c>
       <c r="D16" s="2"/>
       <c r="F16" s="2"/>
@@ -20372,12 +20463,12 @@
     </row>
     <row r="17" spans="1:27" s="52" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A17" s="55" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
       <c r="D17" s="2" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
@@ -20404,16 +20495,16 @@
     </row>
     <row r="18" spans="1:27" s="52" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A18" s="62" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B18" s="61" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D18" s="61" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
@@ -20440,12 +20531,12 @@
     </row>
     <row r="19" spans="1:27" s="52" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A19" s="55" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
       <c r="D19" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
@@ -20472,13 +20563,13 @@
     </row>
     <row r="20" spans="1:27" s="52" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A20" s="63" t="s">
+        <v>392</v>
+      </c>
+      <c r="B20" s="61" t="s">
         <v>393</v>
       </c>
-      <c r="B20" s="61" t="s">
-        <v>394</v>
-      </c>
       <c r="C20" s="2" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="D20" s="2"/>
       <c r="F20" s="2"/>
@@ -20506,12 +20597,12 @@
     </row>
     <row r="21" spans="1:27" s="52" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A21" s="55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
       <c r="D21" s="2" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
@@ -20538,13 +20629,13 @@
     </row>
     <row r="22" spans="1:27" s="52" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A22" s="62" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B22" s="69" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D22" s="2"/>
       <c r="F22" s="2"/>
@@ -20572,13 +20663,13 @@
     </row>
     <row r="23" spans="1:27" s="52" customFormat="1" ht="144" x14ac:dyDescent="0.3">
       <c r="A23" s="67" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="D23" s="2"/>
       <c r="F23" s="2"/>
@@ -20606,12 +20697,12 @@
     </row>
     <row r="24" spans="1:27" s="52" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A24" s="55" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
       <c r="D24" s="2" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
@@ -20638,13 +20729,13 @@
     </row>
     <row r="25" spans="1:27" s="52" customFormat="1" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A25" s="64" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B25" s="69" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D25" s="2"/>
       <c r="F25" s="2"/>
@@ -20672,11 +20763,11 @@
     </row>
     <row r="26" spans="1:27" s="52" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A26" s="67" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B26" s="69"/>
       <c r="C26" s="2" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D26" s="2"/>
       <c r="F26" s="2"/>
@@ -20704,13 +20795,13 @@
     </row>
     <row r="27" spans="1:27" s="52" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A27" s="63" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B27" s="67" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D27" s="2"/>
       <c r="F27" s="2"/>
@@ -20738,13 +20829,13 @@
     </row>
     <row r="28" spans="1:27" s="52" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B28" s="65" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C28" s="61" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D28" s="2"/>
       <c r="F28" s="2"/>
@@ -20773,10 +20864,10 @@
     <row r="29" spans="1:27" s="52" customFormat="1" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A29" s="2"/>
       <c r="B29" s="2" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D29" s="2"/>
       <c r="F29" s="2"/>
@@ -20804,13 +20895,13 @@
     </row>
     <row r="30" spans="1:27" s="52" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="B30" s="66" t="s">
+        <v>407</v>
+      </c>
+      <c r="C30" s="61" t="s">
         <v>404</v>
-      </c>
-      <c r="B30" s="66" t="s">
-        <v>408</v>
-      </c>
-      <c r="C30" s="61" t="s">
-        <v>405</v>
       </c>
       <c r="D30" s="2"/>
       <c r="F30" s="2"/>
@@ -20838,12 +20929,12 @@
     </row>
     <row r="31" spans="1:27" s="52" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A31" s="55" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
       <c r="D31" s="2" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="F31" s="2"/>
       <c r="G31" s="2"/>
@@ -20871,13 +20962,13 @@
     <row r="32" spans="1:27" s="52" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A32" s="2"/>
       <c r="B32" s="69" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C32" s="63" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="D32" s="69" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
@@ -20904,13 +20995,13 @@
     </row>
     <row r="33" spans="1:27" s="52" customFormat="1" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A33" s="69" t="s">
+        <v>424</v>
+      </c>
+      <c r="B33" s="69" t="s">
         <v>425</v>
       </c>
-      <c r="B33" s="69" t="s">
-        <v>426</v>
-      </c>
       <c r="C33" s="2" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D33" s="2"/>
       <c r="F33" s="2"/>
@@ -20938,16 +21029,16 @@
     </row>
     <row r="34" spans="1:27" s="52" customFormat="1" ht="216" x14ac:dyDescent="0.3">
       <c r="A34" s="69" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B34" s="69" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
@@ -20975,13 +21066,13 @@
     <row r="35" spans="1:27" s="52" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A35" s="2"/>
       <c r="B35" s="69" t="s">
+        <v>418</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="D35" s="69" t="s">
         <v>419</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="D35" s="69" t="s">
-        <v>420</v>
       </c>
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
@@ -21008,13 +21099,13 @@
     </row>
     <row r="36" spans="1:27" s="52" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A36" s="69" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B36" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="C36" s="2" t="s">
         <v>423</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>424</v>
       </c>
       <c r="D36" s="2"/>
       <c r="F36" s="2"/>
@@ -21042,7 +21133,7 @@
     </row>
     <row r="37" spans="1:27" s="52" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A37" s="70" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
@@ -21074,7 +21165,7 @@
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="D38" s="2"/>
       <c r="F38" s="2"/>
@@ -21102,13 +21193,13 @@
     </row>
     <row r="39" spans="1:27" s="52" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C39" s="69" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="D39" s="2"/>
       <c r="F39" s="2"/>
@@ -21136,11 +21227,11 @@
     </row>
     <row r="40" spans="1:27" s="52" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B40" s="2"/>
       <c r="C40" s="69" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="D40" s="2"/>
       <c r="F40" s="2"/>
@@ -21168,13 +21259,13 @@
     </row>
     <row r="41" spans="1:27" s="52" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C41" s="69" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D41" s="2"/>
       <c r="F41" s="2"/>
@@ -21202,13 +21293,13 @@
     </row>
     <row r="42" spans="1:27" s="52" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B42" s="69" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C42" s="69" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="D42" s="2"/>
       <c r="F42" s="2"/>
@@ -21291,12 +21382,12 @@
       <c r="B3" s="2"/>
       <c r="C3" s="9"/>
       <c r="D3" s="26" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="52" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="71" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B4" s="48"/>
       <c r="C4" s="48"/>
@@ -21306,13 +21397,13 @@
       <c r="A5" s="9"/>
       <c r="B5" s="48"/>
       <c r="C5" s="74" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="D5" s="9"/>
     </row>
     <row r="6" spans="1:5" s="52" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A6" s="75" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B6" s="48"/>
       <c r="C6" s="48"/>
@@ -21322,7 +21413,7 @@
       <c r="A7" s="9"/>
       <c r="B7" s="48"/>
       <c r="C7" s="74" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="D7" s="9"/>
     </row>
@@ -21330,7 +21421,7 @@
       <c r="A8" s="9"/>
       <c r="B8" s="48"/>
       <c r="C8" s="74" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D8" s="9"/>
     </row>
@@ -21458,7 +21549,7 @@
       </c>
       <c r="B4" s="9"/>
       <c r="C4" s="37" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D4" s="9"/>
     </row>
@@ -21490,7 +21581,7 @@
     </row>
     <row r="7" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="44" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B7" s="9"/>
       <c r="C7" s="9"/>
@@ -21514,10 +21605,10 @@
     <row r="8" spans="1:22" s="7" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A8" s="9"/>
       <c r="B8" s="42" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C8" s="68" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D8" s="9"/>
       <c r="F8" s="1"/>
@@ -21538,7 +21629,7 @@
     </row>
     <row r="9" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="44" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B9" s="9"/>
       <c r="C9" s="45"/>
@@ -21562,10 +21653,10 @@
     <row r="10" spans="1:22" s="7" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A10" s="9"/>
       <c r="B10" s="42" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C10" s="42" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D10" s="9"/>
       <c r="F10" s="1"/>
@@ -21586,7 +21677,7 @@
     </row>
     <row r="11" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11" s="47" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B11" s="9"/>
       <c r="C11" s="9"/>
@@ -21610,10 +21701,10 @@
     <row r="12" spans="1:22" s="7" customFormat="1" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A12" s="9"/>
       <c r="B12" s="46" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C12" s="46" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D12" s="9"/>
       <c r="F12" s="1"/>
@@ -21635,10 +21726,10 @@
     <row r="13" spans="1:22" s="7" customFormat="1" ht="216" x14ac:dyDescent="0.3">
       <c r="A13" s="9"/>
       <c r="B13" s="46" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C13" s="46" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D13" s="9"/>
       <c r="F13" s="1"/>
@@ -22005,7 +22096,7 @@
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A4" s="25" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B4" s="9"/>
       <c r="D4" s="9"/>
@@ -22015,16 +22106,16 @@
     </row>
     <row r="5" spans="1:22" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A5" s="19" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D5" s="41" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="P5" s="1"/>
       <c r="U5" s="1"/>
@@ -22032,7 +22123,7 @@
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A6" s="24" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
@@ -22040,21 +22131,21 @@
     </row>
     <row r="7" spans="1:22" ht="72" x14ac:dyDescent="0.3">
       <c r="A7" s="19" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D7" s="41" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="8" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A8" s="24" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B8" s="9"/>
       <c r="C8" s="9"/>
@@ -22062,126 +22153,126 @@
     </row>
     <row r="9" spans="1:22" ht="216" x14ac:dyDescent="0.3">
       <c r="A9" s="19" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D9" s="41" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A10" s="25" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C10" s="19"/>
       <c r="D10" s="4"/>
     </row>
     <row r="11" spans="1:22" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A11" s="32" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B11" s="32" t="s">
+        <v>140</v>
+      </c>
+      <c r="C11" s="32" t="s">
         <v>141</v>
       </c>
-      <c r="C11" s="32" t="s">
-        <v>142</v>
-      </c>
       <c r="D11" s="33" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12" spans="1:22" ht="72" x14ac:dyDescent="0.3">
       <c r="A12" s="32" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B12" s="31"/>
       <c r="C12" s="32" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D12" s="33"/>
     </row>
     <row r="13" spans="1:22" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A13" s="32" t="s">
+        <v>144</v>
+      </c>
+      <c r="B13" s="32" t="s">
         <v>145</v>
       </c>
-      <c r="B13" s="32" t="s">
+      <c r="C13" s="32" t="s">
         <v>146</v>
-      </c>
-      <c r="C13" s="32" t="s">
-        <v>147</v>
       </c>
       <c r="D13" s="33"/>
     </row>
     <row r="14" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A14" s="32" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B14" s="31"/>
       <c r="C14" s="32" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D14" s="33"/>
     </row>
     <row r="15" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A15" s="32" t="s">
+        <v>149</v>
+      </c>
+      <c r="B15" s="31" t="s">
         <v>150</v>
       </c>
-      <c r="B15" s="31" t="s">
+      <c r="C15" s="32" t="s">
         <v>151</v>
-      </c>
-      <c r="C15" s="32" t="s">
-        <v>152</v>
       </c>
       <c r="D15" s="33"/>
     </row>
     <row r="16" spans="1:22" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A16" s="32" t="s">
+        <v>152</v>
+      </c>
+      <c r="B16" s="31" t="s">
+        <v>150</v>
+      </c>
+      <c r="C16" s="32" t="s">
         <v>153</v>
-      </c>
-      <c r="B16" s="31" t="s">
-        <v>151</v>
-      </c>
-      <c r="C16" s="32" t="s">
-        <v>154</v>
       </c>
       <c r="D16" s="33"/>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A17" s="38" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B17" s="31" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C17" s="32"/>
       <c r="D17" s="33"/>
     </row>
     <row r="18" spans="1:22" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A18" s="32" t="s">
+        <v>158</v>
+      </c>
+      <c r="B18" s="32" t="s">
         <v>159</v>
       </c>
-      <c r="B18" s="32" t="s">
+      <c r="C18" s="32" t="s">
         <v>160</v>
       </c>
-      <c r="C18" s="32" t="s">
-        <v>161</v>
-      </c>
       <c r="D18" s="33" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="19" spans="1:22" s="7" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A19" s="32" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B19" s="31"/>
       <c r="C19" s="32" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D19" s="33"/>
       <c r="F19" s="1"/>
@@ -22202,11 +22293,11 @@
     </row>
     <row r="20" spans="1:22" s="7" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A20" s="32" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B20" s="31"/>
       <c r="C20" s="32" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D20" s="33"/>
       <c r="F20" s="1"/>
@@ -22227,11 +22318,11 @@
     </row>
     <row r="21" spans="1:22" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A21" s="32" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B21" s="31"/>
       <c r="C21" s="32" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D21" s="33"/>
       <c r="F21" s="1"/>
@@ -22252,11 +22343,11 @@
     </row>
     <row r="22" spans="1:22" s="7" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A22" s="32" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B22" s="31"/>
       <c r="C22" s="32" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D22" s="33"/>
       <c r="F22" s="1"/>
@@ -22277,11 +22368,11 @@
     </row>
     <row r="23" spans="1:22" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A23" s="32" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B23" s="31"/>
       <c r="C23" s="32" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D23" s="33"/>
       <c r="F23" s="1"/>
@@ -22302,11 +22393,11 @@
     </row>
     <row r="24" spans="1:22" s="7" customFormat="1" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A24" s="32" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B24" s="31"/>
       <c r="C24" s="32" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D24" s="33"/>
       <c r="F24" s="1"/>
@@ -22327,13 +22418,13 @@
     </row>
     <row r="25" spans="1:22" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A25" s="32" t="s">
+        <v>173</v>
+      </c>
+      <c r="B25" s="31" t="s">
         <v>174</v>
       </c>
-      <c r="B25" s="31" t="s">
+      <c r="C25" s="32" t="s">
         <v>175</v>
-      </c>
-      <c r="C25" s="32" t="s">
-        <v>176</v>
       </c>
       <c r="D25" s="33"/>
       <c r="F25" s="1"/>
@@ -22354,11 +22445,11 @@
     </row>
     <row r="26" spans="1:22" s="7" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A26" s="32" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B26" s="31"/>
       <c r="C26" s="32" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D26" s="33"/>
       <c r="F26" s="1"/>
@@ -22379,13 +22470,13 @@
     </row>
     <row r="27" spans="1:22" s="7" customFormat="1" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A27" s="32" t="s">
+        <v>178</v>
+      </c>
+      <c r="B27" s="31" t="s">
         <v>179</v>
       </c>
-      <c r="B27" s="31" t="s">
+      <c r="C27" s="32" t="s">
         <v>180</v>
-      </c>
-      <c r="C27" s="32" t="s">
-        <v>181</v>
       </c>
       <c r="D27" s="33"/>
       <c r="F27" s="1"/>
@@ -22406,13 +22497,13 @@
     </row>
     <row r="28" spans="1:22" s="7" customFormat="1" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A28" s="32" t="s">
+        <v>181</v>
+      </c>
+      <c r="B28" s="39" t="s">
         <v>182</v>
       </c>
-      <c r="B28" s="39" t="s">
+      <c r="C28" s="32" t="s">
         <v>183</v>
-      </c>
-      <c r="C28" s="32" t="s">
-        <v>184</v>
       </c>
       <c r="D28" s="33"/>
       <c r="F28" s="1"/>
@@ -22433,13 +22524,13 @@
     </row>
     <row r="29" spans="1:22" s="7" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A29" s="32" t="s">
+        <v>184</v>
+      </c>
+      <c r="B29" s="39" t="s">
+        <v>182</v>
+      </c>
+      <c r="C29" s="32" t="s">
         <v>185</v>
-      </c>
-      <c r="B29" s="39" t="s">
-        <v>183</v>
-      </c>
-      <c r="C29" s="32" t="s">
-        <v>186</v>
       </c>
       <c r="D29" s="33"/>
       <c r="F29" s="1"/>
@@ -22460,11 +22551,11 @@
     </row>
     <row r="30" spans="1:22" s="7" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A30" s="32" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B30" s="31"/>
       <c r="C30" s="32" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D30" s="33"/>
       <c r="F30" s="1"/>
@@ -22485,13 +22576,13 @@
     </row>
     <row r="31" spans="1:22" s="7" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A31" s="32" t="s">
+        <v>188</v>
+      </c>
+      <c r="B31" s="39" t="s">
+        <v>182</v>
+      </c>
+      <c r="C31" s="32" t="s">
         <v>189</v>
-      </c>
-      <c r="B31" s="39" t="s">
-        <v>183</v>
-      </c>
-      <c r="C31" s="32" t="s">
-        <v>190</v>
       </c>
       <c r="D31" s="33"/>
       <c r="F31" s="1"/>

--- a/4 четверть_MSSQL.xlsx
+++ b/4 четверть_MSSQL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlexServHW\Desktop\GB_Developer_Workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69E1A5B8-758E-4CE9-927B-8D02ADE78612}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAE66300-6D6C-42EE-BB93-A0F3870CBB93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-6330" yWindow="-16140" windowWidth="17280" windowHeight="8880" firstSheet="9" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-6330" yWindow="-16140" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Изучить" sheetId="21" r:id="rId1"/>
@@ -29,7 +29,7 @@
     <sheet name="UPDATE" sheetId="33" r:id="rId14"/>
     <sheet name="DELETE" sheetId="34" r:id="rId15"/>
     <sheet name="SUM..." sheetId="35" r:id="rId16"/>
-    <sheet name="GROUP" sheetId="36" r:id="rId17"/>
+    <sheet name="GROUP HAVING" sheetId="36" r:id="rId17"/>
     <sheet name="IF" sheetId="23" r:id="rId18"/>
     <sheet name="template" sheetId="14" r:id="rId19"/>
     <sheet name="Каскадное удаление" sheetId="16" r:id="rId20"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="864" uniqueCount="748">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="931" uniqueCount="802">
   <si>
     <t>Урок 1 часть 1</t>
   </si>
@@ -13143,9 +13143,6 @@
       <t xml:space="preserve">
 )</t>
     </r>
-  </si>
-  <si>
-    <t>`https://metanit.com/sql/sqlserver/3.6.php</t>
   </si>
   <si>
     <t xml:space="preserve">ALTER TABLE </t>
@@ -20448,135 +20445,6 @@
   <si>
     <r>
       <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Вариант 2
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-SELECT 
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Manufacturer, 
- COUNT(*) AS Models, 
- SUM(ProductCount) AS Units
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">FROM Products
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>GROUP BY ROLLUP(Manufacturer)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Вариант 1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-SELECT 
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Manufacturer, 
- COUNT(*) AS Models, 
- SUM(ProductCount) AS Units
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">FROM Products
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>GROUP BY Manufacturer WITH ROLLUP</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
@@ -21066,17 +20934,1128 @@
   <si>
     <t>CUBE</t>
   </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Вариант 2
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+SELECT 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Manufacturer, 
+ COUNT(*) AS Models, 
+ SUM(ProductCount) AS Units
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">FROM Products
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>GROUP BY ROLLUP(Manufacturer,…)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Вариант 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+SELECT 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Manufacturer, 
+ COUNT(*) AS Models, 
+ SUM(ProductCount) AS Units
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">FROM Products
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>GROUP BY Manufacturer, ... WITH ROLLUP</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">
+</t>
+  </si>
+  <si>
+    <t>GROUPING SETS</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Пояснение!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> CUBE похож на ROLLUP за тем исключением, что CUBE добавляет суммирующие строки для каждой комбинации групп.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+SELECT
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Manufacturer,
+ COUNT(*) AS Models,
+ SUM(ProductCount) AS Units
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">FROM Products
+GROUP BY Manufacturer, ProductCount </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>WITH CUBE</t>
+    </r>
+  </si>
+  <si>
+    <t>OVER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Пояснение!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> По смыслу делает тоже самое, что и</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> GROUP BY + ROLLUP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, однако он вместо дополнительной строки, добавляет дополнительный стобец</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+SELECT
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">        ProductName,
+        Manufacturer,
+        ProductCount,
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">        COUNT(*) OVER (PARTITION BY Manufacturer) AS Models,
+        SUM(ProductCount) OVER (PARTITION BY Manufacturer) AS Units
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>FROM Products</t>
+    </r>
+  </si>
+  <si>
+    <t>Аналог GROUP BY + ROLLUP</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Пояснение!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Оператор GROUPING SETS аналогично ROLLUP и CUBE добавляет суммирующую строку для групп. Но при этом он не включает сами группам
+SELECT
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Manufacturer, 
+ COUNT(*) AS Models,
+ ProductCount
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">FROM Products
+GROUP BY </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>GROUPING SETS(Manufacturer, ProductCount)</t>
+    </r>
+  </si>
+  <si>
+    <t>INSERT INTO Products 
+VALUES ('iPhone 6', 'Apple', 2, 36000),
+('iPhone 6S', 'Apple', 2, 41000),
+('iPhone 7', 'Apple', 5, 52000),
+('Galaxy S8', 'Samsung', 2, 46000),
+('Galaxy S8 Plus', 'Samsung', 1, 56000),
+('Mi 5X', 'Xiaomi', 2, 26000),
+('OnePlus 5', 'OnePlus', 6, 38000)
+INSERT INTO Customers VALUES ('Tom'), ('Bob'),('Sam')</t>
+  </si>
+  <si>
+    <t>Подзапрос - вариант 1</t>
+  </si>
+  <si>
+    <t>Подзапрос - вариант 2</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">INSERT INTO </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Orders </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>VALUES</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+( 
+    (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SELECT Id FROM Products WHERE ProductName='Galaxy S8'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>), 
+    (SELECT Id FROM Customers WHERE FirstName='Tom'),
+    '2017-07-11',  
+    2, 
+    (SELECT Price FROM Products WHERE ProductName='Galaxy S8')
+),
+( 
+    (SELECT Id FROM Products WHERE ProductName='iPhone 6S'), 
+    (SELECT Id FROM Customers WHERE FirstName='Tom'),
+    '2017-07-13',  
+    1, 
+    (SELECT Price FROM Products WHERE ProductName='iPhone 6S')
+),
+( 
+    (SELECT Id FROM Products WHERE ProductName='iPhone 6S'), 
+    (SELECT Id FROM Customers WHERE FirstName='Bob'),
+    '2017-07-11',  
+    1, 
+    (SELECT Price FROM Products WHERE ProductName='iPhone 6S')
+)</t>
+    </r>
+  </si>
+  <si>
+    <t>Подзапросы</t>
+  </si>
+  <si>
+    <t>Полезные варианты использования</t>
+  </si>
+  <si>
+    <r>
+      <t>SELECT *
+FROM Products
+WHERE Price = (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SELECT MIN(Price) FROM Products</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>Найдем товары из таблицы Products, которые имеют минимальную цену</t>
+  </si>
+  <si>
+    <t>SELECT *
+FROM Products
+WHERE Price &gt; (SELECT AVG(Price) FROM Products)</t>
+  </si>
+  <si>
+    <r>
+      <t>SELECT *
+FROM Products
+WHERE Price</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &gt; (SELECT AVG(Price) FROM Products)</t>
+    </r>
+  </si>
+  <si>
+    <t>Найдем товары, цена которых выше средней</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">SELECT  CreatedAt, 
+        Price, 
+        </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(SELECT ProductName FROM Products 
+        WHERE Products.Id = Orders.ProductId) AS Product</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+FROM Orders</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Коррелирующие подзапросы</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (correlated subquery), результаты зависят от строк, которые выбираются в основном запросе
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Пояснение!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Здесь для каждой строки из таблицы Orders будет выполняться подзапрос, результат которого зависит от столбца ProductId.</t>
+    </r>
+  </si>
+  <si>
+    <t>Вариант 2
+Аналог LEFT JOIN</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">SELECT ProductName,
+       Manufacturer,
+       Price, 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">        (SELECT AVG(Price) FROM Products AS SubProds 
+         WHERE SubProds.Manufacturer=Prods.Manufacturer)  AS AvgPrice
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">FROM Products AS Prods
+WHERE Price &gt; 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">    (SELECT AVG(Price) FROM Products AS SubProds 
+     WHERE SubProds.Manufacturer=Prods.Manufacturer)</t>
+    </r>
+  </si>
+  <si>
+    <t>Выберем из таблицы Products те товары, стоимость которых выше средней цены товаров для данного производителя</t>
+  </si>
+  <si>
+    <t>FROM → WHERE → GROUP BY → HAVING → SELECT → ORDER BY</t>
+  </si>
+  <si>
+    <t>Порядок выполнения SQL запроса</t>
+  </si>
+  <si>
+    <t>Вариант 1
+Аналог LEFT JOIN</t>
+  </si>
+  <si>
+    <t>HAVING</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Примечание!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> JOIN более эффективный способ для извлечения данных из других таблиц</t>
+    </r>
+  </si>
+  <si>
+    <t>…</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Правило!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> В выражении SELECT мы можем вводить подзапросы 4 способами</t>
+    </r>
+  </si>
+  <si>
+    <t>Способ 1</t>
+  </si>
+  <si>
+    <t>Способ 2</t>
+  </si>
+  <si>
+    <t>Способ 3</t>
+  </si>
+  <si>
+    <t>Способ 4</t>
+  </si>
+  <si>
+    <t>Подзапрос</t>
+  </si>
+  <si>
+    <t>ALL, SOME или ANY.</t>
+  </si>
+  <si>
+    <t>ALL</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Правило! </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Любой подзапрос чаще всего должен возвращать одно значение. Если же подзапрос возвращает больше значений, значит необходимо выбрать оператор для работы с полученным набором значений</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">SELECT * FROM Products
+WHERE Price &lt; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ALL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(SELECT Price FROM Products WHERE Manufacturer='Apple')</t>
+    </r>
+  </si>
+  <si>
+    <t>Аналог ['a','a','a'].every((n) =&gt; n == 'a'); true</t>
+  </si>
+  <si>
+    <t>SOME, ANY</t>
+  </si>
+  <si>
+    <t>Аналог ['a','b','c'].some((n) =&gt; n == 'a'); true</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">SELECT * FROM Products
+WHERE Price &lt; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ANY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(SELECT Price FROM Products WHERE Manufacturer='Apple')</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Аналогично</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+SELECT * FROM Products
+WHERE Price &lt; (SELECT MIN(Price) FROM Products WHERE Manufacturer='Apple')
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ИЛИ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+WHERE Price &lt; val1 AND Price &lt; val2 AND Price &lt; val3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Аналогично</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+SELECT * FROM Products
+WHERE Price &lt; (SELECT MAX(Price) FROM Products WHERE Manufacturer='Apple')</t>
+    </r>
+  </si>
+  <si>
+    <t>Подзапрос как спецификация столбца</t>
+  </si>
+  <si>
+    <t>SELECT *
+FROM Customers
+WHERE Id NOT IN (SELECT CustomerId FROM Orders)</t>
+  </si>
+  <si>
+    <t>Выберем всех покупателей из таблицы Customers, у которых нет заказов в таблице Orders:</t>
+  </si>
+  <si>
+    <t>С подзапросом</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">UPDATE Orders
+SET Price = </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(SELECT Price FROM Products WHERE Id=Orders.ProductId)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> + 2000
+WHERE Id=1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>UPDATE Orders
+SET ProductCount = ProductCount + 2
+WHERE CustomerId=</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(SELECT Id FROM Customers WHERE FirstName='Tom')</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>DELETE FROM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Orders
+WHERE ProductId=</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(SELECT Id FROM Products WHERE ProductName='Galaxy S8')</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+AND CustomerId=</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(SELECT Id FROM Customers WHERE FirstName='Bob')</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Правило!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Во всех подзапросах важно писать полностью DELETE FROM</t>
+    </r>
+  </si>
+  <si>
+    <t>`https://metanit.com/sql/sqlserver/6.3.php</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="44" x14ac:knownFonts="1">
+  <fonts count="45" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -21560,9 +22539,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -21573,42 +22552,48 @@
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="14" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -21616,98 +22601,92 @@
     <xf numFmtId="49" fontId="13" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="13" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="13" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="13" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="24" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="23" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="22" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="32" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="33" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="13" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="23" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="24" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="35" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="36" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="23" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="24" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="23" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="24" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="14" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="15" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="36" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="35" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="23" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="24" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -21725,49 +22704,52 @@
     <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="40" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="36" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="36" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="39" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="40" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="35" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="35" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="23" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="24" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -21776,19 +22758,13 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="32" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="33" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -21797,22 +22773,22 @@
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="14" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="15" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="17" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="18" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="17" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="18" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -21821,16 +22797,34 @@
     <xf numFmtId="49" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="26" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="27" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="30" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -22043,13 +23037,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>120016</xdr:colOff>
-      <xdr:row>21</xdr:row>
+      <xdr:row>23</xdr:row>
       <xdr:rowOff>28575</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>1123951</xdr:colOff>
-      <xdr:row>21</xdr:row>
+      <xdr:row>23</xdr:row>
       <xdr:rowOff>686765</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -22083,6 +23077,45 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>30142</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2292389" cy="1299210"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Рисунок 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1E864B7D-6F70-46E0-8293-1938A9268C07}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10848637" y="21595080"/>
+          <a:ext cx="2292389" cy="1299210"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -22092,13 +23125,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>64</xdr:row>
+      <xdr:row>69</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>65</xdr:row>
+      <xdr:row>70</xdr:row>
       <xdr:rowOff>133350</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -22140,13 +23173,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>76636</xdr:colOff>
-      <xdr:row>77</xdr:row>
+      <xdr:row>82</xdr:row>
       <xdr:rowOff>285938</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>3294863</xdr:colOff>
-      <xdr:row>77</xdr:row>
+      <xdr:row>82</xdr:row>
       <xdr:rowOff>859155</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -22282,14 +23315,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>91440</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>22</xdr:row>
       <xdr:rowOff>476249</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>3920731</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>1266824</xdr:rowOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>1278254</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -22331,14 +23364,14 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>91440</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>5</xdr:row>
       <xdr:rowOff>49531</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1963486</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>969645</xdr:rowOff>
+      <xdr:colOff>1959676</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>973455</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -22375,14 +23408,14 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>144781</xdr:colOff>
-      <xdr:row>12</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>48862</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1584086</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>1007745</xdr:rowOff>
+      <xdr:colOff>1580276</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>1011555</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -22419,14 +23452,14 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>152400</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>85423</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1885281</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>1011200</xdr:rowOff>
+      <xdr:colOff>1889091</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>1007390</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -22463,14 +23496,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>76011</xdr:colOff>
-      <xdr:row>18</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>102870</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>2573655</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>1355920</xdr:rowOff>
+      <xdr:colOff>2569845</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>1352110</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -22507,14 +23540,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>209551</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>89327</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>1507959</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>1009650</xdr:rowOff>
+      <xdr:colOff>1504149</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>1005840</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -22539,6 +23572,138 @@
         <a:xfrm>
           <a:off x="2676526" y="11214527"/>
           <a:ext cx="1306028" cy="910798"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>86336</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>49529</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>2761902</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>3200400</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Рисунок 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AAB0F170-18AC-46BA-9D8E-5295F98DB756}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11468711" y="16299179"/>
+          <a:ext cx="2688901" cy="3150871"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>73413</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>59054</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>3029604</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>1752599</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Рисунок 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2A9D45E5-453D-4D76-BF62-8D90A76881D2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11455788" y="21423629"/>
+          <a:ext cx="2952381" cy="1693545"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>66675</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>22585</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>2221230</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>1608861</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Рисунок 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3857BF7B-764F-4B4D-B6B1-A0D48197FD68}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11449050" y="19748860"/>
+          <a:ext cx="2152650" cy="1584371"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -23012,8 +24177,8 @@
       <c r="A15" s="9"/>
       <c r="B15" s="48"/>
       <c r="C15" s="9"/>
-      <c r="D15" s="75" t="s">
-        <v>442</v>
+      <c r="D15" s="96" t="s">
+        <v>801</v>
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.3">
@@ -23226,7 +24391,7 @@
     <tabColor theme="8"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:V98"/>
+  <dimension ref="A2:V103"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="36" style="1" customWidth="1"/>
@@ -23278,8 +24443,8 @@
       <c r="U2" s="5"/>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A3" s="79" t="s">
-        <v>576</v>
+      <c r="A3" s="78" t="s">
+        <v>575</v>
       </c>
       <c r="C3" s="9"/>
       <c r="D3" s="26" t="s">
@@ -23291,7 +24456,7 @@
     </row>
     <row r="4" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C4" s="73" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="P4" s="1"/>
       <c r="U4" s="1"/>
@@ -23299,10 +24464,10 @@
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A5" s="12" t="s">
+        <v>577</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>578</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>579</v>
       </c>
       <c r="P5" s="1"/>
       <c r="U5" s="1"/>
@@ -23310,10 +24475,10 @@
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A6" s="12" t="s">
+        <v>579</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>580</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>581</v>
       </c>
       <c r="P6" s="1"/>
       <c r="U6" s="1"/>
@@ -23321,10 +24486,10 @@
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="s">
+        <v>581</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>582</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>583</v>
       </c>
       <c r="P7" s="1"/>
       <c r="U7" s="1"/>
@@ -23332,10 +24497,10 @@
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
+        <v>583</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>584</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>585</v>
       </c>
       <c r="P8" s="1"/>
       <c r="U8" s="1"/>
@@ -23343,10 +24508,10 @@
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A9" s="12" t="s">
+        <v>585</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>586</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>587</v>
       </c>
       <c r="P9" s="1"/>
       <c r="U9" s="1"/>
@@ -23354,18 +24519,18 @@
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A10" s="12" t="s">
+        <v>587</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>588</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>589</v>
       </c>
       <c r="P10" s="1"/>
       <c r="U10" s="1"/>
       <c r="V10" s="2"/>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A11" s="76" t="s">
-        <v>591</v>
+      <c r="A11" s="75" t="s">
+        <v>590</v>
       </c>
       <c r="C11" s="1"/>
       <c r="P11" s="1"/>
@@ -23374,18 +24539,18 @@
     </row>
     <row r="12" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B12" s="73" t="s">
+        <v>591</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>592</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>593</v>
       </c>
       <c r="P12" s="1"/>
       <c r="U12" s="1"/>
       <c r="V12" s="2"/>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A13" s="76" t="s">
-        <v>590</v>
+      <c r="A13" s="75" t="s">
+        <v>589</v>
       </c>
       <c r="C13" s="73"/>
       <c r="P13" s="1"/>
@@ -23394,15 +24559,15 @@
     </row>
     <row r="14" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C14" s="73" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="P14" s="1"/>
       <c r="U14" s="1"/>
       <c r="V14" s="2"/>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A15" s="76" t="s">
-        <v>595</v>
+      <c r="A15" s="75" t="s">
+        <v>594</v>
       </c>
       <c r="C15" s="73"/>
       <c r="P15" s="1"/>
@@ -23411,13 +24576,13 @@
     </row>
     <row r="16" spans="1:22" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B16" s="73" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="C16" s="73" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="P16" s="1"/>
       <c r="U16" s="1"/>
@@ -23425,13 +24590,13 @@
     </row>
     <row r="17" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="C17" s="73" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="P17" s="1"/>
       <c r="U17" s="1"/>
@@ -23439,24 +24604,24 @@
     </row>
     <row r="18" spans="1:22" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="B18" s="83" t="s">
         <v>601</v>
       </c>
-      <c r="B18" s="84" t="s">
+      <c r="C18" s="73" t="s">
         <v>602</v>
       </c>
-      <c r="C18" s="73" t="s">
+      <c r="D18" s="2" t="s">
         <v>603</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>604</v>
       </c>
       <c r="P18" s="1"/>
       <c r="U18" s="1"/>
       <c r="V18" s="2"/>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A19" s="76" t="s">
-        <v>605</v>
+      <c r="A19" s="75" t="s">
+        <v>604</v>
       </c>
       <c r="C19" s="73"/>
       <c r="P19" s="1"/>
@@ -23465,10 +24630,10 @@
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>609</v>
-      </c>
-      <c r="C20" s="83" t="s">
         <v>608</v>
+      </c>
+      <c r="C20" s="82" t="s">
+        <v>607</v>
       </c>
       <c r="P20" s="1"/>
       <c r="U20" s="1"/>
@@ -23476,13 +24641,13 @@
     </row>
     <row r="21" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B21" s="73" t="s">
+        <v>605</v>
+      </c>
+      <c r="C21" s="73" t="s">
         <v>606</v>
-      </c>
-      <c r="C21" s="73" t="s">
-        <v>607</v>
       </c>
       <c r="P21" s="1"/>
       <c r="U21" s="1"/>
@@ -23492,8 +24657,8 @@
       <c r="A22" s="25" t="s">
         <v>103</v>
       </c>
-      <c r="B22" s="84" t="s">
-        <v>613</v>
+      <c r="B22" s="83" t="s">
+        <v>612</v>
       </c>
       <c r="C22" s="73"/>
       <c r="D22" s="26" t="s">
@@ -23505,7 +24670,7 @@
     </row>
     <row r="23" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C23" s="73" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="P23" s="1"/>
       <c r="U23" s="1"/>
@@ -23513,13 +24678,13 @@
     </row>
     <row r="24" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B24" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="C24" s="73" t="s">
         <v>615</v>
-      </c>
-      <c r="C24" s="73" t="s">
-        <v>616</v>
       </c>
       <c r="P24" s="1"/>
       <c r="U24" s="1"/>
@@ -23527,13 +24692,13 @@
     </row>
     <row r="25" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="C25" s="73" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="P25" s="1"/>
       <c r="U25" s="1"/>
@@ -23545,7 +24710,7 @@
       </c>
       <c r="B26" s="19"/>
       <c r="C26" s="73" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="D26" s="41"/>
       <c r="P26" s="1"/>
@@ -23570,7 +24735,7 @@
         <v>101</v>
       </c>
       <c r="C28" s="73" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="P28" s="1"/>
       <c r="U28" s="1"/>
@@ -23578,13 +24743,13 @@
     </row>
     <row r="29" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
+        <v>622</v>
+      </c>
+      <c r="B29" s="83" t="s">
+        <v>620</v>
+      </c>
+      <c r="C29" s="73" t="s">
         <v>623</v>
-      </c>
-      <c r="B29" s="84" t="s">
-        <v>621</v>
-      </c>
-      <c r="C29" s="73" t="s">
-        <v>624</v>
       </c>
       <c r="P29" s="1"/>
       <c r="U29" s="1"/>
@@ -23592,24 +24757,27 @@
     </row>
     <row r="30" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>623</v>
-      </c>
-      <c r="B30" s="84" t="s">
-        <v>626</v>
+        <v>622</v>
+      </c>
+      <c r="B30" s="83" t="s">
+        <v>625</v>
       </c>
       <c r="C30" s="73" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="P30" s="1"/>
       <c r="U30" s="1"/>
       <c r="V30" s="2"/>
     </row>
     <row r="31" spans="1:22" ht="288" x14ac:dyDescent="0.3">
+      <c r="A31" s="2" t="s">
+        <v>782</v>
+      </c>
       <c r="C31" s="73" t="s">
+        <v>626</v>
+      </c>
+      <c r="D31" s="73" t="s">
         <v>627</v>
-      </c>
-      <c r="D31" s="73" t="s">
-        <v>628</v>
       </c>
       <c r="P31" s="1"/>
       <c r="U31" s="1"/>
@@ -23624,10 +24792,10 @@
       <c r="V32" s="2"/>
     </row>
     <row r="33" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A33" s="25" t="s">
-        <v>629</v>
-      </c>
-      <c r="C33" s="73"/>
+      <c r="A33" s="94" t="s">
+        <v>782</v>
+      </c>
+      <c r="C33" s="19"/>
       <c r="D33" s="26" t="s">
         <v>109</v>
       </c>
@@ -23635,204 +24803,217 @@
       <c r="U33" s="1"/>
       <c r="V33" s="2"/>
     </row>
-    <row r="34" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="C34" s="73" t="s">
-        <v>630</v>
+    <row r="34" spans="1:22" ht="72" x14ac:dyDescent="0.3">
+      <c r="B34" s="91" t="s">
+        <v>785</v>
+      </c>
+      <c r="C34" s="91" t="s">
+        <v>783</v>
       </c>
       <c r="P34" s="1"/>
       <c r="U34" s="1"/>
       <c r="V34" s="2"/>
     </row>
-    <row r="35" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B35" s="84" t="s">
-        <v>634</v>
-      </c>
-      <c r="C35" s="73" t="s">
-        <v>632</v>
+    <row r="35" spans="1:22" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A35" s="1" t="s">
+        <v>784</v>
+      </c>
+      <c r="B35" s="83" t="s">
+        <v>787</v>
+      </c>
+      <c r="C35" s="91" t="s">
+        <v>786</v>
+      </c>
+      <c r="D35" s="91" t="s">
+        <v>791</v>
       </c>
       <c r="P35" s="1"/>
       <c r="U35" s="1"/>
       <c r="V35" s="2"/>
     </row>
-    <row r="36" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B36" s="84" t="s">
-        <v>633</v>
-      </c>
-      <c r="C36" s="73" t="s">
-        <v>631</v>
+    <row r="36" spans="1:22" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A36" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="B36" s="83" t="s">
+        <v>789</v>
+      </c>
+      <c r="C36" s="91" t="s">
+        <v>790</v>
+      </c>
+      <c r="D36" s="91" t="s">
+        <v>792</v>
       </c>
       <c r="P36" s="1"/>
       <c r="U36" s="1"/>
       <c r="V36" s="2"/>
     </row>
-    <row r="37" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="C37" s="73" t="s">
-        <v>635</v>
+    <row r="37" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A37" s="25" t="s">
+        <v>628</v>
+      </c>
+      <c r="C37" s="73"/>
+      <c r="D37" s="26" t="s">
+        <v>109</v>
       </c>
       <c r="P37" s="1"/>
       <c r="U37" s="1"/>
       <c r="V37" s="2"/>
     </row>
-    <row r="38" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A38" s="25" t="s">
-        <v>152</v>
-      </c>
-      <c r="C38" s="73"/>
-      <c r="D38" s="26" t="s">
-        <v>109</v>
+    <row r="38" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="C38" s="73" t="s">
+        <v>629</v>
       </c>
       <c r="P38" s="1"/>
       <c r="U38" s="1"/>
       <c r="V38" s="2"/>
     </row>
-    <row r="39" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B39" s="86" t="s">
-        <v>637</v>
+    <row r="39" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B39" s="83" t="s">
+        <v>633</v>
       </c>
       <c r="C39" s="73" t="s">
-        <v>636</v>
+        <v>631</v>
       </c>
       <c r="P39" s="1"/>
       <c r="U39" s="1"/>
       <c r="V39" s="2"/>
     </row>
-    <row r="40" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A40" s="87" t="s">
-        <v>661</v>
-      </c>
-      <c r="B40" s="86"/>
-      <c r="C40" s="73"/>
+    <row r="40" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B40" s="83" t="s">
+        <v>632</v>
+      </c>
+      <c r="C40" s="73" t="s">
+        <v>630</v>
+      </c>
       <c r="P40" s="1"/>
       <c r="U40" s="1"/>
       <c r="V40" s="2"/>
     </row>
     <row r="41" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A41" s="9" t="s">
-        <v>638</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>643</v>
+      <c r="C41" s="73" t="s">
+        <v>634</v>
       </c>
       <c r="P41" s="1"/>
       <c r="U41" s="1"/>
       <c r="V41" s="2"/>
     </row>
     <row r="42" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A42" s="88" t="s">
-        <v>660</v>
-      </c>
-      <c r="C42" s="2"/>
+      <c r="A42" s="25" t="s">
+        <v>152</v>
+      </c>
+      <c r="C42" s="73"/>
+      <c r="D42" s="26" t="s">
+        <v>109</v>
+      </c>
       <c r="P42" s="1"/>
       <c r="U42" s="1"/>
       <c r="V42" s="2"/>
     </row>
-    <row r="43" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A43" s="9" t="s">
-        <v>639</v>
-      </c>
-      <c r="B43" s="9"/>
+    <row r="43" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B43" s="85" t="s">
+        <v>636</v>
+      </c>
       <c r="C43" s="73" t="s">
-        <v>644</v>
+        <v>635</v>
       </c>
       <c r="P43" s="1"/>
       <c r="U43" s="1"/>
       <c r="V43" s="2"/>
     </row>
     <row r="44" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A44" s="88" t="s">
-        <v>662</v>
-      </c>
-      <c r="B44" s="9"/>
+      <c r="A44" s="86" t="s">
+        <v>660</v>
+      </c>
+      <c r="B44" s="85"/>
       <c r="C44" s="73"/>
       <c r="P44" s="1"/>
       <c r="U44" s="1"/>
       <c r="V44" s="2"/>
     </row>
-    <row r="45" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A45" s="9" t="s">
-        <v>640</v>
-      </c>
-      <c r="B45" s="9"/>
-      <c r="C45" s="73" t="s">
-        <v>645</v>
+        <v>637</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>642</v>
       </c>
       <c r="P45" s="1"/>
       <c r="U45" s="1"/>
       <c r="V45" s="2"/>
     </row>
     <row r="46" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A46" s="73" t="s">
-        <v>641</v>
-      </c>
-      <c r="B46" s="9"/>
-      <c r="C46" s="73" t="s">
-        <v>646</v>
-      </c>
+      <c r="A46" s="87" t="s">
+        <v>659</v>
+      </c>
+      <c r="C46" s="2"/>
       <c r="P46" s="1"/>
       <c r="U46" s="1"/>
       <c r="V46" s="2"/>
     </row>
     <row r="47" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A47" s="9" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="B47" s="9"/>
       <c r="C47" s="73" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="P47" s="1"/>
       <c r="U47" s="1"/>
       <c r="V47" s="2"/>
     </row>
     <row r="48" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A48" s="89" t="s">
-        <v>663</v>
+      <c r="A48" s="87" t="s">
+        <v>661</v>
       </c>
       <c r="B48" s="9"/>
-      <c r="D48" s="9"/>
+      <c r="C48" s="73"/>
       <c r="P48" s="1"/>
       <c r="U48" s="1"/>
       <c r="V48" s="2"/>
     </row>
     <row r="49" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A49" s="73" t="s">
-        <v>648</v>
+      <c r="A49" s="9" t="s">
+        <v>639</v>
       </c>
       <c r="B49" s="9"/>
-      <c r="C49" s="16" t="s">
-        <v>649</v>
-      </c>
-      <c r="D49" s="9"/>
+      <c r="C49" s="73" t="s">
+        <v>644</v>
+      </c>
       <c r="P49" s="1"/>
       <c r="U49" s="1"/>
       <c r="V49" s="2"/>
     </row>
     <row r="50" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A50" s="73"/>
+      <c r="A50" s="73" t="s">
+        <v>640</v>
+      </c>
       <c r="B50" s="9"/>
-      <c r="C50" s="16"/>
-      <c r="D50" s="9"/>
+      <c r="C50" s="73" t="s">
+        <v>645</v>
+      </c>
       <c r="P50" s="1"/>
       <c r="U50" s="1"/>
       <c r="V50" s="2"/>
     </row>
     <row r="51" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A51" s="73" t="s">
-        <v>650</v>
+      <c r="A51" s="9" t="s">
+        <v>641</v>
       </c>
       <c r="B51" s="9"/>
-      <c r="C51" s="16" t="s">
-        <v>651</v>
-      </c>
-      <c r="D51" s="9"/>
+      <c r="C51" s="73" t="s">
+        <v>646</v>
+      </c>
       <c r="P51" s="1"/>
       <c r="U51" s="1"/>
       <c r="V51" s="2"/>
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A52" s="73"/>
+      <c r="A52" s="88" t="s">
+        <v>662</v>
+      </c>
       <c r="B52" s="9"/>
-      <c r="C52" s="16"/>
       <c r="D52" s="9"/>
       <c r="P52" s="1"/>
       <c r="U52" s="1"/>
@@ -23840,11 +25021,11 @@
     </row>
     <row r="53" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A53" s="73" t="s">
-        <v>652</v>
+        <v>647</v>
       </c>
       <c r="B53" s="9"/>
       <c r="C53" s="16" t="s">
-        <v>653</v>
+        <v>648</v>
       </c>
       <c r="D53" s="9"/>
       <c r="P53" s="1"/>
@@ -23852,309 +25033,235 @@
       <c r="V53" s="2"/>
     </row>
     <row r="54" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A54" s="73" t="s">
-        <v>654</v>
-      </c>
+      <c r="A54" s="73"/>
       <c r="B54" s="9"/>
-      <c r="C54" s="16" t="s">
-        <v>655</v>
-      </c>
+      <c r="C54" s="16"/>
       <c r="D54" s="9"/>
       <c r="P54" s="1"/>
       <c r="U54" s="1"/>
       <c r="V54" s="2"/>
     </row>
-    <row r="55" spans="1:22" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A55" s="73" t="s">
-        <v>656</v>
+        <v>649</v>
       </c>
       <c r="B55" s="9"/>
       <c r="C55" s="16" t="s">
-        <v>657</v>
+        <v>650</v>
       </c>
       <c r="D55" s="9"/>
       <c r="P55" s="1"/>
       <c r="U55" s="1"/>
       <c r="V55" s="2"/>
     </row>
-    <row r="56" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A56" s="73" t="s">
-        <v>658</v>
-      </c>
+    <row r="56" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A56" s="73"/>
       <c r="B56" s="9"/>
-      <c r="C56" s="16" t="s">
-        <v>659</v>
-      </c>
+      <c r="C56" s="16"/>
       <c r="D56" s="9"/>
       <c r="P56" s="1"/>
       <c r="U56" s="1"/>
       <c r="V56" s="2"/>
     </row>
-    <row r="57" spans="1:22" ht="187.2" x14ac:dyDescent="0.3">
-      <c r="A57" s="32" t="s">
-        <v>151</v>
-      </c>
-      <c r="B57" s="32" t="s">
-        <v>137</v>
-      </c>
-      <c r="C57" s="32" t="s">
-        <v>138</v>
-      </c>
-      <c r="D57" s="33" t="s">
-        <v>197</v>
-      </c>
+    <row r="57" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A57" s="73" t="s">
+        <v>651</v>
+      </c>
+      <c r="B57" s="9"/>
+      <c r="C57" s="16" t="s">
+        <v>652</v>
+      </c>
+      <c r="D57" s="9"/>
       <c r="P57" s="1"/>
       <c r="U57" s="1"/>
       <c r="V57" s="2"/>
     </row>
-    <row r="58" spans="1:22" ht="72" x14ac:dyDescent="0.3">
-      <c r="A58" s="32" t="s">
-        <v>139</v>
-      </c>
-      <c r="B58" s="31"/>
-      <c r="C58" s="32" t="s">
-        <v>140</v>
-      </c>
-      <c r="D58" s="33"/>
+    <row r="58" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A58" s="73" t="s">
+        <v>653</v>
+      </c>
+      <c r="B58" s="9"/>
+      <c r="C58" s="16" t="s">
+        <v>654</v>
+      </c>
+      <c r="D58" s="9"/>
       <c r="P58" s="1"/>
       <c r="U58" s="1"/>
       <c r="V58" s="2"/>
     </row>
-    <row r="59" spans="1:22" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A59" s="32" t="s">
-        <v>141</v>
-      </c>
-      <c r="B59" s="32" t="s">
-        <v>142</v>
-      </c>
-      <c r="C59" s="32" t="s">
-        <v>143</v>
-      </c>
-      <c r="D59" s="33"/>
+    <row r="59" spans="1:22" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A59" s="73" t="s">
+        <v>655</v>
+      </c>
+      <c r="B59" s="9"/>
+      <c r="C59" s="16" t="s">
+        <v>656</v>
+      </c>
+      <c r="D59" s="9"/>
       <c r="P59" s="1"/>
       <c r="U59" s="1"/>
       <c r="V59" s="2"/>
     </row>
-    <row r="60" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A60" s="32" t="s">
-        <v>144</v>
-      </c>
-      <c r="B60" s="31"/>
-      <c r="C60" s="32" t="s">
-        <v>145</v>
-      </c>
-      <c r="D60" s="33"/>
+    <row r="60" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A60" s="73" t="s">
+        <v>657</v>
+      </c>
+      <c r="B60" s="9"/>
+      <c r="C60" s="16" t="s">
+        <v>658</v>
+      </c>
+      <c r="D60" s="9"/>
       <c r="P60" s="1"/>
       <c r="U60" s="1"/>
       <c r="V60" s="2"/>
     </row>
-    <row r="61" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:22" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A61" s="32" t="s">
-        <v>146</v>
-      </c>
-      <c r="B61" s="31" t="s">
-        <v>147</v>
+        <v>151</v>
+      </c>
+      <c r="B61" s="32" t="s">
+        <v>137</v>
       </c>
       <c r="C61" s="32" t="s">
-        <v>148</v>
-      </c>
-      <c r="D61" s="33"/>
+        <v>138</v>
+      </c>
+      <c r="D61" s="33" t="s">
+        <v>197</v>
+      </c>
       <c r="P61" s="1"/>
       <c r="U61" s="1"/>
       <c r="V61" s="2"/>
     </row>
-    <row r="62" spans="1:22" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:22" ht="72" x14ac:dyDescent="0.3">
       <c r="A62" s="32" t="s">
-        <v>149</v>
-      </c>
-      <c r="B62" s="31" t="s">
-        <v>147</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="B62" s="31"/>
       <c r="C62" s="32" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="D62" s="33"/>
       <c r="P62" s="1"/>
       <c r="U62" s="1"/>
       <c r="V62" s="2"/>
     </row>
-    <row r="63" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A63" s="24" t="s">
-        <v>105</v>
-      </c>
-      <c r="C63" s="2"/>
-      <c r="D63" s="9"/>
-    </row>
-    <row r="64" spans="1:22" ht="216" x14ac:dyDescent="0.3">
-      <c r="A64" s="19" t="s">
-        <v>106</v>
-      </c>
-      <c r="B64" s="19" t="s">
-        <v>100</v>
-      </c>
-      <c r="C64" s="19" t="s">
-        <v>99</v>
-      </c>
-      <c r="D64" s="41" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="65" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A65" s="38" t="s">
-        <v>187</v>
+    <row r="63" spans="1:22" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A63" s="32" t="s">
+        <v>141</v>
+      </c>
+      <c r="B63" s="32" t="s">
+        <v>142</v>
+      </c>
+      <c r="C63" s="32" t="s">
+        <v>143</v>
+      </c>
+      <c r="D63" s="33"/>
+      <c r="P63" s="1"/>
+      <c r="U63" s="1"/>
+      <c r="V63" s="2"/>
+    </row>
+    <row r="64" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A64" s="32" t="s">
+        <v>144</v>
+      </c>
+      <c r="B64" s="31"/>
+      <c r="C64" s="32" t="s">
+        <v>145</v>
+      </c>
+      <c r="D64" s="33"/>
+      <c r="P64" s="1"/>
+      <c r="U64" s="1"/>
+      <c r="V64" s="2"/>
+    </row>
+    <row r="65" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A65" s="32" t="s">
+        <v>146</v>
       </c>
       <c r="B65" s="31" t="s">
-        <v>154</v>
-      </c>
-      <c r="C65" s="19"/>
+        <v>147</v>
+      </c>
+      <c r="C65" s="32" t="s">
+        <v>148</v>
+      </c>
       <c r="D65" s="33"/>
+      <c r="P65" s="1"/>
+      <c r="U65" s="1"/>
+      <c r="V65" s="2"/>
     </row>
     <row r="66" spans="1:22" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A66" s="32" t="s">
+        <v>149</v>
+      </c>
+      <c r="B66" s="31" t="s">
+        <v>147</v>
+      </c>
+      <c r="C66" s="32" t="s">
+        <v>150</v>
+      </c>
+      <c r="D66" s="33"/>
+      <c r="P66" s="1"/>
+      <c r="U66" s="1"/>
+      <c r="V66" s="2"/>
+    </row>
+    <row r="67" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A67" s="24" t="s">
+        <v>105</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" s="76" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="68" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A68" s="19"/>
+      <c r="C68" s="2"/>
+      <c r="D68" s="9"/>
+    </row>
+    <row r="69" spans="1:22" ht="216" x14ac:dyDescent="0.3">
+      <c r="A69" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="B69" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="C69" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="D69" s="41" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="70" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A70" s="38" t="s">
+        <v>187</v>
+      </c>
+      <c r="B70" s="31" t="s">
+        <v>154</v>
+      </c>
+      <c r="C70" s="19"/>
+      <c r="D70" s="33"/>
+    </row>
+    <row r="71" spans="1:22" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A71" s="32" t="s">
         <v>155</v>
       </c>
-      <c r="B66" s="32" t="s">
+      <c r="B71" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="C66" s="32" t="s">
+      <c r="C71" s="32" t="s">
         <v>157</v>
       </c>
-      <c r="D66" s="33" t="s">
+      <c r="D71" s="33" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="67" spans="1:22" s="7" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A67" s="32" t="s">
+    <row r="72" spans="1:22" s="7" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A72" s="32" t="s">
         <v>158</v>
-      </c>
-      <c r="B67" s="31"/>
-      <c r="C67" s="32" t="s">
-        <v>159</v>
-      </c>
-      <c r="D67" s="33"/>
-      <c r="F67" s="1"/>
-      <c r="G67" s="2"/>
-      <c r="H67" s="1"/>
-      <c r="I67" s="1"/>
-      <c r="K67" s="1"/>
-      <c r="L67" s="1"/>
-      <c r="M67" s="1"/>
-      <c r="N67" s="1"/>
-      <c r="P67" s="2"/>
-      <c r="Q67" s="2"/>
-      <c r="R67" s="2"/>
-      <c r="S67" s="1"/>
-      <c r="T67" s="8"/>
-      <c r="U67" s="2"/>
-      <c r="V67" s="1"/>
-    </row>
-    <row r="68" spans="1:22" s="7" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A68" s="32" t="s">
-        <v>160</v>
-      </c>
-      <c r="B68" s="31"/>
-      <c r="C68" s="32" t="s">
-        <v>161</v>
-      </c>
-      <c r="D68" s="33"/>
-      <c r="F68" s="1"/>
-      <c r="G68" s="2"/>
-      <c r="H68" s="1"/>
-      <c r="I68" s="1"/>
-      <c r="K68" s="1"/>
-      <c r="L68" s="1"/>
-      <c r="M68" s="1"/>
-      <c r="N68" s="1"/>
-      <c r="P68" s="2"/>
-      <c r="Q68" s="2"/>
-      <c r="R68" s="2"/>
-      <c r="S68" s="1"/>
-      <c r="T68" s="8"/>
-      <c r="U68" s="2"/>
-      <c r="V68" s="1"/>
-    </row>
-    <row r="69" spans="1:22" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A69" s="32" t="s">
-        <v>162</v>
-      </c>
-      <c r="B69" s="31"/>
-      <c r="C69" s="32" t="s">
-        <v>163</v>
-      </c>
-      <c r="D69" s="33"/>
-      <c r="F69" s="1"/>
-      <c r="G69" s="2"/>
-      <c r="H69" s="1"/>
-      <c r="I69" s="1"/>
-      <c r="K69" s="1"/>
-      <c r="L69" s="1"/>
-      <c r="M69" s="1"/>
-      <c r="N69" s="1"/>
-      <c r="P69" s="2"/>
-      <c r="Q69" s="2"/>
-      <c r="R69" s="2"/>
-      <c r="S69" s="1"/>
-      <c r="T69" s="8"/>
-      <c r="U69" s="2"/>
-      <c r="V69" s="1"/>
-    </row>
-    <row r="70" spans="1:22" s="7" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A70" s="32" t="s">
-        <v>164</v>
-      </c>
-      <c r="B70" s="31"/>
-      <c r="C70" s="32" t="s">
-        <v>165</v>
-      </c>
-      <c r="D70" s="33"/>
-      <c r="F70" s="1"/>
-      <c r="G70" s="2"/>
-      <c r="H70" s="1"/>
-      <c r="I70" s="1"/>
-      <c r="K70" s="1"/>
-      <c r="L70" s="1"/>
-      <c r="M70" s="1"/>
-      <c r="N70" s="1"/>
-      <c r="P70" s="2"/>
-      <c r="Q70" s="2"/>
-      <c r="R70" s="2"/>
-      <c r="S70" s="1"/>
-      <c r="T70" s="8"/>
-      <c r="U70" s="2"/>
-      <c r="V70" s="1"/>
-    </row>
-    <row r="71" spans="1:22" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A71" s="32" t="s">
-        <v>166</v>
-      </c>
-      <c r="B71" s="31"/>
-      <c r="C71" s="32" t="s">
-        <v>167</v>
-      </c>
-      <c r="D71" s="33"/>
-      <c r="F71" s="1"/>
-      <c r="G71" s="2"/>
-      <c r="H71" s="1"/>
-      <c r="I71" s="1"/>
-      <c r="K71" s="1"/>
-      <c r="L71" s="1"/>
-      <c r="M71" s="1"/>
-      <c r="N71" s="1"/>
-      <c r="P71" s="2"/>
-      <c r="Q71" s="2"/>
-      <c r="R71" s="2"/>
-      <c r="S71" s="1"/>
-      <c r="T71" s="8"/>
-      <c r="U71" s="2"/>
-      <c r="V71" s="1"/>
-    </row>
-    <row r="72" spans="1:22" s="7" customFormat="1" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A72" s="32" t="s">
-        <v>168</v>
       </c>
       <c r="B72" s="31"/>
       <c r="C72" s="32" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="D72" s="33"/>
       <c r="F72" s="1"/>
@@ -24173,15 +25280,13 @@
       <c r="U72" s="2"/>
       <c r="V72" s="1"/>
     </row>
-    <row r="73" spans="1:22" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:22" s="7" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A73" s="32" t="s">
-        <v>170</v>
-      </c>
-      <c r="B73" s="31" t="s">
-        <v>171</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="B73" s="31"/>
       <c r="C73" s="32" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="D73" s="33"/>
       <c r="F73" s="1"/>
@@ -24200,13 +25305,13 @@
       <c r="U73" s="2"/>
       <c r="V73" s="1"/>
     </row>
-    <row r="74" spans="1:22" s="7" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:22" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A74" s="32" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="B74" s="31"/>
       <c r="C74" s="32" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="D74" s="33"/>
       <c r="F74" s="1"/>
@@ -24225,15 +25330,13 @@
       <c r="U74" s="2"/>
       <c r="V74" s="1"/>
     </row>
-    <row r="75" spans="1:22" s="7" customFormat="1" ht="201.6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:22" s="7" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A75" s="32" t="s">
-        <v>175</v>
-      </c>
-      <c r="B75" s="31" t="s">
-        <v>176</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="B75" s="31"/>
       <c r="C75" s="32" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="D75" s="33"/>
       <c r="F75" s="1"/>
@@ -24252,15 +25355,13 @@
       <c r="U75" s="2"/>
       <c r="V75" s="1"/>
     </row>
-    <row r="76" spans="1:22" s="7" customFormat="1" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:22" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A76" s="32" t="s">
-        <v>178</v>
-      </c>
-      <c r="B76" s="39" t="s">
-        <v>179</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="B76" s="31"/>
       <c r="C76" s="32" t="s">
-        <v>180</v>
+        <v>167</v>
       </c>
       <c r="D76" s="33"/>
       <c r="F76" s="1"/>
@@ -24279,15 +25380,13 @@
       <c r="U76" s="2"/>
       <c r="V76" s="1"/>
     </row>
-    <row r="77" spans="1:22" s="7" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:22" s="7" customFormat="1" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A77" s="32" t="s">
-        <v>181</v>
-      </c>
-      <c r="B77" s="39" t="s">
-        <v>179</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="B77" s="31"/>
       <c r="C77" s="32" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="D77" s="33"/>
       <c r="F77" s="1"/>
@@ -24306,13 +25405,15 @@
       <c r="U77" s="2"/>
       <c r="V77" s="1"/>
     </row>
-    <row r="78" spans="1:22" s="7" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:22" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A78" s="32" t="s">
-        <v>183</v>
-      </c>
-      <c r="B78" s="31"/>
+        <v>170</v>
+      </c>
+      <c r="B78" s="31" t="s">
+        <v>171</v>
+      </c>
       <c r="C78" s="32" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="D78" s="33"/>
       <c r="F78" s="1"/>
@@ -24331,15 +25432,13 @@
       <c r="U78" s="2"/>
       <c r="V78" s="1"/>
     </row>
-    <row r="79" spans="1:22" s="7" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:22" s="7" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A79" s="32" t="s">
-        <v>185</v>
-      </c>
-      <c r="B79" s="39" t="s">
-        <v>179</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="B79" s="31"/>
       <c r="C79" s="32" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="D79" s="33"/>
       <c r="F79" s="1"/>
@@ -24358,11 +25457,17 @@
       <c r="U79" s="2"/>
       <c r="V79" s="1"/>
     </row>
-    <row r="80" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="9"/>
-      <c r="B80" s="9"/>
-      <c r="C80" s="9"/>
-      <c r="D80" s="9"/>
+    <row r="80" spans="1:22" s="7" customFormat="1" ht="201.6" x14ac:dyDescent="0.3">
+      <c r="A80" s="32" t="s">
+        <v>175</v>
+      </c>
+      <c r="B80" s="31" t="s">
+        <v>176</v>
+      </c>
+      <c r="C80" s="32" t="s">
+        <v>177</v>
+      </c>
+      <c r="D80" s="33"/>
       <c r="F80" s="1"/>
       <c r="G80" s="2"/>
       <c r="H80" s="1"/>
@@ -24379,11 +25484,17 @@
       <c r="U80" s="2"/>
       <c r="V80" s="1"/>
     </row>
-    <row r="81" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="9"/>
-      <c r="B81" s="9"/>
-      <c r="C81" s="9"/>
-      <c r="D81" s="9"/>
+    <row r="81" spans="1:22" s="7" customFormat="1" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A81" s="32" t="s">
+        <v>178</v>
+      </c>
+      <c r="B81" s="39" t="s">
+        <v>179</v>
+      </c>
+      <c r="C81" s="32" t="s">
+        <v>180</v>
+      </c>
+      <c r="D81" s="33"/>
       <c r="F81" s="1"/>
       <c r="G81" s="2"/>
       <c r="H81" s="1"/>
@@ -24400,11 +25511,17 @@
       <c r="U81" s="2"/>
       <c r="V81" s="1"/>
     </row>
-    <row r="82" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="9"/>
-      <c r="B82" s="9"/>
-      <c r="C82" s="9"/>
-      <c r="D82" s="9"/>
+    <row r="82" spans="1:22" s="7" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+      <c r="A82" s="32" t="s">
+        <v>181</v>
+      </c>
+      <c r="B82" s="39" t="s">
+        <v>179</v>
+      </c>
+      <c r="C82" s="32" t="s">
+        <v>182</v>
+      </c>
+      <c r="D82" s="33"/>
       <c r="F82" s="1"/>
       <c r="G82" s="2"/>
       <c r="H82" s="1"/>
@@ -24421,11 +25538,15 @@
       <c r="U82" s="2"/>
       <c r="V82" s="1"/>
     </row>
-    <row r="83" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="9"/>
-      <c r="B83" s="9"/>
-      <c r="C83" s="9"/>
-      <c r="D83" s="9"/>
+    <row r="83" spans="1:22" s="7" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A83" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="B83" s="31"/>
+      <c r="C83" s="32" t="s">
+        <v>184</v>
+      </c>
+      <c r="D83" s="33"/>
       <c r="F83" s="1"/>
       <c r="G83" s="2"/>
       <c r="H83" s="1"/>
@@ -24442,11 +25563,17 @@
       <c r="U83" s="2"/>
       <c r="V83" s="1"/>
     </row>
-    <row r="84" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="9"/>
-      <c r="B84" s="9"/>
-      <c r="C84" s="9"/>
-      <c r="D84" s="9"/>
+    <row r="84" spans="1:22" s="7" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A84" s="32" t="s">
+        <v>185</v>
+      </c>
+      <c r="B84" s="39" t="s">
+        <v>179</v>
+      </c>
+      <c r="C84" s="32" t="s">
+        <v>186</v>
+      </c>
+      <c r="D84" s="33"/>
       <c r="F84" s="1"/>
       <c r="G84" s="2"/>
       <c r="H84" s="1"/>
@@ -24757,17 +25884,124 @@
       <c r="U98" s="2"/>
       <c r="V98" s="1"/>
     </row>
+    <row r="99" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A99" s="9"/>
+      <c r="B99" s="9"/>
+      <c r="C99" s="9"/>
+      <c r="D99" s="9"/>
+      <c r="F99" s="1"/>
+      <c r="G99" s="2"/>
+      <c r="H99" s="1"/>
+      <c r="I99" s="1"/>
+      <c r="K99" s="1"/>
+      <c r="L99" s="1"/>
+      <c r="M99" s="1"/>
+      <c r="N99" s="1"/>
+      <c r="P99" s="2"/>
+      <c r="Q99" s="2"/>
+      <c r="R99" s="2"/>
+      <c r="S99" s="1"/>
+      <c r="T99" s="8"/>
+      <c r="U99" s="2"/>
+      <c r="V99" s="1"/>
+    </row>
+    <row r="100" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="9"/>
+      <c r="B100" s="9"/>
+      <c r="C100" s="9"/>
+      <c r="D100" s="9"/>
+      <c r="F100" s="1"/>
+      <c r="G100" s="2"/>
+      <c r="H100" s="1"/>
+      <c r="I100" s="1"/>
+      <c r="K100" s="1"/>
+      <c r="L100" s="1"/>
+      <c r="M100" s="1"/>
+      <c r="N100" s="1"/>
+      <c r="P100" s="2"/>
+      <c r="Q100" s="2"/>
+      <c r="R100" s="2"/>
+      <c r="S100" s="1"/>
+      <c r="T100" s="8"/>
+      <c r="U100" s="2"/>
+      <c r="V100" s="1"/>
+    </row>
+    <row r="101" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A101" s="9"/>
+      <c r="B101" s="9"/>
+      <c r="C101" s="9"/>
+      <c r="D101" s="9"/>
+      <c r="F101" s="1"/>
+      <c r="G101" s="2"/>
+      <c r="H101" s="1"/>
+      <c r="I101" s="1"/>
+      <c r="K101" s="1"/>
+      <c r="L101" s="1"/>
+      <c r="M101" s="1"/>
+      <c r="N101" s="1"/>
+      <c r="P101" s="2"/>
+      <c r="Q101" s="2"/>
+      <c r="R101" s="2"/>
+      <c r="S101" s="1"/>
+      <c r="T101" s="8"/>
+      <c r="U101" s="2"/>
+      <c r="V101" s="1"/>
+    </row>
+    <row r="102" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A102" s="9"/>
+      <c r="B102" s="9"/>
+      <c r="C102" s="9"/>
+      <c r="D102" s="9"/>
+      <c r="F102" s="1"/>
+      <c r="G102" s="2"/>
+      <c r="H102" s="1"/>
+      <c r="I102" s="1"/>
+      <c r="K102" s="1"/>
+      <c r="L102" s="1"/>
+      <c r="M102" s="1"/>
+      <c r="N102" s="1"/>
+      <c r="P102" s="2"/>
+      <c r="Q102" s="2"/>
+      <c r="R102" s="2"/>
+      <c r="S102" s="1"/>
+      <c r="T102" s="8"/>
+      <c r="U102" s="2"/>
+      <c r="V102" s="1"/>
+    </row>
+    <row r="103" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A103" s="9"/>
+      <c r="B103" s="9"/>
+      <c r="C103" s="9"/>
+      <c r="D103" s="9"/>
+      <c r="F103" s="1"/>
+      <c r="G103" s="2"/>
+      <c r="H103" s="1"/>
+      <c r="I103" s="1"/>
+      <c r="K103" s="1"/>
+      <c r="L103" s="1"/>
+      <c r="M103" s="1"/>
+      <c r="N103" s="1"/>
+      <c r="P103" s="2"/>
+      <c r="Q103" s="2"/>
+      <c r="R103" s="2"/>
+      <c r="S103" s="1"/>
+      <c r="T103" s="8"/>
+      <c r="U103" s="2"/>
+      <c r="V103" s="1"/>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="D3" r:id="rId1" xr:uid="{2B31DE4B-4A38-4756-B415-A01130AE6B4E}"/>
     <hyperlink ref="D22" r:id="rId2" location=":~:text=IS%20NULL" xr:uid="{15FB0A58-134E-44CF-8460-D3867BBF411D}"/>
     <hyperlink ref="D27" r:id="rId3" location=":~:text=%D0%9E%D0%BF%D0%B5%D1%80%D0%B0%D1%82%D0%BE%D1%80%20IN" xr:uid="{44390156-6B41-4DD7-96A8-B538D00D18FB}"/>
-    <hyperlink ref="D33" r:id="rId4" location=":~:text=BETWEEN" xr:uid="{188A472A-EF50-457A-B93E-636D0BC334FD}"/>
-    <hyperlink ref="D38" r:id="rId5" location=":~:text=%D0%9E%D0%BF%D0%B5%D1%80%D0%B0%D1%82%D0%BE%D1%80%20LIKE" xr:uid="{BD8B2934-3646-4513-8D80-FE9D159CE504}"/>
+    <hyperlink ref="D37" r:id="rId4" location=":~:text=BETWEEN" xr:uid="{188A472A-EF50-457A-B93E-636D0BC334FD}"/>
+    <hyperlink ref="D42" r:id="rId5" location=":~:text=%D0%9E%D0%BF%D0%B5%D1%80%D0%B0%D1%82%D0%BE%D1%80%20LIKE" xr:uid="{BD8B2934-3646-4513-8D80-FE9D159CE504}"/>
+    <hyperlink ref="D33" r:id="rId6" location=":~:text=%D0%9F%D0%BE%D0%BB%D1%83%D1%87%D0%B5%D0%BD%D0%B8%D0%B5%20%D0%BD%D0%B0%D0%B1%D0%BE%D1%80%D0%B0%20%D0%B7%D0%BD%D0%B0%D1%87%D0%B5%D0%BD%D0%B8%D0%B9" xr:uid="{C94778A8-72D2-4D1B-A8EA-8B256EECAE21}"/>
+    <hyperlink ref="D67" r:id="rId7" xr:uid="{1B66564C-2B90-4962-9A43-E1209E23C53E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId6"/>
-  <drawing r:id="rId7"/>
+  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId8"/>
+  <drawing r:id="rId9"/>
 </worksheet>
 </file>
 
@@ -24829,8 +26063,8 @@
       <c r="U2" s="5"/>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A3" s="79" t="s">
-        <v>541</v>
+      <c r="A3" s="78" t="s">
+        <v>540</v>
       </c>
       <c r="C3" s="9"/>
       <c r="D3" s="26" t="s">
@@ -24842,13 +26076,13 @@
     </row>
     <row r="4" spans="1:22" ht="72" x14ac:dyDescent="0.3">
       <c r="A4" s="31" t="s">
-        <v>543</v>
-      </c>
-      <c r="B4" s="82" t="s">
-        <v>738</v>
-      </c>
-      <c r="C4" s="82" t="s">
         <v>542</v>
+      </c>
+      <c r="B4" s="81" t="s">
+        <v>735</v>
+      </c>
+      <c r="C4" s="81" t="s">
+        <v>541</v>
       </c>
       <c r="D4" s="9"/>
       <c r="P4" s="1"/>
@@ -24856,11 +26090,11 @@
       <c r="V4" s="2"/>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A5" s="76" t="s">
-        <v>549</v>
+      <c r="A5" s="75" t="s">
+        <v>548</v>
       </c>
       <c r="B5" s="31"/>
-      <c r="C5" s="82"/>
+      <c r="C5" s="81"/>
       <c r="D5" s="9"/>
       <c r="P5" s="1"/>
       <c r="U5" s="1"/>
@@ -24868,34 +26102,34 @@
     </row>
     <row r="6" spans="1:22" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A6" s="31"/>
-      <c r="B6" s="82" t="s">
-        <v>544</v>
+      <c r="B6" s="81" t="s">
+        <v>543</v>
       </c>
       <c r="C6" s="35" t="s">
+        <v>545</v>
+      </c>
+      <c r="D6" s="35" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A7" s="75" t="s">
         <v>546</v>
       </c>
-      <c r="D6" s="35" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A7" s="76" t="s">
-        <v>547</v>
-      </c>
-      <c r="B7" s="82"/>
+      <c r="B7" s="81"/>
       <c r="C7" s="35"/>
       <c r="D7" s="9"/>
     </row>
     <row r="8" spans="1:22" ht="72" x14ac:dyDescent="0.3">
       <c r="B8" s="31"/>
       <c r="C8" s="35" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A9" s="76" t="s">
-        <v>548</v>
+      <c r="A9" s="75" t="s">
+        <v>547</v>
       </c>
       <c r="B9" s="31"/>
       <c r="C9" s="31"/>
@@ -24903,56 +26137,56 @@
     </row>
     <row r="10" spans="1:22" ht="72" x14ac:dyDescent="0.3">
       <c r="A10" s="31"/>
-      <c r="B10" s="82" t="s">
-        <v>552</v>
+      <c r="B10" s="81" t="s">
+        <v>551</v>
       </c>
       <c r="C10" s="31" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="D10" s="4"/>
     </row>
     <row r="11" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A11" s="31"/>
-      <c r="B11" s="82" t="s">
-        <v>554</v>
+      <c r="B11" s="81" t="s">
+        <v>553</v>
       </c>
       <c r="C11" s="31" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="D11" s="33"/>
     </row>
     <row r="12" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="76" t="s">
-        <v>556</v>
+      <c r="A12" s="75" t="s">
+        <v>555</v>
       </c>
       <c r="B12" s="31"/>
       <c r="C12" s="31"/>
       <c r="D12" s="36" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="13" spans="1:22" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A13" s="31"/>
       <c r="B13" s="31" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C13" s="31" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="D13" s="35" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="14" spans="1:22" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A14" s="31"/>
-      <c r="B14" s="82" t="s">
-        <v>739</v>
+      <c r="B14" s="81" t="s">
+        <v>736</v>
       </c>
       <c r="C14" s="35" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="D14" s="36" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.3">
@@ -25719,17 +26953,17 @@
       <c r="U2" s="5"/>
     </row>
     <row r="3" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C3" s="76" t="s">
-        <v>565</v>
+      <c r="C3" s="75" t="s">
+        <v>564</v>
       </c>
       <c r="E3" s="7"/>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A4" s="79" t="s">
-        <v>559</v>
-      </c>
-      <c r="B4" s="85" t="s">
-        <v>571</v>
+      <c r="A4" s="78" t="s">
+        <v>558</v>
+      </c>
+      <c r="B4" s="84" t="s">
+        <v>570</v>
       </c>
       <c r="C4" s="9"/>
       <c r="D4" s="27" t="s">
@@ -25742,8 +26976,8 @@
     <row r="5" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="31"/>
       <c r="B5" s="31"/>
-      <c r="C5" s="82" t="s">
-        <v>566</v>
+      <c r="C5" s="81" t="s">
+        <v>565</v>
       </c>
       <c r="D5" s="9"/>
       <c r="P5" s="1"/>
@@ -25751,11 +26985,11 @@
       <c r="V5" s="2"/>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A6" s="76" t="s">
-        <v>563</v>
+      <c r="A6" s="75" t="s">
+        <v>562</v>
       </c>
       <c r="B6" s="31"/>
-      <c r="C6" s="82"/>
+      <c r="C6" s="81"/>
       <c r="D6" s="9"/>
       <c r="P6" s="1"/>
       <c r="U6" s="1"/>
@@ -25765,7 +26999,7 @@
       <c r="A7" s="31"/>
       <c r="B7" s="35"/>
       <c r="C7" s="73" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="D7" s="9"/>
       <c r="P7" s="1"/>
@@ -25773,11 +27007,11 @@
       <c r="V7" s="2"/>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A8" s="76" t="s">
-        <v>564</v>
+      <c r="A8" s="75" t="s">
+        <v>563</v>
       </c>
       <c r="B8" s="31"/>
-      <c r="C8" s="82"/>
+      <c r="C8" s="81"/>
       <c r="D8" s="9"/>
       <c r="P8" s="1"/>
       <c r="U8" s="1"/>
@@ -25786,49 +27020,49 @@
     <row r="9" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A9" s="31"/>
       <c r="B9" s="35" t="s">
+        <v>559</v>
+      </c>
+      <c r="C9" s="73" t="s">
         <v>560</v>
       </c>
-      <c r="C9" s="73" t="s">
-        <v>561</v>
-      </c>
       <c r="D9" s="35"/>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A10" s="79" t="s">
-        <v>568</v>
-      </c>
-      <c r="B10" s="85" t="s">
-        <v>570</v>
+      <c r="A10" s="78" t="s">
+        <v>567</v>
+      </c>
+      <c r="B10" s="84" t="s">
+        <v>569</v>
       </c>
       <c r="C10" s="31"/>
-      <c r="D10" s="77" t="s">
+      <c r="D10" s="76" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="11" spans="1:22" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A11" s="31"/>
       <c r="B11" s="31"/>
-      <c r="C11" s="82" t="s">
-        <v>567</v>
+      <c r="C11" s="81" t="s">
+        <v>566</v>
       </c>
       <c r="D11" s="41"/>
     </row>
     <row r="12" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A12" s="31"/>
-      <c r="B12" s="82" t="s">
+      <c r="B12" s="81" t="s">
+        <v>571</v>
+      </c>
+      <c r="C12" s="31" t="s">
         <v>572</v>
       </c>
-      <c r="C12" s="31" t="s">
-        <v>573</v>
-      </c>
       <c r="D12" s="4"/>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A13" s="79" t="s">
-        <v>569</v>
-      </c>
-      <c r="B13" s="85" t="s">
-        <v>575</v>
+      <c r="A13" s="78" t="s">
+        <v>568</v>
+      </c>
+      <c r="B13" s="84" t="s">
+        <v>574</v>
       </c>
       <c r="C13" s="31"/>
       <c r="D13" s="36"/>
@@ -25837,7 +27071,7 @@
       <c r="A14" s="31"/>
       <c r="B14" s="31"/>
       <c r="C14" s="31" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="D14" s="35"/>
     </row>
@@ -26559,7 +27793,7 @@
     <tabColor theme="8"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:E12"/>
+  <dimension ref="A2:E13"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="36" style="2" customWidth="1"/>
@@ -26596,88 +27830,105 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="53" t="s">
-        <v>508</v>
-      </c>
-      <c r="D3" s="77" t="s">
+        <v>507</v>
+      </c>
+      <c r="D3" s="76" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="C4" s="73" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A5" s="52"/>
       <c r="B5" s="52" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C5" s="52" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="D5" s="52"/>
     </row>
     <row r="6" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B6" s="73" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="D6" s="73" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B7" s="73" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="D7" s="73" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="D8" s="73" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>756</v>
+      </c>
+      <c r="C9" s="73" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="331.2" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>757</v>
+      </c>
+      <c r="C10" s="91" t="s">
+        <v>758</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
         <v>522</v>
       </c>
-      <c r="C9" s="73" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
+      <c r="B11" s="73" t="s">
+        <v>524</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>523</v>
       </c>
-      <c r="B10" s="73" t="s">
-        <v>525</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="C12" s="2" t="s">
-        <v>535</v>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C13" s="2" t="s">
+        <v>534</v>
       </c>
     </row>
   </sheetData>
@@ -26691,116 +27942,6 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E11B2404-3BCE-4C18-8606-2DD385DF9F42}">
-  <sheetPr>
-    <tabColor theme="8"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A2:E12"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="36" style="2" customWidth="1"/>
-    <col min="2" max="2" width="50.5546875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="71.21875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="56.44140625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="6.21875" style="52" customWidth="1"/>
-    <col min="6" max="6" width="43.21875" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="55.109375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="67.88671875" style="2" customWidth="1"/>
-    <col min="9" max="9" width="64.33203125" style="2" customWidth="1"/>
-    <col min="10" max="10" width="7.77734375" style="2" customWidth="1"/>
-    <col min="11" max="11" width="39.21875" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="48.88671875" style="2" customWidth="1"/>
-    <col min="13" max="13" width="72.6640625" style="2" customWidth="1"/>
-    <col min="14" max="14" width="43.88671875" style="2" customWidth="1"/>
-    <col min="15" max="15" width="7.77734375" style="2" customWidth="1"/>
-    <col min="16" max="16" width="56.77734375" style="2" customWidth="1"/>
-    <col min="17" max="17" width="46.77734375" style="2" customWidth="1"/>
-    <col min="18" max="18" width="62.88671875" style="2" customWidth="1"/>
-    <col min="19" max="19" width="49.21875" style="2" customWidth="1"/>
-    <col min="20" max="20" width="8.77734375" style="2"/>
-    <col min="21" max="21" width="67.77734375" style="2" customWidth="1"/>
-    <col min="22" max="22" width="68.33203125" style="2" customWidth="1"/>
-    <col min="23" max="24" width="59.33203125" style="2" customWidth="1"/>
-    <col min="25" max="25" width="59.6640625" style="2" customWidth="1"/>
-    <col min="26" max="26" width="99.44140625" style="2" customWidth="1"/>
-    <col min="27" max="27" width="41.21875" style="2" customWidth="1"/>
-    <col min="28" max="16384" width="8.77734375" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="1:5" s="51" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="E2" s="52"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="53" t="s">
-        <v>402</v>
-      </c>
-      <c r="D3" s="77" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="90" t="s">
-        <v>671</v>
-      </c>
-      <c r="D4" s="77"/>
-    </row>
-    <row r="5" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A5" s="62"/>
-      <c r="B5" s="2" t="s">
-        <v>665</v>
-      </c>
-      <c r="C5" s="73" t="s">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="90" t="s">
-        <v>576</v>
-      </c>
-      <c r="C6" s="73"/>
-    </row>
-    <row r="7" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="62"/>
-      <c r="B7" s="2" t="s">
-        <v>664</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="90" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="62"/>
-      <c r="B9" s="2" t="s">
-        <v>666</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>669</v>
-      </c>
-      <c r="D9" s="73" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="C12" s="2" t="s">
-        <v>535</v>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="D3" r:id="rId1" xr:uid="{DB56E6E2-330E-42B3-B359-8B2B5C647416}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{604A5B54-859D-4372-BCC7-7C5355B11405}">
   <sheetPr>
     <tabColor theme="8"/>
     <pageSetUpPr fitToPage="1"/>
@@ -26842,83 +27983,100 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="53" t="s">
-        <v>401</v>
-      </c>
-      <c r="D3" s="77" t="s">
+        <v>402</v>
+      </c>
+      <c r="D3" s="76" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="90" t="s">
-        <v>401</v>
-      </c>
-      <c r="D4" s="77"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="73"/>
+      <c r="A4" s="89" t="s">
+        <v>670</v>
+      </c>
+      <c r="D4" s="76"/>
+    </row>
+    <row r="5" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A5" s="62"/>
       <c r="B5" s="2" t="s">
-        <v>677</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>676</v>
-      </c>
-      <c r="D5" s="77"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="90" t="s">
-        <v>576</v>
-      </c>
-      <c r="D6" s="77"/>
-    </row>
-    <row r="7" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="62"/>
-      <c r="C7" s="73" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="90" t="s">
-        <v>670</v>
-      </c>
-      <c r="C8" s="73"/>
-    </row>
-    <row r="9" spans="1:5" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="62"/>
-      <c r="B9" s="73" t="s">
-        <v>675</v>
+        <v>664</v>
+      </c>
+      <c r="C5" s="73" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A6" s="66" t="s">
+        <v>796</v>
+      </c>
+      <c r="C6" s="91" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="89" t="s">
+        <v>575</v>
+      </c>
+      <c r="C7" s="73"/>
+    </row>
+    <row r="8" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="62"/>
+      <c r="B8" s="2" t="s">
+        <v>663</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A9" s="66" t="s">
+        <v>796</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="89" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A11" s="62"/>
+      <c r="B11" s="2" t="s">
+        <v>665</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>668</v>
+      </c>
+      <c r="D11" s="73" t="s">
         <v>673</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="62"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="C14" s="2" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="D3" r:id="rId1" xr:uid="{85FFC1CE-642C-4332-9520-2896E8E45FA6}"/>
+    <hyperlink ref="D3" r:id="rId1" xr:uid="{DB56E6E2-330E-42B3-B359-8B2B5C647416}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId2"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5BD91E9-1EBE-4787-BA8F-72F81F37997A}">
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{604A5B54-859D-4372-BCC7-7C5355B11405}">
   <sheetPr>
     <tabColor theme="8"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:E20"/>
+  <dimension ref="A2:E15"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="36" style="2" customWidth="1"/>
-    <col min="2" max="2" width="58.77734375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="50.5546875" style="2" customWidth="1"/>
     <col min="3" max="3" width="71.21875" style="2" customWidth="1"/>
     <col min="4" max="4" width="56.44140625" style="2" customWidth="1"/>
     <col min="5" max="5" width="6.21875" style="52" customWidth="1"/>
@@ -26951,211 +28109,85 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="53" t="s">
-        <v>680</v>
-      </c>
-      <c r="D3" s="77" t="s">
+        <v>401</v>
+      </c>
+      <c r="D3" s="76" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="259.2" x14ac:dyDescent="0.3">
-      <c r="A4" s="52"/>
-      <c r="B4" s="52" t="s">
-        <v>510</v>
-      </c>
-      <c r="C4" s="52" t="s">
-        <v>692</v>
-      </c>
-      <c r="D4" s="52"/>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="89" t="s">
+        <v>401</v>
+      </c>
+      <c r="D4" s="76"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="90" t="s">
-        <v>681</v>
-      </c>
+      <c r="A5" s="73"/>
       <c r="B5" s="2" t="s">
-        <v>689</v>
+        <v>676</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>685</v>
-      </c>
-      <c r="D5" s="77" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A6" s="73" t="s">
-        <v>681</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="73" t="s">
-        <v>576</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="288" x14ac:dyDescent="0.3">
-      <c r="A8" s="73" t="s">
-        <v>530</v>
-      </c>
-      <c r="B8" s="73" t="s">
-        <v>703</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>700</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>704</v>
+        <v>675</v>
+      </c>
+      <c r="D5" s="76"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="89" t="s">
+        <v>575</v>
+      </c>
+      <c r="D6" s="76"/>
+    </row>
+    <row r="7" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="62"/>
+      <c r="C7" s="73" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A8" s="66" t="s">
+        <v>796</v>
+      </c>
+      <c r="B8" s="91" t="s">
+        <v>800</v>
+      </c>
+      <c r="C8" s="91" t="s">
+        <v>799</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="90" t="s">
-        <v>682</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>689</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>686</v>
-      </c>
-      <c r="D9" s="77" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A10" s="73" t="s">
-        <v>576</v>
-      </c>
-      <c r="C10" s="73" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A11" s="73" t="s">
-        <v>530</v>
-      </c>
-      <c r="C11" s="73" t="s">
-        <v>708</v>
+      <c r="A9" s="89" t="s">
+        <v>669</v>
+      </c>
+      <c r="C9" s="73"/>
+    </row>
+    <row r="10" spans="1:5" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="62"/>
+      <c r="B10" s="73" t="s">
+        <v>674</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>672</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="90" t="s">
-        <v>683</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>690</v>
-      </c>
-      <c r="C12" s="73" t="s">
-        <v>687</v>
-      </c>
-      <c r="D12" s="77" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A13" s="73" t="s">
-        <v>576</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>697</v>
-      </c>
-      <c r="D13" s="77"/>
-    </row>
-    <row r="14" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A14" s="73" t="s">
-        <v>530</v>
-      </c>
-      <c r="B14" s="73"/>
-      <c r="C14" s="2" t="s">
-        <v>707</v>
-      </c>
+      <c r="A12" s="62"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="90" t="s">
-        <v>684</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>690</v>
-      </c>
       <c r="C15" s="2" t="s">
-        <v>688</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A16" s="73" t="s">
-        <v>576</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A17" s="73" t="s">
-        <v>530</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="90" t="s">
-        <v>227</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>690</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>696</v>
-      </c>
-      <c r="D18" s="77" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="244.8" x14ac:dyDescent="0.3">
-      <c r="A19" s="73" t="s">
-        <v>530</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>705</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>701</v>
-      </c>
-      <c r="D19" s="77"/>
-    </row>
-    <row r="20" spans="1:4" ht="288" x14ac:dyDescent="0.3">
-      <c r="A20" s="66" t="s">
-        <v>702</v>
-      </c>
-      <c r="B20" s="73" t="s">
-        <v>693</v>
-      </c>
-      <c r="C20" s="73" t="s">
-        <v>709</v>
-      </c>
-      <c r="D20" s="73" t="s">
-        <v>691</v>
+        <v>534</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="D3" r:id="rId1" xr:uid="{9E74AAEF-A171-4A8F-B94E-830DC591E252}"/>
-    <hyperlink ref="D5" r:id="rId2" location=":~:text=%D0%A4%D1%83%D0%BD%D0%BA%D1%86%D0%B8%D1%8F%20Avg" xr:uid="{543286E0-264B-4323-AECC-02E7F4F0D2ED}"/>
-    <hyperlink ref="D18" r:id="rId3" location=":~:text=%D0%A4%D1%83%D0%BD%D0%BA%D1%86%D0%B8%D1%8F%20Count" xr:uid="{97E8BABA-F918-49A3-B587-137ADB5269E2}"/>
-    <hyperlink ref="D12" r:id="rId4" location=":~:text=%D0%A4%D1%83%D0%BD%D0%BA%D1%86%D0%B8%D0%B8%20Min%20%D0%B8%20Max" xr:uid="{F07A5191-7562-4057-BBC7-484384B822C8}"/>
-    <hyperlink ref="D9" r:id="rId5" location=":~:text=%D0%A4%D1%83%D0%BD%D0%BA%D1%86%D0%B8%D1%8F%20Sum" xr:uid="{1C9F1936-7656-4340-ABA2-1E35A435D5D1}"/>
+    <hyperlink ref="D3" r:id="rId1" xr:uid="{85FFC1CE-642C-4332-9520-2896E8E45FA6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId6"/>
-  <drawing r:id="rId7"/>
+  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId2"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15477BA0-499D-45E0-87E5-D7C7CA4BA6B4}">
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5BD91E9-1EBE-4787-BA8F-72F81F37997A}">
   <sheetPr>
     <tabColor theme="8"/>
     <pageSetUpPr fitToPage="1"/>
@@ -27197,162 +28229,457 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="53" t="s">
+        <v>679</v>
+      </c>
+      <c r="D3" s="76" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="259.2" x14ac:dyDescent="0.3">
+      <c r="A4" s="52"/>
+      <c r="B4" s="52" t="s">
+        <v>509</v>
+      </c>
+      <c r="C4" s="52" t="s">
+        <v>691</v>
+      </c>
+      <c r="D4" s="52"/>
+    </row>
+    <row r="5" spans="1:5" s="93" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="94" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" s="93" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B6" s="93" t="s">
+        <v>762</v>
+      </c>
+      <c r="C6" s="93" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" s="93" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B7" s="93" t="s">
+        <v>765</v>
+      </c>
+      <c r="C7" s="93" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="89" t="s">
+        <v>680</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>688</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>684</v>
+      </c>
+      <c r="D8" s="76" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A9" s="73" t="s">
+        <v>680</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="73" t="s">
+        <v>575</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="288" x14ac:dyDescent="0.3">
+      <c r="A11" s="73" t="s">
+        <v>529</v>
+      </c>
+      <c r="B11" s="73" t="s">
+        <v>702</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>699</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="89" t="s">
+        <v>681</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>688</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>685</v>
+      </c>
+      <c r="D12" s="76" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A13" s="73" t="s">
+        <v>575</v>
+      </c>
+      <c r="C13" s="73" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A14" s="73" t="s">
+        <v>529</v>
+      </c>
+      <c r="C14" s="73" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="89" t="s">
+        <v>682</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>689</v>
+      </c>
+      <c r="C15" s="73" t="s">
+        <v>686</v>
+      </c>
+      <c r="D15" s="76" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A16" s="73" t="s">
+        <v>575</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>696</v>
+      </c>
+      <c r="D16" s="76"/>
+    </row>
+    <row r="17" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A17" s="73" t="s">
+        <v>529</v>
+      </c>
+      <c r="B17" s="73"/>
+      <c r="C17" s="2" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" s="89" t="s">
+        <v>683</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>689</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A19" s="73" t="s">
+        <v>575</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A20" s="73" t="s">
+        <v>529</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" s="89" t="s">
+        <v>227</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>689</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>695</v>
+      </c>
+      <c r="D21" s="76" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="244.8" x14ac:dyDescent="0.3">
+      <c r="A22" s="73" t="s">
+        <v>529</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>704</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>700</v>
+      </c>
+      <c r="D22" s="76"/>
+    </row>
+    <row r="23" spans="1:4" ht="288" x14ac:dyDescent="0.3">
+      <c r="A23" s="66" t="s">
+        <v>701</v>
+      </c>
+      <c r="B23" s="73" t="s">
+        <v>692</v>
+      </c>
+      <c r="C23" s="73" t="s">
+        <v>708</v>
+      </c>
+      <c r="D23" s="73" t="s">
+        <v>690</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D3" r:id="rId1" xr:uid="{9E74AAEF-A171-4A8F-B94E-830DC591E252}"/>
+    <hyperlink ref="D8" r:id="rId2" location=":~:text=%D0%A4%D1%83%D0%BD%D0%BA%D1%86%D0%B8%D1%8F%20Avg" xr:uid="{543286E0-264B-4323-AECC-02E7F4F0D2ED}"/>
+    <hyperlink ref="D21" r:id="rId3" location=":~:text=%D0%A4%D1%83%D0%BD%D0%BA%D1%86%D0%B8%D1%8F%20Count" xr:uid="{97E8BABA-F918-49A3-B587-137ADB5269E2}"/>
+    <hyperlink ref="D15" r:id="rId4" location=":~:text=%D0%A4%D1%83%D0%BD%D0%BA%D1%86%D0%B8%D0%B8%20Min%20%D0%B8%20Max" xr:uid="{F07A5191-7562-4057-BBC7-484384B822C8}"/>
+    <hyperlink ref="D12" r:id="rId5" location=":~:text=%D0%A4%D1%83%D0%BD%D0%BA%D1%86%D0%B8%D1%8F%20Sum" xr:uid="{1C9F1936-7656-4340-ABA2-1E35A435D5D1}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId6"/>
+  <drawing r:id="rId7"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15477BA0-499D-45E0-87E5-D7C7CA4BA6B4}">
+  <sheetPr>
+    <tabColor theme="8"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A2:E27"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="36" style="2" customWidth="1"/>
+    <col min="2" max="2" width="58.77734375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="71.21875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="56.44140625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="6.21875" style="52" customWidth="1"/>
+    <col min="6" max="6" width="43.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="55.109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="67.88671875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="64.33203125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="7.77734375" style="2" customWidth="1"/>
+    <col min="11" max="11" width="39.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="48.88671875" style="2" customWidth="1"/>
+    <col min="13" max="13" width="72.6640625" style="2" customWidth="1"/>
+    <col min="14" max="14" width="43.88671875" style="2" customWidth="1"/>
+    <col min="15" max="15" width="7.77734375" style="2" customWidth="1"/>
+    <col min="16" max="16" width="56.77734375" style="2" customWidth="1"/>
+    <col min="17" max="17" width="46.77734375" style="2" customWidth="1"/>
+    <col min="18" max="18" width="62.88671875" style="2" customWidth="1"/>
+    <col min="19" max="19" width="49.21875" style="2" customWidth="1"/>
+    <col min="20" max="20" width="8.77734375" style="2"/>
+    <col min="21" max="21" width="67.77734375" style="2" customWidth="1"/>
+    <col min="22" max="22" width="68.33203125" style="2" customWidth="1"/>
+    <col min="23" max="24" width="59.33203125" style="2" customWidth="1"/>
+    <col min="25" max="25" width="59.6640625" style="2" customWidth="1"/>
+    <col min="26" max="26" width="99.44140625" style="2" customWidth="1"/>
+    <col min="27" max="27" width="41.21875" style="2" customWidth="1"/>
+    <col min="28" max="16384" width="8.77734375" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:5" s="51" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="E2" s="52"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="53" t="s">
+        <v>709</v>
+      </c>
+      <c r="D3" s="76" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C4" s="91" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A5" s="73"/>
+      <c r="B5" s="73" t="s">
+        <v>713</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>710</v>
       </c>
-      <c r="D3" s="77" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="52"/>
-      <c r="B4" s="52"/>
-      <c r="C4" s="52"/>
-      <c r="D4" s="52"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="C5" s="73" t="s">
-        <v>717</v>
+      <c r="D5" s="2" t="s">
+        <v>711</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A6" s="73"/>
-      <c r="B6" s="73" t="s">
+      <c r="B6" s="73"/>
+      <c r="C6" s="2" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="89" t="s">
+        <v>715</v>
+      </c>
+      <c r="D7" s="76"/>
+    </row>
+    <row r="8" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="73"/>
+      <c r="B8" s="73" t="s">
         <v>714</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>711</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>712</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A7" s="73"/>
-      <c r="B7" s="73"/>
-      <c r="C7" s="2" t="s">
-        <v>713</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="90" t="s">
-        <v>716</v>
-      </c>
-      <c r="D8" s="77"/>
-    </row>
-    <row r="9" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="73"/>
-      <c r="B9" s="73" t="s">
+      <c r="C8" s="73" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="53" t="s">
+        <v>718</v>
+      </c>
+      <c r="D9" s="76" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="C10" s="73" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="C11" s="73" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="C12" s="2" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>723</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>721</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="89" t="s">
         <v>715</v>
       </c>
-      <c r="C9" s="73" t="s">
-        <v>718</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="53" t="s">
-        <v>719</v>
-      </c>
-      <c r="D10" s="77" t="s">
+    </row>
+    <row r="15" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="C15" s="2" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="53" t="s">
+        <v>726</v>
+      </c>
+      <c r="C16" s="43"/>
+      <c r="D16" s="76" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="C11" s="73" t="s">
-        <v>720</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="C12" s="73" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="C13" s="2" t="s">
-        <v>721</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="72" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
-        <v>724</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>722</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="90" t="s">
-        <v>716</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="C16" s="2" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="53" t="s">
+    <row r="17" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="C17" s="73" t="s">
         <v>727</v>
       </c>
-      <c r="C17" s="43"/>
-      <c r="D17" s="77" t="s">
+    </row>
+    <row r="18" spans="1:4" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="C18" s="91" t="s">
+        <v>746</v>
+      </c>
+      <c r="D18" s="91" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="B19" s="43"/>
+      <c r="C19" s="77" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A20" s="73" t="s">
+        <v>742</v>
+      </c>
+      <c r="B20" s="73" t="s">
+        <v>740</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="A21" s="73" t="s">
+        <v>741</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" s="53" t="s">
+        <v>744</v>
+      </c>
+      <c r="D22" s="76" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="C18" s="73" t="s">
-        <v>728</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="C19" s="73" t="s">
-        <v>730</v>
-      </c>
-      <c r="D19" s="73" t="s">
-        <v>729</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="B20" s="43"/>
-      <c r="C20" s="78" t="s">
-        <v>731</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="73" t="s">
-        <v>745</v>
-      </c>
-      <c r="B21" s="73" t="s">
-        <v>743</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>742</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="187.2" x14ac:dyDescent="0.3">
-      <c r="A22" s="73" t="s">
-        <v>744</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="53" t="s">
+    <row r="23" spans="1:4" ht="259.2" x14ac:dyDescent="0.3">
+      <c r="B23" s="2" t="s">
         <v>747</v>
       </c>
-      <c r="D23" s="77" t="s">
-        <v>109</v>
+      <c r="C23" s="91" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" s="53" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="C25" s="91" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" s="53" t="s">
+        <v>750</v>
+      </c>
+      <c r="B26" s="83" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="144" x14ac:dyDescent="0.3">
+      <c r="B27" s="77" t="s">
+        <v>751</v>
+      </c>
+      <c r="C27" s="91" t="s">
+        <v>752</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="D3" r:id="rId1" xr:uid="{77CDA991-63F1-40E4-A41F-F96B264AF4B3}"/>
-    <hyperlink ref="D10" r:id="rId2" location=":~:text=%D0%A4%D0%B8%D0%BB%D1%8C%D1%82%D1%80%D0%B0%D1%86%D0%B8%D1%8F%20%D0%B3%D1%80%D1%83%D0%BF%D0%BF.%20HAVING" xr:uid="{7964F6FF-2EAF-4BD3-82D2-37627A9ACFD4}"/>
-    <hyperlink ref="D17" r:id="rId3" xr:uid="{B3944A25-C0A8-4BEB-926A-B7D97A16EF2A}"/>
-    <hyperlink ref="D23" r:id="rId4" location=":~:text=CUBE%20%D0%BF%D0%BE%D1%85%D0%BE%D0%B6%20%D0%BD%D0%B0%20ROLLUP" xr:uid="{9459E309-91A9-438D-BEC6-62FD725247A9}"/>
+    <hyperlink ref="D9" r:id="rId2" location=":~:text=%D0%A4%D0%B8%D0%BB%D1%8C%D1%82%D1%80%D0%B0%D1%86%D0%B8%D1%8F%20%D0%B3%D1%80%D1%83%D0%BF%D0%BF.%20HAVING" xr:uid="{7964F6FF-2EAF-4BD3-82D2-37627A9ACFD4}"/>
+    <hyperlink ref="D16" r:id="rId3" xr:uid="{B3944A25-C0A8-4BEB-926A-B7D97A16EF2A}"/>
+    <hyperlink ref="D22" r:id="rId4" location=":~:text=CUBE%20%D0%BF%D0%BE%D1%85%D0%BE%D0%B6%20%D0%BD%D0%B0%20ROLLUP" xr:uid="{9459E309-91A9-438D-BEC6-62FD725247A9}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId5"/>
@@ -29290,7 +30617,7 @@
     <row r="6" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A6" s="9"/>
       <c r="C6" s="72" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="D6" s="9"/>
     </row>
@@ -30146,7 +31473,7 @@
     </row>
     <row r="4" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="74" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B4" s="9"/>
       <c r="C4" s="9"/>
@@ -30209,7 +31536,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="11" spans="1:22" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:22" ht="144" x14ac:dyDescent="0.3">
       <c r="A11" s="9"/>
       <c r="B11" s="9"/>
       <c r="C11" s="42" t="s">
@@ -30221,7 +31548,7 @@
     </row>
     <row r="12" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="74" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
@@ -30233,7 +31560,7 @@
         <v>82</v>
       </c>
       <c r="C13" s="73" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D13" s="9"/>
     </row>
@@ -30243,22 +31570,22 @@
         <v>83</v>
       </c>
       <c r="C14" s="73" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="15" spans="1:22" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A15" s="9"/>
       <c r="B15" s="73" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C15" s="73" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="D15" s="9"/>
     </row>
     <row r="16" spans="1:22" s="7" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A16" s="74" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B16" s="9"/>
       <c r="C16" s="9"/>
@@ -30285,7 +31612,7 @@
         <v>82</v>
       </c>
       <c r="C17" s="73" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D17" s="9"/>
       <c r="F17" s="1"/>
@@ -30307,10 +31634,10 @@
     <row r="18" spans="1:22" s="7" customFormat="1" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A18" s="9"/>
       <c r="B18" s="73" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C18" s="73" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D18" s="9"/>
       <c r="F18" s="1"/>
@@ -30331,7 +31658,7 @@
     </row>
     <row r="19" spans="1:22" s="7" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A19" s="74" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B19" s="9"/>
       <c r="C19" s="9"/>
@@ -30356,7 +31683,7 @@
       <c r="A20" s="9"/>
       <c r="B20" s="9"/>
       <c r="C20" s="9" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="D20" s="9"/>
       <c r="F20" s="1"/>
@@ -30378,10 +31705,10 @@
     <row r="21" spans="1:22" s="7" customFormat="1" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A21" s="9"/>
       <c r="B21" s="73" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C21" s="73" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="D21" s="9"/>
       <c r="F21" s="1"/>
@@ -31440,7 +32767,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="16" type="noConversion"/>
+  <phoneticPr fontId="17" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="D46" r:id="rId1" location=":~:text=%D0%A1%D0%BE%D0%B7%D0%B4%D0%B0%D0%BD%D0%B8%D0%B5%20%D0%B1%D0%B0%D0%B7%D1%8B%20%D0%B4%D0%B0%D0%BD%D0%BD%D1%8B%D1%85" xr:uid="{FDFE2116-2B22-4A87-B37D-3DFA9E8F9FE0}"/>
     <hyperlink ref="D44" r:id="rId2" location=":~:text=%D0%A1%D0%BE%D0%B7%D0%B4%D0%B0%D0%BD%D0%B8%D0%B5%20%D0%B1%D0%B0%D0%B7%D1%8B%20%D0%B4%D0%B0%D0%BD%D0%BD%D1%8B%D1%85%20%D0%B2%20SQL%20Management%20Studio" xr:uid="{5B701F02-CEF7-44EA-83C6-0E21D7145608}"/>
@@ -31914,7 +33241,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="16" type="noConversion"/>
+  <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
@@ -31978,11 +33305,11 @@
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A3" s="74" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B3" s="9"/>
       <c r="C3" s="9"/>
-      <c r="D3" s="77" t="s">
+      <c r="D3" s="76" t="s">
         <v>109</v>
       </c>
     </row>
@@ -31990,17 +33317,17 @@
       <c r="A4" s="9"/>
       <c r="B4" s="42"/>
       <c r="C4" s="73" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D4" s="9"/>
     </row>
     <row r="5" spans="1:22" ht="374.4" x14ac:dyDescent="0.3">
       <c r="A5" s="9"/>
       <c r="B5" s="73" t="s">
+        <v>505</v>
+      </c>
+      <c r="C5" s="73" t="s">
         <v>506</v>
-      </c>
-      <c r="C5" s="73" t="s">
-        <v>507</v>
       </c>
       <c r="D5" s="9"/>
     </row>
@@ -32888,7 +34215,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="65" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B15" s="48"/>
       <c r="C15" s="48"/>
@@ -32896,7 +34223,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="70" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B16" s="48"/>
       <c r="C16" s="48"/>
@@ -33110,7 +34437,7 @@
     </row>
     <row r="7" spans="1:27" s="52" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="74" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B7" s="48"/>
       <c r="C7" s="48"/>
@@ -34404,7 +35731,7 @@
     </row>
     <row r="4" spans="1:5" s="52" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="70" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B4" s="48"/>
       <c r="C4" s="48"/>
@@ -34414,109 +35741,109 @@
       <c r="A5" s="9"/>
       <c r="B5" s="48"/>
       <c r="C5" s="73" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="D5" s="9"/>
     </row>
     <row r="6" spans="1:5" s="52" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="76" t="s">
-        <v>471</v>
+      <c r="A6" s="75" t="s">
+        <v>470</v>
       </c>
       <c r="B6" s="48" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C6" s="48"/>
       <c r="D6" s="9"/>
     </row>
     <row r="7" spans="1:5" s="52" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="43" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B7" s="48"/>
       <c r="C7" s="71" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="D7" s="9"/>
     </row>
     <row r="8" spans="1:5" s="52" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="73" t="s">
+        <v>462</v>
+      </c>
+      <c r="B8" s="73" t="s">
         <v>463</v>
       </c>
-      <c r="B8" s="73" t="s">
-        <v>464</v>
-      </c>
       <c r="C8" s="73" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:5" s="52" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A9" s="73" t="s">
+        <v>464</v>
+      </c>
+      <c r="B9" s="73" t="s">
+        <v>466</v>
+      </c>
+      <c r="C9" s="73" t="s">
         <v>465</v>
-      </c>
-      <c r="B9" s="73" t="s">
-        <v>467</v>
-      </c>
-      <c r="C9" s="73" t="s">
-        <v>466</v>
       </c>
       <c r="D9" s="9"/>
     </row>
     <row r="10" spans="1:5" s="52" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A10" s="73" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B10" s="73" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C10" s="73" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="D10" s="9"/>
     </row>
     <row r="11" spans="1:5" s="52" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="76" t="s">
-        <v>477</v>
+      <c r="A11" s="75" t="s">
+        <v>476</v>
       </c>
       <c r="B11" s="73" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C11" s="48"/>
-      <c r="D11" s="77" t="s">
+      <c r="D11" s="76" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="12" spans="1:5" s="52" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="73" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B12" s="73" t="s">
+        <v>471</v>
+      </c>
+      <c r="C12" s="73" t="s">
         <v>472</v>
       </c>
-      <c r="C12" s="73" t="s">
-        <v>473</v>
-      </c>
       <c r="D12" s="9"/>
     </row>
     <row r="13" spans="1:5" s="52" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="76" t="s">
-        <v>476</v>
+      <c r="A13" s="75" t="s">
+        <v>475</v>
       </c>
       <c r="B13" s="73" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C13" s="48"/>
       <c r="D13" s="9"/>
     </row>
     <row r="14" spans="1:5" s="52" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" s="73" t="s">
+        <v>477</v>
+      </c>
+      <c r="B14" s="73" t="s">
+        <v>479</v>
+      </c>
+      <c r="C14" s="73" t="s">
         <v>478</v>
-      </c>
-      <c r="B14" s="73" t="s">
-        <v>480</v>
-      </c>
-      <c r="C14" s="73" t="s">
-        <v>479</v>
       </c>
       <c r="D14" s="9"/>
     </row>
@@ -34532,136 +35859,136 @@
       </c>
       <c r="B16" s="48"/>
       <c r="C16" s="48"/>
-      <c r="D16" s="77" t="s">
+      <c r="D16" s="76" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="17" spans="1:4" s="52" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="91" t="s">
-        <v>678</v>
+      <c r="A17" s="90" t="s">
+        <v>677</v>
       </c>
       <c r="B17" s="48"/>
       <c r="C17" s="48"/>
-      <c r="D17" s="77"/>
+      <c r="D17" s="76"/>
     </row>
     <row r="18" spans="1:4" s="52" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A18" s="91" t="s">
-        <v>678</v>
+      <c r="A18" s="90" t="s">
+        <v>677</v>
       </c>
       <c r="B18" s="48"/>
       <c r="C18" s="73" t="s">
-        <v>679</v>
-      </c>
-      <c r="D18" s="77"/>
+        <v>678</v>
+      </c>
+      <c r="D18" s="76"/>
     </row>
     <row r="19" spans="1:4" s="52" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="91" t="s">
-        <v>678</v>
+      <c r="A19" s="90" t="s">
+        <v>677</v>
       </c>
       <c r="B19" s="48"/>
       <c r="C19" s="48"/>
-      <c r="D19" s="77"/>
+      <c r="D19" s="76"/>
     </row>
     <row r="20" spans="1:4" s="52" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="91" t="s">
-        <v>678</v>
+      <c r="A20" s="90" t="s">
+        <v>677</v>
       </c>
       <c r="B20" s="48"/>
       <c r="C20" s="48"/>
-      <c r="D20" s="77"/>
+      <c r="D20" s="76"/>
     </row>
     <row r="21" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="A21" s="73" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B21" s="73" t="s">
+        <v>481</v>
+      </c>
+      <c r="C21" s="73" t="s">
         <v>482</v>
-      </c>
-      <c r="C21" s="73" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A22" s="73" t="s">
+        <v>484</v>
+      </c>
+      <c r="B22" s="73" t="s">
         <v>485</v>
       </c>
-      <c r="B22" s="73" t="s">
-        <v>486</v>
-      </c>
       <c r="C22" s="73" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="76" t="s">
+      <c r="A23" s="75" t="s">
         <v>403</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
       <c r="B24" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>487</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="D24" s="2" t="s">
         <v>488</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>489</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A25" s="73" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B25" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="D25" s="73" t="s">
         <v>490</v>
-      </c>
-      <c r="D25" s="73" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="59" t="s">
         <v>351</v>
       </c>
-      <c r="D26" s="77" t="s">
+      <c r="D26" s="76" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="D27" s="73" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28" s="76" t="s">
-        <v>499</v>
+      <c r="A28" s="75" t="s">
+        <v>498</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A29" s="73" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C29" s="73" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="D29" s="73" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A30" s="76" t="s">
-        <v>500</v>
+      <c r="A30" s="75" t="s">
+        <v>499</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="158.4" x14ac:dyDescent="0.3">
       <c r="B31" s="73" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C31" s="73" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
   </sheetData>
@@ -34683,7 +36010,7 @@
     <tabColor theme="8"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:V57"/>
+  <dimension ref="A2:V58"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="36" style="1" customWidth="1"/>
@@ -34780,60 +36107,26 @@
       </c>
       <c r="D6" s="1"/>
     </row>
-    <row r="7" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="44" t="s">
-        <v>217</v>
-      </c>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
-      <c r="M7" s="1"/>
-      <c r="N7" s="1"/>
-      <c r="P7" s="2"/>
-      <c r="Q7" s="2"/>
-      <c r="R7" s="2"/>
-      <c r="S7" s="1"/>
-      <c r="T7" s="8"/>
-      <c r="U7" s="2"/>
-      <c r="V7" s="1"/>
-    </row>
-    <row r="8" spans="1:22" s="7" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A8" s="9"/>
-      <c r="B8" s="42" t="s">
-        <v>218</v>
-      </c>
-      <c r="C8" s="67" t="s">
-        <v>220</v>
-      </c>
-      <c r="D8" s="9"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
-      <c r="N8" s="1"/>
-      <c r="P8" s="2"/>
-      <c r="Q8" s="2"/>
-      <c r="R8" s="2"/>
-      <c r="S8" s="1"/>
-      <c r="T8" s="8"/>
-      <c r="U8" s="2"/>
-      <c r="V8" s="1"/>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A7" s="92" t="s">
+        <v>772</v>
+      </c>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A8" s="91"/>
+      <c r="C8" s="91" t="s">
+        <v>771</v>
+      </c>
+      <c r="D8" s="1"/>
     </row>
     <row r="9" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="44" t="s">
-        <v>732</v>
-      </c>
-      <c r="B9" s="42"/>
-      <c r="C9" s="67"/>
+        <v>217</v>
+      </c>
+      <c r="B9" s="9"/>
+      <c r="C9" s="9"/>
       <c r="D9" s="9"/>
       <c r="F9" s="1"/>
       <c r="G9" s="2"/>
@@ -34851,15 +36144,13 @@
       <c r="U9" s="2"/>
       <c r="V9" s="1"/>
     </row>
-    <row r="10" spans="1:22" s="7" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="73" t="s">
-        <v>735</v>
-      </c>
-      <c r="B10" s="73" t="s">
-        <v>734</v>
-      </c>
-      <c r="C10" s="73" t="s">
-        <v>733</v>
+    <row r="10" spans="1:22" s="7" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A10" s="9"/>
+      <c r="B10" s="42" t="s">
+        <v>218</v>
+      </c>
+      <c r="C10" s="67" t="s">
+        <v>220</v>
       </c>
       <c r="D10" s="9"/>
       <c r="F10" s="1"/>
@@ -34878,14 +36169,12 @@
       <c r="U10" s="2"/>
       <c r="V10" s="1"/>
     </row>
-    <row r="11" spans="1:22" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A11" s="73" t="s">
-        <v>736</v>
-      </c>
-      <c r="B11" s="73"/>
-      <c r="C11" s="73" t="s">
-        <v>737</v>
-      </c>
+    <row r="11" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="44" t="s">
+        <v>729</v>
+      </c>
+      <c r="B11" s="42"/>
+      <c r="C11" s="67"/>
       <c r="D11" s="9"/>
       <c r="F11" s="1"/>
       <c r="G11" s="2"/>
@@ -34903,12 +36192,16 @@
       <c r="U11" s="2"/>
       <c r="V11" s="1"/>
     </row>
-    <row r="12" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="44" t="s">
-        <v>219</v>
-      </c>
-      <c r="B12" s="9"/>
-      <c r="C12" s="45"/>
+    <row r="12" spans="1:22" s="7" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="73" t="s">
+        <v>732</v>
+      </c>
+      <c r="B12" s="73" t="s">
+        <v>731</v>
+      </c>
+      <c r="C12" s="73" t="s">
+        <v>730</v>
+      </c>
       <c r="D12" s="9"/>
       <c r="F12" s="1"/>
       <c r="G12" s="2"/>
@@ -34926,13 +36219,13 @@
       <c r="U12" s="2"/>
       <c r="V12" s="1"/>
     </row>
-    <row r="13" spans="1:22" s="7" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A13" s="9"/>
-      <c r="B13" s="42" t="s">
-        <v>218</v>
-      </c>
-      <c r="C13" s="42" t="s">
-        <v>221</v>
+    <row r="13" spans="1:22" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A13" s="73" t="s">
+        <v>733</v>
+      </c>
+      <c r="B13" s="73"/>
+      <c r="C13" s="73" t="s">
+        <v>734</v>
       </c>
       <c r="D13" s="9"/>
       <c r="F13" s="1"/>
@@ -34952,11 +36245,11 @@
       <c r="V13" s="1"/>
     </row>
     <row r="14" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="47" t="s">
-        <v>227</v>
+      <c r="A14" s="44" t="s">
+        <v>219</v>
       </c>
       <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
+      <c r="C14" s="45"/>
       <c r="D14" s="9"/>
       <c r="F14" s="1"/>
       <c r="G14" s="2"/>
@@ -34974,13 +36267,13 @@
       <c r="U14" s="2"/>
       <c r="V14" s="1"/>
     </row>
-    <row r="15" spans="1:22" s="7" customFormat="1" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:22" s="7" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A15" s="9"/>
-      <c r="B15" s="46" t="s">
-        <v>229</v>
-      </c>
-      <c r="C15" s="46" t="s">
-        <v>228</v>
+      <c r="B15" s="42" t="s">
+        <v>218</v>
+      </c>
+      <c r="C15" s="42" t="s">
+        <v>221</v>
       </c>
       <c r="D15" s="9"/>
       <c r="F15" s="1"/>
@@ -34999,14 +36292,12 @@
       <c r="U15" s="2"/>
       <c r="V15" s="1"/>
     </row>
-    <row r="16" spans="1:22" s="7" customFormat="1" ht="216" x14ac:dyDescent="0.3">
-      <c r="A16" s="9"/>
-      <c r="B16" s="46" t="s">
-        <v>231</v>
-      </c>
-      <c r="C16" s="46" t="s">
-        <v>230</v>
-      </c>
+    <row r="16" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="47" t="s">
+        <v>227</v>
+      </c>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
       <c r="D16" s="9"/>
       <c r="F16" s="1"/>
       <c r="G16" s="2"/>
@@ -35024,15 +36315,15 @@
       <c r="U16" s="2"/>
       <c r="V16" s="1"/>
     </row>
-    <row r="17" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="74" t="s">
-        <v>527</v>
-      </c>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="77" t="s">
-        <v>109</v>
-      </c>
+    <row r="17" spans="1:22" s="7" customFormat="1" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A17" s="9"/>
+      <c r="B17" s="46" t="s">
+        <v>229</v>
+      </c>
+      <c r="C17" s="46" t="s">
+        <v>228</v>
+      </c>
+      <c r="D17" s="9"/>
       <c r="F17" s="1"/>
       <c r="G17" s="2"/>
       <c r="H17" s="1"/>
@@ -35049,15 +36340,15 @@
       <c r="U17" s="2"/>
       <c r="V17" s="1"/>
     </row>
-    <row r="18" spans="1:22" s="7" customFormat="1" ht="259.2" x14ac:dyDescent="0.3">
-      <c r="A18" s="80"/>
-      <c r="B18" s="81" t="s">
-        <v>510</v>
-      </c>
-      <c r="C18" s="81" t="s">
-        <v>526</v>
-      </c>
-      <c r="D18" s="80"/>
+    <row r="18" spans="1:22" s="7" customFormat="1" ht="216" x14ac:dyDescent="0.3">
+      <c r="A18" s="9"/>
+      <c r="B18" s="46" t="s">
+        <v>231</v>
+      </c>
+      <c r="C18" s="46" t="s">
+        <v>230</v>
+      </c>
+      <c r="D18" s="9"/>
       <c r="F18" s="1"/>
       <c r="G18" s="2"/>
       <c r="H18" s="1"/>
@@ -35075,12 +36366,12 @@
       <c r="V18" s="1"/>
     </row>
     <row r="19" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="59" t="s">
-        <v>528</v>
+      <c r="A19" s="74" t="s">
+        <v>526</v>
       </c>
       <c r="B19" s="9"/>
       <c r="C19" s="9"/>
-      <c r="D19" s="77" t="s">
+      <c r="D19" s="76" t="s">
         <v>109</v>
       </c>
       <c r="F19" s="1"/>
@@ -35099,13 +36390,15 @@
       <c r="U19" s="2"/>
       <c r="V19" s="1"/>
     </row>
-    <row r="20" spans="1:22" s="7" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A20" s="9"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="73" t="s">
-        <v>529</v>
-      </c>
-      <c r="D20" s="9"/>
+    <row r="20" spans="1:22" s="7" customFormat="1" ht="259.2" x14ac:dyDescent="0.3">
+      <c r="A20" s="79"/>
+      <c r="B20" s="80" t="s">
+        <v>509</v>
+      </c>
+      <c r="C20" s="80" t="s">
+        <v>525</v>
+      </c>
+      <c r="D20" s="79"/>
       <c r="F20" s="1"/>
       <c r="G20" s="2"/>
       <c r="H20" s="1"/>
@@ -35124,11 +36417,11 @@
     </row>
     <row r="21" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A21" s="59" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="B21" s="9"/>
       <c r="C21" s="9"/>
-      <c r="D21" s="77" t="s">
+      <c r="D21" s="76" t="s">
         <v>109</v>
       </c>
       <c r="F21" s="1"/>
@@ -35147,115 +36440,235 @@
       <c r="U21" s="2"/>
       <c r="V21" s="1"/>
     </row>
-    <row r="22" spans="1:22" s="2" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="B22" s="73" t="s">
+    <row r="22" spans="1:22" s="7" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A22" s="9"/>
+      <c r="B22" s="9"/>
+      <c r="C22" s="73" t="s">
+        <v>528</v>
+      </c>
+      <c r="D22" s="9"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+      <c r="K22" s="1"/>
+      <c r="L22" s="1"/>
+      <c r="M22" s="1"/>
+      <c r="N22" s="1"/>
+      <c r="P22" s="2"/>
+      <c r="Q22" s="2"/>
+      <c r="R22" s="2"/>
+      <c r="S22" s="1"/>
+      <c r="T22" s="8"/>
+      <c r="U22" s="2"/>
+      <c r="V22" s="1"/>
+    </row>
+    <row r="23" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="59" t="s">
+        <v>529</v>
+      </c>
+      <c r="B23" s="9"/>
+      <c r="C23" s="9"/>
+      <c r="D23" s="76" t="s">
+        <v>109</v>
+      </c>
+      <c r="F23" s="1"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+      <c r="K23" s="1"/>
+      <c r="L23" s="1"/>
+      <c r="M23" s="1"/>
+      <c r="N23" s="1"/>
+      <c r="P23" s="2"/>
+      <c r="Q23" s="2"/>
+      <c r="R23" s="2"/>
+      <c r="S23" s="1"/>
+      <c r="T23" s="8"/>
+      <c r="U23" s="2"/>
+      <c r="V23" s="1"/>
+    </row>
+    <row r="24" spans="1:22" s="2" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="B24" s="73" t="s">
+        <v>531</v>
+      </c>
+      <c r="C24" s="73" t="s">
+        <v>530</v>
+      </c>
+      <c r="E24" s="7"/>
+    </row>
+    <row r="25" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="74" t="s">
+        <v>538</v>
+      </c>
+      <c r="D25" s="76" t="s">
+        <v>109</v>
+      </c>
+      <c r="E25" s="7"/>
+    </row>
+    <row r="26" spans="1:22" s="2" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="B26" s="73" t="s">
+        <v>533</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>532</v>
       </c>
-      <c r="C22" s="73" t="s">
-        <v>531</v>
-      </c>
-      <c r="E22" s="7"/>
-    </row>
-    <row r="23" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="74" t="s">
+      <c r="E26" s="7"/>
+    </row>
+    <row r="27" spans="1:22" s="2" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="B27" s="73" t="s">
         <v>539</v>
       </c>
-      <c r="D23" s="77" t="s">
+      <c r="C27" s="73" t="s">
+        <v>535</v>
+      </c>
+      <c r="E27" s="7"/>
+    </row>
+    <row r="28" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="92" t="s">
+        <v>759</v>
+      </c>
+      <c r="D28" s="26" t="s">
         <v>109</v>
       </c>
-      <c r="E23" s="7"/>
-    </row>
-    <row r="24" spans="1:22" s="2" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A24" s="2" t="s">
-        <v>537</v>
-      </c>
-      <c r="B24" s="73" t="s">
-        <v>534</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>533</v>
-      </c>
-      <c r="E24" s="7"/>
-    </row>
-    <row r="25" spans="1:22" s="2" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A25" s="2" t="s">
-        <v>538</v>
-      </c>
-      <c r="B25" s="73" t="s">
-        <v>540</v>
-      </c>
-      <c r="C25" s="73" t="s">
-        <v>536</v>
-      </c>
-      <c r="E25" s="7"/>
-    </row>
-    <row r="26" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="E26" s="7"/>
-    </row>
-    <row r="27" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="E27" s="7"/>
-    </row>
-    <row r="28" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="E28" s="7"/>
     </row>
-    <row r="29" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:22" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B29" s="91" t="s">
+        <v>777</v>
+      </c>
       <c r="E29" s="7"/>
     </row>
     <row r="30" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="54" t="s">
+        <v>575</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>778</v>
+      </c>
       <c r="E30" s="7"/>
     </row>
-    <row r="31" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:22" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B31" s="91" t="s">
+        <v>775</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>763</v>
+      </c>
       <c r="E31" s="7"/>
     </row>
-    <row r="32" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:22" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B32" s="91" t="s">
+        <v>795</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>794</v>
+      </c>
       <c r="E32" s="7"/>
     </row>
-    <row r="33" spans="5:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="54" t="s">
+        <v>774</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>779</v>
+      </c>
       <c r="E33" s="7"/>
     </row>
-    <row r="34" spans="5:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B34" s="2" t="s">
+        <v>718</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>776</v>
+      </c>
       <c r="E34" s="7"/>
     </row>
-    <row r="35" spans="5:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="54" t="s">
+        <v>669</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>780</v>
+      </c>
       <c r="E35" s="7"/>
     </row>
-    <row r="36" spans="5:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="C36" s="2" t="s">
+        <v>776</v>
+      </c>
       <c r="E36" s="7"/>
     </row>
-    <row r="37" spans="5:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="54" t="s">
+        <v>526</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>781</v>
+      </c>
+      <c r="D37" s="76" t="s">
+        <v>109</v>
+      </c>
       <c r="E37" s="7"/>
     </row>
-    <row r="38" spans="5:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B38" s="2" t="s">
+        <v>793</v>
+      </c>
       <c r="E38" s="7"/>
     </row>
-    <row r="39" spans="5:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5" s="2" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A39" s="95" t="s">
+        <v>773</v>
+      </c>
+      <c r="B39" s="91" t="s">
+        <v>767</v>
+      </c>
+      <c r="C39" s="91" t="s">
+        <v>766</v>
+      </c>
       <c r="E39" s="7"/>
     </row>
-    <row r="40" spans="5:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5" s="2" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A40" s="95" t="s">
+        <v>768</v>
+      </c>
+      <c r="B40" s="91" t="s">
+        <v>770</v>
+      </c>
+      <c r="C40" s="91" t="s">
+        <v>769</v>
+      </c>
       <c r="E40" s="7"/>
     </row>
-    <row r="41" spans="5:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="E41" s="7"/>
     </row>
-    <row r="42" spans="5:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="E42" s="7"/>
     </row>
-    <row r="43" spans="5:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="E43" s="7"/>
     </row>
-    <row r="44" spans="5:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="E44" s="7"/>
     </row>
-    <row r="45" spans="5:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="E45" s="7"/>
     </row>
-    <row r="46" spans="5:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="E46" s="7"/>
     </row>
-    <row r="47" spans="5:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="E47" s="7"/>
     </row>
-    <row r="48" spans="5:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="E48" s="7"/>
     </row>
     <row r="49" spans="5:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -35285,15 +36698,20 @@
     <row r="57" spans="5:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="E57" s="7"/>
     </row>
+    <row r="58" spans="5:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="E58" s="7"/>
+    </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="D17" r:id="rId1" xr:uid="{73707BC3-C5BC-4A85-98A2-A79995860E58}"/>
-    <hyperlink ref="D19" r:id="rId2" location=":~:text=%D0%B0%D1%80%D0%B8%D1%84%D0%BC%D0%B5%D1%82%D0%B8%D1%87%D0%B5%D1%81%D0%BA%D0%BE%D0%B9%20%D0%BE%D0%BF%D0%B5%D1%80%D0%B0%D1%86%D0%B8%D0%B8." xr:uid="{282AB0FB-0B5F-4555-8317-4AB4310A11F3}"/>
-    <hyperlink ref="D21" r:id="rId3" location=":~:text=DISTINCT" xr:uid="{ECCA5E34-107E-4E9D-879B-B621E0E319B5}"/>
-    <hyperlink ref="D23" r:id="rId4" location=":~:text=%D0%92%D1%8B%D0%B1%D0%BE%D1%80%D0%BA%D0%B0%20%D1%81%20%D0%B4%D0%BE%D0%B1%D0%B0%D0%B2%D0%BB%D0%B5%D0%BD%D0%B8%D0%B5%D0%BC" xr:uid="{EB049B6F-7500-4990-A854-FB63C016D00B}"/>
+    <hyperlink ref="D19" r:id="rId1" xr:uid="{73707BC3-C5BC-4A85-98A2-A79995860E58}"/>
+    <hyperlink ref="D21" r:id="rId2" location=":~:text=%D0%B0%D1%80%D0%B8%D1%84%D0%BC%D0%B5%D1%82%D0%B8%D1%87%D0%B5%D1%81%D0%BA%D0%BE%D0%B9%20%D0%BE%D0%BF%D0%B5%D1%80%D0%B0%D1%86%D0%B8%D0%B8." xr:uid="{282AB0FB-0B5F-4555-8317-4AB4310A11F3}"/>
+    <hyperlink ref="D23" r:id="rId3" location=":~:text=DISTINCT" xr:uid="{ECCA5E34-107E-4E9D-879B-B621E0E319B5}"/>
+    <hyperlink ref="D25" r:id="rId4" location=":~:text=%D0%92%D1%8B%D0%B1%D0%BE%D1%80%D0%BA%D0%B0%20%D1%81%20%D0%B4%D0%BE%D0%B1%D0%B0%D0%B2%D0%BB%D0%B5%D0%BD%D0%B8%D0%B5%D0%BC" xr:uid="{EB049B6F-7500-4990-A854-FB63C016D00B}"/>
+    <hyperlink ref="D28" r:id="rId5" xr:uid="{C2A3DD48-3B38-42BA-91AA-CAE1ED71BF16}"/>
+    <hyperlink ref="D37" r:id="rId6" location=":~:text=%D0%9F%D0%BE%D0%B4%D0%B7%D0%B0%D0%BF%D1%80%D0%BE%D1%81%20%D0%BA%D0%B0%D0%BA%20%D1%81%D0%BF%D0%B5%D1%86%D0%B8%D1%84%D0%B8%D0%BA%D0%B0%D1%86%D0%B8%D1%8F%20%D1%81%D1%82%D0%BE%D0%BB%D0%B1%D1%86%D0%B0" xr:uid="{005E3454-361D-4705-B998-E7BB1C4E13E8}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId5"/>
-  <drawing r:id="rId6"/>
+  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId7"/>
+  <drawing r:id="rId8"/>
 </worksheet>
 </file>
--- a/4 четверть_MSSQL.xlsx
+++ b/4 четверть_MSSQL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlexServHW\Desktop\GB_Developer_Workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{611A6139-7A5F-491B-82F1-BACCF2201498}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82755263-BA51-46D3-BF10-4B908D9379EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6885" yWindow="-18825" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7755" yWindow="-17955" windowWidth="17280" windowHeight="8880" firstSheet="21" activeTab="29" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Изучить" sheetId="21" r:id="rId1"/>
@@ -33,7 +33,7 @@
     <sheet name="GROUP HAVING" sheetId="36" r:id="rId18"/>
     <sheet name="JOIN" sheetId="37" r:id="rId19"/>
     <sheet name="UNION, EXCEPT" sheetId="38" r:id="rId20"/>
-    <sheet name="String" sheetId="39" r:id="rId21"/>
+    <sheet name="NAVCH" sheetId="39" r:id="rId21"/>
     <sheet name="INT" sheetId="40" r:id="rId22"/>
     <sheet name="DATE" sheetId="41" r:id="rId23"/>
     <sheet name="DECLARE" sheetId="43" r:id="rId24"/>
@@ -42,12 +42,13 @@
     <sheet name="TRY" sheetId="45" r:id="rId27"/>
     <sheet name="VIEW" sheetId="46" r:id="rId28"/>
     <sheet name="TABLE vars, CTE" sheetId="47" r:id="rId29"/>
-    <sheet name="Procedures" sheetId="48" r:id="rId30"/>
-    <sheet name="template" sheetId="14" r:id="rId31"/>
-    <sheet name="Каскадное удаление" sheetId="16" r:id="rId32"/>
-    <sheet name="Транзакции" sheetId="17" r:id="rId33"/>
-    <sheet name="bc Массивы" sheetId="18" r:id="rId34"/>
-    <sheet name="bc JSON" sheetId="22" r:id="rId35"/>
+    <sheet name="Trigger" sheetId="49" r:id="rId30"/>
+    <sheet name="Procedures" sheetId="48" r:id="rId31"/>
+    <sheet name="template" sheetId="14" r:id="rId32"/>
+    <sheet name="Каскадное удаление" sheetId="16" r:id="rId33"/>
+    <sheet name="Транзакции" sheetId="17" r:id="rId34"/>
+    <sheet name="bc Массивы" sheetId="18" r:id="rId35"/>
+    <sheet name="bc JSON" sheetId="22" r:id="rId36"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -62,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1581" uniqueCount="1366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1626" uniqueCount="1398">
   <si>
     <t>Урок 1 часть 1</t>
   </si>
@@ -29687,23 +29688,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">DECLARE </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>@name NVARCHAR(20)</t>
-    </r>
-  </si>
-  <si>
     <t>DECLARE</t>
   </si>
   <si>
@@ -31992,24 +31976,274 @@
       <rPr>
         <b/>
         <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>От себя как можно использовать!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Аналог VIEW, который хранится в оперативной памяти на время выполнения одного пакета</t>
+    </r>
+  </si>
+  <si>
+    <t>Аналог временных таблиц</t>
+  </si>
+  <si>
+    <t>Основы</t>
+  </si>
+  <si>
+    <t>Процедуры</t>
+  </si>
+  <si>
+    <t>CRUD</t>
+  </si>
+  <si>
+    <t>Создание процедуры (с параметрами)</t>
+  </si>
+  <si>
+    <t>Создание процедуры (без параметров)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Преимущество!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> И еще один важный аспект - производительность. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Хранимые процедуры обычно выполняются быстрее</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, чем обычные </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
         <color rgb="FFC00000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="204"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">Правило! </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">В отличие от временных таблиц табличные выполнения хранятся в оперативной памяти и существуют </t>
+      <t>SQL-инструкции</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. Все потому что код процедур компилируется один раз при первом ее запуске, а затем сохраняется в скомпилированной форме.
+Для отделения тела процедуры от остальной части скрипта код процедуры нередко помещается в блок BEGIN...END</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">EXEC </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>getSalesPersonData</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>@BusinessEntityID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = 276</t>
+    </r>
+  </si>
+  <si>
+    <t>Удаление процедуры</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">DROP PROCEDURE </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>getSalesPersonData</t>
+    </r>
+  </si>
+  <si>
+    <t>`https://metanit.com/sql/sqlserver/11.2.php</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Дополнительно!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Перед SELECT/INSERT/UPDATE/DELETE можно указывать </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SET NOCOUNT ON</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, чтобы не происходил дополнительный подсчет обработанных строк</t>
+    </r>
+  </si>
+  <si>
+    <t>TRANSACTIONS</t>
+  </si>
+  <si>
+    <t>@TRANCOUNT</t>
+  </si>
+  <si>
+    <t>OVER - из материалов Geekbrains</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">         SET @flag = 1;
+      IF @@TRANCOUNT &gt; 0
+           BEGIN COMMIT TRANSACTION;
+      END
+   END TRY
+</t>
     </r>
     <r>
       <rPr>
@@ -32021,21 +32255,658 @@
         <charset val="204"/>
         <scheme val="minor"/>
       </rPr>
-      <t>только во время первого выполнения запроса</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>, который представляет это табличное выражение.</t>
-    </r>
-  </si>
-  <si>
+      <t xml:space="preserve">   BEGIN CATCH
+        IF @@TRANCOUNT &gt; 0
+              BEGIN ROLLBACK TRANSACTION;
+        END
+        SET @flag = 0;
+   END CATCH</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+END</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">SELECT *
+FROM </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Sales.SalesPersonPluralsightDemo</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">/*Execute procedure for UPDATE*/
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">EXECUTE </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>updateSalesPersonData</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>@BusinessEntityID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">= 300
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, @SalesQuota</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = 300000
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, @Bonus</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = 2000
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, @CommissionPct</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = 0.02</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">/*Execute procedure for DELETE*/
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">EXECUTE </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>deleteSalesPersonData</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>@BusinessEntityID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = 300</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">SELECT *
+FROM </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Sales.SalesPersonPluralsightDemo</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">/*Execute procedure for INSERT*/
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>DECLARE</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>@flag bit</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>EXECUTE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>insertSalesPersonData</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>@flag output</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, @BusinessEntityID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = 300
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, @TerritoryID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = 6
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, @SalesQuota</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = 200000
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, @Bonus</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = 1000
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, @CommissionPct</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = 0.01
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, @SalesYTD</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = 254000
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, @SalesLastYear</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = 0
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">IF </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>@flag = 1</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  PRINT 'Successfully inserted data'
+ELSE
+  PRINT 'An error occurred'</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>SELECT *
+FROM</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Sales.SalesPersonPluralsightDemo</t>
+    </r>
+  </si>
+  <si>
+    <t>Call</t>
+  </si>
+  <si>
+    <t>Get updated data</t>
+  </si>
+  <si>
+    <t>Function</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">INSERT INTO </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Sales.SalesPersonPluralsightDemo</t>
+    </r>
     <r>
       <rPr>
         <b/>
@@ -32046,7 +32917,1897 @@
         <charset val="204"/>
         <scheme val="minor"/>
       </rPr>
-      <t>WITH OrdersInfo AS</t>
+      <t xml:space="preserve">
+(
+    BusinessEntityID, TerritoryID,
+    SalesQuota, Bonus, CommissionPct, SalesYTD,
+    SalesLastYear, rowguid, ModifiedDate
+)
+VALUES
+(   
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">    @BusinessEntityID , @TerritoryID
+    , @SalesQuota , @Bonus , @CommissionPct , @SalesYTD
+    , @SalesLastYear </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, NEWID() , GETDATE()
+)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CREATE OR ALTER PROCEDURE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>insertSalesPersonData</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>@</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>flag</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> bit </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>OUTPUT</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> --return 1 for success, 0 for failure
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>,  @BusinessEntityID</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> int
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, @TerritoryID</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> int
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, @SalesQuota</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> money
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, @Bonus</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> money
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, @CommissionPct</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> money
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, @SalesYTD</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> money
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, @SalesLastYear</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> money
+AS
+BEGIN
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">    BEGIN TRANSACTION
+         BEGIN TRY</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CREATE OR ALTER PROCEDURE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">getSalesPersonData </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>AS
+BEGIN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SELECT sp.BusinessEntityID
+  , sp.TerritoryID
+  , sp.SalesQuota
+  , sp.CommissionPct
+  , sp.SalesYTD
+  , sp.SalesLastYear
+  , sp.Bonus
+   FROM Sales.SalesPerson AS sp
+   INNER JOIN Sales.SalesTerritory AS st ON st.TerritoryID = sp.TerritoryID
+   WHERE sp.BusinessEntityID = 276</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>END</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CREATE OR ALTER PROCEDURE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>getSalesPersonData</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>@BusinessEntityID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>int</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>AS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>BEGIN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SELECT sp.BusinessEntityID
+  , sp.TerritoryID
+  , sp.SalesQuota
+  , sp.CommissionPct
+  , sp.SalesYTD
+  , sp.SalesLastYear
+  , sp.Bonus
+   FROM Sales.SalesPerson AS sp
+   INNER JOIN Sales.SalesTerritory AS st ON st.TerritoryID = sp.TerritoryID
+   WHERE sp.BusinessEntityID =</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>@BusinessEntityID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>END</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CREATE OR ALTER PROCEDURE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>updateSalesPersonData</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>@BusinessEntityID</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>int</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>@SalesQuota</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>money</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>@Bonus</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>money</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>@CommissionPct</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>money</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">AS
+BEGIN
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>UPDATE</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Sales.SalesPersonPluralsightDemo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">SET SalesQuota = </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>@SalesQuota</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, Bonus = </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>@Bonus</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, CommissionPct =</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>@CommissionPct</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">WHERE BusinessEntityID = </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>@BusinessEntityID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>END</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">CREATE OR ALTER PROCEDURE </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>deleteSalesPersonData</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>@BusinessEntityID</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> int</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>AS
+BEGIN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">DELETE FROM Sales.SalesPersonPluralsightDemo
+WHERE BusinessEntityID = </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>@BusinessEntityID</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>END</t>
+    </r>
+  </si>
+  <si>
+    <t>Выполнение процедуры (с параметрами)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">DECLARE @prodName NVARCHAR(20), @company NVARCHAR(20);
+DECLARE @prodCount INT, @price MONEY
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">SET @prodName = 'Galaxy C7'
+SET @company = 'Samsung'
+SET @price = 22000
+SET @prodCount = 5
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 
+EXEC </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>AddProduct</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>@prodName, @company, @prodCount, @price</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">EXEC </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>AddProduct</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>'Galaxy C7', 'Samsung', 5, 22000</t>
+    </r>
+  </si>
+  <si>
+    <t>Вариант 1
+Передать непосредственно значения</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вариант 2
+</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Вариант 3
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Правило!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (1) В этом вариант типы объявленных переменных должны совпадать с типами ожидаемыми в процедуре. (2) При этом значения передаются параметрам процедуры по позиции.</t>
+    </r>
+  </si>
+  <si>
+    <t>Вариант 4</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">DECLARE </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>@prodName NVARCHAR(20)</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>@company NVARCHAR(20)</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">;
+SET </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>@prodName</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = 'Honor 9'
+SET </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>@company</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = 'Huawei'
+EXEC </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>AddProduct</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>@name</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> =</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> @prodName</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, 
+               </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> @manufacturer</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>@company</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">,
+                </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>@count</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, 
+                </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>@price</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>18000</t>
+    </r>
+  </si>
+  <si>
+    <t>DECLARE @ChannelLike nvarchar(100) = NULL;
+IF (@DeliveryChannel IS NOT NULL AND @DeliveryChannel &lt;&gt; '')
+BEGIN
+    SET @ChannelLike = '%"deliveryChannel":"' + @DeliveryChannel + '"%';
+END
+SELECT (SELECT [Idmail]
+     ,[mailText]
+     ,[mailName]
+     ,[mailDate]
+     ,[IsSend]
+ FROM [LK_DATA].[dbo].[html_mail] WITH (NOLOCK)
+ WHERE [mailText] LIKE '%&lt;!--mailing-settings-v2--%'
+    AND (
+        @ChannelLike IS NULL
+        OR [mailText] LIKE @ChannelLike
+        OR (@DeliveryChannel = 'mailing' AND [mailText] NOT LIKE '%"deliveryChannel":%')
+    )
+ ORDER BY [IsSend], [Idmail] DESC
+OFFSET @start ROWS FETCH NEXT @end ROWS ONLY
+FOR JSON PATH, INCLUDE_NULL_VALUES)
+AS [Data]
+, (SELECT COUNT([Idmail]) FROM [LK_DATA].[dbo].[html_mail] WITH (NOLOCK)
+   WHERE [mailText] LIKE '%&lt;!--mailing-settings-v2--%'
+      AND (
+          @ChannelLike IS NULL
+          OR [mailText] LIKE @ChannelLike
+          OR (@DeliveryChannel = 'mailing' AND [mailText] NOT LIKE '%"deliveryChannel":%')
+      ))
+AS [Count]
+FOR JSON PATH</t>
+  </si>
+  <si>
+    <t>FOR JSON PATH</t>
+  </si>
+  <si>
+    <t>STRING_ESCAPE(@text, 'json')</t>
+  </si>
+  <si>
+    <t>ISJSON(@groupId) = 1</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">DECLARE </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>@name NVARCHAR(20);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>;WITH OrdersInfo AS</t>
     </r>
     <r>
       <rPr>
@@ -32111,90 +34872,252 @@
       <rPr>
         <b/>
         <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>От себя как можно использовать!</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Аналог VIEW, который хранится в оперативной памяти на время выполнения одного пакета</t>
-    </r>
-  </si>
-  <si>
-    <t>Аналог временных таблиц</t>
-  </si>
-  <si>
-    <t>Основы</t>
-  </si>
-  <si>
-    <t>Процедуры</t>
-  </si>
-  <si>
-    <t>CRUD</t>
-  </si>
-  <si>
-    <t>/*See current data in the table Sales.SalesPerson*/
-SELECT *
-   FROM Sales.SalesPerson AS sp
-/*Insert data into a new table*/
-SELECT *
-INTO Sales.SalesPersonPluralsightDemo
-   FROM Sales.SalesPerson AS sp</t>
-  </si>
-  <si>
-    <t>/*Create procedure for INSERT*/</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">ALTER PROCEDURE insertSalesPersonData
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Правило! </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">В отличие от временных таблиц табличные выполнения хранятся в оперативной памяти и существуют </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>только во время первого выполнения запроса</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, который представляет это табличное выражение.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
 </t>
     </r>
     <r>
       <rPr>
         <b/>
         <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>@</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
         <color rgb="FFC00000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="204"/>
         <scheme val="minor"/>
       </rPr>
-      <t>flag</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> bit </t>
+      <t>Правило!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Всегда начинается с точки с запятой</t>
+    </r>
+  </si>
+  <si>
+    <t>SET @TextToSend = REPLACE(@TextToSend, N'&lt;br&gt;', CHAR(13) + CHAR(10));</t>
+  </si>
+  <si>
+    <t>DECLARE recipient_cursor CURSOR LOCAL FAST_FORWARD FOR
+SELECT user_id
+FROM @MaxRecipients;</t>
+  </si>
+  <si>
+    <t>DECLARE recipient_cursor CURSOR LOCAL FAST_FORWARD FOR
+SELECT user_id
+FROM @MaxRecipients;
+OPEN recipient_cursor;
+FETCH NEXT FROM recipient_cursor INTO @user_id;
+WHILE @@FETCH_STATUS = 0
+BEGIN
+    BEGIN TRY
+        EXEC [LK_DATA].[dbo].[max_send_text]
+            @chat_id = @user_id,
+            @text = @TextToSend,
+            @typemessage = 1,
+            @format = N'html';
+        INSERT INTO @Result (user_id, StatusCode, ResponseText, RequestBody)
+        VALUES (@user_id, 200, N'Sent via LK_DATA.dbo.max_send_text', @TextToSend);
+    END TRY
+    BEGIN CATCH
+        INSERT INTO @Result (user_id, StatusCode, ResponseText, RequestBody)
+        VALUES (@user_id, -1, ERROR_MESSAGE(), @TextToSend);
+    END CATCH;
+    FETCH NEXT FROM recipient_cursor INTO @user_id;
+END
+CLOSE recipient_cursor;
+DEALLOCATE recipient_cursor;</t>
+  </si>
+  <si>
+    <t>-&gt;</t>
+  </si>
+  <si>
+    <t>Возвращаемое значение</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">CREATE PROCEDURE </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CreateProduct</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>@name</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> NVARCHAR(20),
+    </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>@manufacturer</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> NVARCHAR(20),
+    </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>@count</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> INT,
+    </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>@price</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> MONEY,
+    </t>
     </r>
     <r>
       <rPr>
@@ -32206,20 +35129,811 @@
         <charset val="204"/>
         <scheme val="minor"/>
       </rPr>
+      <t>@id INT</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> OUTPUT
+AS
+    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>INSERT INTO Products(ProductName, Manufacturer, ProductCount, Price)
+    VALUES(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>@name, @manufacturer, @count, @price</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    SET </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>@id</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = @@IDENTITY</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>DECLARE</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>@minPrice</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>MONEY</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>@maxPrice</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>MONEY</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+EXEC </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>GetPriceStats</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>@minPrice</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> OUTPUT, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>@maxPrice</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> OUTPUT
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PRINT 'Минимальная цена ' + CONVERT(VARCHAR,</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>@minPrice</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PRINT 'Максимальная цена ' + CONVERT(VARCHAR,</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>@maxPrice</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">СREATE PROCEDURE </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>GetPriceStats</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>@minPrice MONEY</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> OUTPUT,
+    </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>@maxPrice MONEY</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> OUTPUT
+AS
+SELECT </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">@minPrice </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">= MIN(Price),  </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>@maxPrice</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = MAX(Price)
+FROM </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Products</t>
+    </r>
+  </si>
+  <si>
+    <t>Call and get</t>
+  </si>
+  <si>
+    <t>Только возвращаемые значения</t>
+  </si>
+  <si>
+    <t>Передаваемые и возвращаемые значения</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">DECLARE </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>@id</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> INT
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>EXEC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CreateProduct</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>'LG V30', 'LG', 3, 28000,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>@id</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>OUTPUT</t>
     </r>
     <r>
       <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> --return 1 for success, 0 for failure
-,  </t>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">PRINT </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>@id</t>
+    </r>
+  </si>
+  <si>
+    <t>Триггеры</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Пояснение! </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Триггеры представляют специальный тип хранимой процедуры, которая вызывается автоматически при выполнении определенного действия над таблицей или представлением, в частности, при добавлении, изменении или удалении данных, то есть при выполнении команд INSERT, UPDATE, DELETE.</t>
+    </r>
+  </si>
+  <si>
+    <t>Тип триггера</t>
+  </si>
+  <si>
+    <t>AFTER</t>
+  </si>
+  <si>
+    <t>INSTEAD OF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">выполняется вместо действия (то есть по сути действие - добавление, изменение или удаление - вообще не выполняется). 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">выполняется после выполнения действия. </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">CREATE VIEW </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>vw_ProductInfo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> AS
+SELECT Id, ProductName, Price, CategoryName
+FROM Products p
+JOIN Categories c ON p.CategoryId = c.Id;
+-- Создаем INSTEAD OF триггер для INSERT
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CREATE TRIGGER</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
     </r>
     <r>
       <rPr>
@@ -32231,438 +35945,78 @@
         <charset val="204"/>
         <scheme val="minor"/>
       </rPr>
-      <t>@BusinessEntityID</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> int
-, @</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>TerritoryID</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> int
-, @</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>SalesQuota</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> money
-, @</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Bonus</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> money
-, @</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>CommissionPct</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> money
-, @</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>SalesYTD</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> money
-, @</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>SalesLastYear</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> money
+      <t>trg_vw_ProductInfo_Insert</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+ON </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="5" tint="-0.499984740745262"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>vw_ProductInfo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
 </t>
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>AS
-BEGIN
-BEGIN TRANSACTION
-BEGIN TRY</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">/*Execute procedure for INSERT*/
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>DECLARE @flag bit</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-EXECUTE insertSalesPersonData 
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>@flag output</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-, @BusinessEntityID = 300
-, @TerritoryID = 6
-, @SalesQuota = 200000
-, @Bonus = 1000
-, @CommissionPct = 0.01
-, @SalesYTD = 254000
-, @SalesLastYear = 0
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>IF @flag = 1
-  PRINT 'Successfully inserted data'
-ELSE
-  PRINT 'An error occurred'</t>
-    </r>
-  </si>
-  <si>
-    <t>SET NOCOUNT ON
-INSERT INTO Sales.SalesPersonPluralsightDemo
-(
-    BusinessEntityID,
-    TerritoryID,
-    SalesQuota,
-    Bonus,
-    CommissionPct,
-    SalesYTD,
-    SalesLastYear,
-    rowguid,
-    ModifiedDate
-)
-VALUES
-(   
-    @BusinessEntityID
-    , @TerritoryID
-    , @SalesQuota
-    , @Bonus
-    , @CommissionPct
-    , @SalesYTD
-    , @SalesLastYear
-    , NEWID()
-    , GETDATE()
-    )</t>
-  </si>
-  <si>
-    <t>SELECT *
-FROM Sales.SalesPersonPluralsightDemo</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">SET @flag = 1;
-IF @@TRANCOUNT &gt; 0
-BEGIN COMMIT TRANSACTION;
-END
-END TRY
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>BEGIN CATCH
-IF @@TRANCOUNT &gt; 0
-BEGIN ROLLBACK TRANSACTION;
-END
-SET @flag = 0;
-END CATCH</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-END</t>
-    </r>
-  </si>
-  <si>
-    <t>/*Create procedure for UPDATE*/</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">CREATE PROCEDURE updateSalesPersonData
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">@BusinessEntityID int
-, @SalesQuota money
-, @Bonus money
-, @CommissionPct money
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">AS
-BEGIN
-SET NOCOUNT ON
-UPDATE Sales.SalesPersonPluralsightDemo
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">SET SalesQuota = @SalesQuota
-, Bonus = @Bonus
-, CommissionPct = @CommissionPct
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>WHERE BusinessEntityID = @BusinessEntityID
-END</t>
-    </r>
-  </si>
-  <si>
-    <t>/*Execute procedure for UPDATE*/
-EXECUTE updateSalesPersonData
-@BusinessEntityID = 300
-, @SalesQuota = 300000
-, @Bonus = 2000
-, @CommissionPct = 0.02
-SELECT *
-FROM Sales.SalesPersonPluralsightDemo</t>
-  </si>
-  <si>
-    <t>/*Create procedure for DELETE*/</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">CREATE PROCEDURE deleteSalesPersonData
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>@BusinessEntityID int</t>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>INSTEAD OF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>INSERT</t>
     </r>
     <r>
       <rPr>
@@ -32676,276 +36030,119 @@
       <t xml:space="preserve">
 AS
 BEGIN
-SET NOCOUNT ON
-DELETE FROM Sales.SalesPersonPluralsightDemo
-WHERE BusinessEntityID = @BusinessEntityID
-END</t>
-    </r>
-  </si>
-  <si>
-    <t>/*Execute procedure for DELETE*/
-EXECUTE deleteSalesPersonData
-@BusinessEntityID = 300
-SELECT *
-FROM Sales.SalesPersonPluralsightDemo</t>
-  </si>
-  <si>
-    <t>CREATE PROCEDURE to reduce the bonus by 10% for the worst performing BusinessEntityIDs within the Territory Group</t>
-  </si>
-  <si>
-    <t>/*Return all records*/</t>
-  </si>
-  <si>
-    <t>SELECT sp.BusinessEntityID
-		, sp.TerritoryID
-		, sp.SalesQuota
-		, sp.CommissionPct
-		, sp.SalesYTD
-		, sp.SalesLastYear
-		, sp.Bonus
-		, st.Name AS TerritoryName
-		, st.CountryRegionCode
-		, st.[Group]
-		, st.SalesYTD AS TerritorySalesYTD
-		, st.SalesLastYear AS TerritorySalesLastYear
-		, st.CostYTD AS TerritoryCostYTD
-		, st.CostLastYear AS TerritoryCostLastYear
-   FROM Sales.SalesPersonPluralsightDemo AS sp
-   INNER JOIN Sales.SalesTerritory AS st ON st.TerritoryID = sp.TerritoryID</t>
-  </si>
-  <si>
-    <t>/*Finding the BusinessEntityID with lowest SalesYTD within the Territory Group*/</t>
-  </si>
-  <si>
-    <t>SELECT sp.BusinessEntityID
-	, sp.Bonus
-	, sp.SalesYTD
-	, st.Name
-	, st.CountryRegionCode
-	, st.[Group]
-	, RANK () OVER(PARTITION BY st.[Group] ORDER BY sp.SalesYTD) AS rnk
-   FROM Sales.SalesPersonPluralsightDemo AS sp
-   INNER JOIN Sales.SalesTerritory AS st ON st.TerritoryID = sp.TerritoryID
-   --GROUP BY st.[Group]</t>
-  </si>
-  <si>
-    <t>PROCEDURE</t>
-  </si>
-  <si>
-    <t>CREATE PROCEDURE reduceBonus10
-@rnk int
-AS
-BEGIN
-SET NOCOUNT ON
-; WITH findBadPerformers AS (
-		SELECT sp.BusinessEntityID
-	, sp.Bonus
-	, sp.SalesYTD
-	, st.Name AS TerritoryName
-	, st.CountryRegionCode
-	, st.[Group] AS TerritoryGroup
-	, RANK () OVER(PARTITION BY st.[Group] ORDER BY sp.SalesYTD) AS rnk
-   FROM Sales.SalesPersonPluralsightDemo AS sp
-   INNER JOIN Sales.SalesTerritory AS st ON st.TerritoryID = sp.TerritoryID
-   )
-   UPDATE findBadPerformers
-   SET Bonus = Bonus * 0.9
-   WHERE rnk = @rnk
-   END</t>
-  </si>
-  <si>
-    <t>/*Exec stored procedure*/
-   EXECUTE reduceBonus10 @rnk = 1</t>
-  </si>
-  <si>
-    <t>Finding the BusinessEntityIDs that perform above average in North America</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   SELECT st.CountryRegionCode
-	, AVG(sp.SalesYTD) AS AvgTerritorySalesYTD
-   FROM Sales.SalesPersonPluralsightDemo AS sp
-   INNER JOIN Sales.SalesTerritory AS st ON st.TerritoryID = sp.TerritoryID
-   WHERE st.[Group] = 'North America'
-   GROUP BY st.CountryRegionCode</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   CREATE PROCEDURE increaseBonusPct
-   @pct money
-AS
-BEGIN
-SET NOCOUNT ON
-/*Create temporary table*/
-   CREATE TABLE #AvgNorthAmerica 
-   (CountryRegionCode VARCHAR(2)
-   , AvgTerritorySalesYTD MONEY)</t>
-  </si>
-  <si>
-    <t>/*Exec stored procedure*/
-   EXECUTE increaseBonusPct @pct = 0.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   /*Insert data into temp table*/
-   INSERT INTO #AvgNorthAmerica
-   SELECT st.CountryRegionCode
-	, AVG(sp.SalesYTD) AS AvgTerritorySalesYTD
-   FROM Sales.SalesPersonPluralsightDemo AS sp
-   INNER JOIN Sales.SalesTerritory AS st ON st.TerritoryID = sp.TerritoryID
-   WHERE st.[Group] = 'North America'
-   GROUP BY st.CountryRegionCode</t>
-  </si>
-  <si>
-    <t>;WITH finalDataset AS (
-SELECT sp.BusinessEntityID
-	, sp.Bonus
-	, sp.SalesYTD
-	, st.Name
-	, st.CountryRegionCode
-	, st.[Group]
-	, ana.AvgTerritorySalesYTD
-   FROM Sales.SalesPersonPluralsightDemo AS sp
-   INNER JOIN Sales.SalesTerritory AS st ON st.TerritoryID = sp.TerritoryID
-   INNER JOIN #AvgNorthAmerica AS ana ON ana.CountryRegionCode = st.CountryRegionCode
-   WHERE sp.SalesYTD &gt; ana.AvgTerritorySalesYTD
-   )
-UPDATE finalDataset
-SET Bonus = Bonus * (1+@pct)
-END</t>
-  </si>
-  <si>
-    <t>Create a new role for Sales Manager</t>
-  </si>
-  <si>
-    <t>/*See current data in the table Sales.SalesPerson*/</t>
-  </si>
-  <si>
-    <t>SELECT *
-   FROM Sales.SalesPerson AS sp</t>
-  </si>
-  <si>
-    <t>/*Insert data into a new table*/</t>
-  </si>
-  <si>
-    <t>SELECT *
-INTO Sales.SalesPersonPluralsightDemo
-   FROM Sales.SalesPerson AS sp</t>
-  </si>
-  <si>
-    <t>CREATE PROCEDURE Sales.insertSalesPersonData
- @BusinessEntityID int
-, @TerritoryID int
-, @SalesQuota money
-, @Bonus money
-, @CommissionPct money
-, @SalesYTD money
-, @SalesLastYear money
-AS
-BEGIN
-SET NOCOUNT ON
-INSERT INTO Sales.SalesPersonPluralsightDemo
-(
-    BusinessEntityID,
-    TerritoryID,
-    SalesQuota,
-    Bonus,
-    CommissionPct,
-    SalesYTD,
-    SalesLastYear,
-    rowguid,
-    ModifiedDate
-)
-VALUES
-(   
-    @BusinessEntityID
-	, @TerritoryID
-	, @SalesQuota
-    , @Bonus
-    , @CommissionPct
-    , @SalesYTD
-    , @SalesLastYear
-    , NEWID()
-    , GETDATE()
-    )
-END</t>
-  </si>
-  <si>
-    <t>/*Create a new role for Sales Manager*/</t>
-  </si>
-  <si>
-    <t>CREATE ROLE SalesManager;
-GO
-GRANT EXECUTE ON SCHEMA::Sales TO SalesManager
-GO
-GRANT SELECT ON SCHEMA::Sales TO SalesManager
-GO
-CREATE USER DemoUser WITHOUT LOGIN;
-GO
-ALTER ROLE SalesManager
-ADD MEMBER DemoUser;
-GO</t>
-  </si>
-  <si>
-    <t>Не сработает, так как у пользователя ограничены права на манипуляции с бд</t>
-  </si>
-  <si>
-    <t>Сработает</t>
-  </si>
-  <si>
-    <t>/*Insert rows directly into the table*/</t>
-  </si>
-  <si>
-    <t>EXECUTE AS USER = 'DemoUser';
-GO
-INSERT INTO Sales.SalesPersonPluralsightDemo
-(
-    BusinessEntityID,
-    TerritoryID,
-    SalesQuota,
-    Bonus,
-    CommissionPct,
-    SalesYTD,
-    SalesLastYear,
-    rowguid,
-    ModifiedDate
-)
-VALUES
-(   300,       -- BusinessEntityID - int
-    6,    -- TerritoryID - int
-    200000,    -- SalesQuota - money
-    1000, -- Bonus - money
-    0.01, -- CommissionPct - smallmoney
-    254000, -- SalesYTD - money
-    0, -- SalesLastYear - money
-    NEWID(), -- rowguid - uniqueidentifier
-    GETDATE()  -- ModifiedDate - datetime
-    )</t>
-  </si>
-  <si>
-    <t>*Execute procedure for INSERT*/
-EXECUTE AS USER = 'DemoUser';
-GO
-EXECUTE Sales.insertSalesPersonData 
-@BusinessEntityID = 300
-, @TerritoryID = 6
-, @SalesQuota = 200000
-, @Bonus = 1000
-, @CommissionPct = 0.01
-, @SalesYTD = 254000
-, @SalesLastYear = 0
-SELECT *
-FROM Sales.SalesPersonPluralsightDemo</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>CREATE PROCEDURE</t>
+    -- Вставляем данные в реальные таблицы
+    I</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">NSERT INTO Products (ProductName, Price, CategoryId)
+    SELECT ProductName, Price, 
+           (SELECT Id FROM Categories WHERE CategoryName = i.CategoryName)
+    FROM </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>inserted</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> i;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+END;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Пример </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>AFTER</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> для </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>TABLE</t>
+    </r>
+  </si>
+  <si>
+    <t>Удаление триггера</t>
+  </si>
+  <si>
+    <t>Отключение триггера</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CREATE TRIGGER</t>
     </r>
     <r>
       <rPr>
@@ -32968,20 +36165,7 @@
         <charset val="204"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">getSalesPersonData </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>AS
-BEGIN</t>
+      <t>Products_INSERT_UPDATE</t>
     </r>
     <r>
       <rPr>
@@ -32993,208 +36177,19 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-SELECT sp.BusinessEntityID
-  , sp.TerritoryID
-  , sp.SalesQuota
-  , sp.CommissionPct
-  , sp.SalesYTD
-  , sp.SalesLastYear
-  , sp.Bonus
-   FROM Sales.SalesPerson AS sp
-   INNER JOIN Sales.SalesTerritory AS st ON st.TerritoryID = sp.TerritoryID
-   WHERE sp.BusinessEntityID = 276
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>END</t>
-    </r>
-  </si>
-  <si>
-    <t>Создание процедуры (с параметрами)</t>
-  </si>
-  <si>
-    <t>Создание процедуры (без параметров)</t>
-  </si>
-  <si>
-    <t>Выполнение процедуры</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Преимущество!</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> И еще один важный аспект - производительность. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Хранимые процедуры обычно выполняются быстрее</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, чем обычные </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>SQL-инструкции</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>. Все потому что код процедур компилируется один раз при первом ее запуске, а затем сохраняется в скомпилированной форме.
-Для отделения тела процедуры от остальной части скрипта код процедуры нередко помещается в блок BEGIN...END</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">EXEC </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>getSalesPersonData</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF7030A0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>@BusinessEntityID</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> = 276</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>CREATE PROCEDURE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>getSalesPersonData</t>
+ON </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="5" tint="-0.499984740745262"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Products</t>
     </r>
     <r>
       <rPr>
@@ -33212,13 +36207,89 @@
       <rPr>
         <b/>
         <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>AFTER</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> INSERT, UPDATE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+AS
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">UPDATE Products
+SET Price = Price + Price * 0.38
+WHERE Id = (SELECT Id FROM </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
         <color rgb="FF7030A0"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="204"/>
         <scheme val="minor"/>
       </rPr>
-      <t>@BusinessEntityID</t>
+      <t>inserted</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>DROP TRIGGER</t>
     </r>
     <r>
       <rPr>
@@ -33235,13 +36306,123 @@
       <rPr>
         <b/>
         <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>int</t>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Products_INSERT_UPDATE</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>DISABLE TRIGGER</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Products_INSERT_UPDATE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ON Products</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ENABLE TRIGGER</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Products_INSERT_UPDATE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ON Products</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>INSERTED</t>
     </r>
     <r>
       <rPr>
@@ -33259,13 +36440,54 @@
       <rPr>
         <b/>
         <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>AS</t>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>DELETED</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">CREATE TRIGGER </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Products_INSERT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+ON </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Products</t>
     </r>
     <r>
       <rPr>
@@ -33283,13 +36505,36 @@
       <rPr>
         <b/>
         <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>BEGIN</t>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>AFTER</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>INSERT</t>
     </r>
     <r>
       <rPr>
@@ -33301,16 +36546,10 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-SELECT sp.BusinessEntityID
-  , sp.TerritoryID
-  , sp.SalesQuota
-  , sp.CommissionPct
-  , sp.SalesYTD
-  , sp.SalesLastYear
-  , sp.Bonus
-   FROM Sales.SalesPerson AS sp
-   INNER JOIN Sales.SalesTerritory AS st ON st.TerritoryID = sp.TerritoryID
-   WHERE sp.BusinessEntityID = </t>
+AS
+INSERT INTO History (ProductId, Operation)
+SELECT Id, 'Добавлен товар ' + ProductName + '   фирма ' + Manufacturer
+FROM </t>
     </r>
     <r>
       <rPr>
@@ -33322,7 +36561,48 @@
         <charset val="204"/>
         <scheme val="minor"/>
       </rPr>
-      <t>@BusinessEntityID</t>
+      <t>INSERTED</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">CREATE TRIGGER </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Products_UPDATE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+ON </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Products</t>
     </r>
     <r>
       <rPr>
@@ -33340,49 +36620,876 @@
       <rPr>
         <b/>
         <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>END</t>
-    </r>
-  </si>
-  <si>
-    <t>Удаление процедуры</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">DROP PROCEDURE </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
         <color rgb="FF00B050"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="204"/>
         <scheme val="minor"/>
       </rPr>
-      <t>getSalesPersonData</t>
-    </r>
-  </si>
-  <si>
-    <t>`https://metanit.com/sql/sqlserver/11.2.php</t>
+      <t>AFTER</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>UPDATE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+AS
+INSERT INTO History (ProductId, Operation)
+SELECT Id, 'Обновлен товар ' + ProductName + '   фирма ' + Manufacturer
+FROM </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>INSERTED</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (OR FROM </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>DELETED</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">CREATE TRIGGER </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Products_DELETE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+ON </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Products</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>AFTER</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>DELETE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+AS
+INSERT INTO History (ProductId, Operation)
+SELECT Id, 'Удален товар ' + ProductName + '   фирма ' + Manufacturer
+FROM </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>DELETED</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">DELETED </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Примечание! Inserted является временной таблицей, которая содержит </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>старые значения строк ДО</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> обновления</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+DELETE FROM Products
+WHERE Id=2
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">тут выполняется триггер
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 
+SELECT * FROM History</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>INSERTED</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Примечание! Inserted является временной таблицей, которая содержит </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>новые значения строк ПОСЛЕ</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> обновления</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+INSERT INTO Products (ProductName, Manufacturer, ProductCount, Price)
+VALUES('iPhone X', 'Apple', 2, 79900)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>тут выполняется триггер</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+SELECT * FROM History</t>
+    </r>
+  </si>
+  <si>
+    <t>Дололнительные данные во встроенных таблицах</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>INSERT, UPDATE, DELETE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> для таблиц </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>TABLE,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>VIEW</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>INSERT, UPDATE, DELETE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> для таблиц </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>TABLE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>inserted</t>
+  </si>
+  <si>
+    <t>inserted
+deleted</t>
+  </si>
+  <si>
+    <t>deleted</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Теперь можно делать INSERT в представление!
+INSERT INTO </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="5" tint="-0.499984740745262"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>vw_ProductInfo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (ProductName, Price, CategoryName)
+VALUES ('Новый товар', 100, 'Электроника');
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>INSERTED</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Примечание! Inserted является временной таблицей, которая содержит </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>новые значения строк ПОСЛЕ</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> обновления</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Пример </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>INSTEAD OF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> для </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>VIEW</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Пример </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>INSTEAD OF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> для </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>TABLE</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CREATE TRIGGER</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>products_delete</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+ON </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Products</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>INSTEAD OF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>DELETE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+AS
+UPDATE Products
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SET IsDeleted = 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+WHERE ID =(SELECT Id FROM </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>deleted</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="68" x14ac:knownFonts="1">
+  <fonts count="73" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -33937,6 +38044,32 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF7030A0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="5" tint="-0.499984740745262"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="5"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="22">
     <fill>
@@ -34157,9 +38290,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="143">
+  <cellXfs count="148">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -34170,141 +38303,141 @@
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="18" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="20" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="17" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="17" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="17" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    <xf numFmtId="49" fontId="28" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    <xf numFmtId="49" fontId="27" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="17" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="37" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    <xf numFmtId="49" fontId="17" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="28" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="40" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="28" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="28" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="15" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="26" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="25" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="35" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="26" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="38" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="26" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="26" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="14" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="40" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="38" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="26" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="28" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -34322,37 +38455,49 @@
     <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="44" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="45" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="40" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="40" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="43" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="38" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="38" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="28" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -34361,28 +38506,16 @@
     <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="26" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="35" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="37" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -34391,16 +38524,16 @@
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="20" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="22" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="20" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="22" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -34409,67 +38542,67 @@
     <xf numFmtId="49" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="29" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="31" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="32" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="34" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="20" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="22" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="25" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="27" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="25" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="27" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -34481,7 +38614,7 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -34499,16 +38632,16 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="20" fillId="17" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="22" fillId="17" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="35" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="33" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="35" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="49" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="51" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -34517,38 +38650,38 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="38" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="40" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="38" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="40" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="65" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="67" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="66" fillId="9" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="68" fillId="9" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -34557,28 +38690,43 @@
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="35" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="37" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="20" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="22" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="26" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="28" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -36377,7 +40525,7 @@
       <c r="B15" s="48"/>
       <c r="C15" s="9"/>
       <c r="D15" s="142" t="s">
-        <v>1365</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.3">
@@ -36395,50 +40543,70 @@
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="9"/>
       <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
+      <c r="C18" s="143" t="s">
+        <v>1321</v>
+      </c>
       <c r="D18" s="9"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="9"/>
       <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
+      <c r="C19" s="143" t="s">
+        <v>1322</v>
+      </c>
       <c r="D19" s="9"/>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="9"/>
       <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
+      <c r="C20" s="143" t="s">
+        <v>1323</v>
+      </c>
       <c r="D20" s="9"/>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A21" s="9"/>
       <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
+      <c r="C21" s="143" t="s">
+        <v>1349</v>
+      </c>
+      <c r="D21" s="143" t="s">
+        <v>1348</v>
+      </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="9"/>
       <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
+      <c r="C22" s="143" t="s">
+        <v>1350</v>
+      </c>
       <c r="D22" s="9"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="9"/>
       <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
+      <c r="C23" s="143" t="s">
+        <v>1351</v>
+      </c>
       <c r="D23" s="9"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="9"/>
       <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
+      <c r="C24" s="143" t="s">
+        <v>1355</v>
+      </c>
       <c r="D24" s="9"/>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A25" s="9"/>
       <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
+      <c r="C25" s="143" t="s">
+        <v>1356</v>
+      </c>
+      <c r="D25" s="143" t="s">
+        <v>1357</v>
+      </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="9"/>
@@ -38661,7 +42829,7 @@
     <row r="75" spans="1:22" ht="331.2" x14ac:dyDescent="0.3">
       <c r="A75" s="94"/>
       <c r="B75" s="81" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="C75" s="122" t="s">
         <v>222</v>
@@ -39620,12 +43788,12 @@
         <v>537</v>
       </c>
     </row>
-    <row r="14" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" s="132" t="s">
         <v>1213</v>
       </c>
       <c r="B14" s="82" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="C14" s="31"/>
       <c r="D14" s="35"/>
@@ -40416,7 +44584,7 @@
         <v>545</v>
       </c>
       <c r="B4" s="82" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="C4" s="9"/>
       <c r="D4" s="27" t="s">
@@ -40485,7 +44653,7 @@
         <v>554</v>
       </c>
       <c r="B10" s="82" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="C10" s="31"/>
       <c r="D10" s="76" t="s">
@@ -42505,7 +46673,7 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BA2B658-8DD3-4355-BA32-205FF02DBD74}">
   <sheetPr>
-    <tabColor rgb="FF7030A0"/>
+    <tabColor rgb="FFFFFF00"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:E59"/>
@@ -42922,7 +47090,7 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07071483-68B8-4A83-8459-BC9077F7B963}">
   <sheetPr>
-    <tabColor rgb="FF7030A0"/>
+    <tabColor rgb="FFFFFF00"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:E68"/>
@@ -43384,7 +47552,7 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F45C4F92-001F-4E91-8F03-EB46A8027543}">
   <sheetPr>
-    <tabColor rgb="FF7030A0"/>
+    <tabColor rgb="FFFFFF00"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:E61"/>
@@ -43888,7 +48056,7 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B618FF8A-AEBE-4109-8CD3-90151CF88DFD}">
   <sheetPr>
-    <tabColor theme="5"/>
+    <tabColor rgb="FF7030A0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:E15"/>
@@ -43929,7 +48097,7 @@
         <v>1221</v>
       </c>
       <c r="C3" s="127" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="D3" s="135" t="s">
         <v>108</v>
@@ -43937,7 +48105,7 @@
     </row>
     <row r="4" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
       <c r="B4" s="120" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="C4" s="126" t="s">
         <v>1222</v>
@@ -43945,19 +48113,19 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="136" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="C5" s="126"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="120" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="B6" s="120" t="s">
         <v>1224</v>
       </c>
       <c r="C6" s="120" t="s">
-        <v>1226</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
@@ -43970,7 +48138,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="136" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
@@ -43978,26 +48146,26 @@
         <v>655</v>
       </c>
       <c r="B9" s="126" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="C9" s="126" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="B10" s="126" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="C10" s="126" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="B11" s="126" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="C11" s="126" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="72" x14ac:dyDescent="0.3">
@@ -44005,10 +48173,10 @@
         <v>518</v>
       </c>
       <c r="B12" s="126" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="C12" s="126" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="D12" s="135" t="s">
         <v>108</v>
@@ -44016,16 +48184,16 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="136" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="B13" s="126"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="120" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C14" s="120" t="s">
         <v>1228</v>
-      </c>
-      <c r="C14" s="120" t="s">
-        <v>1229</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
@@ -44033,10 +48201,10 @@
         <v>518</v>
       </c>
       <c r="B15" s="120" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="C15" s="120" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
     </row>
   </sheetData>
@@ -44053,7 +48221,7 @@
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4794FD93-B283-45AF-BCD9-82490C321ADD}">
   <sheetPr>
-    <tabColor theme="5"/>
+    <tabColor rgb="FF7030A0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:V53"/>
@@ -44109,7 +48277,7 @@
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A3" s="78" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="C3" s="9"/>
       <c r="D3" s="76" t="s">
@@ -44121,7 +48289,7 @@
     </row>
     <row r="4" spans="1:22" ht="57.6" x14ac:dyDescent="0.3">
       <c r="C4" s="122" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="P4" s="1"/>
       <c r="U4" s="1"/>
@@ -44140,7 +48308,7 @@
         <v>214</v>
       </c>
       <c r="C6" s="122" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="D6" s="9"/>
     </row>
@@ -44148,7 +48316,7 @@
       <c r="A7" s="9"/>
       <c r="B7" s="42"/>
       <c r="C7" s="122" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="D7" s="9"/>
     </row>
@@ -44156,7 +48324,7 @@
       <c r="A8" s="9"/>
       <c r="B8" s="122"/>
       <c r="C8" s="122" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="D8" s="9"/>
     </row>
@@ -44164,7 +48332,7 @@
       <c r="A9" s="9"/>
       <c r="B9" s="42"/>
       <c r="C9" s="122" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="D9" s="9"/>
     </row>
@@ -44179,10 +48347,10 @@
     <row r="11" spans="1:22" ht="216" x14ac:dyDescent="0.3">
       <c r="A11" s="9"/>
       <c r="B11" s="122" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="C11" s="122" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="D11" s="9"/>
     </row>
@@ -44933,7 +49101,7 @@
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B39B1FF9-091B-40BE-9FD0-8662822E487B}">
   <sheetPr>
-    <tabColor theme="5"/>
+    <tabColor rgb="FF7030A0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:V52"/>
@@ -44989,7 +49157,7 @@
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A3" s="78" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="C3" s="9"/>
       <c r="D3" s="76" t="s">
@@ -45003,7 +49171,7 @@
       <c r="A4" s="9"/>
       <c r="B4" s="9"/>
       <c r="C4" s="122" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="P4" s="1"/>
       <c r="U4" s="1"/>
@@ -45012,26 +49180,26 @@
     <row r="5" spans="1:22" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A5" s="9"/>
       <c r="B5" s="122" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="C5" s="122" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="D5" s="9"/>
     </row>
     <row r="6" spans="1:22" ht="273.60000000000002" x14ac:dyDescent="0.3">
       <c r="A6" s="9"/>
       <c r="B6" s="122" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="C6" s="122" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="D6" s="9"/>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A7" s="121" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="B7" s="9"/>
       <c r="C7" s="122"/>
@@ -45043,7 +49211,7 @@
       <c r="A8" s="9"/>
       <c r="B8" s="9"/>
       <c r="C8" s="122" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="D8" s="9"/>
     </row>
@@ -45803,7 +49971,7 @@
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{714A04EA-98A4-480D-A5F1-767156A145A3}">
   <sheetPr>
-    <tabColor theme="5"/>
+    <tabColor rgb="FF7030A0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:V50"/>
@@ -45859,7 +50027,7 @@
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A3" s="78" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="C3" s="9"/>
       <c r="D3" s="76" t="s">
@@ -45873,7 +50041,7 @@
       <c r="A4" s="9"/>
       <c r="B4" s="9"/>
       <c r="C4" s="122" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="P4" s="1"/>
       <c r="U4" s="1"/>
@@ -45881,7 +50049,7 @@
     </row>
     <row r="5" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="132" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="B5" s="9"/>
       <c r="C5" s="122"/>
@@ -45891,43 +50059,43 @@
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="B6" s="122"/>
       <c r="C6" s="9" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="D6" s="9"/>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="B7" s="122"/>
       <c r="C7" s="9" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="D7" s="9"/>
     </row>
     <row r="8" spans="1:22" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="B8" s="122" t="s">
+        <v>1271</v>
+      </c>
+      <c r="C8" s="122" t="s">
         <v>1272</v>
-      </c>
-      <c r="C8" s="122" t="s">
-        <v>1273</v>
       </c>
       <c r="D8" s="76"/>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="B9" s="9"/>
       <c r="C9" s="9" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="D9" s="9"/>
     </row>
@@ -45939,13 +50107,13 @@
       <c r="C10" s="9"/>
       <c r="D10" s="9"/>
     </row>
-    <row r="11" spans="1:22" ht="144" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:22" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A11" s="9"/>
       <c r="B11" s="122" t="s">
+        <v>1273</v>
+      </c>
+      <c r="C11" s="122" t="s">
         <v>1274</v>
-      </c>
-      <c r="C11" s="122" t="s">
-        <v>1275</v>
       </c>
       <c r="D11" s="9"/>
     </row>
@@ -46731,7 +50899,7 @@
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A3" s="78" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="C3" s="9"/>
       <c r="D3" s="76" t="s">
@@ -46745,7 +50913,7 @@
       <c r="A4" s="9"/>
       <c r="B4" s="9"/>
       <c r="C4" s="122" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="P4" s="1"/>
       <c r="U4" s="1"/>
@@ -46753,7 +50921,7 @@
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A5" s="132" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="B5" s="9"/>
       <c r="C5" s="122"/>
@@ -46765,17 +50933,17 @@
       <c r="A6" s="9"/>
       <c r="B6" s="122"/>
       <c r="C6" s="122" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="D6" s="9"/>
     </row>
     <row r="7" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="9"/>
       <c r="B7" s="122" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="C7" s="122" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="D7" s="9"/>
     </row>
@@ -46783,13 +50951,13 @@
       <c r="A8" s="9"/>
       <c r="B8" s="122"/>
       <c r="C8" s="122" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="D8" s="76"/>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A9" s="132" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="B9" s="122"/>
       <c r="C9" s="122"/>
@@ -46798,30 +50966,30 @@
     <row r="10" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="9"/>
       <c r="B10" s="37" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="C10" s="122" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="D10" s="76"/>
     </row>
     <row r="11" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="9"/>
       <c r="B11" s="70" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="C11" s="122" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="D11" s="76"/>
     </row>
-    <row r="12" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="9"/>
       <c r="B12" s="37" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="C12" s="122" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="D12" s="76"/>
     </row>
@@ -46837,7 +51005,7 @@
       <c r="A14" s="9"/>
       <c r="B14" s="9"/>
       <c r="C14" s="122" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="D14" s="9"/>
     </row>
@@ -46845,13 +51013,13 @@
       <c r="A15" s="122"/>
       <c r="B15" s="122"/>
       <c r="C15" s="122" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="D15" s="9"/>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A16" s="37" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="B16" s="9"/>
       <c r="C16" s="9"/>
@@ -46861,13 +51029,13 @@
       <c r="A17" s="9"/>
       <c r="B17" s="9"/>
       <c r="C17" s="122" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="D17" s="9"/>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A18" s="121" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="B18" s="9"/>
       <c r="C18" s="9"/>
@@ -46879,7 +51047,7 @@
       <c r="A19" s="9"/>
       <c r="B19" s="9"/>
       <c r="C19" s="122" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="D19" s="9"/>
     </row>
@@ -47642,7 +51810,7 @@
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A3" s="78" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="C3" s="9"/>
       <c r="D3" s="76" t="s">
@@ -47656,7 +51824,7 @@
       <c r="A4" s="9"/>
       <c r="B4" s="9"/>
       <c r="C4" s="122" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="P4" s="1"/>
       <c r="U4" s="1"/>
@@ -47664,7 +51832,7 @@
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A5" s="136" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="B5" s="9"/>
       <c r="C5" s="122"/>
@@ -47676,7 +51844,7 @@
       <c r="A6" s="9"/>
       <c r="B6" s="9"/>
       <c r="C6" s="122" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="P6" s="1"/>
       <c r="U6" s="1"/>
@@ -47684,7 +51852,7 @@
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A7" s="136" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="B7" s="9"/>
       <c r="C7" s="9"/>
@@ -47696,13 +51864,13 @@
       </c>
       <c r="B8" s="9"/>
       <c r="C8" s="122" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A9" s="136" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
@@ -47712,16 +51880,16 @@
       <c r="A10" s="9"/>
       <c r="B10" s="9"/>
       <c r="C10" s="122" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="D10" s="76"/>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A11" s="121" t="s">
+        <v>1302</v>
+      </c>
+      <c r="B11" s="139" t="s">
         <v>1303</v>
-      </c>
-      <c r="B11" s="139" t="s">
-        <v>1304</v>
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="76" t="s">
@@ -47734,7 +51902,7 @@
         <v>342</v>
       </c>
       <c r="C12" s="122" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="D12" s="76"/>
     </row>
@@ -47744,16 +51912,16 @@
         <v>1209</v>
       </c>
       <c r="C13" s="122" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="D13" s="76"/>
     </row>
     <row r="14" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" s="121" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="B14" s="139" t="s">
-        <v>1312</v>
+        <v>1309</v>
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="76" t="s">
@@ -47763,20 +51931,20 @@
     <row r="15" spans="1:22" ht="72" x14ac:dyDescent="0.3">
       <c r="A15" s="9"/>
       <c r="B15" s="122" t="s">
-        <v>1311</v>
+        <v>1308</v>
       </c>
       <c r="C15" s="122" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="D15" s="9"/>
     </row>
     <row r="16" spans="1:22" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A16" s="9"/>
-      <c r="B16" s="122" t="s">
-        <v>1309</v>
-      </c>
-      <c r="C16" s="122" t="s">
-        <v>1310</v>
+      <c r="B16" s="143" t="s">
+        <v>1354</v>
+      </c>
+      <c r="C16" s="143" t="s">
+        <v>1353</v>
       </c>
       <c r="D16" s="9"/>
     </row>
@@ -48972,7 +53140,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="19" type="noConversion"/>
+  <phoneticPr fontId="21" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="D46" r:id="rId1" location=":~:text=%D0%A1%D0%BE%D0%B7%D0%B4%D0%B0%D0%BD%D0%B8%D0%B5%20%D0%B1%D0%B0%D0%B7%D1%8B%20%D0%B4%D0%B0%D0%BD%D0%BD%D1%8B%D1%85" xr:uid="{FDFE2116-2B22-4A87-B37D-3DFA9E8F9FE0}"/>
     <hyperlink ref="D44" r:id="rId2" location=":~:text=%D0%A1%D0%BE%D0%B7%D0%B4%D0%B0%D0%BD%D0%B8%D0%B5%20%D0%B1%D0%B0%D0%B7%D1%8B%20%D0%B4%D0%B0%D0%BD%D0%BD%D1%8B%D1%85%20%D0%B2%20SQL%20Management%20Studio" xr:uid="{5B701F02-CEF7-44EA-83C6-0E21D7145608}"/>
@@ -48986,12 +53154,12 @@
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{406FA542-E35D-441D-A937-7835B6AE1BC8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C01B65FF-3E11-4C6D-98D7-9E777AE32C33}">
   <sheetPr>
     <tabColor theme="5"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:U48"/>
+  <dimension ref="A2:U28"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="36" style="1" customWidth="1"/>
@@ -49043,11 +53211,302 @@
       <c r="U2" s="5"/>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A3" s="146" t="s">
+        <v>1367</v>
+      </c>
+      <c r="B3" s="122"/>
+      <c r="D3" s="76" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" ht="72" x14ac:dyDescent="0.3">
+      <c r="A4" s="43"/>
+      <c r="B4" s="122"/>
+      <c r="C4" s="145" t="s">
+        <v>1368</v>
+      </c>
+      <c r="D4" s="122"/>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A5" s="147" t="s">
+        <v>1369</v>
+      </c>
+      <c r="B5" s="122"/>
+      <c r="D5" s="122"/>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A6" s="43" t="s">
+        <v>1370</v>
+      </c>
+      <c r="B6" s="145" t="s">
+        <v>1390</v>
+      </c>
+      <c r="C6" s="145" t="s">
+        <v>1373</v>
+      </c>
+      <c r="D6" s="122"/>
+    </row>
+    <row r="7" spans="1:21" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="43" t="s">
+        <v>1371</v>
+      </c>
+      <c r="B7" s="145" t="s">
+        <v>1389</v>
+      </c>
+      <c r="C7" s="145" t="s">
+        <v>1372</v>
+      </c>
+      <c r="D7" s="76"/>
+    </row>
+    <row r="8" spans="1:21" ht="244.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="145" t="s">
+        <v>1395</v>
+      </c>
+      <c r="B8" s="145" t="s">
+        <v>1394</v>
+      </c>
+      <c r="C8" s="145" t="s">
+        <v>1374</v>
+      </c>
+      <c r="D8" s="76"/>
+    </row>
+    <row r="9" spans="1:21" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A9" s="145" t="s">
+        <v>1396</v>
+      </c>
+      <c r="B9" s="145"/>
+      <c r="C9" s="145" t="s">
+        <v>1397</v>
+      </c>
+      <c r="D9" s="76"/>
+    </row>
+    <row r="10" spans="1:21" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="145" t="s">
+        <v>1375</v>
+      </c>
+      <c r="B10" s="145" t="s">
+        <v>1375</v>
+      </c>
+      <c r="C10" s="145" t="s">
+        <v>1378</v>
+      </c>
+      <c r="D10" s="122"/>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A11" s="145"/>
+      <c r="B11" s="145"/>
+      <c r="C11" s="145"/>
+      <c r="D11" s="122"/>
+    </row>
+    <row r="12" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A12" s="147" t="s">
+        <v>1388</v>
+      </c>
+      <c r="B12" s="145"/>
+      <c r="C12" s="145"/>
+      <c r="D12" s="122"/>
+    </row>
+    <row r="13" spans="1:21" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A13" s="43" t="s">
+        <v>1391</v>
+      </c>
+      <c r="B13" s="145" t="s">
+        <v>1387</v>
+      </c>
+      <c r="C13" s="145" t="s">
+        <v>1383</v>
+      </c>
+      <c r="D13" s="76" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A14" s="43" t="s">
+        <v>1392</v>
+      </c>
+      <c r="B14" s="145" t="s">
+        <v>1382</v>
+      </c>
+      <c r="C14" s="145" t="s">
+        <v>1384</v>
+      </c>
+      <c r="D14" s="76" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" ht="144" x14ac:dyDescent="0.3">
+      <c r="A15" s="43" t="s">
+        <v>1393</v>
+      </c>
+      <c r="B15" s="145" t="s">
+        <v>1386</v>
+      </c>
+      <c r="C15" s="145" t="s">
+        <v>1385</v>
+      </c>
+      <c r="D15" s="76" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A16" s="147" t="s">
+        <v>1376</v>
+      </c>
+      <c r="B16" s="143"/>
+      <c r="C16" s="43"/>
+      <c r="D16" s="122"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="43"/>
+      <c r="B17" s="122"/>
+      <c r="C17" s="145" t="s">
+        <v>1379</v>
+      </c>
+      <c r="D17" s="122"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" s="147" t="s">
+        <v>1377</v>
+      </c>
+      <c r="B18" s="122"/>
+      <c r="C18" s="43"/>
+      <c r="D18" s="122"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" s="43"/>
+      <c r="B19" s="122"/>
+      <c r="C19" s="145" t="s">
+        <v>1380</v>
+      </c>
+      <c r="D19" s="76"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" s="43"/>
+      <c r="B20" s="145"/>
+      <c r="C20" s="145" t="s">
+        <v>1381</v>
+      </c>
+      <c r="D20" s="122"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" s="122"/>
+      <c r="B21" s="145"/>
+      <c r="C21" s="43"/>
+      <c r="D21" s="122"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" s="145"/>
+      <c r="B22" s="145"/>
+      <c r="C22" s="43"/>
+      <c r="D22" s="122"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" s="122"/>
+      <c r="B23" s="145"/>
+      <c r="C23" s="43"/>
+      <c r="D23" s="122"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" s="122"/>
+      <c r="B24" s="145"/>
+      <c r="C24" s="145"/>
+      <c r="D24" s="122"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" s="122"/>
+      <c r="B25" s="122"/>
+      <c r="D25" s="122"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" s="122"/>
+      <c r="B26" s="122"/>
+      <c r="D26" s="122"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" s="122"/>
+      <c r="B27" s="122"/>
+      <c r="D27" s="122"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" s="122"/>
+      <c r="B28" s="122"/>
+      <c r="D28" s="122"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D3" r:id="rId1" xr:uid="{11DAF42D-B8B1-47E1-A75A-2C0BFF2FAE8A}"/>
+    <hyperlink ref="D13" r:id="rId2" location=":~:text=%D0%94%D0%BE%D0%B1%D0%B0%D0%B2%D0%BB%D0%B5%D0%BD%D0%B8%D0%B5" xr:uid="{4F3B4D94-0365-41B1-B499-3CD4376D6526}"/>
+    <hyperlink ref="D15" r:id="rId3" location=":~:text=%D0%A3%D0%B4%D0%B0%D0%BB%D0%B5%D0%BD%D0%B8%D0%B5%20%D0%B4%D0%B0%D0%BD%D0%BD%D1%8B%D1%85" xr:uid="{60EC9005-8137-48E3-9B76-490F8804D873}"/>
+    <hyperlink ref="D14" r:id="rId4" location=":~:text=%D0%98%D0%B7%D0%BC%D0%B5%D0%BD%D0%B5%D0%BD%D0%B8%D0%B5%20%D0%B4%D0%B0%D0%BD%D0%BD%D1%8B%D1%85" xr:uid="{8CAD3495-B81A-4C84-97B9-C4B18827245E}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{406FA542-E35D-441D-A937-7835B6AE1BC8}">
+  <sheetPr>
+    <tabColor theme="5"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A2:U42"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="36" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.5546875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="71.21875" style="122" customWidth="1"/>
+    <col min="4" max="4" width="56.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="6.21875" style="7" customWidth="1"/>
+    <col min="6" max="6" width="43.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="55.109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="67.88671875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="64.33203125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="7.77734375" style="7" customWidth="1"/>
+    <col min="11" max="11" width="39.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="48.88671875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="72.6640625" style="1" customWidth="1"/>
+    <col min="14" max="14" width="43.88671875" style="1" customWidth="1"/>
+    <col min="15" max="15" width="7.77734375" style="7" customWidth="1"/>
+    <col min="16" max="16" width="56.77734375" style="2" customWidth="1"/>
+    <col min="17" max="17" width="46.77734375" style="2" customWidth="1"/>
+    <col min="18" max="18" width="62.88671875" style="2" customWidth="1"/>
+    <col min="19" max="19" width="49.21875" style="1" customWidth="1"/>
+    <col min="20" max="20" width="8.77734375" style="8"/>
+    <col min="21" max="21" width="67.77734375" style="2" customWidth="1"/>
+    <col min="22" max="22" width="68.33203125" style="1" customWidth="1"/>
+    <col min="23" max="24" width="59.33203125" style="1" customWidth="1"/>
+    <col min="25" max="25" width="59.6640625" style="1" customWidth="1"/>
+    <col min="26" max="26" width="99.44140625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="41.21875" style="1" customWidth="1"/>
+    <col min="28" max="16384" width="8.77734375" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A2" s="3"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="140"/>
+      <c r="D2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="P2" s="5"/>
+      <c r="Q2" s="5"/>
+      <c r="R2" s="5"/>
+      <c r="S2" s="5"/>
+      <c r="U2" s="5"/>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>1313</v>
+        <v>1310</v>
       </c>
       <c r="C3" s="137" t="s">
-        <v>1314</v>
+        <v>1311</v>
       </c>
       <c r="E3" s="1"/>
       <c r="J3" s="1"/>
@@ -49057,7 +53516,7 @@
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4" s="121" t="s">
-        <v>1358</v>
+        <v>1314</v>
       </c>
       <c r="B4" s="122"/>
       <c r="D4" s="76" t="s">
@@ -49067,177 +53526,163 @@
     <row r="5" spans="1:21" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A5" s="122"/>
       <c r="B5" s="122" t="s">
-        <v>1360</v>
-      </c>
-      <c r="C5" s="122" t="s">
-        <v>1356</v>
+        <v>1315</v>
+      </c>
+      <c r="C5" s="143" t="s">
+        <v>1336</v>
       </c>
       <c r="D5" s="122"/>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A6" s="121" t="s">
-        <v>1357</v>
+        <v>1313</v>
       </c>
       <c r="B6" s="122"/>
       <c r="D6" s="122"/>
     </row>
     <row r="7" spans="1:21" ht="216" x14ac:dyDescent="0.3">
-      <c r="C7" s="122" t="s">
-        <v>1362</v>
+      <c r="C7" s="143" t="s">
+        <v>1337</v>
       </c>
       <c r="D7" s="122"/>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A8" s="121" t="s">
-        <v>1359</v>
+    <row r="8" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="144" t="s">
+        <v>1340</v>
       </c>
       <c r="B8" s="122"/>
       <c r="D8" s="76" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="122"/>
-      <c r="B9" s="122"/>
-      <c r="C9" s="122" t="s">
+      <c r="B9" s="143" t="s">
+        <v>1343</v>
+      </c>
+      <c r="C9" s="43" t="s">
+        <v>1342</v>
+      </c>
+      <c r="D9" s="76"/>
+    </row>
+    <row r="10" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="122"/>
+      <c r="B10" s="143" t="s">
+        <v>1344</v>
+      </c>
+      <c r="C10" s="122" t="s">
+        <v>1316</v>
+      </c>
+      <c r="D10" s="122"/>
+    </row>
+    <row r="11" spans="1:21" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="122"/>
+      <c r="B11" s="143" t="s">
+        <v>1345</v>
+      </c>
+      <c r="C11" s="43" t="s">
+        <v>1341</v>
+      </c>
+      <c r="D11" s="122"/>
+    </row>
+    <row r="12" spans="1:21" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A12" s="122"/>
+      <c r="B12" s="143" t="s">
+        <v>1346</v>
+      </c>
+      <c r="C12" s="43" t="s">
+        <v>1347</v>
+      </c>
+      <c r="D12" s="122"/>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A13" s="121" t="s">
+        <v>1317</v>
+      </c>
+      <c r="B13" s="122"/>
+      <c r="D13" s="122"/>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A14" s="122"/>
+      <c r="B14" s="122"/>
+      <c r="C14" s="43" t="s">
+        <v>1318</v>
+      </c>
+      <c r="D14" s="122"/>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A15" s="121" t="s">
+        <v>1359</v>
+      </c>
+      <c r="B15" s="122"/>
+      <c r="D15" s="76" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A16" s="145" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B16" s="145" t="s">
+        <v>1333</v>
+      </c>
+      <c r="C16" s="43" t="s">
+        <v>1362</v>
+      </c>
+      <c r="D16" s="122"/>
+    </row>
+    <row r="17" spans="1:21" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A17" s="122"/>
+      <c r="B17" s="145" t="s">
+        <v>1363</v>
+      </c>
+      <c r="C17" s="43" t="s">
         <v>1361</v>
       </c>
-      <c r="D9" s="122"/>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A10" s="121" t="s">
+      <c r="D17" s="122"/>
+    </row>
+    <row r="18" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A18" s="145" t="s">
+        <v>1365</v>
+      </c>
+      <c r="B18" s="145"/>
+      <c r="C18" s="43"/>
+      <c r="D18" s="122"/>
+    </row>
+    <row r="19" spans="1:21" ht="144" x14ac:dyDescent="0.3">
+      <c r="A19" s="122"/>
+      <c r="B19" s="145" t="s">
+        <v>1333</v>
+      </c>
+      <c r="C19" s="43" t="s">
+        <v>1360</v>
+      </c>
+      <c r="D19" s="122"/>
+    </row>
+    <row r="20" spans="1:21" ht="72" x14ac:dyDescent="0.3">
+      <c r="A20" s="122"/>
+      <c r="B20" s="145" t="s">
         <v>1363</v>
       </c>
-      <c r="B10" s="122"/>
-      <c r="D10" s="122"/>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A11" s="122"/>
-      <c r="B11" s="122"/>
-      <c r="C11" s="43" t="s">
-        <v>1364</v>
-      </c>
-      <c r="D11" s="122"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A12" s="122"/>
-      <c r="B12" s="122"/>
-      <c r="D12" s="122"/>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A13" s="3"/>
-      <c r="B13" s="5"/>
-      <c r="C13" s="140"/>
-      <c r="D13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="K13" s="3"/>
-      <c r="L13" s="3"/>
-      <c r="M13" s="3"/>
-      <c r="N13" s="3"/>
-      <c r="P13" s="5"/>
-      <c r="Q13" s="5"/>
-      <c r="R13" s="5"/>
-      <c r="S13" s="5"/>
-      <c r="U13" s="5"/>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="s">
-        <v>1315</v>
-      </c>
-      <c r="C14" s="137" t="s">
-        <v>1314</v>
-      </c>
-      <c r="E14" s="1"/>
-      <c r="J14" s="1"/>
-      <c r="O14" s="1"/>
-      <c r="S14" s="2"/>
-      <c r="T14"/>
-    </row>
-    <row r="15" spans="1:21" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A15" s="122"/>
-      <c r="B15" s="122"/>
-      <c r="C15" s="122" t="s">
-        <v>1316</v>
-      </c>
-      <c r="D15" s="122"/>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A16" s="30" t="s">
-        <v>500</v>
-      </c>
-      <c r="B16" s="122"/>
-      <c r="D16" s="122"/>
-    </row>
-    <row r="17" spans="1:21" ht="216" x14ac:dyDescent="0.3">
-      <c r="A17" s="122" t="s">
-        <v>1317</v>
-      </c>
-      <c r="B17" s="122"/>
-      <c r="C17" s="122" t="s">
-        <v>1318</v>
-      </c>
-      <c r="D17" s="122" t="s">
-        <v>1319</v>
-      </c>
-    </row>
-    <row r="18" spans="1:21" ht="360" x14ac:dyDescent="0.3">
-      <c r="A18" s="122"/>
-      <c r="B18" s="122"/>
-      <c r="C18" s="122" t="s">
-        <v>1320</v>
-      </c>
-      <c r="D18" s="122" t="s">
-        <v>1321</v>
-      </c>
-    </row>
-    <row r="19" spans="1:21" ht="172.8" x14ac:dyDescent="0.3">
-      <c r="A19" s="122"/>
-      <c r="B19" s="122"/>
-      <c r="C19" s="122" t="s">
-        <v>1322</v>
-      </c>
-      <c r="D19" s="122"/>
-    </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A20" s="141" t="s">
-        <v>395</v>
-      </c>
-      <c r="B20" s="122"/>
+      <c r="C20" s="145" t="s">
+        <v>1366</v>
+      </c>
       <c r="D20" s="122"/>
     </row>
-    <row r="21" spans="1:21" ht="201.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="122" t="s">
-        <v>1323</v>
-      </c>
+    <row r="21" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A21" s="122"/>
       <c r="B21" s="122"/>
-      <c r="C21" s="122" t="s">
-        <v>1324</v>
-      </c>
-      <c r="D21" s="122" t="s">
-        <v>1325</v>
-      </c>
+      <c r="D21" s="122"/>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A22" s="37" t="s">
-        <v>394</v>
-      </c>
+      <c r="A22" s="122"/>
       <c r="B22" s="122"/>
       <c r="D22" s="122"/>
     </row>
-    <row r="23" spans="1:21" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A23" s="122" t="s">
-        <v>1326</v>
-      </c>
+    <row r="23" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A23" s="122"/>
       <c r="B23" s="122"/>
-      <c r="C23" s="122" t="s">
-        <v>1327</v>
-      </c>
-      <c r="D23" s="122" t="s">
-        <v>1328</v>
-      </c>
+      <c r="D23" s="122"/>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A24" s="122"/>
@@ -49263,12 +53708,12 @@
       <c r="S25" s="5"/>
       <c r="U25" s="5"/>
     </row>
-    <row r="26" spans="1:21" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A26" s="121" t="s">
-        <v>1329</v>
+    <row r="26" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
+        <v>1312</v>
       </c>
       <c r="C26" s="137" t="s">
-        <v>1314</v>
+        <v>1311</v>
       </c>
       <c r="E26" s="1"/>
       <c r="J26" s="1"/>
@@ -49276,223 +53721,162 @@
       <c r="S26" s="2"/>
       <c r="T26"/>
     </row>
-    <row r="27" spans="1:21" ht="230.4" x14ac:dyDescent="0.3">
-      <c r="B27" s="122" t="s">
+    <row r="27" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A27" s="30" t="s">
+        <v>500</v>
+      </c>
+      <c r="B27" s="145" t="s">
+        <v>1358</v>
+      </c>
+      <c r="C27" s="145" t="s">
+        <v>1358</v>
+      </c>
+      <c r="D27" s="145" t="s">
+        <v>1358</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="A28" s="143" t="s">
+        <v>1333</v>
+      </c>
+      <c r="B28" s="143" t="s">
+        <v>1335</v>
+      </c>
+      <c r="C28" s="62" t="s">
+        <v>1334</v>
+      </c>
+      <c r="D28" s="143" t="s">
+        <v>1324</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21" ht="230.4" x14ac:dyDescent="0.3">
+      <c r="A29" s="143" t="s">
+        <v>1331</v>
+      </c>
+      <c r="B29" s="143"/>
+      <c r="C29" s="143" t="s">
+        <v>1329</v>
+      </c>
+      <c r="D29" s="122"/>
+    </row>
+    <row r="30" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A30" s="143" t="s">
+        <v>1332</v>
+      </c>
+      <c r="B30" s="143"/>
+      <c r="C30" s="143" t="s">
         <v>1330</v>
       </c>
-      <c r="C27" s="122" t="s">
+      <c r="D30" s="122"/>
+    </row>
+    <row r="31" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A31" s="141" t="s">
+        <v>395</v>
+      </c>
+      <c r="B31" s="122"/>
+      <c r="D31" s="122"/>
+    </row>
+    <row r="32" spans="1:21" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="A32" s="143" t="s">
+        <v>1333</v>
+      </c>
+      <c r="B32" s="143"/>
+      <c r="C32" s="143" t="s">
+        <v>1338</v>
+      </c>
+      <c r="D32" s="143" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A33" s="143" t="s">
         <v>1331</v>
       </c>
-      <c r="D27" s="122"/>
-    </row>
-    <row r="28" spans="1:21" ht="144" x14ac:dyDescent="0.3">
-      <c r="B28" s="122" t="s">
+      <c r="B33" s="143"/>
+      <c r="C33" s="143" t="s">
+        <v>1326</v>
+      </c>
+      <c r="D33" s="143"/>
+    </row>
+    <row r="34" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A34" s="143" t="s">
         <v>1332</v>
       </c>
-      <c r="C28" s="122" t="s">
+      <c r="B34" s="143"/>
+      <c r="C34" s="143" t="s">
+        <v>1325</v>
+      </c>
+      <c r="D34" s="143"/>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A35" s="37" t="s">
+        <v>394</v>
+      </c>
+      <c r="B35" s="122"/>
+      <c r="D35" s="122"/>
+    </row>
+    <row r="36" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A36" s="143" t="s">
         <v>1333</v>
       </c>
-      <c r="D28" s="122"/>
-    </row>
-    <row r="29" spans="1:21" ht="316.8" x14ac:dyDescent="0.3">
-      <c r="A29" s="122" t="s">
-        <v>1334</v>
-      </c>
-      <c r="B29" s="122"/>
-      <c r="C29" s="122" t="s">
-        <v>1335</v>
-      </c>
-      <c r="D29" s="122" t="s">
-        <v>1336</v>
-      </c>
-    </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A30" s="122"/>
-      <c r="B30" s="122"/>
-      <c r="D30" s="122"/>
-    </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A31" s="3"/>
-      <c r="B31" s="5"/>
-      <c r="C31" s="140"/>
-      <c r="D31" s="3"/>
-      <c r="F31" s="3"/>
-      <c r="G31" s="5"/>
-      <c r="H31" s="3"/>
-      <c r="I31" s="3"/>
-      <c r="K31" s="3"/>
-      <c r="L31" s="3"/>
-      <c r="M31" s="3"/>
-      <c r="N31" s="3"/>
-      <c r="P31" s="5"/>
-      <c r="Q31" s="5"/>
-      <c r="R31" s="5"/>
-      <c r="S31" s="5"/>
-      <c r="U31" s="5"/>
-    </row>
-    <row r="32" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A32" s="121" t="s">
-        <v>1337</v>
-      </c>
-      <c r="B32" s="122"/>
-      <c r="C32" s="137" t="s">
-        <v>1314</v>
-      </c>
-      <c r="D32" s="122"/>
-    </row>
-    <row r="33" spans="1:21" ht="144" x14ac:dyDescent="0.3">
-      <c r="A33" s="122"/>
-      <c r="B33" s="122" t="s">
-        <v>1338</v>
-      </c>
-      <c r="C33" s="122" t="s">
+      <c r="B36" s="143"/>
+      <c r="C36" s="143" t="s">
         <v>1339</v>
       </c>
-      <c r="D33" s="122" t="s">
-        <v>1340</v>
-      </c>
-    </row>
-    <row r="34" spans="1:21" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A34" s="122"/>
-      <c r="B34" s="122"/>
-      <c r="C34" s="122" t="s">
-        <v>1341</v>
-      </c>
-      <c r="D34" s="122"/>
-    </row>
-    <row r="35" spans="1:21" ht="259.2" x14ac:dyDescent="0.3">
-      <c r="A35" s="122"/>
-      <c r="B35" s="122"/>
-      <c r="C35" s="122" t="s">
-        <v>1342</v>
-      </c>
-      <c r="D35" s="122"/>
-    </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A36" s="122"/>
-      <c r="B36" s="122"/>
-      <c r="D36" s="122"/>
-    </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A37" s="3"/>
-      <c r="B37" s="5"/>
-      <c r="C37" s="140"/>
-      <c r="D37" s="3"/>
-      <c r="F37" s="3"/>
-      <c r="G37" s="5"/>
-      <c r="H37" s="3"/>
-      <c r="I37" s="3"/>
-      <c r="K37" s="3"/>
-      <c r="L37" s="3"/>
-      <c r="M37" s="3"/>
-      <c r="N37" s="3"/>
-      <c r="P37" s="5"/>
-      <c r="Q37" s="5"/>
-      <c r="R37" s="5"/>
-      <c r="S37" s="5"/>
-      <c r="U37" s="5"/>
-    </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A38" s="121" t="s">
-        <v>1343</v>
-      </c>
-      <c r="B38" s="122"/>
-      <c r="C38" s="137" t="s">
-        <v>1314</v>
+      <c r="D36" s="143"/>
+    </row>
+    <row r="37" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A37" s="143" t="s">
+        <v>1331</v>
+      </c>
+      <c r="B37" s="143"/>
+      <c r="C37" s="143" t="s">
+        <v>1327</v>
+      </c>
+      <c r="D37" s="122"/>
+    </row>
+    <row r="38" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A38" s="143" t="s">
+        <v>1332</v>
+      </c>
+      <c r="B38" s="143"/>
+      <c r="C38" s="143" t="s">
+        <v>1328</v>
       </c>
       <c r="D38" s="122"/>
     </row>
-    <row r="39" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="122"/>
-      <c r="B39" s="122" t="s">
-        <v>1344</v>
-      </c>
-      <c r="C39" s="122" t="s">
-        <v>1345</v>
-      </c>
+      <c r="B39" s="122"/>
       <c r="D39" s="122"/>
     </row>
-    <row r="40" spans="1:21" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="122"/>
-      <c r="B40" s="122" t="s">
-        <v>1346</v>
-      </c>
-      <c r="C40" s="122" t="s">
-        <v>1347</v>
-      </c>
+      <c r="B40" s="122"/>
       <c r="D40" s="122"/>
     </row>
-    <row r="41" spans="1:21" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="122"/>
-      <c r="B41" s="122" t="s">
-        <v>1317</v>
-      </c>
-      <c r="C41" s="122" t="s">
-        <v>1348</v>
-      </c>
+      <c r="B41" s="122"/>
       <c r="D41" s="122"/>
     </row>
-    <row r="42" spans="1:21" ht="216" x14ac:dyDescent="0.3">
-      <c r="A42" s="122" t="s">
-        <v>1349</v>
-      </c>
-      <c r="C42" s="122" t="s">
-        <v>1350</v>
-      </c>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A42" s="122"/>
+      <c r="B42" s="122"/>
       <c r="D42" s="122"/>
-    </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A43" s="122"/>
-      <c r="C43" s="121" t="s">
-        <v>1351</v>
-      </c>
-      <c r="D43" s="121" t="s">
-        <v>1352</v>
-      </c>
-    </row>
-    <row r="44" spans="1:21" ht="374.4" x14ac:dyDescent="0.3">
-      <c r="A44" s="122" t="s">
-        <v>1353</v>
-      </c>
-      <c r="B44" s="122"/>
-      <c r="C44" s="122" t="s">
-        <v>1354</v>
-      </c>
-      <c r="D44" s="122" t="s">
-        <v>1355</v>
-      </c>
-    </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A45" s="122"/>
-      <c r="B45" s="122"/>
-      <c r="D45" s="122"/>
-    </row>
-    <row r="46" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A46" s="122"/>
-      <c r="B46" s="122"/>
-      <c r="D46" s="122"/>
-    </row>
-    <row r="47" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A47" s="122"/>
-      <c r="B47" s="122"/>
-      <c r="D47" s="122"/>
-    </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A48" s="122"/>
-      <c r="B48" s="122"/>
-      <c r="D48" s="122"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="D4" r:id="rId1" xr:uid="{DAE58DFD-52AA-429B-A308-F060AE2B5DAC}"/>
     <hyperlink ref="D8" r:id="rId2" location=":~:text=%D0%92%D1%8B%D0%BF%D0%BE%D0%BB%D0%BD%D0%B5%D0%BD%D0%B8%D0%B5%20%D0%BF%D1%80%D0%BE%D1%86%D0%B5%D0%B4%D1%83%D1%80%D1%8B" xr:uid="{050B3E25-DBD1-4A0A-ACE0-7568ED17698C}"/>
+    <hyperlink ref="D15" r:id="rId3" xr:uid="{0A8FC476-0E14-491D-BAE3-FE1AB08C73C8}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId3"/>
+  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId4"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DB01197-FE1C-4ED1-B3B4-7B774B71A2A6}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -49543,7 +53927,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8347859-D7B0-40A5-9B17-0069AC1E92BB}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -49908,7 +54292,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16AAE27B-B1A5-470A-8C56-1AC981AA4A71}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -50245,7 +54629,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B13A24C-6305-48F4-A1E6-55B31CAA1F4A}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -51118,7 +55502,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA83B601-5B0E-4344-A36B-7DD0432A3007}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -51248,7 +55632,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="11" spans="1:22" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:22" ht="144" x14ac:dyDescent="0.3">
       <c r="A11" s="9"/>
       <c r="B11" s="9"/>
       <c r="C11" s="42" t="s">
@@ -52476,7 +56860,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="19" type="noConversion"/>
+  <phoneticPr fontId="21" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="D40" r:id="rId1" location=":~:text=%D0%94%D0%BB%D1%8F%20%D0%B3%D0%B5%D0%BD%D0%B5%D1%80%D0%B0%D1%86%D0%B8%D0%B8%20%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82%D0%B0%20UNIQUEIDENTIFIER" xr:uid="{8276130C-D262-49CA-89B1-D60C8C3E4E63}"/>
   </hyperlinks>

--- a/4 четверть_MSSQL.xlsx
+++ b/4 четверть_MSSQL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlexServHW\Desktop\GB_Developer_Workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2D03CA2-6D1B-4F6F-BCB7-F7F5538FB5D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A57485EE-D7C0-4BBD-933F-58D093D3EA9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24" yWindow="1104" windowWidth="23016" windowHeight="11136" firstSheet="21" activeTab="24" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="24" yWindow="1104" windowWidth="23016" windowHeight="11136" firstSheet="19" activeTab="25" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Изучить" sheetId="21" r:id="rId1"/>
@@ -37,8 +37,8 @@
     <sheet name="NAVCH" sheetId="39" r:id="rId22"/>
     <sheet name="INT" sheetId="40" r:id="rId23"/>
     <sheet name="DATE" sheetId="41" r:id="rId24"/>
-    <sheet name="JSON" sheetId="52" r:id="rId25"/>
-    <sheet name="JSON -&gt; APP" sheetId="53" r:id="rId26"/>
+    <sheet name="JSON&gt;TAB&gt;SQL" sheetId="52" r:id="rId25"/>
+    <sheet name="TAB&gt;JSON&gt;APP" sheetId="53" r:id="rId26"/>
     <sheet name="DECLARE" sheetId="43" r:id="rId27"/>
     <sheet name="IF" sheetId="23" r:id="rId28"/>
     <sheet name="WHILE" sheetId="44" r:id="rId29"/>
@@ -54287,12 +54287,20 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="95" x14ac:knownFonts="1">
+  <fonts count="96" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -55353,7 +55361,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="193">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -55366,42 +55374,48 @@
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="36" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="37" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="36" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="37" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="36" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="36" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="36" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="36" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="49" fontId="35" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="35" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="35" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="35" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="38" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="49" fontId="34" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -55409,57 +55423,60 @@
     <xf numFmtId="49" fontId="34" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="34" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="33" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="34" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="33" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="34" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="33" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="33" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="45" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="44" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="43" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="53" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="54" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="33" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="34" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="44" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="45" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="56" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="57" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="38" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="39" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="44" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="45" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="35" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="36" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="32" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -55467,22 +55484,13 @@
     <xf numFmtId="49" fontId="31" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="30" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="57" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="56" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="44" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="45" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -55497,49 +55505,52 @@
     <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="40" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="29" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="28" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="39" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="28" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="27" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="62" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="57" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="57" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="48" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="60" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="56" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="56" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="44" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="45" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -55548,25 +55559,22 @@
     <xf numFmtId="49" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="23" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="22" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="23" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="22" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="53" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="54" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="38" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="39" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -55575,61 +55583,61 @@
     <xf numFmtId="49" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="22" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="23" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="47" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="48" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="49" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="50" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="51" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="21" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="21" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="50" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="39" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="21" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="40" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="44" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="44" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="20" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="38" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="43" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="43" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="21" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="20" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="21" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="20" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="21" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -55641,7 +55649,7 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="20" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="21" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -55659,59 +55667,65 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="38" fillId="17" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="39" fillId="17" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="51" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="52" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="51" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="52" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="67" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="68" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="19" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="20" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="57" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="57" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="84" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="85" fillId="9" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="54" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="45" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="45" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="56" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="56" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="83" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="84" fillId="9" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="53" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="38" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="44" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="19" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -55720,49 +55734,43 @@
     <xf numFmtId="49" fontId="18" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="39" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="17" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="38" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="16" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="16" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="16" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -55777,10 +55785,13 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="90" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="91" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -55789,93 +55800,93 @@
     <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="13" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="54" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="54" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="54" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="53" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="53" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="53" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="38" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="10" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="45" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="46" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="9" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="47" fillId="17" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="48" fillId="17" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="47" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="48" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="50" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="51" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -55893,34 +55904,31 @@
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="48" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="47" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="94" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="95" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="67" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="68" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="94" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="95" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -71244,7 +71252,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="37" type="noConversion"/>
+  <phoneticPr fontId="38" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="D46" r:id="rId1" location=":~:text=%D0%A1%D0%BE%D0%B7%D0%B4%D0%B0%D0%BD%D0%B8%D0%B5%20%D0%B1%D0%B0%D0%B7%D1%8B%20%D0%B4%D0%B0%D0%BD%D0%BD%D1%8B%D1%85" xr:uid="{FDFE2116-2B22-4A87-B37D-3DFA9E8F9FE0}"/>
     <hyperlink ref="D44" r:id="rId2" location=":~:text=%D0%A1%D0%BE%D0%B7%D0%B4%D0%B0%D0%BD%D0%B8%D0%B5%20%D0%B1%D0%B0%D0%B7%D1%8B%20%D0%B4%D0%B0%D0%BD%D0%BD%D1%8B%D1%85%20%D0%B2%20SQL%20Management%20Studio" xr:uid="{5B701F02-CEF7-44EA-83C6-0E21D7145608}"/>
@@ -77245,7 +77253,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="37" type="noConversion"/>
+  <phoneticPr fontId="38" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="D40" r:id="rId1" location=":~:text=%D0%94%D0%BB%D1%8F%20%D0%B3%D0%B5%D0%BD%D0%B5%D1%80%D0%B0%D1%86%D0%B8%D0%B8%20%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82%D0%B0%20UNIQUEIDENTIFIER" xr:uid="{8276130C-D262-49CA-89B1-D60C8C3E4E63}"/>
   </hyperlinks>

--- a/4 четверть_MSSQL.xlsx
+++ b/4 четверть_MSSQL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlexServHW\Desktop\GB_Developer_Workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A57485EE-D7C0-4BBD-933F-58D093D3EA9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81C4250A-7EA0-4C70-A2DD-B30527FCE26B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24" yWindow="1104" windowWidth="23016" windowHeight="11136" firstSheet="19" activeTab="25" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-1125" yWindow="-18030" windowWidth="23010" windowHeight="16845" firstSheet="19" activeTab="24" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Изучить" sheetId="21" r:id="rId1"/>
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2239" uniqueCount="1853">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2240" uniqueCount="1854">
   <si>
     <t>Урок 1 часть 1</t>
   </si>
@@ -54281,6 +54281,9 @@
       </rPr>
       <t>на точки в Alias</t>
     </r>
+  </si>
+  <si>
+    <t>Использовать в SELECT</t>
   </si>
 </sst>
 </file>
@@ -55080,7 +55083,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="22">
+  <fills count="23">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -55204,6 +55207,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1" tint="0.499984740745262"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -55363,7 +55372,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="193">
+  <cellXfs count="194">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -55929,6 +55938,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="95" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="45" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -67060,7 +67072,9 @@
       <c r="B4" s="2" t="s">
         <v>1546</v>
       </c>
-      <c r="C4" s="167"/>
+      <c r="C4" s="193" t="s">
+        <v>1853</v>
+      </c>
       <c r="D4" s="157"/>
     </row>
     <row r="5" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
@@ -71404,7 +71418,7 @@
       <c r="C10" s="9"/>
       <c r="D10" s="9"/>
     </row>
-    <row r="11" spans="1:22" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:22" ht="144" x14ac:dyDescent="0.3">
       <c r="A11" s="9"/>
       <c r="B11" s="108" t="s">
         <v>1253</v>

--- a/4 четверть_MSSQL.xlsx
+++ b/4 четверть_MSSQL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlexServHW\Desktop\GB_Developer_Workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81C4250A-7EA0-4C70-A2DD-B30527FCE26B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE220F5F-DE05-43FB-AD09-5B11EBE729C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-1125" yWindow="-18030" windowWidth="23010" windowHeight="16845" firstSheet="19" activeTab="24" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-8415" yWindow="-17610" windowWidth="23010" windowHeight="16845" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Изучить" sheetId="21" r:id="rId1"/>
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2240" uniqueCount="1854">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2255" uniqueCount="1868">
   <si>
     <t>Урок 1 часть 1</t>
   </si>
@@ -30232,31 +30232,6 @@
       <rPr>
         <b/>
         <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Пояснение!</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Табличные переменные (table variable) позволяют сохранить содержимое целой таблицы.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
         <color rgb="FF7030A0"/>
         <rFont val="Calibri"/>
         <family val="2"/>
@@ -30315,37 +30290,6 @@
         <scheme val="minor"/>
       </rPr>
       <t>@Abrends</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">INSERT INTO </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>@ABrends</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-VALUES
-(1, 'iPhone 8'),
-(2, 'Samsumg Galaxy S8')</t>
     </r>
   </si>
   <si>
@@ -54285,17 +54229,715 @@
   <si>
     <t>Использовать в SELECT</t>
   </si>
+  <si>
+    <t>INSERT INTO @selectTable (IdUser, UserName, UserMail, SMMEmailAccept, SMMTelegramAccept, SMMMaxAccept)
+SELECT [IdUser]
+      ,[UserName]
+      ,[UserMail]
+      ,[SMMEmailAccept]
+      ,[SMMTelegramAccept]
+      ,[SMMMaxAccept]
+FROM [LK_DATA].[dbo].[usr_Users]
+WHERE [UserMail] LIKE '%rassylka%'
+DECLARE @countRows INT = @@ROWCOUNT</t>
+  </si>
+  <si>
+    <t>DECLARE + TABLE</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Смотри!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> более подробно в </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>TABLE vars, CTE</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">DECLARE </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>@selectTable</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>TABLE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (
+    IdUser INT, 
+    UserName NVARCHAR(255),  -- или VARCHAR, в зависимости от ваших данных
+    UserMail NVARCHAR(255),
+    SMMEmailAccept BIT,      -- или INT, в зависимости от типа
+    SMMTelegramAccept BIT,
+    SMMMaxAccept INT
+)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>INSERT INTO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> @selectTable (IdUser, UserName, UserMail, SMMEmailAccept, SMMTelegramAccept, SMMMaxAccept)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SELECT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> [IdUser]
+      ,[UserName]
+      ,[UserMail]
+      ,[SMMEmailAccept]
+      ,[SMMTelegramAccept]
+      ,[SMMMaxAccept]
+FROM [LK_DATA].[dbo].[usr_Users]
+WHERE [UserMail] LIKE '%rassylka%'
+DECLARE @countRows INT = @@ROWCOUNT</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">INSERT INTO </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>@ABrends</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>VALUES</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+(1, 'iPhone 8'),
+(2, 'Samsumg Galaxy S8')</t>
+    </r>
+  </si>
+  <si>
+    <t>INSERT INTO + VALUES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Шаг 2
+</t>
+  </si>
+  <si>
+    <t>INSERT INTO + SELECT</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>DECLARE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>@selectTable</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>TABLE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (
+    IdUser INT, 
+    UserName NVARCHAR(255), 
+    UserMail NVARCHAR(255),
+    SMMEmailAccept BIT,  
+    SMMTelegramAccept BIT,
+    SMMMaxAccept INT
+)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>`-- Табличная переменная</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+DECLARE @selectTable TABLE (Id INT, Name NVARCHAR(100))
+INSERT INTO @selectTable VALUES (1, 'Test')
+GO </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> -- Здесь @selectTable уже не существует!
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>`-- Временная таблица</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+CREATE TABLE #ProductSummary (ProdId INT IDENTITY, ProdName NVARCHAR(20), Price MONEY)
+INSERT INTO #ProductSummary VALUES ('Test', 100)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>GO  -- #ProductSummary всё ещё существует</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SELECT * FROM #ProductSummary  -- Работает!</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Важно!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Табличные переменные (заданы через DECLARE) хранятся только в момент исполнения скрипта (до очередного GO)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Используйте Table Variable (@table), если:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1 Данных мало (&lt; 1000 строк)
+2 Нужно использовать в функциях (нельзя использовать временные таблицы)
+3 Нет сложных JOIN-ов
+4 Не нужны индексы кроме PRIMARY KEY</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Важно!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Временные таблицы (заданы через CREATE TABLE) хранятся в течение жизни всего скрипта .sql (между пакетами GO)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Используйте Temp Table (#table), если:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+1 Данных много (&gt; 1000 строк)
+2 Нужны сложные индексы для оптимизации
+3 Требуется точная статистика для оптимизатора
+4 Данные используются в нескольких вложенных процедурах
+5 Нужно передавать данные между разными пакетами (GO)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">В плане производительности являются более эффективным решением, чем </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>временные</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Основное пояснение!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> FK создаётся в зависимой таблице (child, например </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>usr_Users содержит данные всех пользователей</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">) и указывает на другую (parent, например </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>usr_AccountClassLib содержит маленький словарь типов пользователей</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Для случая ON DELETE / ON UPDATE - NO ACTION</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Таким образом удаление записи в parent таблице возможно только, если в child таблице отсутствует зависимое поле (например IdParent)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">ON DELETE / ON UPDATE - CASCADE </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(Очень осторожно! Почти никогда не используется)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Удалит все записи из child таблицы, которые идут с зависимым полем parent таблицы</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="96" x14ac:knownFonts="1">
+  <fonts count="97" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -55370,9 +56012,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="194">
+  <cellXfs count="199">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -55383,42 +56025,48 @@
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="37" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="38" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="37" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="38" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="37" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="37" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="37" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="37" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="40" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="49" fontId="36" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="36" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="36" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="36" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="49" fontId="35" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -55426,57 +56074,60 @@
     <xf numFmtId="49" fontId="35" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="34" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="35" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="34" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="35" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="34" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="35" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="34" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="34" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="46" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="45" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="44" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="54" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="55" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="34" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="35" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="45" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="46" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="57" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="58" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="39" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="40" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="45" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="46" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="36" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="37" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="34" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="33" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -55484,22 +56135,13 @@
     <xf numFmtId="49" fontId="32" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="31" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="58" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="57" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="45" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="46" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -55514,49 +56156,52 @@
     <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="30" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="29" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="40" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="62" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="29" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="48" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="28" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="63" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="58" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="58" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="49" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="62" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="57" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="57" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="48" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="45" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="46" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -55565,25 +56210,22 @@
     <xf numFmtId="49" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="24" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="23" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="24" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="23" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="54" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="55" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="39" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="40" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -55592,61 +56234,61 @@
     <xf numFmtId="49" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="23" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="24" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="48" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="49" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="50" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="51" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="23" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="52" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="23" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="22" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="22" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="51" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="40" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="22" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="45" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="45" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="21" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="40" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="44" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="44" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="22" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="21" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="22" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="21" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="22" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -55658,7 +56300,7 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="21" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="22" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -55676,59 +56318,65 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="39" fillId="17" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="40" fillId="17" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="52" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="53" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="52" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="53" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="68" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="69" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="20" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="21" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="58" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="58" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="85" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="86" fillId="9" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="55" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="40" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="57" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="57" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="84" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="85" fillId="9" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="54" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="45" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="20" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -55737,49 +56385,43 @@
     <xf numFmtId="49" fontId="19" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="40" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="18" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="17" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="17" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="17" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -55794,10 +56436,13 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="91" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="92" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -55806,93 +56451,90 @@
     <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="14" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="55" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="55" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="55" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="13" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="54" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="54" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="54" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="39" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="11" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="46" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="47" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="10" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="48" fillId="17" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="49" fillId="17" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="48" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="49" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="51" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="52" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -55910,37 +56552,52 @@
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="49" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="48" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="96" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="69" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="96" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="51" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="95" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="40" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="68" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="95" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="45" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -56559,13 +57216,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>163830</xdr:colOff>
-      <xdr:row>17</xdr:row>
+      <xdr:row>20</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>1085365</xdr:colOff>
-      <xdr:row>17</xdr:row>
+      <xdr:row>20</xdr:row>
       <xdr:rowOff>1038225</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -58894,32 +59551,32 @@
     <row r="14" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A14" s="9"/>
       <c r="B14" s="9"/>
-      <c r="C14" s="178" t="s">
-        <v>1812</v>
+      <c r="C14" s="177" t="s">
+        <v>1810</v>
       </c>
       <c r="D14" s="9"/>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A15" s="9"/>
       <c r="B15" s="42"/>
-      <c r="C15" s="179" t="s">
-        <v>1813</v>
-      </c>
-      <c r="D15" s="177"/>
+      <c r="C15" s="178" t="s">
+        <v>1811</v>
+      </c>
+      <c r="D15" s="176"/>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A16" s="9"/>
       <c r="B16" s="9"/>
-      <c r="C16" s="179" t="s">
-        <v>1814</v>
+      <c r="C16" s="178" t="s">
+        <v>1812</v>
       </c>
       <c r="D16" s="9"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="9"/>
       <c r="B17" s="9"/>
-      <c r="C17" s="179" t="s">
-        <v>1815</v>
+      <c r="C17" s="178" t="s">
+        <v>1813</v>
       </c>
       <c r="D17" s="9"/>
     </row>
@@ -58927,7 +59584,7 @@
       <c r="A18" s="9"/>
       <c r="B18" s="9"/>
       <c r="C18" s="122" t="s">
-        <v>1816</v>
+        <v>1814</v>
       </c>
       <c r="D18" s="9"/>
     </row>
@@ -58935,43 +59592,43 @@
       <c r="A19" s="9"/>
       <c r="B19" s="9"/>
       <c r="C19" s="9" t="s">
-        <v>1817</v>
+        <v>1815</v>
       </c>
       <c r="D19" s="147"/>
     </row>
     <row r="20" spans="1:4" ht="345.6" x14ac:dyDescent="0.3">
       <c r="A20" s="9"/>
       <c r="B20" s="122"/>
-      <c r="C20" s="180" t="s">
-        <v>1818</v>
+      <c r="C20" s="179" t="s">
+        <v>1816</v>
       </c>
       <c r="D20" s="9"/>
     </row>
     <row r="21" spans="1:4" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A21" s="9"/>
       <c r="B21" s="9"/>
-      <c r="C21" s="181" t="s">
-        <v>1819</v>
+      <c r="C21" s="180" t="s">
+        <v>1817</v>
       </c>
       <c r="D21" s="9"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="9"/>
       <c r="B22" s="9"/>
-      <c r="C22" s="167"/>
+      <c r="C22" s="166"/>
       <c r="D22" s="9"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="9"/>
       <c r="B23" s="9"/>
-      <c r="C23" s="167"/>
-      <c r="D23" s="167"/>
+      <c r="C23" s="166"/>
+      <c r="D23" s="166"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="9"/>
       <c r="B24" s="9"/>
       <c r="C24" s="147"/>
-      <c r="D24" s="167"/>
+      <c r="D24" s="166"/>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="9"/>
@@ -59185,13 +59842,13 @@
     </row>
     <row r="7" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A7" s="32" t="s">
-        <v>1421</v>
+        <v>1419</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1617</v>
-      </c>
-      <c r="C7" s="183" t="s">
-        <v>1616</v>
+        <v>1615</v>
+      </c>
+      <c r="C7" s="182" t="s">
+        <v>1614</v>
       </c>
       <c r="D7" s="69" t="s">
         <v>106</v>
@@ -59201,7 +59858,7 @@
       <c r="A8" s="77" t="s">
         <v>548</v>
       </c>
-      <c r="C8" s="157"/>
+      <c r="C8" s="156"/>
     </row>
     <row r="9" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A9" s="55"/>
@@ -59239,18 +59896,18 @@
     </row>
     <row r="13" spans="1:5" ht="129.6" x14ac:dyDescent="0.3">
       <c r="B13" s="2" t="s">
-        <v>1439</v>
+        <v>1437</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>1440</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="129.6" x14ac:dyDescent="0.3">
       <c r="B14" s="2" t="s">
-        <v>1823</v>
+        <v>1821</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
@@ -59368,15 +60025,15 @@
         <v>644</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1441</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="187.2" x14ac:dyDescent="0.3">
       <c r="B11" s="2" t="s">
-        <v>1444</v>
+        <v>1442</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1445</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
@@ -59515,28 +60172,28 @@
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A9" s="44" t="s">
-        <v>1766</v>
+        <v>1764</v>
       </c>
       <c r="C9" s="79"/>
       <c r="D9" s="1"/>
     </row>
     <row r="10" spans="1:22" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A10" s="79"/>
-      <c r="B10" s="167"/>
-      <c r="C10" s="183" t="s">
-        <v>1764</v>
+      <c r="B10" s="166"/>
+      <c r="C10" s="182" t="s">
+        <v>1762</v>
       </c>
       <c r="D10" s="1"/>
     </row>
     <row r="11" spans="1:22" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A11" s="167" t="s">
-        <v>1765</v>
-      </c>
-      <c r="B11" s="167" t="s">
-        <v>1783</v>
-      </c>
-      <c r="C11" s="167" t="s">
-        <v>1784</v>
+      <c r="A11" s="166" t="s">
+        <v>1763</v>
+      </c>
+      <c r="B11" s="166" t="s">
+        <v>1781</v>
+      </c>
+      <c r="C11" s="166" t="s">
+        <v>1782</v>
       </c>
       <c r="D11" s="1"/>
     </row>
@@ -59563,7 +60220,7 @@
     <row r="14" spans="1:22" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A14" s="9"/>
       <c r="B14" s="128" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
       <c r="C14" s="66" t="s">
         <v>508</v>
@@ -59592,7 +60249,7 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="34" t="s">
-        <v>1509</v>
+        <v>1507</v>
       </c>
       <c r="B17" s="66"/>
       <c r="C17" s="66"/>
@@ -59602,28 +60259,28 @@
     </row>
     <row r="18" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A18" s="72" t="s">
-        <v>1513</v>
+        <v>1511</v>
       </c>
       <c r="B18" s="147" t="s">
-        <v>1510</v>
+        <v>1508</v>
       </c>
       <c r="C18" s="147" t="s">
-        <v>1511</v>
+        <v>1509</v>
       </c>
       <c r="D18" s="147" t="s">
-        <v>1498</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="A19" s="2"/>
       <c r="C19" s="147" t="s">
-        <v>1512</v>
+        <v>1510</v>
       </c>
       <c r="D19" s="147"/>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="34" t="s">
-        <v>1514</v>
+        <v>1512</v>
       </c>
       <c r="B20" s="147"/>
       <c r="C20" s="147"/>
@@ -59633,26 +60290,26 @@
     </row>
     <row r="21" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A21" s="72" t="s">
-        <v>1527</v>
+        <v>1525</v>
       </c>
       <c r="C21" s="147" t="s">
-        <v>1515</v>
+        <v>1513</v>
       </c>
       <c r="D21" s="147" t="s">
-        <v>1498</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="A22" s="2"/>
       <c r="B22" s="147"/>
       <c r="C22" s="152" t="s">
-        <v>1516</v>
+        <v>1514</v>
       </c>
       <c r="D22" s="147"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="34" t="s">
-        <v>1517</v>
+        <v>1515</v>
       </c>
       <c r="B23" s="147"/>
       <c r="C23" s="147"/>
@@ -59662,28 +60319,28 @@
     </row>
     <row r="24" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A24" s="72" t="s">
-        <v>1526</v>
+        <v>1524</v>
       </c>
       <c r="C24" s="147" t="s">
-        <v>1521</v>
+        <v>1519</v>
       </c>
       <c r="D24" s="147" t="s">
-        <v>1498</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A25" s="2"/>
       <c r="B25" s="147" t="s">
-        <v>1519</v>
+        <v>1517</v>
       </c>
       <c r="C25" s="147" t="s">
-        <v>1518</v>
+        <v>1516</v>
       </c>
       <c r="D25" s="147"/>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="34" t="s">
-        <v>1520</v>
+        <v>1518</v>
       </c>
       <c r="B26" s="147"/>
       <c r="C26" s="147"/>
@@ -59693,31 +60350,31 @@
     </row>
     <row r="27" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A27" s="72" t="s">
-        <v>1525</v>
+        <v>1523</v>
       </c>
       <c r="C27" s="147" t="s">
-        <v>1524</v>
+        <v>1522</v>
       </c>
       <c r="D27" s="147" t="s">
-        <v>1498</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="144" x14ac:dyDescent="0.3">
       <c r="A28" s="2"/>
       <c r="B28" s="147" t="s">
-        <v>1523</v>
+        <v>1521</v>
       </c>
       <c r="C28" s="147" t="s">
-        <v>1522</v>
+        <v>1520</v>
       </c>
       <c r="D28" s="147"/>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="34" t="s">
-        <v>1528</v>
+        <v>1526</v>
       </c>
       <c r="B29" s="72" t="s">
-        <v>1540</v>
+        <v>1538</v>
       </c>
       <c r="C29" s="147"/>
       <c r="D29" s="151" t="s">
@@ -59726,44 +60383,44 @@
     </row>
     <row r="30" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A30" s="72" t="s">
-        <v>1533</v>
+        <v>1531</v>
       </c>
       <c r="B30" s="152" t="s">
-        <v>1532</v>
+        <v>1530</v>
       </c>
       <c r="C30" s="152" t="s">
-        <v>1529</v>
+        <v>1527</v>
       </c>
       <c r="D30" s="147" t="s">
-        <v>1498</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A31" s="2"/>
       <c r="B31" s="152" t="s">
-        <v>1531</v>
+        <v>1529</v>
       </c>
       <c r="C31" s="152" t="s">
-        <v>1538</v>
+        <v>1536</v>
       </c>
       <c r="D31" s="147"/>
     </row>
     <row r="32" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A32" s="2"/>
       <c r="B32" s="152" t="s">
-        <v>1530</v>
+        <v>1528</v>
       </c>
       <c r="C32" s="152" t="s">
-        <v>1534</v>
+        <v>1532</v>
       </c>
       <c r="D32" s="147"/>
     </row>
     <row r="33" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A33" s="34" t="s">
-        <v>1535</v>
+        <v>1533</v>
       </c>
       <c r="B33" s="72" t="s">
-        <v>1540</v>
+        <v>1538</v>
       </c>
       <c r="C33" s="152"/>
       <c r="D33" s="151" t="s">
@@ -59772,21 +60429,21 @@
     </row>
     <row r="34" spans="1:22" ht="72" x14ac:dyDescent="0.3">
       <c r="A34" s="72" t="s">
-        <v>1541</v>
+        <v>1539</v>
       </c>
       <c r="B34" s="152"/>
       <c r="C34" s="152" t="s">
-        <v>1536</v>
+        <v>1534</v>
       </c>
       <c r="D34" s="151"/>
     </row>
     <row r="35" spans="1:22" ht="144" x14ac:dyDescent="0.3">
       <c r="A35" s="2"/>
       <c r="B35" s="152" t="s">
+        <v>1535</v>
+      </c>
+      <c r="C35" s="152" t="s">
         <v>1537</v>
-      </c>
-      <c r="C35" s="152" t="s">
-        <v>1539</v>
       </c>
       <c r="D35" s="151"/>
     </row>
@@ -60453,23 +61110,23 @@
     <row r="4" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A4" s="18"/>
       <c r="B4" s="9"/>
-      <c r="C4" s="176" t="s">
-        <v>1824</v>
+      <c r="C4" s="175" t="s">
+        <v>1822</v>
       </c>
       <c r="D4" s="9"/>
     </row>
     <row r="5" spans="1:22" s="2" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="B5" s="167" t="s">
+      <c r="B5" s="166" t="s">
+        <v>1798</v>
+      </c>
+      <c r="C5" s="166" t="s">
         <v>1800</v>
       </c>
-      <c r="C5" s="167" t="s">
-        <v>1802</v>
-      </c>
       <c r="E5" s="7"/>
     </row>
     <row r="6" spans="1:22" s="2" customFormat="1" ht="345.6" x14ac:dyDescent="0.3">
-      <c r="C6" s="167" t="s">
-        <v>1801</v>
+      <c r="C6" s="166" t="s">
+        <v>1799</v>
       </c>
       <c r="E6" s="7"/>
     </row>
@@ -61061,7 +61718,7 @@
     </row>
     <row r="42" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B42" s="72" t="s">
-        <v>1506</v>
+        <v>1504</v>
       </c>
       <c r="C42" s="66" t="s">
         <v>604</v>
@@ -61073,7 +61730,7 @@
     </row>
     <row r="43" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B43" s="72" t="s">
-        <v>1505</v>
+        <v>1503</v>
       </c>
       <c r="C43" s="66" t="s">
         <v>603</v>
@@ -61093,7 +61750,7 @@
     </row>
     <row r="45" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A45" s="70" t="s">
-        <v>1507</v>
+        <v>1505</v>
       </c>
       <c r="C45" s="66"/>
       <c r="P45" s="1"/>
@@ -61102,10 +61759,10 @@
     </row>
     <row r="46" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
+        <v>1499</v>
+      </c>
+      <c r="C46" s="2" t="s">
         <v>1501</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>1503</v>
       </c>
       <c r="P46" s="1"/>
       <c r="U46" s="1"/>
@@ -61113,13 +61770,13 @@
     </row>
     <row r="47" spans="1:22" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
+        <v>1500</v>
+      </c>
+      <c r="B47" s="147" t="s">
+        <v>1498</v>
+      </c>
+      <c r="C47" s="147" t="s">
         <v>1502</v>
-      </c>
-      <c r="B47" s="147" t="s">
-        <v>1500</v>
-      </c>
-      <c r="C47" s="147" t="s">
-        <v>1504</v>
       </c>
       <c r="P47" s="1"/>
       <c r="U47" s="1"/>
@@ -61469,13 +62126,13 @@
       <c r="A77" s="83" t="s">
         <v>775</v>
       </c>
-      <c r="B77" s="182" t="s">
-        <v>1821</v>
-      </c>
-      <c r="C77" s="182" t="s">
-        <v>1820</v>
-      </c>
-      <c r="D77" s="182" t="s">
+      <c r="B77" s="181" t="s">
+        <v>1819</v>
+      </c>
+      <c r="C77" s="181" t="s">
+        <v>1818</v>
+      </c>
+      <c r="D77" s="181" t="s">
         <v>188</v>
       </c>
     </row>
@@ -61487,35 +62144,35 @@
         <v>151</v>
       </c>
       <c r="C78" s="149" t="s">
-        <v>1477</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="79" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A79" s="34" t="s">
-        <v>1492</v>
+        <v>1490</v>
       </c>
       <c r="C79" s="2"/>
     </row>
     <row r="80" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
+        <v>1491</v>
+      </c>
+      <c r="C80" s="2" t="s">
         <v>1493</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>1495</v>
       </c>
     </row>
     <row r="81" spans="1:22" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
+        <v>1492</v>
+      </c>
+      <c r="B81" s="147" t="s">
+        <v>1497</v>
+      </c>
+      <c r="C81" s="147" t="s">
         <v>1494</v>
       </c>
-      <c r="B81" s="147" t="s">
-        <v>1499</v>
-      </c>
-      <c r="C81" s="147" t="s">
+      <c r="D81" s="147" t="s">
         <v>1496</v>
-      </c>
-      <c r="D81" s="147" t="s">
-        <v>1498</v>
       </c>
       <c r="E81" s="150" t="s">
         <v>106</v>
@@ -61523,7 +62180,7 @@
     </row>
     <row r="82" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A82" s="34" t="s">
-        <v>1497</v>
+        <v>1495</v>
       </c>
       <c r="C82" s="147"/>
     </row>
@@ -61532,10 +62189,10 @@
         <v>152</v>
       </c>
       <c r="B83" s="147" t="s">
-        <v>1481</v>
+        <v>1479</v>
       </c>
       <c r="C83" s="147" t="s">
-        <v>1491</v>
+        <v>1489</v>
       </c>
       <c r="D83" s="19" t="s">
         <v>153</v>
@@ -61546,10 +62203,10 @@
         <v>154</v>
       </c>
       <c r="B84" s="147" t="s">
+        <v>1478</v>
+      </c>
+      <c r="C84" s="147" t="s">
         <v>1480</v>
-      </c>
-      <c r="C84" s="147" t="s">
-        <v>1482</v>
       </c>
       <c r="D84" s="1"/>
       <c r="F84" s="1"/>
@@ -61573,10 +62230,10 @@
         <v>155</v>
       </c>
       <c r="B85" s="147" t="s">
-        <v>1478</v>
+        <v>1476</v>
       </c>
       <c r="C85" s="147" t="s">
-        <v>1483</v>
+        <v>1481</v>
       </c>
       <c r="D85" s="1"/>
       <c r="F85" s="1"/>
@@ -61600,10 +62257,10 @@
         <v>156</v>
       </c>
       <c r="B86" s="147" t="s">
-        <v>1488</v>
+        <v>1486</v>
       </c>
       <c r="C86" s="147" t="s">
-        <v>1484</v>
+        <v>1482</v>
       </c>
       <c r="D86" s="1"/>
       <c r="F86" s="1"/>
@@ -61627,10 +62284,10 @@
         <v>157</v>
       </c>
       <c r="B87" s="147" t="s">
-        <v>1489</v>
+        <v>1487</v>
       </c>
       <c r="C87" s="147" t="s">
-        <v>1485</v>
+        <v>1483</v>
       </c>
       <c r="D87" s="1"/>
       <c r="F87" s="1"/>
@@ -61654,10 +62311,10 @@
         <v>158</v>
       </c>
       <c r="B88" s="147" t="s">
-        <v>1490</v>
+        <v>1488</v>
       </c>
       <c r="C88" s="147" t="s">
-        <v>1486</v>
+        <v>1484</v>
       </c>
       <c r="D88" s="1"/>
       <c r="F88" s="1"/>
@@ -61681,10 +62338,10 @@
         <v>159</v>
       </c>
       <c r="B89" s="147" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
       <c r="C89" s="147" t="s">
-        <v>1487</v>
+        <v>1485</v>
       </c>
       <c r="D89" s="1"/>
       <c r="F89" s="1"/>
@@ -64108,56 +64765,56 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="184" t="s">
+      <c r="A2" s="183" t="s">
         <v>650</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="184" t="s">
+      <c r="A3" s="183" t="s">
         <v>651</v>
       </c>
       <c r="C3" s="66"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="184" t="s">
+      <c r="A4" s="183" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="184" t="s">
+      <c r="A5" s="183" t="s">
         <v>653</v>
       </c>
       <c r="C5" s="66"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="184" t="s">
+      <c r="A6" s="183" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="184" t="s">
-        <v>1767</v>
+      <c r="A7" s="183" t="s">
+        <v>1765</v>
       </c>
       <c r="C7" s="66"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="184" t="s">
-        <v>1770</v>
+      <c r="A8" s="183" t="s">
+        <v>1768</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="184" t="s">
-        <v>1773</v>
+      <c r="A9" s="183" t="s">
+        <v>1771</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="184" t="s">
-        <v>1776</v>
+      <c r="A10" s="183" t="s">
+        <v>1774</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="184" t="s">
-        <v>1785</v>
+      <c r="A11" s="183" t="s">
+        <v>1783</v>
       </c>
     </row>
     <row r="13" spans="1:5" s="45" customFormat="1" x14ac:dyDescent="0.3">
@@ -64383,62 +65040,62 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="77" t="s">
-        <v>1767</v>
+        <v>1765</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="66"/>
       <c r="B37" s="66" t="s">
-        <v>1768</v>
+        <v>1766</v>
       </c>
       <c r="C37" s="66" t="s">
-        <v>1769</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="77" t="s">
-        <v>1770</v>
+        <v>1768</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="66"/>
       <c r="B39" s="66" t="s">
-        <v>1771</v>
+        <v>1769</v>
       </c>
       <c r="C39" s="66" t="s">
-        <v>1772</v>
+        <v>1770</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="77" t="s">
-        <v>1773</v>
+        <v>1771</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="66"/>
       <c r="B41" s="66" t="s">
-        <v>1774</v>
+        <v>1772</v>
       </c>
       <c r="C41" s="66" t="s">
-        <v>1775</v>
+        <v>1773</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="77" t="s">
-        <v>1776</v>
+        <v>1774</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B43" s="66" t="s">
-        <v>1777</v>
+        <v>1775</v>
       </c>
       <c r="C43" s="66" t="s">
-        <v>1778</v>
+        <v>1776</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="77" t="s">
-        <v>1785</v>
+        <v>1783</v>
       </c>
       <c r="D44" s="69" t="s">
         <v>106</v>
@@ -64446,26 +65103,26 @@
     </row>
     <row r="45" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
       <c r="B45" s="2" t="s">
-        <v>1786</v>
+        <v>1784</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>1789</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B46" s="2" t="s">
-        <v>1787</v>
+        <v>1785</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>1788</v>
+        <v>1786</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
       <c r="B47" s="2" t="s">
-        <v>1791</v>
+        <v>1789</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>1790</v>
+        <v>1788</v>
       </c>
     </row>
   </sheetData>
@@ -64526,7 +65183,7 @@
     </row>
     <row r="3" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A3" s="133" t="s">
-        <v>1400</v>
+        <v>1398</v>
       </c>
       <c r="B3" s="90"/>
       <c r="C3" s="134"/>
@@ -64534,7 +65191,7 @@
     </row>
     <row r="4" spans="1:5" ht="144" x14ac:dyDescent="0.3">
       <c r="A4" s="99" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="C4" s="128"/>
       <c r="D4" s="94"/>
@@ -64543,33 +65200,33 @@
       <c r="A5" s="95"/>
       <c r="B5" s="135"/>
       <c r="C5" s="136" t="s">
-        <v>1402</v>
+        <v>1400</v>
       </c>
       <c r="D5" s="98"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="170" t="s">
-        <v>1779</v>
-      </c>
-      <c r="B6" s="171" t="s">
-        <v>1780</v>
-      </c>
-      <c r="C6" s="169"/>
+      <c r="A6" s="169" t="s">
+        <v>1777</v>
+      </c>
+      <c r="B6" s="170" t="s">
+        <v>1778</v>
+      </c>
+      <c r="C6" s="168"/>
       <c r="D6" s="94"/>
     </row>
     <row r="7" spans="1:5" ht="231" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="102"/>
-      <c r="B7" s="173" t="s">
-        <v>1782</v>
-      </c>
-      <c r="C7" s="172" t="s">
-        <v>1781</v>
+      <c r="B7" s="172" t="s">
+        <v>1780</v>
+      </c>
+      <c r="C7" s="171" t="s">
+        <v>1779</v>
       </c>
       <c r="D7" s="94"/>
     </row>
     <row r="8" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="133" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="B8" s="90"/>
       <c r="C8" s="134"/>
@@ -64577,37 +65234,37 @@
     </row>
     <row r="9" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A9" s="102" t="s">
+        <v>1402</v>
+      </c>
+      <c r="B9" s="128" t="s">
+        <v>1403</v>
+      </c>
+      <c r="C9" s="128" t="s">
         <v>1404</v>
-      </c>
-      <c r="B9" s="128" t="s">
-        <v>1405</v>
-      </c>
-      <c r="C9" s="128" t="s">
-        <v>1406</v>
       </c>
       <c r="D9" s="94"/>
     </row>
     <row r="10" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A10" s="102" t="s">
+        <v>1405</v>
+      </c>
+      <c r="B10" s="128" t="s">
+        <v>1406</v>
+      </c>
+      <c r="C10" s="128" t="s">
         <v>1407</v>
-      </c>
-      <c r="B10" s="128" t="s">
-        <v>1408</v>
-      </c>
-      <c r="C10" s="128" t="s">
-        <v>1409</v>
       </c>
       <c r="D10" s="94"/>
     </row>
     <row r="11" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A11" s="102" t="s">
+        <v>1408</v>
+      </c>
+      <c r="B11" s="128" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C11" s="128" t="s">
         <v>1410</v>
-      </c>
-      <c r="B11" s="128" t="s">
-        <v>1411</v>
-      </c>
-      <c r="C11" s="128" t="s">
-        <v>1412</v>
       </c>
       <c r="D11" s="94"/>
     </row>
@@ -64623,38 +65280,38 @@
       <c r="A13" s="140"/>
       <c r="B13" s="141"/>
       <c r="C13" s="141" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
       <c r="D13" s="142"/>
     </row>
     <row r="14" spans="1:5" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A14" s="143" t="s">
+        <v>1412</v>
+      </c>
+      <c r="B14" s="128" t="s">
+        <v>1413</v>
+      </c>
+      <c r="C14" s="128" t="s">
         <v>1414</v>
-      </c>
-      <c r="B14" s="128" t="s">
-        <v>1415</v>
-      </c>
-      <c r="C14" s="128" t="s">
-        <v>1416</v>
       </c>
       <c r="D14" s="94"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="143" t="s">
-        <v>1417</v>
+        <v>1415</v>
       </c>
       <c r="C15" s="128"/>
       <c r="D15" s="94"/>
     </row>
     <row r="16" spans="1:5" ht="173.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="136" t="s">
+        <v>1416</v>
+      </c>
+      <c r="B16" s="136" t="s">
+        <v>1417</v>
+      </c>
+      <c r="C16" s="136" t="s">
         <v>1418</v>
-      </c>
-      <c r="B16" s="136" t="s">
-        <v>1419</v>
-      </c>
-      <c r="C16" s="136" t="s">
-        <v>1420</v>
       </c>
       <c r="D16" s="98"/>
     </row>
@@ -64708,7 +65365,7 @@
         <v>678</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1759</v>
+        <v>1757</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
@@ -64716,7 +65373,7 @@
         <v>735</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>1760</v>
+        <v>1758</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
@@ -64724,7 +65381,7 @@
         <v>694</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1761</v>
+        <v>1759</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
@@ -64732,7 +65389,7 @@
         <v>711</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1758</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="45" customFormat="1" x14ac:dyDescent="0.3">
@@ -64747,7 +65404,7 @@
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="C10" s="167" t="s">
+      <c r="C10" s="166" t="s">
         <v>684</v>
       </c>
     </row>
@@ -64803,7 +65460,7 @@
       </c>
     </row>
     <row r="17" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="C17" s="167" t="s">
+      <c r="C17" s="166" t="s">
         <v>687</v>
       </c>
     </row>
@@ -64848,7 +65505,7 @@
       </c>
     </row>
     <row r="24" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="C24" s="167" t="s">
+      <c r="C24" s="166" t="s">
         <v>695</v>
       </c>
     </row>
@@ -64923,7 +65580,7 @@
       <c r="B34" s="2" t="s">
         <v>712</v>
       </c>
-      <c r="C34" s="167" t="s">
+      <c r="C34" s="166" t="s">
         <v>713</v>
       </c>
     </row>
@@ -66031,15 +66688,15 @@
         <v>915</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>1762</v>
+        <v>1760</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>1763</v>
+        <v>1761</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="86.4" x14ac:dyDescent="0.3">
       <c r="B41" s="2" t="s">
-        <v>1757</v>
+        <v>1755</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>71</v>
@@ -67046,77 +67703,77 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="D1" s="167"/>
+      <c r="D1" s="166"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="189" t="s">
+      <c r="A2" s="188" t="s">
+        <v>1843</v>
+      </c>
+      <c r="B2" s="189" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="188" t="s">
+        <v>1844</v>
+      </c>
+      <c r="B3" s="189" t="s">
         <v>1845</v>
       </c>
-      <c r="B2" s="190" t="s">
-        <v>1848</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="189" t="s">
-        <v>1846</v>
-      </c>
-      <c r="B3" s="190" t="s">
-        <v>1847</v>
-      </c>
-      <c r="D3" s="186"/>
+      <c r="D3" s="185"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="191" t="s">
-        <v>1596</v>
+      <c r="A4" s="190" t="s">
+        <v>1594</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1546</v>
-      </c>
-      <c r="C4" s="193" t="s">
-        <v>1853</v>
-      </c>
-      <c r="D4" s="157"/>
+        <v>1544</v>
+      </c>
+      <c r="C4" s="192" t="s">
+        <v>1851</v>
+      </c>
+      <c r="D4" s="156"/>
     </row>
     <row r="5" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A5" s="191" t="s">
-        <v>1555</v>
+      <c r="A5" s="190" t="s">
+        <v>1553</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1718</v>
-      </c>
-      <c r="D5" s="157"/>
+        <v>1716</v>
+      </c>
+      <c r="D5" s="156"/>
     </row>
     <row r="6" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A6" s="191" t="s">
-        <v>1652</v>
+      <c r="A6" s="190" t="s">
+        <v>1650</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1717</v>
-      </c>
-      <c r="D6" s="157"/>
-    </row>
-    <row r="7" spans="1:5" s="187" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="D7" s="188"/>
+        <v>1715</v>
+      </c>
+      <c r="D6" s="156"/>
+    </row>
+    <row r="7" spans="1:5" s="186" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="D7" s="187"/>
     </row>
     <row r="8" spans="1:5" s="45" customFormat="1" x14ac:dyDescent="0.3">
       <c r="E8" s="46"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="C9" s="48" t="s">
-        <v>1421</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="189" t="s">
-        <v>1845</v>
-      </c>
-      <c r="B10" s="186" t="s">
-        <v>1844</v>
+      <c r="A10" s="188" t="s">
+        <v>1843</v>
+      </c>
+      <c r="B10" s="185" t="s">
+        <v>1842</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="153" t="s">
-        <v>1553</v>
+        <v>1551</v>
       </c>
       <c r="D11" s="69" t="s">
         <v>106</v>
@@ -67124,346 +67781,346 @@
     </row>
     <row r="12" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C12" s="2" t="s">
-        <v>1554</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="168" t="s">
-        <v>1719</v>
+      <c r="A13" s="167" t="s">
+        <v>1717</v>
       </c>
       <c r="B13" s="25" t="s">
-        <v>1742</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="172.8" x14ac:dyDescent="0.3">
-      <c r="A14" s="163" t="s">
-        <v>1726</v>
+      <c r="A14" s="162" t="s">
+        <v>1724</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>1720</v>
+      </c>
+      <c r="C14" s="162" t="s">
         <v>1722</v>
       </c>
-      <c r="C14" s="163" t="s">
-        <v>1724</v>
-      </c>
     </row>
     <row r="15" spans="1:5" ht="144" x14ac:dyDescent="0.3">
-      <c r="A15" s="163" t="s">
+      <c r="A15" s="162" t="s">
+        <v>1737</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>1721</v>
+      </c>
+      <c r="C15" s="162" t="s">
         <v>1739</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>1723</v>
-      </c>
-      <c r="C15" s="163" t="s">
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="167" t="s">
+        <v>1718</v>
+      </c>
+      <c r="B16" s="112" t="s">
         <v>1741</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="168" t="s">
-        <v>1720</v>
-      </c>
-      <c r="B16" s="112" t="s">
-        <v>1743</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A17" s="66"/>
       <c r="B17" s="66"/>
       <c r="C17" s="2" t="s">
-        <v>1721</v>
+        <v>1719</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>1558</v>
+        <v>1556</v>
       </c>
       <c r="B18" s="66" t="s">
         <v>436</v>
       </c>
-      <c r="C18" s="167" t="s">
-        <v>1745</v>
+      <c r="C18" s="166" t="s">
+        <v>1743</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>1558</v>
+        <v>1556</v>
       </c>
       <c r="B19" s="66" t="s">
         <v>440</v>
       </c>
-      <c r="C19" s="167" t="s">
+      <c r="C19" s="166" t="s">
+        <v>1742</v>
+      </c>
+      <c r="D19" s="166"/>
+    </row>
+    <row r="20" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A20" s="162" t="s">
+        <v>1736</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>1726</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>1744</v>
       </c>
-      <c r="D19" s="167"/>
-    </row>
-    <row r="20" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A20" s="163" t="s">
-        <v>1738</v>
-      </c>
-      <c r="B20" s="2" t="s">
+    </row>
+    <row r="21" spans="1:4" ht="201.6" x14ac:dyDescent="0.3">
+      <c r="A21" s="162" t="s">
+        <v>1736</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>1735</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>1723</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="345.6" x14ac:dyDescent="0.3">
+      <c r="A22" s="162" t="s">
+        <v>1736</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>1727</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>1725</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" s="160" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A24" s="166" t="s">
+        <v>1750</v>
+      </c>
+      <c r="B24" s="166" t="s">
+        <v>1752</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>1751</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" s="167" t="s">
         <v>1728</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>1746</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="201.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="163" t="s">
-        <v>1738</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>1737</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>1725</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="345.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="163" t="s">
-        <v>1738</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>1729</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>1727</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="161" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A24" s="167" t="s">
-        <v>1752</v>
-      </c>
-      <c r="B24" s="167" t="s">
-        <v>1754</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>1753</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="168" t="s">
-        <v>1730</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>1734</v>
+        <v>1732</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>1733</v>
+        <v>1731</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>1731</v>
-      </c>
-      <c r="D26" s="163" t="s">
-        <v>1732</v>
+        <v>1729</v>
+      </c>
+      <c r="D26" s="162" t="s">
+        <v>1730</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>1735</v>
+        <v>1733</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>1736</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>1740</v>
+        <v>1738</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>1748</v>
+        <v>1746</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>1747</v>
+        <v>1745</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
+        <v>1747</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>1748</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="244.8" x14ac:dyDescent="0.3">
+      <c r="A30" s="166" t="s">
         <v>1749</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>1750</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" ht="244.8" x14ac:dyDescent="0.3">
-      <c r="A30" s="167" t="s">
-        <v>1751</v>
-      </c>
       <c r="B30" s="2" t="s">
-        <v>1756</v>
-      </c>
-      <c r="C30" s="167" t="s">
-        <v>1755</v>
+        <v>1754</v>
+      </c>
+      <c r="C30" s="166" t="s">
+        <v>1753</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A31" s="189" t="s">
-        <v>1846</v>
+      <c r="A31" s="188" t="s">
+        <v>1844</v>
       </c>
       <c r="B31" s="152"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="153" t="s">
-        <v>1544</v>
-      </c>
-      <c r="C32" s="157" t="s">
-        <v>1583</v>
+        <v>1542</v>
+      </c>
+      <c r="C32" s="156" t="s">
+        <v>1581</v>
       </c>
       <c r="D32" s="117" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="144" x14ac:dyDescent="0.3">
-      <c r="A33" s="162" t="s">
+      <c r="A33" s="161" t="s">
         <v>332</v>
       </c>
-      <c r="B33" s="186" t="s">
-        <v>1843</v>
+      <c r="B33" s="185" t="s">
+        <v>1841</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>1562</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A34" s="162" t="s">
+      <c r="A34" s="161" t="s">
         <v>1190</v>
       </c>
-      <c r="B34" s="186" t="s">
-        <v>1842</v>
+      <c r="B34" s="185" t="s">
+        <v>1840</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A35" s="166" t="s">
-        <v>1841</v>
-      </c>
-      <c r="B35" s="163" t="s">
-        <v>1700</v>
+      <c r="A35" s="165" t="s">
+        <v>1839</v>
+      </c>
+      <c r="B35" s="162" t="s">
+        <v>1698</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>1699</v>
+        <v>1697</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="153" t="s">
-        <v>1545</v>
+        <v>1543</v>
       </c>
       <c r="D36" s="69"/>
     </row>
     <row r="37" spans="1:4" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
+        <v>1565</v>
+      </c>
+      <c r="B37" s="2" t="s">
         <v>1567</v>
       </c>
-      <c r="B37" s="2" t="s">
-        <v>1569</v>
-      </c>
-      <c r="C37" s="157" t="s">
-        <v>1582</v>
+      <c r="C37" s="156" t="s">
+        <v>1580</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>1568</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>1811</v>
+        <v>1809</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>1810</v>
-      </c>
-      <c r="C38" s="157"/>
+        <v>1808</v>
+      </c>
+      <c r="C38" s="156"/>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="153" t="s">
-        <v>1547</v>
+        <v>1545</v>
       </c>
       <c r="D39" s="69" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A40" s="162" t="s">
+      <c r="A40" s="161" t="s">
         <v>332</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>1632</v>
+        <v>1630</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>1619</v>
+        <v>1617</v>
       </c>
       <c r="D40" s="69"/>
     </row>
     <row r="41" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A41"/>
       <c r="B41" s="2" t="s">
-        <v>1631</v>
+        <v>1629</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>1620</v>
+        <v>1618</v>
       </c>
       <c r="D41" s="69"/>
     </row>
     <row r="42" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A42"/>
       <c r="B42" s="2" t="s">
-        <v>1630</v>
+        <v>1628</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>1621</v>
+        <v>1619</v>
       </c>
       <c r="D42" s="69"/>
     </row>
     <row r="43" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A43"/>
       <c r="B43" s="2" t="s">
-        <v>1629</v>
+        <v>1627</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>1622</v>
+        <v>1620</v>
       </c>
       <c r="D43" s="69"/>
     </row>
     <row r="44" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A44"/>
       <c r="B44" s="2" t="s">
-        <v>1628</v>
+        <v>1626</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="D44" s="69"/>
     </row>
     <row r="45" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A45"/>
       <c r="B45" s="2" t="s">
-        <v>1627</v>
+        <v>1625</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>1624</v>
+        <v>1622</v>
       </c>
       <c r="D45" s="69"/>
     </row>
     <row r="46" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="A46"/>
       <c r="B46" s="2" t="s">
-        <v>1626</v>
+        <v>1624</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>1625</v>
+        <v>1623</v>
       </c>
       <c r="D46" s="69"/>
     </row>
     <row r="47" spans="1:4" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A47"/>
       <c r="B47" s="2" t="s">
-        <v>1633</v>
+        <v>1631</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>1634</v>
+        <v>1632</v>
       </c>
       <c r="D47" s="69"/>
     </row>
@@ -67471,17 +68128,17 @@
       <c r="A48" t="s">
         <v>1190</v>
       </c>
-      <c r="B48" s="163" t="s">
-        <v>1701</v>
+      <c r="B48" s="162" t="s">
+        <v>1699</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>1699</v>
+        <v>1697</v>
       </c>
       <c r="D48" s="69"/>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="153" t="s">
-        <v>1548</v>
+        <v>1546</v>
       </c>
       <c r="D49" s="69" t="s">
         <v>106</v>
@@ -67489,52 +68146,52 @@
     </row>
     <row r="50" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B50" s="2" t="s">
-        <v>1635</v>
+        <v>1633</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>1636</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="B51" s="2" t="s">
-        <v>1637</v>
+        <v>1635</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>1638</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B52" s="2" t="s">
-        <v>1639</v>
+        <v>1637</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>1640</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B53" s="2" t="s">
-        <v>1641</v>
+        <v>1639</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>1642</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="158.4" x14ac:dyDescent="0.3">
       <c r="B54" s="2" t="s">
-        <v>1643</v>
+        <v>1641</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>1644</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="47" t="s">
-        <v>1596</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="153" t="s">
-        <v>1546</v>
+        <v>1544</v>
       </c>
       <c r="D56" s="69" t="s">
         <v>106</v>
@@ -67543,85 +68200,85 @@
     <row r="57" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A57"/>
       <c r="B57" s="2" t="s">
+        <v>1583</v>
+      </c>
+      <c r="C57" s="156" t="s">
+        <v>1582</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A58" s="158" t="s">
+        <v>1601</v>
+      </c>
+      <c r="C58" s="156"/>
+    </row>
+    <row r="59" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="A59" s="156" t="s">
+        <v>1589</v>
+      </c>
+      <c r="B59" s="157" t="s">
+        <v>1595</v>
+      </c>
+      <c r="C59" s="156" t="s">
+        <v>1587</v>
+      </c>
+      <c r="D59" s="156" t="s">
+        <v>1605</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A60" s="156" t="s">
+        <v>1590</v>
+      </c>
+      <c r="B60" s="157" t="s">
+        <v>1599</v>
+      </c>
+      <c r="C60" s="156" t="s">
+        <v>1588</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A61" s="156" t="s">
+        <v>1591</v>
+      </c>
+      <c r="B61" s="157" t="s">
+        <v>1596</v>
+      </c>
+      <c r="C61" s="156" t="s">
+        <v>1584</v>
+      </c>
+      <c r="D61" s="156" t="s">
+        <v>1605</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A62" s="156" t="s">
+        <v>1592</v>
+      </c>
+      <c r="B62" s="157" t="s">
+        <v>1598</v>
+      </c>
+      <c r="C62" s="156" t="s">
         <v>1585</v>
       </c>
-      <c r="C57" s="157" t="s">
-        <v>1584</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A58" s="159" t="s">
-        <v>1603</v>
-      </c>
-      <c r="C58" s="157"/>
-    </row>
-    <row r="59" spans="1:4" ht="72" x14ac:dyDescent="0.3">
-      <c r="A59" s="157" t="s">
-        <v>1591</v>
-      </c>
-      <c r="B59" s="158" t="s">
+      <c r="D62" s="156" t="s">
+        <v>1605</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="A63" s="156" t="s">
+        <v>1593</v>
+      </c>
+      <c r="B63" s="157" t="s">
         <v>1597</v>
       </c>
-      <c r="C59" s="157" t="s">
-        <v>1589</v>
-      </c>
-      <c r="D59" s="157" t="s">
-        <v>1607</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A60" s="157" t="s">
-        <v>1592</v>
-      </c>
-      <c r="B60" s="158" t="s">
-        <v>1601</v>
-      </c>
-      <c r="C60" s="157" t="s">
-        <v>1590</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A61" s="157" t="s">
-        <v>1593</v>
-      </c>
-      <c r="B61" s="158" t="s">
-        <v>1598</v>
-      </c>
-      <c r="C61" s="157" t="s">
+      <c r="C63" s="156" t="s">
         <v>1586</v>
-      </c>
-      <c r="D61" s="157" t="s">
-        <v>1607</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A62" s="157" t="s">
-        <v>1594</v>
-      </c>
-      <c r="B62" s="158" t="s">
-        <v>1600</v>
-      </c>
-      <c r="C62" s="157" t="s">
-        <v>1587</v>
-      </c>
-      <c r="D62" s="157" t="s">
-        <v>1607</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" ht="72" x14ac:dyDescent="0.3">
-      <c r="A63" s="157" t="s">
-        <v>1595</v>
-      </c>
-      <c r="B63" s="158" t="s">
-        <v>1599</v>
-      </c>
-      <c r="C63" s="157" t="s">
-        <v>1588</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" s="109" t="s">
-        <v>1602</v>
+        <v>1600</v>
       </c>
       <c r="D64" s="69" t="s">
         <v>106</v>
@@ -67630,74 +68287,74 @@
     <row r="65" spans="1:4" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A65"/>
       <c r="B65" s="2" t="s">
-        <v>1606</v>
+        <v>1604</v>
       </c>
       <c r="C65" s="50" t="s">
-        <v>1604</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A66" s="160" t="s">
-        <v>1605</v>
+      <c r="A66" s="159" t="s">
+        <v>1603</v>
       </c>
       <c r="D66" s="69" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="244.8" x14ac:dyDescent="0.3">
-      <c r="A67" s="157"/>
+      <c r="A67" s="156"/>
       <c r="B67" s="2" t="s">
+        <v>1606</v>
+      </c>
+      <c r="C67" s="156" t="s">
+        <v>1605</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A68" s="167" t="s">
         <v>1608</v>
-      </c>
-      <c r="C67" s="157" t="s">
-        <v>1607</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A68" s="168" t="s">
-        <v>1610</v>
       </c>
       <c r="D68" s="69" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="69" spans="1:4" ht="201.6" x14ac:dyDescent="0.3">
-      <c r="A69" s="157"/>
+      <c r="A69" s="156"/>
       <c r="B69" s="2" t="s">
+        <v>1607</v>
+      </c>
+      <c r="C69" s="156" t="s">
+        <v>1605</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A70" s="167" t="s">
         <v>1609</v>
-      </c>
-      <c r="C69" s="157" t="s">
-        <v>1607</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A70" s="168" t="s">
-        <v>1611</v>
       </c>
       <c r="D70" s="69" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="71" spans="1:4" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A71" s="157"/>
+      <c r="A71" s="156"/>
       <c r="B71" s="2" t="s">
+        <v>1610</v>
+      </c>
+      <c r="C71" s="156" t="s">
+        <v>1611</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A72" s="156"/>
+      <c r="B72" s="2" t="s">
+        <v>1613</v>
+      </c>
+      <c r="C72" s="156" t="s">
         <v>1612</v>
       </c>
-      <c r="C71" s="157" t="s">
-        <v>1613</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A72" s="157"/>
-      <c r="B72" s="2" t="s">
-        <v>1615</v>
-      </c>
-      <c r="C72" s="157" t="s">
-        <v>1614</v>
-      </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A73" s="161" t="s">
+      <c r="A73" s="160" t="s">
         <v>385</v>
       </c>
       <c r="D73" s="69" t="s">
@@ -67705,25 +68362,25 @@
       </c>
     </row>
     <row r="74" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A74" s="157"/>
-      <c r="B74" s="157" t="s">
+      <c r="A74" s="156"/>
+      <c r="B74" s="156" t="s">
+        <v>1614</v>
+      </c>
+      <c r="C74" s="2" t="s">
         <v>1616</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>1618</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" s="47" t="s">
-        <v>1555</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" s="153" t="s">
-        <v>1542</v>
+        <v>1540</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>1543</v>
+        <v>1541</v>
       </c>
       <c r="D76" s="117" t="s">
         <v>106</v>
@@ -67731,70 +68388,70 @@
     </row>
     <row r="77" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
-        <v>1556</v>
+        <v>1554</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>1575</v>
-      </c>
-      <c r="C77" s="157" t="s">
-        <v>1581</v>
+        <v>1573</v>
+      </c>
+      <c r="C77" s="156" t="s">
+        <v>1579</v>
       </c>
     </row>
     <row r="78" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
-        <v>1557</v>
-      </c>
-      <c r="B78" s="157" t="s">
-        <v>1574</v>
-      </c>
-      <c r="C78" s="157" t="s">
-        <v>1580</v>
+        <v>1555</v>
+      </c>
+      <c r="B78" s="156" t="s">
+        <v>1572</v>
+      </c>
+      <c r="C78" s="156" t="s">
+        <v>1578</v>
       </c>
     </row>
     <row r="79" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
-        <v>1558</v>
-      </c>
-      <c r="B79" s="157" t="s">
-        <v>1572</v>
-      </c>
-      <c r="C79" s="157" t="s">
-        <v>1579</v>
+        <v>1556</v>
+      </c>
+      <c r="B79" s="156" t="s">
+        <v>1570</v>
+      </c>
+      <c r="C79" s="156" t="s">
+        <v>1577</v>
       </c>
     </row>
     <row r="80" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
-        <v>1559</v>
-      </c>
-      <c r="B80" s="157" t="s">
-        <v>1573</v>
-      </c>
-      <c r="C80" s="157" t="s">
-        <v>1578</v>
+        <v>1557</v>
+      </c>
+      <c r="B80" s="156" t="s">
+        <v>1571</v>
+      </c>
+      <c r="C80" s="156" t="s">
+        <v>1576</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" s="153" t="s">
-        <v>1570</v>
+        <v>1568</v>
       </c>
       <c r="D81" s="69" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="82" spans="1:4" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A82" s="157" t="s">
-        <v>1571</v>
+      <c r="A82" s="156" t="s">
+        <v>1569</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>1576</v>
-      </c>
-      <c r="C82" s="157" t="s">
-        <v>1577</v>
+        <v>1574</v>
+      </c>
+      <c r="C82" s="156" t="s">
+        <v>1575</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" s="153" t="s">
-        <v>1549</v>
+        <v>1547</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>106</v>
@@ -67802,42 +68459,42 @@
     </row>
     <row r="84" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="C84" s="2" t="s">
-        <v>1645</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="85" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
-        <v>1651</v>
+        <v>1649</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>1648</v>
+        <v>1646</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>1646</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="86" spans="1:4" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
-        <v>1650</v>
+        <v>1648</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>1649</v>
+        <v>1647</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>1647</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87" s="47" t="s">
-        <v>1652</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="88" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A88" s="153" t="s">
-        <v>1550</v>
+        <v>1548</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>1693</v>
+        <v>1691</v>
       </c>
       <c r="D88" s="69" t="s">
         <v>106</v>
@@ -67845,147 +68502,147 @@
     </row>
     <row r="89" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
       <c r="B89" s="2" t="s">
-        <v>1654</v>
+        <v>1652</v>
       </c>
       <c r="D89" s="69" t="s">
-        <v>1653</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A90" s="165" t="s">
-        <v>1695</v>
+      <c r="A90" s="164" t="s">
+        <v>1693</v>
       </c>
       <c r="D90" s="69"/>
     </row>
     <row r="91" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B91" s="2" t="s">
-        <v>1674</v>
+        <v>1672</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>1663</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B92" s="2" t="s">
-        <v>1666</v>
+        <v>1664</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>1655</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B93" s="2" t="s">
-        <v>1667</v>
+        <v>1665</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>1656</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B94" s="2" t="s">
-        <v>1668</v>
+        <v>1666</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>1657</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B95" s="2" t="s">
-        <v>1669</v>
+        <v>1667</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>1658</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B96" s="2" t="s">
-        <v>1670</v>
+        <v>1668</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>1659</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B97" s="2" t="s">
-        <v>1671</v>
+        <v>1669</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>1660</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B98" s="2" t="s">
-        <v>1672</v>
+        <v>1670</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>1661</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B99" s="2" t="s">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>1662</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A100" s="165" t="s">
-        <v>1696</v>
+      <c r="A100" s="164" t="s">
+        <v>1694</v>
       </c>
     </row>
     <row r="101" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B101" s="2" t="s">
-        <v>1697</v>
-      </c>
-      <c r="C101" s="163" t="s">
-        <v>1702</v>
+        <v>1695</v>
+      </c>
+      <c r="C101" s="162" t="s">
+        <v>1700</v>
       </c>
     </row>
     <row r="102" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
       <c r="B102" s="2" t="s">
-        <v>1698</v>
-      </c>
-      <c r="C102" s="163" t="s">
-        <v>1703</v>
+        <v>1696</v>
+      </c>
+      <c r="C102" s="162" t="s">
+        <v>1701</v>
       </c>
     </row>
     <row r="103" spans="1:4" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A103" s="2" t="s">
-        <v>1557</v>
+        <v>1555</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>1705</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="104" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B104" s="2" t="s">
-        <v>1704</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="105" spans="1:4" ht="172.8" x14ac:dyDescent="0.3">
-      <c r="A105" s="163" t="s">
-        <v>1665</v>
+      <c r="A105" s="162" t="s">
+        <v>1663</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>1675</v>
+        <v>1673</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>1664</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A106" s="165" t="s">
+      <c r="A106" s="164" t="s">
+        <v>1687</v>
+      </c>
+      <c r="B106" s="163" t="s">
         <v>1689</v>
       </c>
-      <c r="B106" s="164" t="s">
-        <v>1691</v>
-      </c>
-      <c r="C106" s="164" t="s">
-        <v>1692</v>
+      <c r="C106" s="163" t="s">
+        <v>1690</v>
       </c>
       <c r="D106" s="109" t="s">
-        <v>1690</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.3">
@@ -67993,91 +68650,91 @@
         <v>154</v>
       </c>
       <c r="B107" s="106" t="s">
-        <v>1676</v>
+        <v>1674</v>
       </c>
       <c r="C107" s="106" t="s">
-        <v>1676</v>
+        <v>1674</v>
       </c>
       <c r="D107" s="106"/>
     </row>
     <row r="108" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A108" s="106" t="s">
+        <v>1675</v>
+      </c>
+      <c r="B108" s="106" t="s">
+        <v>1676</v>
+      </c>
+      <c r="C108" s="106" t="s">
         <v>1677</v>
       </c>
-      <c r="B108" s="106" t="s">
-        <v>1678</v>
-      </c>
-      <c r="C108" s="106" t="s">
-        <v>1679</v>
-      </c>
       <c r="D108" s="106" t="s">
-        <v>1694</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="109" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A109" s="106" t="s">
-        <v>1680</v>
+        <v>1678</v>
       </c>
       <c r="B109" s="106" t="s">
-        <v>1678</v>
+        <v>1676</v>
       </c>
       <c r="C109" s="106" t="s">
-        <v>1679</v>
+        <v>1677</v>
       </c>
       <c r="D109" s="106" t="s">
-        <v>1694</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A110" s="106" t="s">
-        <v>1681</v>
+        <v>1679</v>
       </c>
       <c r="B110" s="106" t="s">
-        <v>1682</v>
+        <v>1680</v>
       </c>
       <c r="C110" s="106" t="s">
-        <v>1682</v>
+        <v>1680</v>
       </c>
       <c r="D110" s="106"/>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A111" s="106" t="s">
-        <v>1683</v>
+        <v>1681</v>
       </c>
       <c r="B111" s="106" t="s">
-        <v>1684</v>
+        <v>1682</v>
       </c>
       <c r="C111" s="106" t="s">
-        <v>1684</v>
+        <v>1682</v>
       </c>
       <c r="D111" s="106"/>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A112" s="106" t="s">
-        <v>1685</v>
+        <v>1683</v>
       </c>
       <c r="B112" s="106" t="s">
-        <v>1678</v>
+        <v>1676</v>
       </c>
       <c r="C112" s="106" t="s">
-        <v>1679</v>
+        <v>1677</v>
       </c>
       <c r="D112" s="106" t="s">
-        <v>1686</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A113" s="106" t="s">
-        <v>1687</v>
+        <v>1685</v>
       </c>
       <c r="B113" s="106" t="s">
-        <v>1678</v>
+        <v>1676</v>
       </c>
       <c r="C113" s="106" t="s">
-        <v>1679</v>
+        <v>1677</v>
       </c>
       <c r="D113" s="106" t="s">
-        <v>1688</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.3">
@@ -68088,11 +68745,11 @@
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A115" s="153" t="s">
-        <v>1551</v>
+        <v>1549</v>
       </c>
       <c r="B115" s="106"/>
       <c r="C115" s="2" t="s">
-        <v>1552</v>
+        <v>1550</v>
       </c>
       <c r="D115" s="69" t="s">
         <v>106</v>
@@ -68101,7 +68758,7 @@
     <row r="116" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A116" s="106"/>
       <c r="B116" s="106" t="s">
-        <v>1716</v>
+        <v>1714</v>
       </c>
       <c r="C116" s="106"/>
       <c r="D116" s="69"/>
@@ -68109,45 +68766,45 @@
     <row r="117" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A117" s="106"/>
       <c r="B117" s="106" t="s">
-        <v>1713</v>
+        <v>1711</v>
       </c>
       <c r="C117" s="106" t="s">
-        <v>1711</v>
+        <v>1709</v>
       </c>
       <c r="D117" s="69"/>
     </row>
     <row r="118" spans="1:4" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A118" s="106"/>
       <c r="B118" s="106" t="s">
-        <v>1715</v>
+        <v>1713</v>
       </c>
       <c r="C118" s="106" t="s">
-        <v>1714</v>
+        <v>1712</v>
       </c>
       <c r="D118" s="69"/>
     </row>
     <row r="119" spans="1:4" ht="201.6" x14ac:dyDescent="0.3">
-      <c r="A119" s="163" t="s">
-        <v>1665</v>
+      <c r="A119" s="162" t="s">
+        <v>1663</v>
       </c>
       <c r="B119" s="106" t="s">
-        <v>1710</v>
+        <v>1708</v>
       </c>
       <c r="C119" s="106"/>
       <c r="D119" s="106"/>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A120" s="165" t="s">
+      <c r="A120" s="164" t="s">
+        <v>1687</v>
+      </c>
+      <c r="B120" s="163" t="s">
         <v>1689</v>
       </c>
-      <c r="B120" s="164" t="s">
-        <v>1691</v>
-      </c>
-      <c r="C120" s="164" t="s">
-        <v>1692</v>
+      <c r="C120" s="163" t="s">
+        <v>1690</v>
       </c>
       <c r="D120" s="109" t="s">
-        <v>1690</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="121" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
@@ -68155,97 +68812,97 @@
         <v>154</v>
       </c>
       <c r="B121" s="106" t="s">
-        <v>1678</v>
+        <v>1676</v>
       </c>
       <c r="C121" s="106" t="s">
-        <v>1679</v>
+        <v>1677</v>
       </c>
       <c r="D121" s="106" t="s">
-        <v>1709</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A122" s="106" t="s">
-        <v>1677</v>
+        <v>1675</v>
       </c>
       <c r="B122" s="106" t="s">
-        <v>1706</v>
+        <v>1704</v>
       </c>
       <c r="C122" s="106" t="s">
-        <v>1706</v>
+        <v>1704</v>
       </c>
       <c r="D122" s="106" t="s">
-        <v>1707</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A123" s="106" t="s">
-        <v>1680</v>
+        <v>1678</v>
       </c>
       <c r="B123" s="106" t="s">
-        <v>1708</v>
+        <v>1706</v>
       </c>
       <c r="C123" s="106" t="s">
-        <v>1708</v>
+        <v>1706</v>
       </c>
       <c r="D123" s="106" t="s">
-        <v>1707</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="124" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A124" s="106" t="s">
-        <v>1681</v>
+        <v>1679</v>
       </c>
       <c r="B124" s="106" t="s">
-        <v>1678</v>
+        <v>1676</v>
       </c>
       <c r="C124" s="106" t="s">
-        <v>1679</v>
+        <v>1677</v>
       </c>
       <c r="D124" s="106" t="s">
-        <v>1709</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="125" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A125" s="106" t="s">
-        <v>1683</v>
+        <v>1681</v>
       </c>
       <c r="B125" s="106" t="s">
-        <v>1678</v>
+        <v>1676</v>
       </c>
       <c r="C125" s="106" t="s">
-        <v>1679</v>
+        <v>1677</v>
       </c>
       <c r="D125" s="106" t="s">
-        <v>1709</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A126" s="106" t="s">
-        <v>1685</v>
+        <v>1683</v>
       </c>
       <c r="B126" s="106" t="s">
-        <v>1678</v>
+        <v>1676</v>
       </c>
       <c r="C126" s="106" t="s">
-        <v>1679</v>
+        <v>1677</v>
       </c>
       <c r="D126" s="106" t="s">
-        <v>1686</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A127" s="106" t="s">
-        <v>1687</v>
+        <v>1685</v>
       </c>
       <c r="B127" s="106" t="s">
-        <v>1678</v>
+        <v>1676</v>
       </c>
       <c r="C127" s="106" t="s">
-        <v>1679</v>
+        <v>1677</v>
       </c>
       <c r="D127" s="106" t="s">
-        <v>1688</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="128" spans="1:4" s="46" customFormat="1" x14ac:dyDescent="0.3">
@@ -68329,62 +68986,62 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="189" t="s">
-        <v>1846</v>
-      </c>
-      <c r="B2" s="186" t="s">
-        <v>1850</v>
+      <c r="A2" s="188" t="s">
+        <v>1844</v>
+      </c>
+      <c r="B2" s="185" t="s">
+        <v>1848</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="34" t="s">
-        <v>1422</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="34" t="s">
-        <v>1423</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="34" t="s">
-        <v>1424</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="47" t="s">
-        <v>1438</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="34" t="s">
-        <v>1447</v>
+        <v>1445</v>
       </c>
       <c r="B7" s="147" t="s">
-        <v>1451</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="34" t="s">
-        <v>1446</v>
-      </c>
-      <c r="B8" s="186" t="s">
-        <v>1852</v>
+        <v>1444</v>
+      </c>
+      <c r="B8" s="185" t="s">
+        <v>1850</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="47" t="s">
-        <v>1470</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="47" t="s">
-        <v>1474</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="185" t="s">
-        <v>1851</v>
+      <c r="A11" s="184" t="s">
+        <v>1849</v>
       </c>
     </row>
     <row r="13" spans="1:5" s="45" customFormat="1" x14ac:dyDescent="0.3">
@@ -68392,39 +69049,39 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B14" s="117" t="s">
-        <v>1427</v>
-      </c>
-      <c r="C14" s="192" t="s">
-        <v>1846</v>
+        <v>1425</v>
+      </c>
+      <c r="C14" s="191" t="s">
+        <v>1844</v>
       </c>
       <c r="D14" s="117" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A15" s="189" t="s">
-        <v>1846</v>
+      <c r="A15" s="188" t="s">
+        <v>1844</v>
       </c>
       <c r="B15" s="117" t="s">
-        <v>1432</v>
-      </c>
-      <c r="C15" s="174" t="s">
-        <v>1797</v>
+        <v>1430</v>
+      </c>
+      <c r="C15" s="173" t="s">
+        <v>1795</v>
       </c>
       <c r="D15" s="117"/>
     </row>
     <row r="16" spans="1:5" ht="316.8" x14ac:dyDescent="0.3">
-      <c r="B16" s="186" t="s">
-        <v>1849</v>
+      <c r="B16" s="185" t="s">
+        <v>1847</v>
       </c>
       <c r="C16" s="144" t="s">
-        <v>1431</v>
+        <v>1429</v>
       </c>
       <c r="D16" s="117"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="34" t="s">
-        <v>1422</v>
+        <v>1420</v>
       </c>
       <c r="D17" s="69" t="s">
         <v>106</v>
@@ -68432,18 +69089,18 @@
     </row>
     <row r="18" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
       <c r="B18" s="2" t="s">
-        <v>1433</v>
+        <v>1431</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>1426</v>
+        <v>1424</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>1429</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="19" spans="1:4" s="46" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A19" s="34" t="s">
-        <v>1423</v>
+        <v>1421</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -68454,18 +69111,18 @@
     <row r="20" spans="1:4" s="46" customFormat="1" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A20" s="2"/>
       <c r="B20" s="2" t="s">
-        <v>1434</v>
+        <v>1432</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>1425</v>
+        <v>1423</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>1428</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="21" spans="1:4" s="46" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A21" s="34" t="s">
-        <v>1424</v>
+        <v>1422</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -68476,18 +69133,18 @@
     <row r="22" spans="1:4" s="46" customFormat="1" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A22" s="2"/>
       <c r="B22" s="2" t="s">
-        <v>1794</v>
+        <v>1792</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>1795</v>
+        <v>1793</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>1430</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="23" spans="1:4" s="46" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A23" s="47" t="s">
-        <v>1438</v>
+        <v>1436</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -68497,10 +69154,10 @@
     </row>
     <row r="24" spans="1:4" s="46" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A24" s="34" t="s">
-        <v>1447</v>
+        <v>1445</v>
       </c>
       <c r="B24" s="110" t="s">
-        <v>1457</v>
+        <v>1455</v>
       </c>
       <c r="C24" s="145"/>
       <c r="D24" s="69" t="s">
@@ -68509,127 +69166,127 @@
     </row>
     <row r="25" spans="1:4" s="46" customFormat="1" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A25" s="147" t="s">
+        <v>1449</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>1450</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>1451</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>1452</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>1453</v>
       </c>
       <c r="D25" s="2"/>
     </row>
     <row r="26" spans="1:4" s="46" customFormat="1" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A26" s="2"/>
       <c r="B26" s="2" t="s">
-        <v>1450</v>
+        <v>1448</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>1449</v>
+        <v>1447</v>
       </c>
       <c r="D26" s="2"/>
     </row>
     <row r="27" spans="1:4" s="46" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A27" s="34" t="s">
-        <v>1446</v>
+        <v>1444</v>
       </c>
       <c r="B27" s="147" t="s">
-        <v>1456</v>
+        <v>1454</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" s="69"/>
     </row>
     <row r="28" spans="1:4" s="46" customFormat="1" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A28" s="147" t="s">
-        <v>1455</v>
+        <v>1453</v>
       </c>
       <c r="B28" s="2" t="s">
+        <v>1433</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>1435</v>
       </c>
-      <c r="C28" s="2" t="s">
-        <v>1437</v>
-      </c>
       <c r="D28" s="2" t="s">
-        <v>1454</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="29" spans="1:4" s="46" customFormat="1" ht="144" x14ac:dyDescent="0.3">
       <c r="A29" s="147" t="s">
-        <v>1456</v>
+        <v>1454</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>1448</v>
+        <v>1446</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>1436</v>
+        <v>1434</v>
       </c>
       <c r="D29" s="2"/>
     </row>
     <row r="30" spans="1:4" s="46" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A30" s="47" t="s">
-        <v>1458</v>
+        <v>1456</v>
       </c>
       <c r="B30" s="47" t="s">
-        <v>1469</v>
+        <v>1467</v>
       </c>
       <c r="C30" s="47" t="s">
-        <v>1468</v>
+        <v>1466</v>
       </c>
       <c r="D30" s="2"/>
     </row>
     <row r="31" spans="1:4" s="46" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A31" s="2"/>
       <c r="B31" s="2" t="s">
-        <v>1459</v>
+        <v>1457</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="D31" s="2"/>
     </row>
     <row r="32" spans="1:4" s="46" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A32" s="2"/>
       <c r="B32" s="2" t="s">
-        <v>1461</v>
+        <v>1459</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>1462</v>
+        <v>1460</v>
       </c>
       <c r="D32" s="2"/>
     </row>
     <row r="33" spans="1:4" s="46" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A33" s="2"/>
       <c r="B33" s="2" t="s">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>1464</v>
+        <v>1462</v>
       </c>
       <c r="D33" s="2"/>
     </row>
     <row r="34" spans="1:4" s="46" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A34" s="2"/>
       <c r="B34" s="2" t="s">
-        <v>1465</v>
+        <v>1463</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="D34" s="2"/>
     </row>
     <row r="35" spans="1:4" s="46" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A35" s="2"/>
       <c r="B35" s="2" t="s">
-        <v>1466</v>
+        <v>1464</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>1467</v>
+        <v>1465</v>
       </c>
       <c r="D35" s="2"/>
     </row>
     <row r="36" spans="1:4" s="46" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A36" s="47" t="s">
-        <v>1470</v>
+        <v>1468</v>
       </c>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -68640,16 +69297,16 @@
     <row r="37" spans="1:4" s="46" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A37" s="2"/>
       <c r="B37" s="147" t="s">
-        <v>1472</v>
+        <v>1470</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>1471</v>
+        <v>1469</v>
       </c>
       <c r="D37" s="2"/>
     </row>
     <row r="38" spans="1:4" s="46" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A38" s="47" t="s">
-        <v>1474</v>
+        <v>1472</v>
       </c>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
@@ -68661,13 +69318,13 @@
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2" t="s">
-        <v>1473</v>
+        <v>1471</v>
       </c>
       <c r="D39" s="2"/>
     </row>
     <row r="40" spans="1:4" s="46" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A40" s="148" t="s">
-        <v>1476</v>
+        <v>1474</v>
       </c>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -68679,7 +69336,7 @@
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2" t="s">
-        <v>1475</v>
+        <v>1473</v>
       </c>
       <c r="D41" s="2"/>
     </row>
@@ -68768,7 +69425,7 @@
     <tabColor rgb="FF7030A0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:E28"/>
+  <dimension ref="A2:E29"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="42.88671875" style="2" customWidth="1"/>
@@ -68834,7 +69491,7 @@
         <v>1205</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1323</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
@@ -68847,183 +69504,197 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>1561</v>
+        <v>1559</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1560</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
+        <v>1803</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>1805</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>1807</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>1808</v>
+        <v>1806</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1809</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="47" t="s">
+        <v>1807</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>1853</v>
+      </c>
+      <c r="B11" s="193" t="s">
+        <v>1854</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>1855</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>1852</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="47" t="s">
+        <v>1832</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B13" s="182" t="s">
         <v>1834</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
-        <v>1207</v>
-      </c>
-      <c r="B12" s="183" t="s">
-        <v>1836</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>1835</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="47" t="s">
-        <v>1421</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
+      <c r="C13" s="2" t="s">
+        <v>1833</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="47" t="s">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>1826</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>1829</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>1831</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="216" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>1826</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>1828</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>1831</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>1833</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="216" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
-        <v>1828</v>
-      </c>
-      <c r="B15" s="2" t="s">
+      <c r="C16" s="2" t="s">
+        <v>1827</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="144" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>1826</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>1830</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>1829</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="144" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
-        <v>1828</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>1832</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>1806</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
+      <c r="C17" s="2" t="s">
+        <v>1804</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
+        <v>1794</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>1796</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>1798</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>1792</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>1793</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="34" t="s">
+      <c r="C19" s="2" t="s">
+        <v>1790</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>1791</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" s="34" t="s">
         <v>1213</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="72" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
+    <row r="22" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
         <v>641</v>
       </c>
-      <c r="B21" s="108" t="s">
+      <c r="B22" s="108" t="s">
         <v>1222</v>
       </c>
-      <c r="C21" s="108" t="s">
+      <c r="C22" s="108" t="s">
         <v>1216</v>
       </c>
-      <c r="D21" s="127" t="s">
-        <v>1366</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="72" x14ac:dyDescent="0.3">
-      <c r="B22" s="108" t="s">
-        <v>1223</v>
-      </c>
-      <c r="C22" s="108" t="s">
-        <v>1229</v>
+      <c r="D22" s="127" t="s">
+        <v>1364</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="B23" s="108" t="s">
+        <v>1223</v>
+      </c>
+      <c r="C23" s="108" t="s">
+        <v>1229</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="B24" s="108" t="s">
         <v>1224</v>
       </c>
-      <c r="C23" s="108" t="s">
+      <c r="C24" s="108" t="s">
         <v>1215</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="72" x14ac:dyDescent="0.3">
-      <c r="A24" s="2" t="s">
+    <row r="25" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
         <v>506</v>
       </c>
-      <c r="B24" s="108" t="s">
+      <c r="B25" s="108" t="s">
         <v>1221</v>
       </c>
-      <c r="C24" s="108" t="s">
+      <c r="C25" s="108" t="s">
         <v>1228</v>
       </c>
-      <c r="D24" s="117" t="s">
+      <c r="D25" s="117" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="B25" s="146" t="s">
-        <v>1443</v>
-      </c>
-      <c r="C25" s="146" t="s">
-        <v>1442</v>
-      </c>
-      <c r="D25" s="117"/>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" s="34" t="s">
+    <row r="26" spans="1:4" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="B26" s="146" t="s">
+        <v>1441</v>
+      </c>
+      <c r="C26" s="146" t="s">
+        <v>1440</v>
+      </c>
+      <c r="D26" s="117"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" s="34" t="s">
         <v>1214</v>
       </c>
-      <c r="B26" s="108"/>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" s="2" t="s">
+      <c r="B27" s="108"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
         <v>1208</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C28" s="2" t="s">
         <v>1209</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A28" s="2" t="s">
+    <row r="29" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A29" s="2" t="s">
         <v>506</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B29" s="2" t="s">
         <v>1211</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C29" s="2" t="s">
         <v>1217</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="D3" r:id="rId1" xr:uid="{905E1A37-58B6-4E12-8CCE-35C0ED3614B3}"/>
-    <hyperlink ref="D24" r:id="rId2" xr:uid="{77C85831-4549-4C52-BBEA-1E1A7B8D7BDD}"/>
+    <hyperlink ref="D25" r:id="rId2" xr:uid="{77C85831-4549-4C52-BBEA-1E1A7B8D7BDD}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId3"/>
@@ -69102,7 +69773,7 @@
     </row>
     <row r="4" spans="1:22" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B4" s="127" t="s">
-        <v>1367</v>
+        <v>1365</v>
       </c>
       <c r="C4" s="108" t="s">
         <v>1220</v>
@@ -69165,7 +69836,7 @@
       <c r="B11" s="108" t="s">
         <v>1232</v>
       </c>
-      <c r="C11" s="183" t="s">
+      <c r="C11" s="182" t="s">
         <v>1231</v>
       </c>
       <c r="D11" s="9"/>
@@ -70851,8 +71522,8 @@
       <c r="V3" s="2"/>
     </row>
     <row r="4" spans="1:22" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="B4" s="175" t="s">
-        <v>1799</v>
+      <c r="B4" s="174" t="s">
+        <v>1797</v>
       </c>
       <c r="C4" s="19" t="s">
         <v>87</v>
@@ -71254,7 +71925,7 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="29" t="s">
-        <v>1803</v>
+        <v>1801</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="374.4" x14ac:dyDescent="0.3">
@@ -71266,7 +71937,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="38" type="noConversion"/>
+  <phoneticPr fontId="39" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="D46" r:id="rId1" location=":~:text=%D0%A1%D0%BE%D0%B7%D0%B4%D0%B0%D0%BD%D0%B8%D0%B5%20%D0%B1%D0%B0%D0%B7%D1%8B%20%D0%B4%D0%B0%D0%BD%D0%BD%D1%8B%D1%85" xr:uid="{FDFE2116-2B22-4A87-B37D-3DFA9E8F9FE0}"/>
     <hyperlink ref="D44" r:id="rId2" location=":~:text=%D0%A1%D0%BE%D0%B7%D0%B4%D0%B0%D0%BD%D0%B8%D0%B5%20%D0%B1%D0%B0%D0%B7%D1%8B%20%D0%B4%D0%B0%D0%BD%D0%BD%D1%8B%D1%85%20%D0%B2%20SQL%20Management%20Studio" xr:uid="{5B701F02-CEF7-44EA-83C6-0E21D7145608}"/>
@@ -71418,7 +72089,7 @@
       <c r="C10" s="9"/>
       <c r="D10" s="9"/>
     </row>
-    <row r="11" spans="1:22" ht="144" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:22" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A11" s="9"/>
       <c r="B11" s="108" t="s">
         <v>1253</v>
@@ -71430,7 +72101,7 @@
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A12" s="116" t="s">
-        <v>1839</v>
+        <v>1837</v>
       </c>
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
@@ -71438,14 +72109,14 @@
     </row>
     <row r="13" spans="1:22" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A13" s="9"/>
-      <c r="B13" s="183" t="s">
-        <v>1840</v>
-      </c>
-      <c r="C13" s="183" t="s">
-        <v>1837</v>
-      </c>
-      <c r="D13" s="183" t="s">
+      <c r="B13" s="182" t="s">
         <v>1838</v>
+      </c>
+      <c r="C13" s="182" t="s">
+        <v>1835</v>
+      </c>
+      <c r="D13" s="182" t="s">
+        <v>1836</v>
       </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.3">
@@ -73076,7 +73747,7 @@
     <tabColor rgb="FF0070C0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:V55"/>
+  <dimension ref="A2:V58"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="36" style="1" customWidth="1"/>
@@ -73109,206 +73780,208 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A2" s="3"/>
-      <c r="B2" s="5"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
-      <c r="N2" s="3"/>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="5"/>
-      <c r="R2" s="5"/>
-      <c r="S2" s="5"/>
-      <c r="U2" s="5"/>
+      <c r="A2" s="70" t="s">
+        <v>1277</v>
+      </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A3" s="70" t="s">
+      <c r="A3" s="107" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="107" t="s">
+        <v>1284</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>1866</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A6" s="3"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="K6" s="3"/>
+      <c r="L6" s="3"/>
+      <c r="M6" s="3"/>
+      <c r="N6" s="3"/>
+      <c r="P6" s="5"/>
+      <c r="Q6" s="5"/>
+      <c r="R6" s="5"/>
+      <c r="S6" s="5"/>
+      <c r="U6" s="5"/>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A7" s="70" t="s">
         <v>1277</v>
       </c>
-      <c r="B3" s="47"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="154" t="s">
+      <c r="B7" s="47"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="154" t="s">
         <v>106</v>
       </c>
-      <c r="P3" s="1"/>
-      <c r="U3" s="1"/>
-      <c r="V3" s="2"/>
-    </row>
-    <row r="4" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A4" s="9"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="108" t="s">
+      <c r="P7" s="1"/>
+      <c r="U7" s="1"/>
+      <c r="V7" s="2"/>
+    </row>
+    <row r="8" spans="1:22" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A8" s="9"/>
+      <c r="B8" s="193" t="s">
+        <v>1862</v>
+      </c>
+      <c r="C8" s="193" t="s">
+        <v>1864</v>
+      </c>
+      <c r="P8" s="1"/>
+      <c r="U8" s="1"/>
+      <c r="V8" s="2"/>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A9" s="9"/>
+      <c r="B9" s="119" t="s">
+        <v>1860</v>
+      </c>
+      <c r="C9" s="72" t="s">
+        <v>1858</v>
+      </c>
+      <c r="P9" s="1"/>
+      <c r="U9" s="1"/>
+      <c r="V9" s="2"/>
+    </row>
+    <row r="10" spans="1:22" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A10" s="193" t="s">
+        <v>82</v>
+      </c>
+      <c r="B10" s="193" t="s">
+        <v>1861</v>
+      </c>
+      <c r="C10" s="146" t="s">
         <v>1278</v>
       </c>
-      <c r="P4" s="1"/>
-      <c r="U4" s="1"/>
-      <c r="V4" s="2"/>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A5" s="34" t="s">
-        <v>1212</v>
-      </c>
-      <c r="B5" s="9"/>
-      <c r="C5" s="108"/>
-      <c r="P5" s="1"/>
-      <c r="U5" s="1"/>
-      <c r="V5" s="2"/>
-    </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A6" s="9"/>
-      <c r="B6" s="9"/>
-      <c r="C6" s="146" t="s">
+      <c r="P10" s="1"/>
+      <c r="U10" s="1"/>
+      <c r="V10" s="2"/>
+    </row>
+    <row r="11" spans="1:22" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="193" t="s">
+        <v>1859</v>
+      </c>
+      <c r="B11" s="193" t="s">
+        <v>1856</v>
+      </c>
+      <c r="C11" s="193" t="s">
+        <v>1857</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A12" s="193" t="s">
+        <v>434</v>
+      </c>
+      <c r="C12" s="108" t="s">
         <v>1279</v>
       </c>
-      <c r="P6" s="1"/>
-      <c r="U6" s="1"/>
-      <c r="V6" s="2"/>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A7" s="34" t="s">
-        <v>1213</v>
-      </c>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-    </row>
-    <row r="8" spans="1:22" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="108" t="s">
-        <v>488</v>
-      </c>
-      <c r="B8" s="9"/>
-      <c r="C8" s="146" t="s">
+      <c r="D12" s="9"/>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A13" s="107" t="s">
+        <v>1280</v>
+      </c>
+      <c r="B13" s="4"/>
+      <c r="D13" s="154" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="193"/>
+      <c r="B14" s="193" t="s">
+        <v>1863</v>
+      </c>
+      <c r="C14" s="193" t="s">
+        <v>1865</v>
+      </c>
+      <c r="D14" s="193"/>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A15" s="195"/>
+      <c r="B15" s="196"/>
+      <c r="C15" s="194" t="s">
+        <v>332</v>
+      </c>
+      <c r="D15" s="194" t="s">
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A16" s="119" t="s">
         <v>1281</v>
       </c>
-      <c r="D8" s="9"/>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A9" s="34" t="s">
-        <v>1214</v>
-      </c>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="69"/>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A10" s="9"/>
-      <c r="B10" s="9"/>
-      <c r="C10" s="108" t="s">
-        <v>1280</v>
-      </c>
-      <c r="D10" s="69"/>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A11" s="107" t="s">
+      <c r="C16" s="193" t="s">
         <v>1282</v>
       </c>
-      <c r="B11" s="155"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="154" t="s">
+      <c r="D16" s="108" t="s">
+        <v>1283</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A17" s="197" t="s">
+        <v>1284</v>
+      </c>
+      <c r="B17" s="126"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="154" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="12" spans="1:22" ht="144" x14ac:dyDescent="0.3">
-      <c r="A12" s="119" t="s">
-        <v>1283</v>
-      </c>
-      <c r="B12" s="108" t="s">
-        <v>332</v>
-      </c>
-      <c r="C12" s="108" t="s">
-        <v>1284</v>
-      </c>
-      <c r="D12" s="69"/>
-    </row>
-    <row r="13" spans="1:22" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A13" s="108"/>
-      <c r="B13" s="108" t="s">
-        <v>332</v>
-      </c>
-      <c r="C13" s="108" t="s">
+    <row r="18" spans="1:22" ht="72" x14ac:dyDescent="0.3">
+      <c r="A18" s="72" t="s">
+        <v>1561</v>
+      </c>
+      <c r="B18" s="108" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C18" s="193" t="s">
         <v>1285</v>
       </c>
-      <c r="D13" s="69"/>
-    </row>
-    <row r="14" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A14" s="107" t="s">
-        <v>1286</v>
-      </c>
-      <c r="B14" s="126"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="154" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="15" spans="1:22" ht="72" x14ac:dyDescent="0.3">
-      <c r="A15" s="72" t="s">
+      <c r="D18" s="9"/>
+    </row>
+    <row r="19" spans="1:22" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A19" s="9"/>
+      <c r="B19" s="122" t="s">
+        <v>1323</v>
+      </c>
+      <c r="C19" s="122" t="s">
+        <v>1322</v>
+      </c>
+      <c r="D19" s="9"/>
+    </row>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A20" s="155" t="s">
         <v>1563</v>
       </c>
-      <c r="B15" s="108" t="s">
-        <v>1288</v>
-      </c>
-      <c r="C15" s="108" t="s">
-        <v>1287</v>
-      </c>
-      <c r="D15" s="9"/>
-    </row>
-    <row r="16" spans="1:22" ht="172.8" x14ac:dyDescent="0.3">
-      <c r="A16" s="9"/>
-      <c r="B16" s="122" t="s">
-        <v>1325</v>
-      </c>
-      <c r="C16" s="122" t="s">
-        <v>1324</v>
-      </c>
-      <c r="D16" s="9"/>
-    </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A17" s="156" t="s">
-        <v>1565</v>
-      </c>
-      <c r="B17" s="10"/>
-      <c r="C17" s="10"/>
-      <c r="D17" s="10"/>
-    </row>
-    <row r="18" spans="1:22" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A18" s="9"/>
-      <c r="B18" s="152" t="s">
-        <v>1566</v>
-      </c>
-      <c r="C18" s="152" t="s">
+      <c r="B20" s="10"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="10"/>
+    </row>
+    <row r="21" spans="1:22" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A21" s="9"/>
+      <c r="B21" s="152" t="s">
         <v>1564</v>
       </c>
-      <c r="D18" s="9"/>
-    </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A19" s="9"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="69"/>
-    </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A20" s="9"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-    </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A21" s="9"/>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
+      <c r="C21" s="152" t="s">
+        <v>1562</v>
+      </c>
       <c r="D21" s="9"/>
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A22" s="9"/>
       <c r="B22" s="9"/>
       <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
+      <c r="D22" s="69"/>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A23" s="9"/>
@@ -73316,68 +73989,23 @@
       <c r="C23" s="9"/>
       <c r="D23" s="9"/>
     </row>
-    <row r="24" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A24" s="9"/>
       <c r="B24" s="9"/>
       <c r="C24" s="9"/>
       <c r="D24" s="9"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="1"/>
-      <c r="I24" s="1"/>
-      <c r="K24" s="1"/>
-      <c r="L24" s="1"/>
-      <c r="M24" s="1"/>
-      <c r="N24" s="1"/>
-      <c r="P24" s="2"/>
-      <c r="Q24" s="2"/>
-      <c r="R24" s="2"/>
-      <c r="S24" s="1"/>
-      <c r="T24" s="8"/>
-      <c r="U24" s="2"/>
-      <c r="V24" s="1"/>
-    </row>
-    <row r="25" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="25" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A25" s="9"/>
       <c r="B25" s="9"/>
       <c r="C25" s="9"/>
       <c r="D25" s="9"/>
-      <c r="F25" s="1"/>
-      <c r="G25" s="2"/>
-      <c r="H25" s="1"/>
-      <c r="I25" s="1"/>
-      <c r="K25" s="1"/>
-      <c r="L25" s="1"/>
-      <c r="M25" s="1"/>
-      <c r="N25" s="1"/>
-      <c r="P25" s="2"/>
-      <c r="Q25" s="2"/>
-      <c r="R25" s="2"/>
-      <c r="S25" s="1"/>
-      <c r="T25" s="8"/>
-      <c r="U25" s="2"/>
-      <c r="V25" s="1"/>
-    </row>
-    <row r="26" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A26" s="9"/>
       <c r="B26" s="9"/>
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
-      <c r="F26" s="1"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="1"/>
-      <c r="I26" s="1"/>
-      <c r="K26" s="1"/>
-      <c r="L26" s="1"/>
-      <c r="M26" s="1"/>
-      <c r="N26" s="1"/>
-      <c r="P26" s="2"/>
-      <c r="Q26" s="2"/>
-      <c r="R26" s="2"/>
-      <c r="S26" s="1"/>
-      <c r="T26" s="8"/>
-      <c r="U26" s="2"/>
-      <c r="V26" s="1"/>
     </row>
     <row r="27" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A27" s="9"/>
@@ -73988,11 +74616,74 @@
       <c r="U55" s="2"/>
       <c r="V55" s="1"/>
     </row>
+    <row r="56" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="9"/>
+      <c r="B56" s="9"/>
+      <c r="C56" s="9"/>
+      <c r="D56" s="9"/>
+      <c r="F56" s="1"/>
+      <c r="G56" s="2"/>
+      <c r="H56" s="1"/>
+      <c r="I56" s="1"/>
+      <c r="K56" s="1"/>
+      <c r="L56" s="1"/>
+      <c r="M56" s="1"/>
+      <c r="N56" s="1"/>
+      <c r="P56" s="2"/>
+      <c r="Q56" s="2"/>
+      <c r="R56" s="2"/>
+      <c r="S56" s="1"/>
+      <c r="T56" s="8"/>
+      <c r="U56" s="2"/>
+      <c r="V56" s="1"/>
+    </row>
+    <row r="57" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="9"/>
+      <c r="B57" s="9"/>
+      <c r="C57" s="9"/>
+      <c r="D57" s="9"/>
+      <c r="F57" s="1"/>
+      <c r="G57" s="2"/>
+      <c r="H57" s="1"/>
+      <c r="I57" s="1"/>
+      <c r="K57" s="1"/>
+      <c r="L57" s="1"/>
+      <c r="M57" s="1"/>
+      <c r="N57" s="1"/>
+      <c r="P57" s="2"/>
+      <c r="Q57" s="2"/>
+      <c r="R57" s="2"/>
+      <c r="S57" s="1"/>
+      <c r="T57" s="8"/>
+      <c r="U57" s="2"/>
+      <c r="V57" s="1"/>
+    </row>
+    <row r="58" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="9"/>
+      <c r="B58" s="9"/>
+      <c r="C58" s="9"/>
+      <c r="D58" s="9"/>
+      <c r="F58" s="1"/>
+      <c r="G58" s="2"/>
+      <c r="H58" s="1"/>
+      <c r="I58" s="1"/>
+      <c r="K58" s="1"/>
+      <c r="L58" s="1"/>
+      <c r="M58" s="1"/>
+      <c r="N58" s="1"/>
+      <c r="P58" s="2"/>
+      <c r="Q58" s="2"/>
+      <c r="R58" s="2"/>
+      <c r="S58" s="1"/>
+      <c r="T58" s="8"/>
+      <c r="U58" s="2"/>
+      <c r="V58" s="1"/>
+    </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="D3" r:id="rId1" xr:uid="{736BA9FA-54EE-43D2-8B4B-4FEF0426B9DD}"/>
-    <hyperlink ref="D11" r:id="rId2" xr:uid="{C5D25AED-0E26-43DE-AAF9-61FE8B134821}"/>
-    <hyperlink ref="D14" r:id="rId3" location=":~:text=%D0%9E%D0%B1%D0%BE%D0%B1%D1%89%D0%B5%D0%BD%D0%BD%D1%8B%D0%B5%20%D1%82%D0%B0%D0%B1%D0%BB%D0%B8%D1%87%D0%BD%D1%8B%D0%B5%20%D0%B2%D1%8B%D1%80%D0%B0%D0%B6%D0%B5%D0%BD%D0%B8%D1%8F" xr:uid="{D8A655CC-4613-4077-BAB3-7D1AB33D308B}"/>
+    <hyperlink ref="D7" r:id="rId1" xr:uid="{736BA9FA-54EE-43D2-8B4B-4FEF0426B9DD}"/>
+    <hyperlink ref="D13" r:id="rId2" xr:uid="{C5D25AED-0E26-43DE-AAF9-61FE8B134821}"/>
+    <hyperlink ref="D17" r:id="rId3" location=":~:text=%D0%9E%D0%B1%D0%BE%D0%B1%D1%89%D0%B5%D0%BD%D0%BD%D1%8B%D0%B5%20%D1%82%D0%B0%D0%B1%D0%BB%D0%B8%D1%87%D0%BD%D1%8B%D0%B5%20%D0%B2%D1%8B%D1%80%D0%B0%D0%B6%D0%B5%D0%BD%D0%B8%D1%8F" xr:uid="{D8A655CC-4613-4077-BAB3-7D1AB33D308B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId4"/>
@@ -74059,7 +74750,7 @@
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A3" s="125" t="s">
-        <v>1335</v>
+        <v>1333</v>
       </c>
       <c r="B3" s="108"/>
       <c r="D3" s="69" t="s">
@@ -74070,72 +74761,72 @@
       <c r="A4" s="32"/>
       <c r="B4" s="108"/>
       <c r="C4" s="124" t="s">
-        <v>1336</v>
+        <v>1334</v>
       </c>
       <c r="D4" s="108"/>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A5" s="126" t="s">
-        <v>1337</v>
+        <v>1335</v>
       </c>
       <c r="B5" s="108"/>
       <c r="D5" s="108"/>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A6" s="32" t="s">
-        <v>1338</v>
+        <v>1336</v>
       </c>
       <c r="B6" s="124" t="s">
-        <v>1358</v>
+        <v>1356</v>
       </c>
       <c r="C6" s="124" t="s">
-        <v>1341</v>
+        <v>1339</v>
       </c>
       <c r="D6" s="108"/>
     </row>
     <row r="7" spans="1:21" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A7" s="32" t="s">
-        <v>1339</v>
+        <v>1337</v>
       </c>
       <c r="B7" s="124" t="s">
-        <v>1357</v>
+        <v>1355</v>
       </c>
       <c r="C7" s="124" t="s">
-        <v>1340</v>
+        <v>1338</v>
       </c>
       <c r="D7" s="69"/>
     </row>
     <row r="8" spans="1:21" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A8" s="124" t="s">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="B8" s="124" t="s">
-        <v>1362</v>
+        <v>1360</v>
       </c>
       <c r="C8" s="124" t="s">
-        <v>1342</v>
+        <v>1340</v>
       </c>
       <c r="D8" s="69"/>
     </row>
     <row r="9" spans="1:21" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A9" s="124" t="s">
-        <v>1364</v>
+        <v>1362</v>
       </c>
       <c r="B9" s="124"/>
       <c r="C9" s="124" t="s">
-        <v>1365</v>
+        <v>1363</v>
       </c>
       <c r="D9" s="69"/>
     </row>
     <row r="10" spans="1:21" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A10" s="124" t="s">
-        <v>1343</v>
+        <v>1341</v>
       </c>
       <c r="B10" s="124" t="s">
-        <v>1343</v>
+        <v>1341</v>
       </c>
       <c r="C10" s="124" t="s">
-        <v>1346</v>
+        <v>1344</v>
       </c>
       <c r="D10" s="108"/>
     </row>
@@ -74147,7 +74838,7 @@
     </row>
     <row r="12" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="126" t="s">
-        <v>1356</v>
+        <v>1354</v>
       </c>
       <c r="B12" s="124"/>
       <c r="C12" s="124"/>
@@ -74155,13 +74846,13 @@
     </row>
     <row r="13" spans="1:21" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A13" s="32" t="s">
-        <v>1359</v>
+        <v>1357</v>
       </c>
       <c r="B13" s="124" t="s">
-        <v>1355</v>
+        <v>1353</v>
       </c>
       <c r="C13" s="124" t="s">
-        <v>1351</v>
+        <v>1349</v>
       </c>
       <c r="D13" s="69" t="s">
         <v>106</v>
@@ -74169,13 +74860,13 @@
     </row>
     <row r="14" spans="1:21" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A14" s="32" t="s">
-        <v>1360</v>
+        <v>1358</v>
       </c>
       <c r="B14" s="124" t="s">
+        <v>1348</v>
+      </c>
+      <c r="C14" s="124" t="s">
         <v>1350</v>
-      </c>
-      <c r="C14" s="124" t="s">
-        <v>1352</v>
       </c>
       <c r="D14" s="69" t="s">
         <v>106</v>
@@ -74183,13 +74874,13 @@
     </row>
     <row r="15" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A15" s="32" t="s">
-        <v>1361</v>
+        <v>1359</v>
       </c>
       <c r="B15" s="124" t="s">
-        <v>1354</v>
+        <v>1352</v>
       </c>
       <c r="C15" s="124" t="s">
-        <v>1353</v>
+        <v>1351</v>
       </c>
       <c r="D15" s="69" t="s">
         <v>106</v>
@@ -74197,7 +74888,7 @@
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A16" s="126" t="s">
-        <v>1344</v>
+        <v>1342</v>
       </c>
       <c r="B16" s="122"/>
       <c r="C16" s="32"/>
@@ -74207,13 +74898,13 @@
       <c r="A17" s="32"/>
       <c r="B17" s="108"/>
       <c r="C17" s="124" t="s">
-        <v>1347</v>
+        <v>1345</v>
       </c>
       <c r="D17" s="108"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="126" t="s">
-        <v>1345</v>
+        <v>1343</v>
       </c>
       <c r="B18" s="108"/>
       <c r="C18" s="32"/>
@@ -74223,7 +74914,7 @@
       <c r="A19" s="32"/>
       <c r="B19" s="108"/>
       <c r="C19" s="124" t="s">
-        <v>1348</v>
+        <v>1346</v>
       </c>
       <c r="D19" s="69"/>
     </row>
@@ -74231,7 +74922,7 @@
       <c r="A20" s="32"/>
       <c r="B20" s="124"/>
       <c r="C20" s="124" t="s">
-        <v>1349</v>
+        <v>1347</v>
       </c>
       <c r="D20" s="108"/>
     </row>
@@ -74350,10 +75041,10 @@
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
       <c r="C3" s="118" t="s">
-        <v>1290</v>
+        <v>1288</v>
       </c>
       <c r="E3" s="1"/>
       <c r="J3" s="1"/>
@@ -74363,7 +75054,7 @@
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4" s="107" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="B4" s="108"/>
       <c r="D4" s="69" t="s">
@@ -74373,29 +75064,29 @@
     <row r="5" spans="1:21" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A5" s="108"/>
       <c r="B5" s="108" t="s">
-        <v>1294</v>
+        <v>1292</v>
       </c>
       <c r="C5" s="122" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
       <c r="D5" s="108"/>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A6" s="107" t="s">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="B6" s="108"/>
       <c r="D6" s="108"/>
     </row>
     <row r="7" spans="1:21" ht="216" x14ac:dyDescent="0.3">
       <c r="C7" s="122" t="s">
-        <v>1312</v>
+        <v>1310</v>
       </c>
       <c r="D7" s="108"/>
     </row>
     <row r="8" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="123" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
       <c r="B8" s="108"/>
       <c r="D8" s="69" t="s">
@@ -74405,46 +75096,46 @@
     <row r="9" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="108"/>
       <c r="B9" s="122" t="s">
-        <v>1318</v>
+        <v>1316</v>
       </c>
       <c r="C9" s="32" t="s">
-        <v>1317</v>
+        <v>1315</v>
       </c>
       <c r="D9" s="69"/>
     </row>
     <row r="10" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="108"/>
       <c r="B10" s="122" t="s">
-        <v>1319</v>
+        <v>1317</v>
       </c>
       <c r="C10" s="108" t="s">
-        <v>1295</v>
+        <v>1293</v>
       </c>
       <c r="D10" s="108"/>
     </row>
     <row r="11" spans="1:21" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A11" s="108"/>
       <c r="B11" s="122" t="s">
-        <v>1320</v>
+        <v>1318</v>
       </c>
       <c r="C11" s="32" t="s">
-        <v>1316</v>
+        <v>1314</v>
       </c>
       <c r="D11" s="108"/>
     </row>
     <row r="12" spans="1:21" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A12" s="108"/>
       <c r="B12" s="122" t="s">
-        <v>1321</v>
+        <v>1319</v>
       </c>
       <c r="C12" s="32" t="s">
-        <v>1322</v>
+        <v>1320</v>
       </c>
       <c r="D12" s="108"/>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A13" s="107" t="s">
-        <v>1296</v>
+        <v>1294</v>
       </c>
       <c r="B13" s="108"/>
       <c r="D13" s="108"/>
@@ -74453,13 +75144,13 @@
       <c r="A14" s="108"/>
       <c r="B14" s="108"/>
       <c r="C14" s="32" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
       <c r="D14" s="108"/>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A15" s="107" t="s">
-        <v>1327</v>
+        <v>1325</v>
       </c>
       <c r="B15" s="108"/>
       <c r="D15" s="69" t="s">
@@ -74468,29 +75159,29 @@
     </row>
     <row r="16" spans="1:21" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A16" s="124" t="s">
-        <v>1332</v>
+        <v>1330</v>
       </c>
       <c r="B16" s="124" t="s">
-        <v>1308</v>
+        <v>1306</v>
       </c>
       <c r="C16" s="32" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="D16" s="108"/>
     </row>
     <row r="17" spans="1:21" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A17" s="108"/>
       <c r="B17" s="124" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="C17" s="32" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="D17" s="108"/>
     </row>
     <row r="18" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A18" s="124" t="s">
-        <v>1333</v>
+        <v>1331</v>
       </c>
       <c r="B18" s="124"/>
       <c r="C18" s="32"/>
@@ -74499,20 +75190,20 @@
     <row r="19" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A19" s="108"/>
       <c r="B19" s="124" t="s">
-        <v>1308</v>
+        <v>1306</v>
       </c>
       <c r="C19" s="32" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="D19" s="108"/>
     </row>
     <row r="20" spans="1:21" ht="72" x14ac:dyDescent="0.3">
       <c r="A20" s="108"/>
       <c r="B20" s="124" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="C20" s="124" t="s">
-        <v>1334</v>
+        <v>1332</v>
       </c>
       <c r="D20" s="108"/>
     </row>
@@ -74557,10 +75248,10 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>1291</v>
+        <v>1289</v>
       </c>
       <c r="C26" s="118" t="s">
-        <v>1290</v>
+        <v>1288</v>
       </c>
       <c r="E26" s="1"/>
       <c r="J26" s="1"/>
@@ -74573,46 +75264,46 @@
         <v>488</v>
       </c>
       <c r="B27" s="124" t="s">
-        <v>1326</v>
+        <v>1324</v>
       </c>
       <c r="C27" s="124" t="s">
-        <v>1326</v>
+        <v>1324</v>
       </c>
       <c r="D27" s="124" t="s">
-        <v>1326</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="28" spans="1:21" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A28" s="122" t="s">
+        <v>1306</v>
+      </c>
+      <c r="B28" s="122" t="s">
         <v>1308</v>
       </c>
-      <c r="B28" s="122" t="s">
-        <v>1310</v>
-      </c>
       <c r="C28" s="55" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="D28" s="122" t="s">
-        <v>1299</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="29" spans="1:21" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A29" s="122" t="s">
-        <v>1306</v>
+        <v>1304</v>
       </c>
       <c r="B29" s="122"/>
       <c r="C29" s="122" t="s">
-        <v>1304</v>
+        <v>1302</v>
       </c>
       <c r="D29" s="108"/>
     </row>
     <row r="30" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A30" s="122" t="s">
-        <v>1307</v>
+        <v>1305</v>
       </c>
       <c r="B30" s="122"/>
       <c r="C30" s="122" t="s">
-        <v>1305</v>
+        <v>1303</v>
       </c>
       <c r="D30" s="108"/>
     </row>
@@ -74625,33 +75316,33 @@
     </row>
     <row r="32" spans="1:21" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A32" s="122" t="s">
-        <v>1308</v>
+        <v>1306</v>
       </c>
       <c r="B32" s="122"/>
       <c r="C32" s="122" t="s">
-        <v>1313</v>
+        <v>1311</v>
       </c>
       <c r="D32" s="122" t="s">
-        <v>1298</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A33" s="122" t="s">
-        <v>1306</v>
+        <v>1304</v>
       </c>
       <c r="B33" s="122"/>
       <c r="C33" s="122" t="s">
-        <v>1301</v>
+        <v>1299</v>
       </c>
       <c r="D33" s="122"/>
     </row>
     <row r="34" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A34" s="122" t="s">
-        <v>1307</v>
+        <v>1305</v>
       </c>
       <c r="B34" s="122"/>
       <c r="C34" s="122" t="s">
-        <v>1300</v>
+        <v>1298</v>
       </c>
       <c r="D34" s="122"/>
     </row>
@@ -74664,31 +75355,31 @@
     </row>
     <row r="36" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A36" s="122" t="s">
-        <v>1308</v>
+        <v>1306</v>
       </c>
       <c r="B36" s="122"/>
       <c r="C36" s="122" t="s">
-        <v>1314</v>
+        <v>1312</v>
       </c>
       <c r="D36" s="122"/>
     </row>
     <row r="37" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A37" s="122" t="s">
-        <v>1306</v>
+        <v>1304</v>
       </c>
       <c r="B37" s="122"/>
       <c r="C37" s="122" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="D37" s="108"/>
     </row>
     <row r="38" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A38" s="122" t="s">
-        <v>1307</v>
+        <v>1305</v>
       </c>
       <c r="B38" s="122"/>
       <c r="C38" s="122" t="s">
-        <v>1303</v>
+        <v>1301</v>
       </c>
       <c r="D38" s="108"/>
     </row>
@@ -74782,7 +75473,7 @@
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.3">
       <c r="C3" s="129" t="s">
-        <v>1368</v>
+        <v>1366</v>
       </c>
       <c r="J3" s="1"/>
       <c r="O3" s="1"/>
@@ -74791,7 +75482,7 @@
     </row>
     <row r="4" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="130" t="s">
-        <v>1369</v>
+        <v>1367</v>
       </c>
       <c r="B4" s="122"/>
       <c r="C4" s="122"/>
@@ -74821,7 +75512,7 @@
     </row>
     <row r="5" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="131" t="s">
-        <v>1370</v>
+        <v>1368</v>
       </c>
       <c r="B5" s="108"/>
       <c r="C5" s="108"/>
@@ -74853,7 +75544,7 @@
       <c r="A6" s="108"/>
       <c r="B6" s="108"/>
       <c r="C6" s="128" t="s">
-        <v>1379</v>
+        <v>1377</v>
       </c>
       <c r="D6" s="108"/>
       <c r="F6" s="1"/>
@@ -74879,7 +75570,7 @@
     </row>
     <row r="7" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="131" t="s">
-        <v>1371</v>
+        <v>1369</v>
       </c>
       <c r="B7" s="108"/>
       <c r="C7" s="108"/>
@@ -74911,7 +75602,7 @@
       <c r="A8" s="108"/>
       <c r="B8" s="108"/>
       <c r="C8" s="128" t="s">
-        <v>1376</v>
+        <v>1374</v>
       </c>
       <c r="D8" s="108"/>
       <c r="F8" s="1"/>
@@ -74937,7 +75628,7 @@
     </row>
     <row r="9" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="28" t="s">
-        <v>1373</v>
+        <v>1371</v>
       </c>
       <c r="B9" s="108"/>
       <c r="C9" s="128"/>
@@ -74969,7 +75660,7 @@
       <c r="A10" s="108"/>
       <c r="B10" s="108"/>
       <c r="C10" s="128" t="s">
-        <v>1374</v>
+        <v>1372</v>
       </c>
       <c r="D10" s="108"/>
       <c r="F10" s="1"/>
@@ -74995,7 +75686,7 @@
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A11" s="28" t="s">
-        <v>1372</v>
+        <v>1370</v>
       </c>
       <c r="D11" s="26" t="s">
         <v>106</v>
@@ -75003,17 +75694,17 @@
     </row>
     <row r="12" spans="1:27" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C12" s="128" t="s">
-        <v>1376</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="13" spans="1:27" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C13" s="128" t="s">
-        <v>1377</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A14" s="28" t="s">
-        <v>1375</v>
+        <v>1373</v>
       </c>
       <c r="D14" s="26" t="s">
         <v>106</v>
@@ -75021,33 +75712,33 @@
     </row>
     <row r="15" spans="1:27" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C15" s="128" t="s">
-        <v>1376</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="16" spans="1:27" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C16" s="128" t="s">
-        <v>1377</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="C17" s="128" t="s">
-        <v>1378</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C18" s="128"/>
     </row>
     <row r="19" spans="1:4" ht="403.2" x14ac:dyDescent="0.3">
-      <c r="B19" s="183" t="s">
-        <v>1827</v>
-      </c>
-      <c r="C19" s="183" t="s">
-        <v>1826</v>
+      <c r="B19" s="182" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C19" s="182" t="s">
+        <v>1824</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="70" t="s">
-        <v>1384</v>
+        <v>1382</v>
       </c>
       <c r="D20" s="26" t="s">
         <v>106</v>
@@ -75055,12 +75746,12 @@
     </row>
     <row r="21" spans="1:4" ht="273.60000000000002" x14ac:dyDescent="0.3">
       <c r="C21" s="128" t="s">
-        <v>1380</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="70" t="s">
-        <v>1385</v>
+        <v>1383</v>
       </c>
       <c r="C22" s="128"/>
       <c r="D22" s="26" t="s">
@@ -75069,13 +75760,13 @@
     </row>
     <row r="23" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>1391</v>
+        <v>1389</v>
       </c>
       <c r="B23" s="128" t="s">
-        <v>1398</v>
+        <v>1396</v>
       </c>
       <c r="C23" s="128" t="s">
-        <v>1386</v>
+        <v>1384</v>
       </c>
       <c r="D23" s="26" t="s">
         <v>106</v>
@@ -75083,10 +75774,10 @@
     </row>
     <row r="24" spans="1:4" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A24" s="132" t="s">
-        <v>1390</v>
-      </c>
-      <c r="C24" s="183" t="s">
-        <v>1387</v>
+        <v>1388</v>
+      </c>
+      <c r="C24" s="182" t="s">
+        <v>1385</v>
       </c>
       <c r="D24" s="26" t="s">
         <v>106</v>
@@ -75094,10 +75785,10 @@
     </row>
     <row r="25" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>1392</v>
-      </c>
-      <c r="C25" s="183" t="s">
-        <v>1388</v>
+        <v>1390</v>
+      </c>
+      <c r="C25" s="182" t="s">
+        <v>1386</v>
       </c>
       <c r="D25" s="26" t="s">
         <v>106</v>
@@ -75105,13 +75796,13 @@
     </row>
     <row r="26" spans="1:4" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>1389</v>
+        <v>1387</v>
       </c>
       <c r="B26" s="128" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="C26" s="128" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
       <c r="D26" s="26" t="s">
         <v>106</v>
@@ -75122,7 +75813,7 @@
         <v>132</v>
       </c>
       <c r="B27" s="33" t="s">
-        <v>1397</v>
+        <v>1395</v>
       </c>
       <c r="C27" s="128"/>
       <c r="D27" s="26" t="s">
@@ -75131,21 +75822,21 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="70" t="s">
-        <v>1395</v>
+        <v>1393</v>
       </c>
       <c r="C28" s="128"/>
     </row>
     <row r="29" spans="1:4" ht="244.8" x14ac:dyDescent="0.3">
       <c r="C29" s="128" t="s">
-        <v>1396</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A30" s="70" t="s">
-        <v>1381</v>
+        <v>1379</v>
       </c>
       <c r="B30" s="57" t="s">
-        <v>1382</v>
+        <v>1380</v>
       </c>
       <c r="D30" s="26" t="s">
         <v>106</v>
@@ -75153,7 +75844,7 @@
     </row>
     <row r="31" spans="1:4" ht="158.4" x14ac:dyDescent="0.3">
       <c r="C31" s="128" t="s">
-        <v>1383</v>
+        <v>1381</v>
       </c>
     </row>
   </sheetData>
@@ -77104,7 +77795,7 @@
         <v>295</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>1825</v>
+        <v>1823</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
@@ -77267,7 +77958,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="38" type="noConversion"/>
+  <phoneticPr fontId="39" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="D40" r:id="rId1" location=":~:text=%D0%94%D0%BB%D1%8F%20%D0%B3%D0%B5%D0%BD%D0%B5%D1%80%D0%B0%D1%86%D0%B8%D0%B8%20%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82%D0%B0%20UNIQUEIDENTIFIER" xr:uid="{8276130C-D262-49CA-89B1-D60C8C3E4E63}"/>
   </hyperlinks>
@@ -78666,7 +79357,7 @@
         <v>1149</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>1804</v>
+        <v>1802</v>
       </c>
     </row>
     <row r="54" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
@@ -78929,7 +79620,7 @@
     <tabColor theme="9" tint="0.39997558519241921"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A3:AA46"/>
+  <dimension ref="A3:AA47"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="36" style="2" customWidth="1"/>
@@ -79061,12 +79752,12 @@
       <c r="AA6" s="2"/>
     </row>
     <row r="7" spans="1:27" s="46" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A7" s="163" t="s">
-        <v>1421</v>
+      <c r="A7" s="162" t="s">
+        <v>1419</v>
       </c>
       <c r="B7" s="42"/>
-      <c r="C7" s="163" t="s">
-        <v>1712</v>
+      <c r="C7" s="162" t="s">
+        <v>1710</v>
       </c>
       <c r="D7" s="19"/>
       <c r="F7" s="2"/>
@@ -79703,10 +80394,10 @@
     <row r="26" spans="1:27" s="46" customFormat="1" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A26" s="59"/>
       <c r="B26" s="59" t="s">
-        <v>1494</v>
+        <v>1492</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="D26" s="69" t="s">
         <v>106</v>
@@ -80032,17 +80723,13 @@
       <c r="Z35" s="2"/>
       <c r="AA35" s="2"/>
     </row>
-    <row r="36" spans="1:27" s="46" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:27" s="46" customFormat="1" ht="144" x14ac:dyDescent="0.3">
       <c r="A36" s="2"/>
-      <c r="B36" s="61" t="s">
-        <v>392</v>
-      </c>
-      <c r="C36" s="55" t="s">
-        <v>391</v>
-      </c>
-      <c r="D36" s="61" t="s">
-        <v>395</v>
-      </c>
+      <c r="B36" s="2"/>
+      <c r="C36" s="198" t="s">
+        <v>1867</v>
+      </c>
+      <c r="D36" s="2"/>
       <c r="F36" s="2"/>
       <c r="G36" s="2"/>
       <c r="H36" s="2"/>
@@ -80066,17 +80753,17 @@
       <c r="Z36" s="2"/>
       <c r="AA36" s="2"/>
     </row>
-    <row r="37" spans="1:27" s="46" customFormat="1" ht="230.4" x14ac:dyDescent="0.3">
-      <c r="A37" s="61" t="s">
-        <v>402</v>
-      </c>
+    <row r="37" spans="1:27" s="46" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A37" s="55"/>
       <c r="B37" s="61" t="s">
-        <v>403</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="D37" s="2"/>
+        <v>392</v>
+      </c>
+      <c r="C37" s="55" t="s">
+        <v>391</v>
+      </c>
+      <c r="D37" s="61" t="s">
+        <v>395</v>
+      </c>
       <c r="F37" s="2"/>
       <c r="G37" s="2"/>
       <c r="H37" s="2"/>
@@ -80100,19 +80787,17 @@
       <c r="Z37" s="2"/>
       <c r="AA37" s="2"/>
     </row>
-    <row r="38" spans="1:27" s="46" customFormat="1" ht="216" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:27" s="46" customFormat="1" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A38" s="61" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="B38" s="61" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>393</v>
-      </c>
+        <v>399</v>
+      </c>
+      <c r="D38" s="2"/>
       <c r="F38" s="2"/>
       <c r="G38" s="2"/>
       <c r="H38" s="2"/>
@@ -80136,16 +80821,18 @@
       <c r="Z38" s="2"/>
       <c r="AA38" s="2"/>
     </row>
-    <row r="39" spans="1:27" s="46" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
-      <c r="A39" s="2"/>
+    <row r="39" spans="1:27" s="46" customFormat="1" ht="216" x14ac:dyDescent="0.3">
+      <c r="A39" s="61" t="s">
+        <v>405</v>
+      </c>
       <c r="B39" s="61" t="s">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="D39" s="61" t="s">
-        <v>397</v>
+        <v>394</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>393</v>
       </c>
       <c r="F39" s="2"/>
       <c r="G39" s="2"/>
@@ -80171,16 +80858,16 @@
       <c r="AA39" s="2"/>
     </row>
     <row r="40" spans="1:27" s="46" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
-      <c r="A40" s="61" t="s">
-        <v>406</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>400</v>
+      <c r="A40" s="2"/>
+      <c r="B40" s="61" t="s">
+        <v>396</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="D40" s="2"/>
+        <v>398</v>
+      </c>
+      <c r="D40" s="61" t="s">
+        <v>397</v>
+      </c>
       <c r="F40" s="2"/>
       <c r="G40" s="2"/>
       <c r="H40" s="2"/>
@@ -80204,12 +80891,16 @@
       <c r="Z40" s="2"/>
       <c r="AA40" s="2"/>
     </row>
-    <row r="41" spans="1:27" s="46" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="62" t="s">
-        <v>412</v>
-      </c>
-      <c r="B41" s="2"/>
-      <c r="C41" s="2"/>
+    <row r="41" spans="1:27" s="46" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A41" s="61" t="s">
+        <v>406</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>401</v>
+      </c>
       <c r="D41" s="2"/>
       <c r="F41" s="2"/>
       <c r="G41" s="2"/>
@@ -80234,12 +80925,12 @@
       <c r="Z41" s="2"/>
       <c r="AA41" s="2"/>
     </row>
-    <row r="42" spans="1:27" s="46" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A42" s="2"/>
+    <row r="42" spans="1:27" s="46" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="62" t="s">
+        <v>412</v>
+      </c>
       <c r="B42" s="2"/>
-      <c r="C42" s="2" t="s">
-        <v>413</v>
-      </c>
+      <c r="C42" s="2"/>
       <c r="D42" s="2"/>
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
@@ -80264,15 +80955,11 @@
       <c r="Z42" s="2"/>
       <c r="AA42" s="2"/>
     </row>
-    <row r="43" spans="1:27" s="46" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A43" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="C43" s="61" t="s">
-        <v>419</v>
+    <row r="43" spans="1:27" s="46" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A43" s="2"/>
+      <c r="B43" s="2"/>
+      <c r="C43" s="2" t="s">
+        <v>413</v>
       </c>
       <c r="D43" s="2"/>
       <c r="F43" s="2"/>
@@ -80298,13 +80985,15 @@
       <c r="Z43" s="2"/>
       <c r="AA43" s="2"/>
     </row>
-    <row r="44" spans="1:27" s="46" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:27" s="46" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="B44" s="2"/>
+        <v>414</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>422</v>
+      </c>
       <c r="C44" s="61" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D44" s="2"/>
       <c r="F44" s="2"/>
@@ -80330,15 +81019,13 @@
       <c r="Z44" s="2"/>
       <c r="AA44" s="2"/>
     </row>
-    <row r="45" spans="1:27" s="46" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:27" s="46" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>423</v>
-      </c>
+        <v>415</v>
+      </c>
+      <c r="B45" s="2"/>
       <c r="C45" s="61" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D45" s="2"/>
       <c r="F45" s="2"/>
@@ -80364,15 +81051,15 @@
       <c r="Z45" s="2"/>
       <c r="AA45" s="2"/>
     </row>
-    <row r="46" spans="1:27" s="46" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:27" s="46" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="B46" s="61" t="s">
-        <v>424</v>
+        <v>416</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>423</v>
       </c>
       <c r="C46" s="61" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D46" s="2"/>
       <c r="F46" s="2"/>
@@ -80397,6 +81084,40 @@
       <c r="Y46" s="2"/>
       <c r="Z46" s="2"/>
       <c r="AA46" s="2"/>
+    </row>
+    <row r="47" spans="1:27" s="46" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A47" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="B47" s="61" t="s">
+        <v>424</v>
+      </c>
+      <c r="C47" s="61" t="s">
+        <v>421</v>
+      </c>
+      <c r="D47" s="2"/>
+      <c r="F47" s="2"/>
+      <c r="G47" s="2"/>
+      <c r="H47" s="2"/>
+      <c r="I47" s="2"/>
+      <c r="J47" s="2"/>
+      <c r="K47" s="2"/>
+      <c r="L47" s="2"/>
+      <c r="M47" s="2"/>
+      <c r="N47" s="2"/>
+      <c r="O47" s="2"/>
+      <c r="P47" s="2"/>
+      <c r="Q47" s="2"/>
+      <c r="R47" s="2"/>
+      <c r="S47" s="2"/>
+      <c r="T47" s="2"/>
+      <c r="U47" s="2"/>
+      <c r="V47" s="2"/>
+      <c r="W47" s="2"/>
+      <c r="X47" s="2"/>
+      <c r="Y47" s="2"/>
+      <c r="Z47" s="2"/>
+      <c r="AA47" s="2"/>
     </row>
   </sheetData>
   <hyperlinks>
